--- a/fuel_cost_chungcheong.xlsx
+++ b/fuel_cost_chungcheong.xlsx
@@ -9782,10 +9782,8 @@
         <f t="shared" si="6"/>
         <v>90260</v>
       </c>
-      <c r="Q51" s="12" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
+      <c r="Q51" s="12" t="s">
+        <v>61</v>
       </c>
       <c r="R51" s="13">
         <f t="shared" si="7"/>
@@ -9946,10 +9944,8 @@
         <f t="shared" si="6"/>
         <v>90260</v>
       </c>
-      <c r="Q53" s="12" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
+      <c r="Q53" s="12" t="s">
+        <v>61</v>
       </c>
       <c r="R53" s="13">
         <f t="shared" si="7"/>
@@ -11310,10 +11306,8 @@
         <f t="shared" si="6"/>
         <v>90950</v>
       </c>
-      <c r="Q70" s="12" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
+      <c r="Q70" s="12" t="s">
+        <v>61</v>
       </c>
       <c r="R70" s="13">
         <f t="shared" si="7"/>
@@ -11394,10 +11388,8 @@
         <f t="shared" si="6"/>
         <v>90975</v>
       </c>
-      <c r="Q71" s="12" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
+      <c r="Q71" s="12" t="s">
+        <v>61</v>
       </c>
       <c r="R71" s="13">
         <f t="shared" si="7"/>
@@ -11718,10 +11710,8 @@
         <f t="shared" si="6"/>
         <v>91105</v>
       </c>
-      <c r="Q75" s="12" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
+      <c r="Q75" s="12" t="s">
+        <v>61</v>
       </c>
       <c r="R75" s="13">
         <f t="shared" si="7"/>
@@ -12442,10 +12432,8 @@
         <f t="shared" si="19"/>
         <v>91485</v>
       </c>
-      <c r="Q84" s="12" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
+      <c r="Q84" s="12" t="s">
+        <v>61</v>
       </c>
       <c r="R84" s="13">
         <f t="shared" si="20"/>
@@ -14206,10 +14194,8 @@
         <f t="shared" si="19"/>
         <v>92010</v>
       </c>
-      <c r="Q106" s="12" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
+      <c r="Q106" s="12" t="s">
+        <v>61</v>
       </c>
       <c r="R106" s="13">
         <f t="shared" si="20"/>
@@ -37422,10 +37408,8 @@
         <f t="shared" ref="P399:P462" si="84">IF($B$10=0,"",IFERROR(IF($B$4&gt;0,IF($L399="",1/0,$L399*$B$4),0)+IF($B$5&gt;0,IF($M399="",1/0,$M399*$B$5),0)+IF($B$6&gt;0,IF($N399="",1/0,$N399*$B$6),0),""))</f>
         <v/>
       </c>
-      <c r="Q399" s="12" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
+      <c r="Q399" s="12" t="s">
+        <v>61</v>
       </c>
       <c r="R399" s="13" t="str">
         <f t="shared" ref="R399:R462" si="85">IF($P399="","",IF($Q399="Y",IFERROR(VLOOKUP($B399,$C$4:$D$13,2,FALSE()),0),0))</f>
@@ -41036,10 +41020,8 @@
         <f t="shared" si="84"/>
         <v/>
       </c>
-      <c r="Q445" s="12" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
+      <c r="Q445" s="12" t="s">
+        <v>61</v>
       </c>
       <c r="R445" s="13" t="str">
         <f t="shared" si="85"/>
@@ -41810,10 +41792,8 @@
         <f t="shared" si="84"/>
         <v/>
       </c>
-      <c r="Q455" s="12" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
+      <c r="Q455" s="12" t="s">
+        <v>61</v>
       </c>
       <c r="R455" s="13" t="str">
         <f t="shared" si="85"/>
@@ -42815,10 +42795,8 @@
         <f t="shared" si="97"/>
         <v/>
       </c>
-      <c r="Q468" s="12" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
+      <c r="Q468" s="12" t="s">
+        <v>61</v>
       </c>
       <c r="R468" s="13" t="str">
         <f t="shared" si="98"/>
@@ -42896,10 +42874,8 @@
         <f t="shared" si="97"/>
         <v/>
       </c>
-      <c r="Q469" s="12" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
+      <c r="Q469" s="12" t="s">
+        <v>61</v>
       </c>
       <c r="R469" s="13" t="str">
         <f t="shared" si="98"/>
@@ -43131,10 +43107,8 @@
         <f t="shared" si="97"/>
         <v/>
       </c>
-      <c r="Q472" s="12" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
+      <c r="Q472" s="12" t="s">
+        <v>61</v>
       </c>
       <c r="R472" s="13" t="str">
         <f t="shared" si="98"/>
@@ -45830,10 +45804,8 @@
         <f t="shared" si="97"/>
         <v/>
       </c>
-      <c r="Q507" s="12" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
+      <c r="Q507" s="12" t="s">
+        <v>61</v>
       </c>
       <c r="R507" s="13" t="str">
         <f t="shared" si="98"/>
@@ -49911,10 +49883,8 @@
         <f t="shared" si="110"/>
         <v/>
       </c>
-      <c r="Q560" s="12" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
+      <c r="Q560" s="12" t="s">
+        <v>61</v>
       </c>
       <c r="R560" s="13" t="str">
         <f t="shared" si="111"/>
@@ -50069,10 +50039,8 @@
         <f t="shared" si="110"/>
         <v/>
       </c>
-      <c r="Q562" s="12" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
+      <c r="Q562" s="12" t="s">
+        <v>61</v>
       </c>
       <c r="R562" s="13" t="str">
         <f t="shared" si="111"/>
@@ -50300,10 +50268,8 @@
         <f t="shared" si="110"/>
         <v/>
       </c>
-      <c r="Q565" s="12" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
+      <c r="Q565" s="12" t="s">
+        <v>61</v>
       </c>
       <c r="R565" s="13" t="str">
         <f t="shared" si="111"/>
@@ -50916,10 +50882,8 @@
         <f t="shared" si="110"/>
         <v/>
       </c>
-      <c r="Q573" s="12" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
+      <c r="Q573" s="12" t="s">
+        <v>61</v>
       </c>
       <c r="R573" s="13" t="str">
         <f t="shared" si="111"/>
@@ -51844,10 +51808,8 @@
         <f t="shared" si="110"/>
         <v/>
       </c>
-      <c r="Q585" s="12" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
+      <c r="Q585" s="12" t="s">
+        <v>61</v>
       </c>
       <c r="R585" s="13" t="str">
         <f t="shared" si="111"/>
@@ -56002,10 +55964,8 @@
         <f t="shared" si="123"/>
         <v/>
       </c>
-      <c r="Q639" s="12" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
+      <c r="Q639" s="12" t="s">
+        <v>61</v>
       </c>
       <c r="R639" s="13" t="str">
         <f t="shared" si="124"/>
@@ -58855,10 +58815,8 @@
         <f t="shared" si="136"/>
         <v/>
       </c>
-      <c r="Q676" s="12" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
+      <c r="Q676" s="12" t="s">
+        <v>61</v>
       </c>
       <c r="R676" s="13" t="str">
         <f t="shared" si="137"/>
@@ -59548,10 +59506,8 @@
         <f t="shared" si="136"/>
         <v/>
       </c>
-      <c r="Q685" s="12" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
+      <c r="Q685" s="12" t="s">
+        <v>61</v>
       </c>
       <c r="R685" s="13" t="str">
         <f t="shared" si="137"/>
@@ -63397,10 +63353,8 @@
         <f t="shared" si="149"/>
         <v/>
       </c>
-      <c r="Q735" s="12" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
+      <c r="Q735" s="12" t="s">
+        <v>61</v>
       </c>
       <c r="R735" s="13" t="str">
         <f t="shared" si="150"/>
@@ -65480,10 +65434,8 @@
         <f t="shared" si="149"/>
         <v/>
       </c>
-      <c r="Q762" s="12" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
+      <c r="Q762" s="12" t="s">
+        <v>61</v>
       </c>
       <c r="R762" s="13" t="str">
         <f t="shared" si="150"/>
@@ -66711,10 +66663,8 @@
         <f t="shared" si="149"/>
         <v/>
       </c>
-      <c r="Q778" s="12" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
+      <c r="Q778" s="12" t="s">
+        <v>61</v>
       </c>
       <c r="R778" s="13" t="str">
         <f t="shared" si="150"/>
@@ -66941,10 +66891,8 @@
         <f t="shared" si="149"/>
         <v/>
       </c>
-      <c r="Q781" s="12" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
+      <c r="Q781" s="12" t="s">
+        <v>61</v>
       </c>
       <c r="R781" s="13" t="str">
         <f t="shared" si="150"/>
@@ -69401,10 +69349,8 @@
         <f t="shared" si="164"/>
         <v/>
       </c>
-      <c r="Q813" s="12" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
+      <c r="Q813" s="12" t="s">
+        <v>61</v>
       </c>
       <c r="R813" s="13" t="str">
         <f t="shared" si="165"/>
@@ -71407,10 +71353,8 @@
         <f t="shared" si="164"/>
         <v/>
       </c>
-      <c r="Q839" s="12" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
+      <c r="Q839" s="12" t="s">
+        <v>61</v>
       </c>
       <c r="R839" s="13" t="str">
         <f t="shared" si="165"/>
@@ -72104,10 +72048,8 @@
         <f t="shared" si="178"/>
         <v/>
       </c>
-      <c r="Q848" s="12" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
+      <c r="Q848" s="12" t="s">
+        <v>61</v>
       </c>
       <c r="R848" s="13" t="str">
         <f t="shared" si="179"/>
@@ -72566,10 +72508,8 @@
         <f t="shared" si="178"/>
         <v/>
       </c>
-      <c r="Q854" s="12" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
+      <c r="Q854" s="12" t="s">
+        <v>61</v>
       </c>
       <c r="R854" s="13" t="str">
         <f t="shared" si="179"/>
@@ -74106,10 +74046,8 @@
         <f t="shared" si="178"/>
         <v/>
       </c>
-      <c r="Q874" s="12" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
+      <c r="Q874" s="12" t="s">
+        <v>61</v>
       </c>
       <c r="R874" s="13" t="str">
         <f t="shared" si="179"/>
@@ -74337,10 +74275,8 @@
         <f t="shared" si="178"/>
         <v/>
       </c>
-      <c r="Q877" s="12" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
+      <c r="Q877" s="12" t="s">
+        <v>61</v>
       </c>
       <c r="R877" s="13" t="str">
         <f t="shared" si="179"/>

--- a/fuel_cost_chungcheong.xlsx
+++ b/fuel_cost_chungcheong.xlsx
@@ -20559,6 +20559,7 @@
     <row r="186" spans="1:23" s="16" customFormat="1" ht="28.5" customHeight="1">
       <c r="A186" s="11" t="str">
         <f t="shared" si="26"/>
+        <v/>
       </c>
       <c r="B186" s="11" t="s">
         <v>16</v>
@@ -20610,15 +20611,19 @@
       <c r="Q186" s="12"/>
       <c r="R186" s="13" t="str">
         <f t="shared" si="33"/>
+        <v/>
       </c>
       <c r="S186" s="12" t="str">
         <f t="shared" si="34"/>
+        <v/>
       </c>
       <c r="T186" s="12" t="str">
         <f t="shared" si="35"/>
+        <v/>
       </c>
       <c r="U186" s="12" t="str">
         <f t="shared" si="36"/>
+        <v/>
       </c>
       <c r="V186" s="12" t="str">
         <f t="shared" si="37"/>
@@ -20632,6 +20637,7 @@
     <row r="187" spans="1:23" s="2" customFormat="1" ht="28.5" customHeight="1">
       <c r="A187" s="11" t="str">
         <f t="shared" si="26"/>
+        <v/>
       </c>
       <c r="B187" s="11" t="s">
         <v>16</v>
@@ -20711,6 +20717,7 @@
     <row r="188" spans="1:23" s="2" customFormat="1" ht="28.5" customHeight="1">
       <c r="A188" s="11" t="str">
         <f t="shared" si="26"/>
+        <v/>
       </c>
       <c r="B188" s="11" t="s">
         <v>16</v>
@@ -20790,6 +20797,7 @@
     <row r="189" spans="1:23" s="2" customFormat="1" ht="28.5" customHeight="1">
       <c r="A189" s="11" t="str">
         <f t="shared" si="26"/>
+        <v/>
       </c>
       <c r="B189" s="11" t="s">
         <v>12</v>
@@ -20869,6 +20877,7 @@
     <row r="190" spans="1:23" s="2" customFormat="1" ht="28.5" customHeight="1">
       <c r="A190" s="11" t="str">
         <f t="shared" si="26"/>
+        <v/>
       </c>
       <c r="B190" s="11" t="s">
         <v>16</v>
@@ -20948,6 +20957,7 @@
     <row r="191" spans="1:23" s="16" customFormat="1" ht="28.5" customHeight="1">
       <c r="A191" s="11" t="str">
         <f t="shared" si="26"/>
+        <v/>
       </c>
       <c r="B191" s="11" t="s">
         <v>16</v>
@@ -21027,6 +21037,7 @@
     <row r="192" spans="1:23" s="2" customFormat="1" ht="28.5" customHeight="1">
       <c r="A192" s="11" t="str">
         <f t="shared" si="26"/>
+        <v/>
       </c>
       <c r="B192" s="11" t="s">
         <v>16</v>
@@ -21106,6 +21117,7 @@
     <row r="193" spans="1:23" s="16" customFormat="1" ht="28.5" customHeight="1">
       <c r="A193" s="11" t="str">
         <f t="shared" si="26"/>
+        <v/>
       </c>
       <c r="B193" s="11" t="s">
         <v>6</v>
@@ -21185,6 +21197,7 @@
     <row r="194" spans="1:23" s="2" customFormat="1" ht="28.5" customHeight="1">
       <c r="A194" s="11" t="str">
         <f t="shared" si="26"/>
+        <v/>
       </c>
       <c r="B194" s="11" t="s">
         <v>12</v>
@@ -21264,6 +21277,7 @@
     <row r="195" spans="1:23" s="7" customFormat="1" ht="28.5" customHeight="1">
       <c r="A195" s="11" t="str">
         <f t="shared" si="26"/>
+        <v/>
       </c>
       <c r="B195" s="11" t="s">
         <v>6</v>
@@ -21343,6 +21357,7 @@
     <row r="196" spans="1:23" s="16" customFormat="1" ht="28.5" customHeight="1">
       <c r="A196" s="11" t="str">
         <f t="shared" si="26"/>
+        <v/>
       </c>
       <c r="B196" s="11" t="s">
         <v>16</v>
@@ -21422,6 +21437,7 @@
     <row r="197" spans="1:23" s="2" customFormat="1" ht="28.5" customHeight="1">
       <c r="A197" s="11" t="str">
         <f t="shared" si="26"/>
+        <v/>
       </c>
       <c r="B197" s="11" t="s">
         <v>18</v>
@@ -21501,6 +21517,7 @@
     <row r="198" spans="1:23" s="7" customFormat="1" ht="28.5" customHeight="1">
       <c r="A198" s="11" t="str">
         <f t="shared" si="26"/>
+        <v/>
       </c>
       <c r="B198" s="11" t="s">
         <v>18</v>
@@ -21580,6 +21597,7 @@
     <row r="199" spans="1:23" s="2" customFormat="1" ht="28.5" customHeight="1">
       <c r="A199" s="11" t="str">
         <f t="shared" si="26"/>
+        <v/>
       </c>
       <c r="B199" s="11" t="s">
         <v>16</v>
@@ -21659,6 +21677,7 @@
     <row r="200" spans="1:23" s="2" customFormat="1" ht="28.5" customHeight="1">
       <c r="A200" s="11" t="str">
         <f t="shared" si="26"/>
+        <v/>
       </c>
       <c r="B200" s="11" t="s">
         <v>10</v>
@@ -21738,6 +21757,7 @@
     <row r="201" spans="1:23" s="2" customFormat="1" ht="28.5" customHeight="1">
       <c r="A201" s="11" t="str">
         <f t="shared" si="26"/>
+        <v/>
       </c>
       <c r="B201" s="11" t="s">
         <v>12</v>
@@ -21817,6 +21837,7 @@
     <row r="202" spans="1:23" s="2" customFormat="1" ht="28.5" customHeight="1">
       <c r="A202" s="11" t="str">
         <f t="shared" si="26"/>
+        <v/>
       </c>
       <c r="B202" s="11" t="s">
         <v>18</v>
@@ -21896,6 +21917,7 @@
     <row r="203" spans="1:23" s="16" customFormat="1" ht="28.5" customHeight="1">
       <c r="A203" s="11" t="str">
         <f t="shared" si="26"/>
+        <v/>
       </c>
       <c r="B203" s="11" t="s">
         <v>18</v>
@@ -21975,6 +21997,7 @@
     <row r="204" spans="1:23" s="16" customFormat="1" ht="28.5" customHeight="1">
       <c r="A204" s="11" t="str">
         <f t="shared" si="26"/>
+        <v/>
       </c>
       <c r="B204" s="11" t="s">
         <v>6</v>
@@ -22054,6 +22077,7 @@
     <row r="205" spans="1:23" s="7" customFormat="1" ht="28.5" customHeight="1">
       <c r="A205" s="11" t="str">
         <f t="shared" si="26"/>
+        <v/>
       </c>
       <c r="B205" s="11" t="s">
         <v>12</v>
@@ -22133,6 +22157,7 @@
     <row r="206" spans="1:23" s="16" customFormat="1" ht="28.5" customHeight="1">
       <c r="A206" s="11" t="str">
         <f t="shared" si="26"/>
+        <v/>
       </c>
       <c r="B206" s="11" t="s">
         <v>6</v>
@@ -22212,6 +22237,7 @@
     <row r="207" spans="1:23" s="2" customFormat="1" ht="28.5" customHeight="1">
       <c r="A207" s="11" t="str">
         <f t="shared" ref="A207:A270" si="39">IF($T207="","",1+COUNTIF($W$15:$W$883,"&lt;"&amp;W207))</f>
+        <v/>
       </c>
       <c r="B207" s="11" t="s">
         <v>16</v>
@@ -22291,6 +22317,7 @@
     <row r="208" spans="1:23" s="2" customFormat="1" ht="28.5" customHeight="1">
       <c r="A208" s="11" t="str">
         <f t="shared" si="39"/>
+        <v/>
       </c>
       <c r="B208" s="11" t="s">
         <v>18</v>
@@ -22370,6 +22397,7 @@
     <row r="209" spans="1:23" s="16" customFormat="1" ht="28.5" customHeight="1">
       <c r="A209" s="11" t="str">
         <f t="shared" si="39"/>
+        <v/>
       </c>
       <c r="B209" s="11" t="s">
         <v>18</v>
@@ -22449,6 +22477,7 @@
     <row r="210" spans="1:23" s="16" customFormat="1" ht="28.5" customHeight="1">
       <c r="A210" s="11" t="str">
         <f t="shared" si="39"/>
+        <v/>
       </c>
       <c r="B210" s="11" t="s">
         <v>6</v>
@@ -22528,6 +22557,7 @@
     <row r="211" spans="1:23" s="2" customFormat="1" ht="28.5" customHeight="1">
       <c r="A211" s="11" t="str">
         <f t="shared" si="39"/>
+        <v/>
       </c>
       <c r="B211" s="11" t="s">
         <v>14</v>
@@ -22607,6 +22637,7 @@
     <row r="212" spans="1:23" s="2" customFormat="1" ht="28.5" customHeight="1">
       <c r="A212" s="11" t="str">
         <f t="shared" si="39"/>
+        <v/>
       </c>
       <c r="B212" s="11" t="s">
         <v>12</v>
@@ -22686,6 +22717,7 @@
     <row r="213" spans="1:23" s="2" customFormat="1" ht="28.5" customHeight="1">
       <c r="A213" s="11" t="str">
         <f t="shared" si="39"/>
+        <v/>
       </c>
       <c r="B213" s="11" t="s">
         <v>6</v>
@@ -22765,6 +22797,7 @@
     <row r="214" spans="1:23" s="7" customFormat="1" ht="28.5" customHeight="1">
       <c r="A214" s="11" t="str">
         <f t="shared" si="39"/>
+        <v/>
       </c>
       <c r="B214" s="11" t="s">
         <v>14</v>
@@ -22844,6 +22877,7 @@
     <row r="215" spans="1:23" s="16" customFormat="1" ht="28.5" customHeight="1">
       <c r="A215" s="11" t="str">
         <f t="shared" si="39"/>
+        <v/>
       </c>
       <c r="B215" s="11" t="s">
         <v>18</v>
@@ -22923,6 +22957,7 @@
     <row r="216" spans="1:23" s="7" customFormat="1" ht="28.5" customHeight="1">
       <c r="A216" s="11" t="str">
         <f t="shared" si="39"/>
+        <v/>
       </c>
       <c r="B216" s="11" t="s">
         <v>18</v>
@@ -23002,6 +23037,7 @@
     <row r="217" spans="1:23" s="2" customFormat="1" ht="28.5" customHeight="1">
       <c r="A217" s="11" t="str">
         <f t="shared" si="39"/>
+        <v/>
       </c>
       <c r="B217" s="11" t="s">
         <v>18</v>
@@ -23081,6 +23117,7 @@
     <row r="218" spans="1:23" s="2" customFormat="1" ht="28.5" customHeight="1">
       <c r="A218" s="11" t="str">
         <f t="shared" si="39"/>
+        <v/>
       </c>
       <c r="B218" s="11" t="s">
         <v>18</v>
@@ -23160,6 +23197,7 @@
     <row r="219" spans="1:23" s="16" customFormat="1" ht="28.5" customHeight="1">
       <c r="A219" s="11" t="str">
         <f t="shared" si="39"/>
+        <v/>
       </c>
       <c r="B219" s="11" t="s">
         <v>16</v>
@@ -23239,6 +23277,7 @@
     <row r="220" spans="1:23" s="2" customFormat="1" ht="28.5" customHeight="1">
       <c r="A220" s="11" t="str">
         <f t="shared" si="39"/>
+        <v/>
       </c>
       <c r="B220" s="11" t="s">
         <v>18</v>
@@ -23318,6 +23357,7 @@
     <row r="221" spans="1:23" s="7" customFormat="1" ht="28.5" customHeight="1">
       <c r="A221" s="11" t="str">
         <f t="shared" si="39"/>
+        <v/>
       </c>
       <c r="B221" s="11" t="s">
         <v>18</v>
@@ -23397,6 +23437,7 @@
     <row r="222" spans="1:23" s="2" customFormat="1" ht="28.5" customHeight="1">
       <c r="A222" s="11" t="str">
         <f t="shared" si="39"/>
+        <v/>
       </c>
       <c r="B222" s="11" t="s">
         <v>16</v>
@@ -23476,6 +23517,7 @@
     <row r="223" spans="1:23" s="16" customFormat="1" ht="28.5" customHeight="1">
       <c r="A223" s="11" t="str">
         <f t="shared" si="39"/>
+        <v/>
       </c>
       <c r="B223" s="11" t="s">
         <v>16</v>
@@ -23555,6 +23597,7 @@
     <row r="224" spans="1:23" s="2" customFormat="1" ht="28.5" customHeight="1">
       <c r="A224" s="11" t="str">
         <f t="shared" si="39"/>
+        <v/>
       </c>
       <c r="B224" s="11" t="s">
         <v>16</v>
@@ -23634,6 +23677,7 @@
     <row r="225" spans="1:23" s="2" customFormat="1" ht="28.5" customHeight="1">
       <c r="A225" s="11" t="str">
         <f t="shared" si="39"/>
+        <v/>
       </c>
       <c r="B225" s="11" t="s">
         <v>18</v>
@@ -23713,6 +23757,7 @@
     <row r="226" spans="1:23" s="2" customFormat="1" ht="28.5" customHeight="1">
       <c r="A226" s="11" t="str">
         <f t="shared" si="39"/>
+        <v/>
       </c>
       <c r="B226" s="11" t="s">
         <v>6</v>
@@ -23792,6 +23837,7 @@
     <row r="227" spans="1:23" s="16" customFormat="1" ht="28.5" customHeight="1">
       <c r="A227" s="11" t="str">
         <f t="shared" si="39"/>
+        <v/>
       </c>
       <c r="B227" s="11" t="s">
         <v>6</v>
@@ -23871,6 +23917,7 @@
     <row r="228" spans="1:23" s="2" customFormat="1" ht="28.5" customHeight="1">
       <c r="A228" s="11" t="str">
         <f t="shared" si="39"/>
+        <v/>
       </c>
       <c r="B228" s="11" t="s">
         <v>6</v>
@@ -23950,6 +23997,7 @@
     <row r="229" spans="1:23" s="2" customFormat="1" ht="28.5" customHeight="1">
       <c r="A229" s="11" t="str">
         <f t="shared" si="39"/>
+        <v/>
       </c>
       <c r="B229" s="11" t="s">
         <v>10</v>
@@ -24029,6 +24077,7 @@
     <row r="230" spans="1:23" s="2" customFormat="1" ht="28.5" customHeight="1">
       <c r="A230" s="11" t="str">
         <f t="shared" si="39"/>
+        <v/>
       </c>
       <c r="B230" s="11" t="s">
         <v>18</v>
@@ -24108,6 +24157,7 @@
     <row r="231" spans="1:23" s="2" customFormat="1" ht="28.5" customHeight="1">
       <c r="A231" s="11" t="str">
         <f t="shared" si="39"/>
+        <v/>
       </c>
       <c r="B231" s="11" t="s">
         <v>16</v>
@@ -24187,6 +24237,7 @@
     <row r="232" spans="1:23" s="2" customFormat="1" ht="28.5" customHeight="1">
       <c r="A232" s="11" t="str">
         <f t="shared" si="39"/>
+        <v/>
       </c>
       <c r="B232" s="11" t="s">
         <v>18</v>
@@ -24266,6 +24317,7 @@
     <row r="233" spans="1:23" s="16" customFormat="1" ht="28.5" customHeight="1">
       <c r="A233" s="11" t="str">
         <f t="shared" si="39"/>
+        <v/>
       </c>
       <c r="B233" s="11" t="s">
         <v>18</v>
@@ -24345,6 +24397,7 @@
     <row r="234" spans="1:23" s="2" customFormat="1" ht="28.5" customHeight="1">
       <c r="A234" s="11" t="str">
         <f t="shared" si="39"/>
+        <v/>
       </c>
       <c r="B234" s="11" t="s">
         <v>10</v>
@@ -24424,6 +24477,7 @@
     <row r="235" spans="1:23" s="2" customFormat="1" ht="28.5" customHeight="1">
       <c r="A235" s="11" t="str">
         <f t="shared" si="39"/>
+        <v/>
       </c>
       <c r="B235" s="11" t="s">
         <v>6</v>
@@ -24503,6 +24557,7 @@
     <row r="236" spans="1:23" s="2" customFormat="1" ht="28.5" customHeight="1">
       <c r="A236" s="11" t="str">
         <f t="shared" si="39"/>
+        <v/>
       </c>
       <c r="B236" s="11" t="s">
         <v>6</v>
@@ -24582,6 +24637,7 @@
     <row r="237" spans="1:23" s="2" customFormat="1" ht="28.5" customHeight="1">
       <c r="A237" s="11" t="str">
         <f t="shared" si="39"/>
+        <v/>
       </c>
       <c r="B237" s="11" t="s">
         <v>10</v>
@@ -24661,6 +24717,7 @@
     <row r="238" spans="1:23" s="2" customFormat="1" ht="28.5" customHeight="1">
       <c r="A238" s="11" t="str">
         <f t="shared" si="39"/>
+        <v/>
       </c>
       <c r="B238" s="11" t="s">
         <v>16</v>
@@ -24740,6 +24797,7 @@
     <row r="239" spans="1:23" s="2" customFormat="1" ht="28.5" customHeight="1">
       <c r="A239" s="11" t="str">
         <f t="shared" si="39"/>
+        <v/>
       </c>
       <c r="B239" s="11" t="s">
         <v>18</v>
@@ -24819,6 +24877,7 @@
     <row r="240" spans="1:23" s="16" customFormat="1" ht="28.5" customHeight="1">
       <c r="A240" s="11" t="str">
         <f t="shared" si="39"/>
+        <v/>
       </c>
       <c r="B240" s="11" t="s">
         <v>12</v>
@@ -24898,6 +24957,7 @@
     <row r="241" spans="1:23" s="2" customFormat="1" ht="28.5" customHeight="1">
       <c r="A241" s="11" t="str">
         <f t="shared" si="39"/>
+        <v/>
       </c>
       <c r="B241" s="11" t="s">
         <v>14</v>
@@ -24977,6 +25037,7 @@
     <row r="242" spans="1:23" s="16" customFormat="1" ht="28.5" customHeight="1">
       <c r="A242" s="11" t="str">
         <f t="shared" si="39"/>
+        <v/>
       </c>
       <c r="B242" s="11" t="s">
         <v>16</v>
@@ -25056,6 +25117,7 @@
     <row r="243" spans="1:23" s="7" customFormat="1" ht="28.5" customHeight="1">
       <c r="A243" s="11" t="str">
         <f t="shared" si="39"/>
+        <v/>
       </c>
       <c r="B243" s="11" t="s">
         <v>18</v>
@@ -25135,6 +25197,7 @@
     <row r="244" spans="1:23" s="2" customFormat="1" ht="28.5" customHeight="1">
       <c r="A244" s="11" t="str">
         <f t="shared" si="39"/>
+        <v/>
       </c>
       <c r="B244" s="11" t="s">
         <v>10</v>
@@ -25214,6 +25277,7 @@
     <row r="245" spans="1:23" s="2" customFormat="1" ht="28.5" customHeight="1">
       <c r="A245" s="11" t="str">
         <f t="shared" si="39"/>
+        <v/>
       </c>
       <c r="B245" s="11" t="s">
         <v>10</v>
@@ -25293,6 +25357,7 @@
     <row r="246" spans="1:23" s="7" customFormat="1" ht="28.5" customHeight="1">
       <c r="A246" s="11" t="str">
         <f t="shared" si="39"/>
+        <v/>
       </c>
       <c r="B246" s="11" t="s">
         <v>12</v>
@@ -25372,6 +25437,7 @@
     <row r="247" spans="1:23" s="2" customFormat="1" ht="28.5" customHeight="1">
       <c r="A247" s="11" t="str">
         <f t="shared" si="39"/>
+        <v/>
       </c>
       <c r="B247" s="11" t="s">
         <v>16</v>
@@ -25451,6 +25517,7 @@
     <row r="248" spans="1:23" s="2" customFormat="1" ht="28.5" customHeight="1">
       <c r="A248" s="11" t="str">
         <f t="shared" si="39"/>
+        <v/>
       </c>
       <c r="B248" s="11" t="s">
         <v>16</v>
@@ -25530,6 +25597,7 @@
     <row r="249" spans="1:23" s="2" customFormat="1" ht="28.5" customHeight="1">
       <c r="A249" s="11" t="str">
         <f t="shared" si="39"/>
+        <v/>
       </c>
       <c r="B249" s="11" t="s">
         <v>16</v>
@@ -25609,6 +25677,7 @@
     <row r="250" spans="1:23" s="2" customFormat="1" ht="28.5" customHeight="1">
       <c r="A250" s="11" t="str">
         <f t="shared" si="39"/>
+        <v/>
       </c>
       <c r="B250" s="11" t="s">
         <v>18</v>
@@ -25688,6 +25757,7 @@
     <row r="251" spans="1:23" s="2" customFormat="1" ht="28.5" customHeight="1">
       <c r="A251" s="11" t="str">
         <f t="shared" si="39"/>
+        <v/>
       </c>
       <c r="B251" s="11" t="s">
         <v>18</v>
@@ -25767,6 +25837,7 @@
     <row r="252" spans="1:23" s="16" customFormat="1" ht="28.5" customHeight="1">
       <c r="A252" s="11" t="str">
         <f t="shared" si="39"/>
+        <v/>
       </c>
       <c r="B252" s="11" t="s">
         <v>12</v>
@@ -25818,15 +25889,19 @@
       <c r="Q252" s="12"/>
       <c r="R252" s="13" t="str">
         <f t="shared" si="46"/>
+        <v/>
       </c>
       <c r="S252" s="12" t="str">
         <f t="shared" si="47"/>
+        <v/>
       </c>
       <c r="T252" s="12" t="str">
         <f t="shared" si="48"/>
+        <v/>
       </c>
       <c r="U252" s="12" t="str">
         <f t="shared" si="49"/>
+        <v/>
       </c>
       <c r="V252" s="12" t="str">
         <f t="shared" si="50"/>
@@ -25840,6 +25915,7 @@
     <row r="253" spans="1:23" s="2" customFormat="1" ht="28.5" customHeight="1">
       <c r="A253" s="11" t="str">
         <f t="shared" si="39"/>
+        <v/>
       </c>
       <c r="B253" s="11" t="s">
         <v>6</v>
@@ -25919,6 +25995,7 @@
     <row r="254" spans="1:23" s="2" customFormat="1" ht="28.5" customHeight="1">
       <c r="A254" s="11" t="str">
         <f t="shared" si="39"/>
+        <v/>
       </c>
       <c r="B254" s="11" t="s">
         <v>10</v>
@@ -25998,6 +26075,7 @@
     <row r="255" spans="1:23" s="2" customFormat="1" ht="28.5" customHeight="1">
       <c r="A255" s="11" t="str">
         <f t="shared" si="39"/>
+        <v/>
       </c>
       <c r="B255" s="11" t="s">
         <v>6</v>
@@ -26077,6 +26155,7 @@
     <row r="256" spans="1:23" s="2" customFormat="1" ht="28.5" customHeight="1">
       <c r="A256" s="11" t="str">
         <f t="shared" si="39"/>
+        <v/>
       </c>
       <c r="B256" s="11" t="s">
         <v>6</v>
@@ -26156,6 +26235,7 @@
     <row r="257" spans="1:23" s="2" customFormat="1" ht="28.5" customHeight="1">
       <c r="A257" s="11" t="str">
         <f t="shared" si="39"/>
+        <v/>
       </c>
       <c r="B257" s="11" t="s">
         <v>12</v>
@@ -26235,6 +26315,7 @@
     <row r="258" spans="1:23" s="16" customFormat="1" ht="28.5" customHeight="1">
       <c r="A258" s="11" t="str">
         <f t="shared" si="39"/>
+        <v/>
       </c>
       <c r="B258" s="11" t="s">
         <v>10</v>
@@ -26314,6 +26395,7 @@
     <row r="259" spans="1:23" s="7" customFormat="1" ht="28.5" customHeight="1">
       <c r="A259" s="11" t="str">
         <f t="shared" si="39"/>
+        <v/>
       </c>
       <c r="B259" s="11" t="s">
         <v>10</v>
@@ -26393,6 +26475,7 @@
     <row r="260" spans="1:23" s="2" customFormat="1" ht="28.5" customHeight="1">
       <c r="A260" s="11" t="str">
         <f t="shared" si="39"/>
+        <v/>
       </c>
       <c r="B260" s="11" t="s">
         <v>10</v>
@@ -26472,6 +26555,7 @@
     <row r="261" spans="1:23" s="16" customFormat="1" ht="28.5" customHeight="1">
       <c r="A261" s="11" t="str">
         <f t="shared" si="39"/>
+        <v/>
       </c>
       <c r="B261" s="11" t="s">
         <v>10</v>
@@ -26551,6 +26635,7 @@
     <row r="262" spans="1:23" s="16" customFormat="1" ht="28.5" customHeight="1">
       <c r="A262" s="11" t="str">
         <f t="shared" si="39"/>
+        <v/>
       </c>
       <c r="B262" s="11" t="s">
         <v>18</v>
@@ -26630,6 +26715,7 @@
     <row r="263" spans="1:23" s="2" customFormat="1" ht="28.5" customHeight="1">
       <c r="A263" s="11" t="str">
         <f t="shared" si="39"/>
+        <v/>
       </c>
       <c r="B263" s="11" t="s">
         <v>18</v>
@@ -26709,6 +26795,7 @@
     <row r="264" spans="1:23" s="2" customFormat="1" ht="28.5" customHeight="1">
       <c r="A264" s="11" t="str">
         <f t="shared" si="39"/>
+        <v/>
       </c>
       <c r="B264" s="11" t="s">
         <v>10</v>
@@ -26788,6 +26875,7 @@
     <row r="265" spans="1:23" s="16" customFormat="1" ht="28.5" customHeight="1">
       <c r="A265" s="11" t="str">
         <f t="shared" si="39"/>
+        <v/>
       </c>
       <c r="B265" s="11" t="s">
         <v>6</v>
@@ -26867,6 +26955,7 @@
     <row r="266" spans="1:23" s="2" customFormat="1" ht="28.5" customHeight="1">
       <c r="A266" s="11" t="str">
         <f t="shared" si="39"/>
+        <v/>
       </c>
       <c r="B266" s="11" t="s">
         <v>6</v>
@@ -26946,6 +27035,7 @@
     <row r="267" spans="1:23" s="2" customFormat="1" ht="28.5" customHeight="1">
       <c r="A267" s="11" t="str">
         <f t="shared" si="39"/>
+        <v/>
       </c>
       <c r="B267" s="11" t="s">
         <v>10</v>
@@ -27025,6 +27115,7 @@
     <row r="268" spans="1:23" s="16" customFormat="1" ht="28.5" customHeight="1">
       <c r="A268" s="11" t="str">
         <f t="shared" si="39"/>
+        <v/>
       </c>
       <c r="B268" s="11" t="s">
         <v>6</v>
@@ -27104,6 +27195,7 @@
     <row r="269" spans="1:23" s="2" customFormat="1" ht="28.5" customHeight="1">
       <c r="A269" s="11" t="str">
         <f t="shared" si="39"/>
+        <v/>
       </c>
       <c r="B269" s="11" t="s">
         <v>12</v>
@@ -27183,6 +27275,7 @@
     <row r="270" spans="1:23" s="2" customFormat="1" ht="28.5" customHeight="1">
       <c r="A270" s="11" t="str">
         <f t="shared" si="39"/>
+        <v/>
       </c>
       <c r="B270" s="11" t="s">
         <v>18</v>
@@ -27262,6 +27355,7 @@
     <row r="271" spans="1:23" s="2" customFormat="1" ht="28.5" customHeight="1">
       <c r="A271" s="11" t="str">
         <f t="shared" ref="A271:A334" si="52">IF($T271="","",1+COUNTIF($W$15:$W$883,"&lt;"&amp;W271))</f>
+        <v/>
       </c>
       <c r="B271" s="11" t="s">
         <v>18</v>
@@ -27341,6 +27435,7 @@
     <row r="272" spans="1:23" s="16" customFormat="1" ht="28.5" customHeight="1">
       <c r="A272" s="11" t="str">
         <f t="shared" si="52"/>
+        <v/>
       </c>
       <c r="B272" s="11" t="s">
         <v>6</v>
@@ -27420,6 +27515,7 @@
     <row r="273" spans="1:23" s="2" customFormat="1" ht="28.5" customHeight="1">
       <c r="A273" s="11" t="str">
         <f t="shared" si="52"/>
+        <v/>
       </c>
       <c r="B273" s="11" t="s">
         <v>18</v>
@@ -27499,6 +27595,7 @@
     <row r="274" spans="1:23" s="2" customFormat="1" ht="28.5" customHeight="1">
       <c r="A274" s="11" t="str">
         <f t="shared" si="52"/>
+        <v/>
       </c>
       <c r="B274" s="11" t="s">
         <v>10</v>
@@ -27578,6 +27675,7 @@
     <row r="275" spans="1:23" s="2" customFormat="1" ht="28.5" customHeight="1">
       <c r="A275" s="11" t="str">
         <f t="shared" si="52"/>
+        <v/>
       </c>
       <c r="B275" s="11" t="s">
         <v>10</v>
@@ -27657,6 +27755,7 @@
     <row r="276" spans="1:23" s="2" customFormat="1" ht="28.5" customHeight="1">
       <c r="A276" s="11" t="str">
         <f t="shared" si="52"/>
+        <v/>
       </c>
       <c r="B276" s="11" t="s">
         <v>10</v>
@@ -27736,6 +27835,7 @@
     <row r="277" spans="1:23" s="2" customFormat="1" ht="28.5" customHeight="1">
       <c r="A277" s="11" t="str">
         <f t="shared" si="52"/>
+        <v/>
       </c>
       <c r="B277" s="11" t="s">
         <v>18</v>
@@ -27815,6 +27915,7 @@
     <row r="278" spans="1:23" s="2" customFormat="1" ht="28.5" customHeight="1">
       <c r="A278" s="11" t="str">
         <f t="shared" si="52"/>
+        <v/>
       </c>
       <c r="B278" s="11" t="s">
         <v>14</v>
@@ -27894,6 +27995,7 @@
     <row r="279" spans="1:23" s="16" customFormat="1" ht="28.5" customHeight="1">
       <c r="A279" s="11" t="str">
         <f t="shared" si="52"/>
+        <v/>
       </c>
       <c r="B279" s="11" t="s">
         <v>10</v>
@@ -27973,6 +28075,7 @@
     <row r="280" spans="1:23" s="2" customFormat="1" ht="28.5" customHeight="1">
       <c r="A280" s="11" t="str">
         <f t="shared" si="52"/>
+        <v/>
       </c>
       <c r="B280" s="11" t="s">
         <v>6</v>
@@ -28052,6 +28155,7 @@
     <row r="281" spans="1:23" s="2" customFormat="1" ht="28.5" customHeight="1">
       <c r="A281" s="11" t="str">
         <f t="shared" si="52"/>
+        <v/>
       </c>
       <c r="B281" s="11" t="s">
         <v>8</v>
@@ -28129,6 +28233,7 @@
     <row r="282" spans="1:23" s="2" customFormat="1" ht="28.5" customHeight="1">
       <c r="A282" s="11" t="str">
         <f t="shared" si="52"/>
+        <v/>
       </c>
       <c r="B282" s="11" t="s">
         <v>12</v>
@@ -28208,6 +28313,7 @@
     <row r="283" spans="1:23" s="7" customFormat="1" ht="28.5" customHeight="1">
       <c r="A283" s="11" t="str">
         <f t="shared" si="52"/>
+        <v/>
       </c>
       <c r="B283" s="11" t="s">
         <v>10</v>
@@ -28287,6 +28393,7 @@
     <row r="284" spans="1:23" s="7" customFormat="1" ht="28.5" customHeight="1">
       <c r="A284" s="11" t="str">
         <f t="shared" si="52"/>
+        <v/>
       </c>
       <c r="B284" s="11" t="s">
         <v>12</v>
@@ -28338,15 +28445,19 @@
       <c r="Q284" s="12"/>
       <c r="R284" s="13" t="str">
         <f t="shared" si="59"/>
+        <v/>
       </c>
       <c r="S284" s="12" t="str">
         <f t="shared" si="60"/>
+        <v/>
       </c>
       <c r="T284" s="12" t="str">
         <f t="shared" si="61"/>
+        <v/>
       </c>
       <c r="U284" s="12" t="str">
         <f t="shared" si="62"/>
+        <v/>
       </c>
       <c r="V284" s="12" t="str">
         <f t="shared" si="63"/>
@@ -28360,6 +28471,7 @@
     <row r="285" spans="1:23" s="2" customFormat="1" ht="28.5" customHeight="1">
       <c r="A285" s="11" t="str">
         <f t="shared" si="52"/>
+        <v/>
       </c>
       <c r="B285" s="11" t="s">
         <v>6</v>
@@ -28439,6 +28551,7 @@
     <row r="286" spans="1:23" s="2" customFormat="1" ht="28.5" customHeight="1">
       <c r="A286" s="11" t="str">
         <f t="shared" si="52"/>
+        <v/>
       </c>
       <c r="B286" s="11" t="s">
         <v>16</v>
@@ -28518,6 +28631,7 @@
     <row r="287" spans="1:23" s="2" customFormat="1" ht="28.5" customHeight="1">
       <c r="A287" s="11" t="str">
         <f t="shared" si="52"/>
+        <v/>
       </c>
       <c r="B287" s="11" t="s">
         <v>12</v>
@@ -28597,6 +28711,7 @@
     <row r="288" spans="1:23" s="2" customFormat="1" ht="28.5" customHeight="1">
       <c r="A288" s="11" t="str">
         <f t="shared" si="52"/>
+        <v/>
       </c>
       <c r="B288" s="11" t="s">
         <v>10</v>
@@ -28676,6 +28791,7 @@
     <row r="289" spans="1:23" s="2" customFormat="1" ht="28.5" customHeight="1">
       <c r="A289" s="11" t="str">
         <f t="shared" si="52"/>
+        <v/>
       </c>
       <c r="B289" s="11" t="s">
         <v>18</v>
@@ -28755,6 +28871,7 @@
     <row r="290" spans="1:23" s="2" customFormat="1" ht="28.5" customHeight="1">
       <c r="A290" s="11" t="str">
         <f t="shared" si="52"/>
+        <v/>
       </c>
       <c r="B290" s="11" t="s">
         <v>14</v>
@@ -28834,6 +28951,7 @@
     <row r="291" spans="1:23" s="16" customFormat="1" ht="28.5" customHeight="1">
       <c r="A291" s="11" t="str">
         <f t="shared" si="52"/>
+        <v/>
       </c>
       <c r="B291" s="11" t="s">
         <v>18</v>
@@ -28913,6 +29031,7 @@
     <row r="292" spans="1:23" s="2" customFormat="1" ht="28.5" customHeight="1">
       <c r="A292" s="11" t="str">
         <f t="shared" si="52"/>
+        <v/>
       </c>
       <c r="B292" s="11" t="s">
         <v>18</v>
@@ -28992,6 +29111,7 @@
     <row r="293" spans="1:23" s="2" customFormat="1" ht="28.5" customHeight="1">
       <c r="A293" s="11" t="str">
         <f t="shared" si="52"/>
+        <v/>
       </c>
       <c r="B293" s="11" t="s">
         <v>16</v>
@@ -29071,6 +29191,7 @@
     <row r="294" spans="1:23" s="2" customFormat="1" ht="28.5" customHeight="1">
       <c r="A294" s="11" t="str">
         <f t="shared" si="52"/>
+        <v/>
       </c>
       <c r="B294" s="11" t="s">
         <v>16</v>
@@ -29150,6 +29271,7 @@
     <row r="295" spans="1:23" s="2" customFormat="1" ht="28.5" customHeight="1">
       <c r="A295" s="11" t="str">
         <f t="shared" si="52"/>
+        <v/>
       </c>
       <c r="B295" s="11" t="s">
         <v>14</v>
@@ -29229,6 +29351,7 @@
     <row r="296" spans="1:23" s="7" customFormat="1" ht="28.5" customHeight="1">
       <c r="A296" s="11" t="str">
         <f t="shared" si="52"/>
+        <v/>
       </c>
       <c r="B296" s="11" t="s">
         <v>10</v>
@@ -29308,6 +29431,7 @@
     <row r="297" spans="1:23" s="2" customFormat="1" ht="28.5" customHeight="1">
       <c r="A297" s="11" t="str">
         <f t="shared" si="52"/>
+        <v/>
       </c>
       <c r="B297" s="11" t="s">
         <v>6</v>
@@ -29387,6 +29511,7 @@
     <row r="298" spans="1:23" s="2" customFormat="1" ht="28.5" customHeight="1">
       <c r="A298" s="11" t="str">
         <f t="shared" si="52"/>
+        <v/>
       </c>
       <c r="B298" s="11" t="s">
         <v>12</v>
@@ -29466,6 +29591,7 @@
     <row r="299" spans="1:23" s="2" customFormat="1" ht="28.5" customHeight="1">
       <c r="A299" s="11" t="str">
         <f t="shared" si="52"/>
+        <v/>
       </c>
       <c r="B299" s="11" t="s">
         <v>12</v>
@@ -29545,6 +29671,7 @@
     <row r="300" spans="1:23" s="2" customFormat="1" ht="28.5" customHeight="1">
       <c r="A300" s="11" t="str">
         <f t="shared" si="52"/>
+        <v/>
       </c>
       <c r="B300" s="11" t="s">
         <v>10</v>
@@ -29624,6 +29751,7 @@
     <row r="301" spans="1:23" s="2" customFormat="1" ht="28.5" customHeight="1">
       <c r="A301" s="11" t="str">
         <f t="shared" si="52"/>
+        <v/>
       </c>
       <c r="B301" s="11" t="s">
         <v>12</v>
@@ -29703,6 +29831,7 @@
     <row r="302" spans="1:23" s="2" customFormat="1" ht="28.5" customHeight="1">
       <c r="A302" s="11" t="str">
         <f t="shared" si="52"/>
+        <v/>
       </c>
       <c r="B302" s="11" t="s">
         <v>18</v>
@@ -29782,6 +29911,7 @@
     <row r="303" spans="1:23" s="2" customFormat="1" ht="28.5" customHeight="1">
       <c r="A303" s="11" t="str">
         <f t="shared" si="52"/>
+        <v/>
       </c>
       <c r="B303" s="11" t="s">
         <v>8</v>
@@ -29861,6 +29991,7 @@
     <row r="304" spans="1:23" s="2" customFormat="1" ht="28.5" customHeight="1">
       <c r="A304" s="11" t="str">
         <f t="shared" si="52"/>
+        <v/>
       </c>
       <c r="B304" s="11" t="s">
         <v>8</v>
@@ -29940,6 +30071,7 @@
     <row r="305" spans="1:23" s="16" customFormat="1" ht="28.5" customHeight="1">
       <c r="A305" s="11" t="str">
         <f t="shared" si="52"/>
+        <v/>
       </c>
       <c r="B305" s="11" t="s">
         <v>6</v>
@@ -30019,6 +30151,7 @@
     <row r="306" spans="1:23" s="2" customFormat="1" ht="28.5" customHeight="1">
       <c r="A306" s="11" t="str">
         <f t="shared" si="52"/>
+        <v/>
       </c>
       <c r="B306" s="11" t="s">
         <v>6</v>
@@ -30098,6 +30231,7 @@
     <row r="307" spans="1:23" s="2" customFormat="1" ht="28.5" customHeight="1">
       <c r="A307" s="11" t="str">
         <f t="shared" si="52"/>
+        <v/>
       </c>
       <c r="B307" s="11" t="s">
         <v>18</v>
@@ -30177,6 +30311,7 @@
     <row r="308" spans="1:23" s="7" customFormat="1" ht="28.5" customHeight="1">
       <c r="A308" s="11" t="str">
         <f t="shared" si="52"/>
+        <v/>
       </c>
       <c r="B308" s="11" t="s">
         <v>18</v>
@@ -30256,6 +30391,7 @@
     <row r="309" spans="1:23" s="2" customFormat="1" ht="28.5" customHeight="1">
       <c r="A309" s="11" t="str">
         <f t="shared" si="52"/>
+        <v/>
       </c>
       <c r="B309" s="11" t="s">
         <v>18</v>
@@ -30335,6 +30471,7 @@
     <row r="310" spans="1:23" s="7" customFormat="1" ht="28.5" customHeight="1">
       <c r="A310" s="11" t="str">
         <f t="shared" si="52"/>
+        <v/>
       </c>
       <c r="B310" s="11" t="s">
         <v>10</v>
@@ -30414,6 +30551,7 @@
     <row r="311" spans="1:23" s="2" customFormat="1" ht="28.5" customHeight="1">
       <c r="A311" s="11" t="str">
         <f t="shared" si="52"/>
+        <v/>
       </c>
       <c r="B311" s="11" t="s">
         <v>10</v>
@@ -30493,6 +30631,7 @@
     <row r="312" spans="1:23" s="2" customFormat="1" ht="28.5" customHeight="1">
       <c r="A312" s="11" t="str">
         <f t="shared" si="52"/>
+        <v/>
       </c>
       <c r="B312" s="11" t="s">
         <v>14</v>
@@ -30572,6 +30711,7 @@
     <row r="313" spans="1:23" s="16" customFormat="1" ht="28.5" customHeight="1">
       <c r="A313" s="11" t="str">
         <f t="shared" si="52"/>
+        <v/>
       </c>
       <c r="B313" s="11" t="s">
         <v>6</v>
@@ -30651,6 +30791,7 @@
     <row r="314" spans="1:23" s="7" customFormat="1" ht="28.5" customHeight="1">
       <c r="A314" s="11" t="str">
         <f t="shared" si="52"/>
+        <v/>
       </c>
       <c r="B314" s="11" t="s">
         <v>12</v>
@@ -30730,6 +30871,7 @@
     <row r="315" spans="1:23" s="2" customFormat="1" ht="28.5" customHeight="1">
       <c r="A315" s="11" t="str">
         <f t="shared" si="52"/>
+        <v/>
       </c>
       <c r="B315" s="11" t="s">
         <v>10</v>
@@ -30809,6 +30951,7 @@
     <row r="316" spans="1:23" s="2" customFormat="1" ht="28.5" customHeight="1">
       <c r="A316" s="11" t="str">
         <f t="shared" si="52"/>
+        <v/>
       </c>
       <c r="B316" s="11" t="s">
         <v>6</v>
@@ -30888,6 +31031,7 @@
     <row r="317" spans="1:23" s="2" customFormat="1" ht="28.5" customHeight="1">
       <c r="A317" s="11" t="str">
         <f t="shared" si="52"/>
+        <v/>
       </c>
       <c r="B317" s="11" t="s">
         <v>10</v>
@@ -30967,6 +31111,7 @@
     <row r="318" spans="1:23" s="2" customFormat="1" ht="28.5" customHeight="1">
       <c r="A318" s="11" t="str">
         <f t="shared" si="52"/>
+        <v/>
       </c>
       <c r="B318" s="11" t="s">
         <v>8</v>
@@ -31046,6 +31191,7 @@
     <row r="319" spans="1:23" s="7" customFormat="1" ht="28.5" customHeight="1">
       <c r="A319" s="11" t="str">
         <f t="shared" si="52"/>
+        <v/>
       </c>
       <c r="B319" s="11" t="s">
         <v>12</v>
@@ -31125,6 +31271,7 @@
     <row r="320" spans="1:23" s="2" customFormat="1" ht="28.5" customHeight="1">
       <c r="A320" s="11" t="str">
         <f t="shared" si="52"/>
+        <v/>
       </c>
       <c r="B320" s="11" t="s">
         <v>10</v>
@@ -31204,6 +31351,7 @@
     <row r="321" spans="1:23" s="7" customFormat="1" ht="28.5" customHeight="1">
       <c r="A321" s="11" t="str">
         <f t="shared" si="52"/>
+        <v/>
       </c>
       <c r="B321" s="11" t="s">
         <v>6</v>
@@ -31283,6 +31431,7 @@
     <row r="322" spans="1:23" s="2" customFormat="1" ht="28.5" customHeight="1">
       <c r="A322" s="11" t="str">
         <f t="shared" si="52"/>
+        <v/>
       </c>
       <c r="B322" s="11" t="s">
         <v>6</v>
@@ -31362,6 +31511,7 @@
     <row r="323" spans="1:23" s="2" customFormat="1" ht="28.5" customHeight="1">
       <c r="A323" s="11" t="str">
         <f t="shared" si="52"/>
+        <v/>
       </c>
       <c r="B323" s="11" t="s">
         <v>6</v>
@@ -31441,6 +31591,7 @@
     <row r="324" spans="1:23" s="16" customFormat="1" ht="28.5" customHeight="1">
       <c r="A324" s="11" t="str">
         <f t="shared" si="52"/>
+        <v/>
       </c>
       <c r="B324" s="11" t="s">
         <v>12</v>
@@ -31520,6 +31671,7 @@
     <row r="325" spans="1:23" s="16" customFormat="1" ht="28.5" customHeight="1">
       <c r="A325" s="11" t="str">
         <f t="shared" si="52"/>
+        <v/>
       </c>
       <c r="B325" s="11" t="s">
         <v>12</v>
@@ -31599,6 +31751,7 @@
     <row r="326" spans="1:23" s="7" customFormat="1" ht="28.5" customHeight="1">
       <c r="A326" s="11" t="str">
         <f t="shared" si="52"/>
+        <v/>
       </c>
       <c r="B326" s="11" t="s">
         <v>10</v>
@@ -31678,6 +31831,7 @@
     <row r="327" spans="1:23" s="2" customFormat="1" ht="28.5" customHeight="1">
       <c r="A327" s="11" t="str">
         <f t="shared" si="52"/>
+        <v/>
       </c>
       <c r="B327" s="11" t="s">
         <v>12</v>
@@ -31757,6 +31911,7 @@
     <row r="328" spans="1:23" s="2" customFormat="1" ht="28.5" customHeight="1">
       <c r="A328" s="11" t="str">
         <f t="shared" si="52"/>
+        <v/>
       </c>
       <c r="B328" s="11" t="s">
         <v>10</v>
@@ -31836,6 +31991,7 @@
     <row r="329" spans="1:23" s="2" customFormat="1" ht="28.5" customHeight="1">
       <c r="A329" s="11" t="str">
         <f t="shared" si="52"/>
+        <v/>
       </c>
       <c r="B329" s="11" t="s">
         <v>10</v>
@@ -31915,6 +32071,7 @@
     <row r="330" spans="1:23" s="2" customFormat="1" ht="28.5" customHeight="1">
       <c r="A330" s="11" t="str">
         <f t="shared" si="52"/>
+        <v/>
       </c>
       <c r="B330" s="11" t="s">
         <v>8</v>
@@ -31994,6 +32151,7 @@
     <row r="331" spans="1:23" s="16" customFormat="1" ht="28.5" customHeight="1">
       <c r="A331" s="11" t="str">
         <f t="shared" si="52"/>
+        <v/>
       </c>
       <c r="B331" s="11" t="s">
         <v>12</v>
@@ -32073,6 +32231,7 @@
     <row r="332" spans="1:23" s="16" customFormat="1" ht="28.5" customHeight="1">
       <c r="A332" s="11" t="str">
         <f t="shared" si="52"/>
+        <v/>
       </c>
       <c r="B332" s="11" t="s">
         <v>12</v>
@@ -32152,6 +32311,7 @@
     <row r="333" spans="1:23" s="2" customFormat="1" ht="28.5" customHeight="1">
       <c r="A333" s="11" t="str">
         <f t="shared" si="52"/>
+        <v/>
       </c>
       <c r="B333" s="11" t="s">
         <v>12</v>
@@ -32231,6 +32391,7 @@
     <row r="334" spans="1:23" s="7" customFormat="1" ht="28.5" customHeight="1">
       <c r="A334" s="11" t="str">
         <f t="shared" si="52"/>
+        <v/>
       </c>
       <c r="B334" s="11" t="s">
         <v>14</v>
@@ -32310,6 +32471,7 @@
     <row r="335" spans="1:23" s="2" customFormat="1" ht="28.5" customHeight="1">
       <c r="A335" s="11" t="str">
         <f t="shared" ref="A335:A398" si="65">IF($T335="","",1+COUNTIF($W$15:$W$883,"&lt;"&amp;W335))</f>
+        <v/>
       </c>
       <c r="B335" s="11" t="s">
         <v>10</v>
@@ -32389,6 +32551,7 @@
     <row r="336" spans="1:23" s="2" customFormat="1" ht="28.5" customHeight="1">
       <c r="A336" s="11" t="str">
         <f t="shared" si="65"/>
+        <v/>
       </c>
       <c r="B336" s="11" t="s">
         <v>10</v>
@@ -32468,6 +32631,7 @@
     <row r="337" spans="1:23" s="2" customFormat="1" ht="28.5" customHeight="1">
       <c r="A337" s="11" t="str">
         <f t="shared" si="65"/>
+        <v/>
       </c>
       <c r="B337" s="11" t="s">
         <v>10</v>
@@ -32547,6 +32711,7 @@
     <row r="338" spans="1:23" s="16" customFormat="1" ht="28.5" customHeight="1">
       <c r="A338" s="11" t="str">
         <f t="shared" si="65"/>
+        <v/>
       </c>
       <c r="B338" s="11" t="s">
         <v>6</v>
@@ -32626,6 +32791,7 @@
     <row r="339" spans="1:23" s="2" customFormat="1" ht="28.5" customHeight="1">
       <c r="A339" s="11" t="str">
         <f t="shared" si="65"/>
+        <v/>
       </c>
       <c r="B339" s="11" t="s">
         <v>12</v>
@@ -32705,6 +32871,7 @@
     <row r="340" spans="1:23" s="2" customFormat="1" ht="28.5" customHeight="1">
       <c r="A340" s="11" t="str">
         <f t="shared" si="65"/>
+        <v/>
       </c>
       <c r="B340" s="11" t="s">
         <v>14</v>
@@ -32784,6 +32951,7 @@
     <row r="341" spans="1:23" s="2" customFormat="1" ht="28.5" customHeight="1">
       <c r="A341" s="11" t="str">
         <f t="shared" si="65"/>
+        <v/>
       </c>
       <c r="B341" s="11" t="s">
         <v>14</v>
@@ -32863,6 +33031,7 @@
     <row r="342" spans="1:23" s="2" customFormat="1" ht="28.5" customHeight="1">
       <c r="A342" s="11" t="str">
         <f t="shared" si="65"/>
+        <v/>
       </c>
       <c r="B342" s="11" t="s">
         <v>8</v>
@@ -32942,6 +33111,7 @@
     <row r="343" spans="1:23" s="2" customFormat="1" ht="28.5" customHeight="1">
       <c r="A343" s="11" t="str">
         <f t="shared" si="65"/>
+        <v/>
       </c>
       <c r="B343" s="11" t="s">
         <v>8</v>
@@ -33021,6 +33191,7 @@
     <row r="344" spans="1:23" s="2" customFormat="1" ht="28.5" customHeight="1">
       <c r="A344" s="11" t="str">
         <f t="shared" si="65"/>
+        <v/>
       </c>
       <c r="B344" s="11" t="s">
         <v>8</v>
@@ -33100,6 +33271,7 @@
     <row r="345" spans="1:23" s="2" customFormat="1" ht="28.5" customHeight="1">
       <c r="A345" s="11" t="str">
         <f t="shared" si="65"/>
+        <v/>
       </c>
       <c r="B345" s="11" t="s">
         <v>12</v>
@@ -33179,6 +33351,7 @@
     <row r="346" spans="1:23" s="16" customFormat="1" ht="28.5" customHeight="1">
       <c r="A346" s="11" t="str">
         <f t="shared" si="65"/>
+        <v/>
       </c>
       <c r="B346" s="11" t="s">
         <v>14</v>
@@ -33258,6 +33431,7 @@
     <row r="347" spans="1:23" s="2" customFormat="1" ht="28.5" customHeight="1">
       <c r="A347" s="11" t="str">
         <f t="shared" si="65"/>
+        <v/>
       </c>
       <c r="B347" s="11" t="s">
         <v>8</v>
@@ -33337,6 +33511,7 @@
     <row r="348" spans="1:23" s="2" customFormat="1" ht="28.5" customHeight="1">
       <c r="A348" s="11" t="str">
         <f t="shared" si="65"/>
+        <v/>
       </c>
       <c r="B348" s="11" t="s">
         <v>14</v>
@@ -33416,6 +33591,7 @@
     <row r="349" spans="1:23" s="16" customFormat="1" ht="28.5" customHeight="1">
       <c r="A349" s="11" t="str">
         <f t="shared" si="65"/>
+        <v/>
       </c>
       <c r="B349" s="11" t="s">
         <v>8</v>
@@ -33495,6 +33671,7 @@
     <row r="350" spans="1:23" s="2" customFormat="1" ht="28.5" customHeight="1">
       <c r="A350" s="11" t="str">
         <f t="shared" si="65"/>
+        <v/>
       </c>
       <c r="B350" s="11" t="s">
         <v>8</v>
@@ -33574,6 +33751,7 @@
     <row r="351" spans="1:23" s="2" customFormat="1" ht="28.5" customHeight="1">
       <c r="A351" s="11" t="str">
         <f t="shared" si="65"/>
+        <v/>
       </c>
       <c r="B351" s="11" t="s">
         <v>10</v>
@@ -33653,6 +33831,7 @@
     <row r="352" spans="1:23" s="16" customFormat="1" ht="28.5" customHeight="1">
       <c r="A352" s="11" t="str">
         <f t="shared" si="65"/>
+        <v/>
       </c>
       <c r="B352" s="11" t="s">
         <v>8</v>
@@ -33732,6 +33911,7 @@
     <row r="353" spans="1:23" s="16" customFormat="1" ht="28.5" customHeight="1">
       <c r="A353" s="11" t="str">
         <f t="shared" si="65"/>
+        <v/>
       </c>
       <c r="B353" s="11" t="s">
         <v>14</v>
@@ -33811,6 +33991,7 @@
     <row r="354" spans="1:23" s="7" customFormat="1" ht="28.5" customHeight="1">
       <c r="A354" s="11" t="str">
         <f t="shared" si="65"/>
+        <v/>
       </c>
       <c r="B354" s="11" t="s">
         <v>10</v>
@@ -33890,6 +34071,7 @@
     <row r="355" spans="1:23" s="2" customFormat="1" ht="28.5" customHeight="1">
       <c r="A355" s="11" t="str">
         <f t="shared" si="65"/>
+        <v/>
       </c>
       <c r="B355" s="11" t="s">
         <v>10</v>
@@ -33969,6 +34151,7 @@
     <row r="356" spans="1:23" s="2" customFormat="1" ht="28.5" customHeight="1">
       <c r="A356" s="11" t="str">
         <f t="shared" si="65"/>
+        <v/>
       </c>
       <c r="B356" s="11" t="s">
         <v>6</v>
@@ -34048,6 +34231,7 @@
     <row r="357" spans="1:23" s="2" customFormat="1" ht="28.5" customHeight="1">
       <c r="A357" s="11" t="str">
         <f t="shared" si="65"/>
+        <v/>
       </c>
       <c r="B357" s="11" t="s">
         <v>12</v>
@@ -34127,6 +34311,7 @@
     <row r="358" spans="1:23" s="2" customFormat="1" ht="28.5" customHeight="1">
       <c r="A358" s="11" t="str">
         <f t="shared" si="65"/>
+        <v/>
       </c>
       <c r="B358" s="11" t="s">
         <v>10</v>
@@ -34206,6 +34391,7 @@
     <row r="359" spans="1:23" s="2" customFormat="1" ht="28.5" customHeight="1">
       <c r="A359" s="11" t="str">
         <f t="shared" si="65"/>
+        <v/>
       </c>
       <c r="B359" s="11" t="s">
         <v>6</v>
@@ -34285,6 +34471,7 @@
     <row r="360" spans="1:23" s="2" customFormat="1" ht="28.5" customHeight="1">
       <c r="A360" s="11" t="str">
         <f t="shared" si="65"/>
+        <v/>
       </c>
       <c r="B360" s="11" t="s">
         <v>10</v>
@@ -34364,6 +34551,7 @@
     <row r="361" spans="1:23" s="2" customFormat="1" ht="28.5" customHeight="1">
       <c r="A361" s="11" t="str">
         <f t="shared" si="65"/>
+        <v/>
       </c>
       <c r="B361" s="11" t="s">
         <v>6</v>
@@ -34443,6 +34631,7 @@
     <row r="362" spans="1:23" s="2" customFormat="1" ht="28.5" customHeight="1">
       <c r="A362" s="11" t="str">
         <f t="shared" si="65"/>
+        <v/>
       </c>
       <c r="B362" s="11" t="s">
         <v>14</v>
@@ -34522,6 +34711,7 @@
     <row r="363" spans="1:23" s="2" customFormat="1" ht="28.5" customHeight="1">
       <c r="A363" s="11" t="str">
         <f t="shared" si="65"/>
+        <v/>
       </c>
       <c r="B363" s="11" t="s">
         <v>8</v>
@@ -34601,6 +34791,7 @@
     <row r="364" spans="1:23" s="7" customFormat="1" ht="28.5" customHeight="1">
       <c r="A364" s="11" t="str">
         <f t="shared" si="65"/>
+        <v/>
       </c>
       <c r="B364" s="11" t="s">
         <v>14</v>
@@ -34680,6 +34871,7 @@
     <row r="365" spans="1:23" s="7" customFormat="1" ht="28.5" customHeight="1">
       <c r="A365" s="11" t="str">
         <f t="shared" si="65"/>
+        <v/>
       </c>
       <c r="B365" s="11" t="s">
         <v>14</v>
@@ -34759,6 +34951,7 @@
     <row r="366" spans="1:23" s="16" customFormat="1" ht="28.5" customHeight="1">
       <c r="A366" s="11" t="str">
         <f t="shared" si="65"/>
+        <v/>
       </c>
       <c r="B366" s="11" t="s">
         <v>10</v>
@@ -34838,6 +35031,7 @@
     <row r="367" spans="1:23" s="2" customFormat="1" ht="28.5" customHeight="1">
       <c r="A367" s="11" t="str">
         <f t="shared" si="65"/>
+        <v/>
       </c>
       <c r="B367" s="11" t="s">
         <v>10</v>
@@ -34917,6 +35111,7 @@
     <row r="368" spans="1:23" s="2" customFormat="1" ht="28.5" customHeight="1">
       <c r="A368" s="11" t="str">
         <f t="shared" si="65"/>
+        <v/>
       </c>
       <c r="B368" s="11" t="s">
         <v>10</v>
@@ -34996,6 +35191,7 @@
     <row r="369" spans="1:23" s="7" customFormat="1" ht="28.5" customHeight="1">
       <c r="A369" s="11" t="str">
         <f t="shared" si="65"/>
+        <v/>
       </c>
       <c r="B369" s="11" t="s">
         <v>8</v>
@@ -35075,6 +35271,7 @@
     <row r="370" spans="1:23" s="16" customFormat="1" ht="28.5" customHeight="1">
       <c r="A370" s="11" t="str">
         <f t="shared" si="65"/>
+        <v/>
       </c>
       <c r="B370" s="11" t="s">
         <v>8</v>
@@ -35154,6 +35351,7 @@
     <row r="371" spans="1:23" s="2" customFormat="1" ht="28.5" customHeight="1">
       <c r="A371" s="11" t="str">
         <f t="shared" si="65"/>
+        <v/>
       </c>
       <c r="B371" s="11" t="s">
         <v>12</v>
@@ -35233,6 +35431,7 @@
     <row r="372" spans="1:23" s="2" customFormat="1" ht="28.5" customHeight="1">
       <c r="A372" s="11" t="str">
         <f t="shared" si="65"/>
+        <v/>
       </c>
       <c r="B372" s="11" t="s">
         <v>12</v>
@@ -35312,6 +35511,7 @@
     <row r="373" spans="1:23" s="2" customFormat="1" ht="28.5" customHeight="1">
       <c r="A373" s="11" t="str">
         <f t="shared" si="65"/>
+        <v/>
       </c>
       <c r="B373" s="11" t="s">
         <v>6</v>
@@ -35391,6 +35591,7 @@
     <row r="374" spans="1:23" s="7" customFormat="1" ht="28.5" customHeight="1">
       <c r="A374" s="11" t="str">
         <f t="shared" si="65"/>
+        <v/>
       </c>
       <c r="B374" s="11" t="s">
         <v>12</v>
@@ -35470,6 +35671,7 @@
     <row r="375" spans="1:23" s="2" customFormat="1" ht="28.5" customHeight="1">
       <c r="A375" s="11" t="str">
         <f t="shared" si="65"/>
+        <v/>
       </c>
       <c r="B375" s="11" t="s">
         <v>10</v>
@@ -35549,6 +35751,7 @@
     <row r="376" spans="1:23" s="2" customFormat="1" ht="28.5" customHeight="1">
       <c r="A376" s="11" t="str">
         <f t="shared" si="65"/>
+        <v/>
       </c>
       <c r="B376" s="11" t="s">
         <v>6</v>
@@ -35628,6 +35831,7 @@
     <row r="377" spans="1:23" s="2" customFormat="1" ht="28.5" customHeight="1">
       <c r="A377" s="11" t="str">
         <f t="shared" si="65"/>
+        <v/>
       </c>
       <c r="B377" s="11" t="s">
         <v>8</v>
@@ -35707,6 +35911,7 @@
     <row r="378" spans="1:23" s="2" customFormat="1" ht="28.5" customHeight="1">
       <c r="A378" s="11" t="str">
         <f t="shared" si="65"/>
+        <v/>
       </c>
       <c r="B378" s="11" t="s">
         <v>12</v>
@@ -35786,6 +35991,7 @@
     <row r="379" spans="1:23" s="2" customFormat="1" ht="28.5" customHeight="1">
       <c r="A379" s="11" t="str">
         <f t="shared" si="65"/>
+        <v/>
       </c>
       <c r="B379" s="11" t="s">
         <v>10</v>
@@ -35865,6 +36071,7 @@
     <row r="380" spans="1:23" s="7" customFormat="1" ht="28.5" customHeight="1">
       <c r="A380" s="11" t="str">
         <f t="shared" si="65"/>
+        <v/>
       </c>
       <c r="B380" s="11" t="s">
         <v>6</v>
@@ -35944,6 +36151,7 @@
     <row r="381" spans="1:23" s="2" customFormat="1" ht="28.5" customHeight="1">
       <c r="A381" s="11" t="str">
         <f t="shared" si="65"/>
+        <v/>
       </c>
       <c r="B381" s="11" t="s">
         <v>8</v>
@@ -36023,6 +36231,7 @@
     <row r="382" spans="1:23" s="2" customFormat="1" ht="28.5" customHeight="1">
       <c r="A382" s="11" t="str">
         <f t="shared" si="65"/>
+        <v/>
       </c>
       <c r="B382" s="11" t="s">
         <v>12</v>
@@ -36074,15 +36283,19 @@
       <c r="Q382" s="12"/>
       <c r="R382" s="13" t="str">
         <f t="shared" si="72"/>
+        <v/>
       </c>
       <c r="S382" s="12" t="str">
         <f t="shared" si="73"/>
+        <v/>
       </c>
       <c r="T382" s="12" t="str">
         <f t="shared" si="74"/>
+        <v/>
       </c>
       <c r="U382" s="12" t="str">
         <f t="shared" si="75"/>
+        <v/>
       </c>
       <c r="V382" s="12" t="str">
         <f t="shared" si="76"/>
@@ -36096,6 +36309,7 @@
     <row r="383" spans="1:23" s="2" customFormat="1" ht="28.5" customHeight="1">
       <c r="A383" s="11" t="str">
         <f t="shared" si="65"/>
+        <v/>
       </c>
       <c r="B383" s="11" t="s">
         <v>14</v>
@@ -36175,6 +36389,7 @@
     <row r="384" spans="1:23" s="2" customFormat="1" ht="28.5" customHeight="1">
       <c r="A384" s="11" t="str">
         <f t="shared" si="65"/>
+        <v/>
       </c>
       <c r="B384" s="11" t="s">
         <v>12</v>
@@ -36254,6 +36469,7 @@
     <row r="385" spans="1:23" s="2" customFormat="1" ht="28.5" customHeight="1">
       <c r="A385" s="11" t="str">
         <f t="shared" si="65"/>
+        <v/>
       </c>
       <c r="B385" s="11" t="s">
         <v>14</v>
@@ -36333,6 +36549,7 @@
     <row r="386" spans="1:23" s="7" customFormat="1" ht="28.5" customHeight="1">
       <c r="A386" s="11" t="str">
         <f t="shared" si="65"/>
+        <v/>
       </c>
       <c r="B386" s="11" t="s">
         <v>12</v>
@@ -36412,6 +36629,7 @@
     <row r="387" spans="1:23" s="2" customFormat="1" ht="28.5" customHeight="1">
       <c r="A387" s="11" t="str">
         <f t="shared" si="65"/>
+        <v/>
       </c>
       <c r="B387" s="11" t="s">
         <v>12</v>
@@ -36491,6 +36709,7 @@
     <row r="388" spans="1:23" s="16" customFormat="1" ht="28.5" customHeight="1">
       <c r="A388" s="11" t="str">
         <f t="shared" si="65"/>
+        <v/>
       </c>
       <c r="B388" s="11" t="s">
         <v>12</v>
@@ -36570,6 +36789,7 @@
     <row r="389" spans="1:23" s="2" customFormat="1" ht="28.5" customHeight="1">
       <c r="A389" s="11" t="str">
         <f t="shared" si="65"/>
+        <v/>
       </c>
       <c r="B389" s="11" t="s">
         <v>14</v>
@@ -36649,6 +36869,7 @@
     <row r="390" spans="1:23" s="2" customFormat="1" ht="28.5" customHeight="1">
       <c r="A390" s="11" t="str">
         <f t="shared" si="65"/>
+        <v/>
       </c>
       <c r="B390" s="11" t="s">
         <v>12</v>
@@ -36728,6 +36949,7 @@
     <row r="391" spans="1:23" s="2" customFormat="1" ht="28.5" customHeight="1">
       <c r="A391" s="11" t="str">
         <f t="shared" si="65"/>
+        <v/>
       </c>
       <c r="B391" s="11" t="s">
         <v>12</v>
@@ -36807,6 +37029,7 @@
     <row r="392" spans="1:23" s="16" customFormat="1" ht="28.5" customHeight="1">
       <c r="A392" s="11" t="str">
         <f t="shared" si="65"/>
+        <v/>
       </c>
       <c r="B392" s="11" t="s">
         <v>10</v>
@@ -36886,6 +37109,7 @@
     <row r="393" spans="1:23" s="2" customFormat="1" ht="28.5" customHeight="1">
       <c r="A393" s="11" t="str">
         <f t="shared" si="65"/>
+        <v/>
       </c>
       <c r="B393" s="11" t="s">
         <v>6</v>
@@ -36965,6 +37189,7 @@
     <row r="394" spans="1:23" s="2" customFormat="1" ht="28.5" customHeight="1">
       <c r="A394" s="11" t="str">
         <f t="shared" si="65"/>
+        <v/>
       </c>
       <c r="B394" s="11" t="s">
         <v>14</v>
@@ -37044,6 +37269,7 @@
     <row r="395" spans="1:23" s="2" customFormat="1" ht="28.5" customHeight="1">
       <c r="A395" s="11" t="str">
         <f t="shared" si="65"/>
+        <v/>
       </c>
       <c r="B395" s="11" t="s">
         <v>6</v>
@@ -37123,6 +37349,7 @@
     <row r="396" spans="1:23" s="2" customFormat="1" ht="28.5" customHeight="1">
       <c r="A396" s="11" t="str">
         <f t="shared" si="65"/>
+        <v/>
       </c>
       <c r="B396" s="11" t="s">
         <v>14</v>
@@ -37202,6 +37429,7 @@
     <row r="397" spans="1:23" s="2" customFormat="1" ht="28.5" customHeight="1">
       <c r="A397" s="11" t="str">
         <f t="shared" si="65"/>
+        <v/>
       </c>
       <c r="B397" s="11" t="s">
         <v>14</v>
@@ -37281,6 +37509,7 @@
     <row r="398" spans="1:23" s="7" customFormat="1" ht="28.5" customHeight="1">
       <c r="A398" s="11" t="str">
         <f t="shared" si="65"/>
+        <v/>
       </c>
       <c r="B398" s="11" t="s">
         <v>14</v>
@@ -37360,6 +37589,7 @@
     <row r="399" spans="1:23" s="2" customFormat="1" ht="28.5" customHeight="1">
       <c r="A399" s="11" t="str">
         <f t="shared" ref="A399:A462" si="78">IF($T399="","",1+COUNTIF($W$15:$W$883,"&lt;"&amp;W399))</f>
+        <v/>
       </c>
       <c r="B399" s="11" t="s">
         <v>14</v>
@@ -37413,15 +37643,19 @@
       </c>
       <c r="R399" s="13" t="str">
         <f t="shared" ref="R399:R462" si="85">IF($P399="","",IF($Q399="Y",IFERROR(VLOOKUP($B399,$C$4:$D$13,2,FALSE()),0),0))</f>
+        <v/>
       </c>
       <c r="S399" s="12" t="str">
         <f t="shared" ref="S399:S462" si="86">IF($P399="","",ROUNDDOWN($P399*$R399,0))</f>
+        <v/>
       </c>
       <c r="T399" s="12" t="str">
         <f t="shared" ref="T399:T462" si="87">IF($P399="","",$P399-$S399)</f>
+        <v/>
       </c>
       <c r="U399" s="12" t="str">
         <f t="shared" ref="U399:U462" si="88">IF($T399="","",IF($B$10=0,"",$T399/$B$10))</f>
+        <v/>
       </c>
       <c r="V399" s="12" t="str">
         <f t="shared" ref="V399:V462" si="89">IF($P399="","",IF($B$10=0,"",$P399/$B$10))</f>
@@ -37435,6 +37669,7 @@
     <row r="400" spans="1:23" s="16" customFormat="1" ht="28.5" customHeight="1">
       <c r="A400" s="11" t="str">
         <f t="shared" si="78"/>
+        <v/>
       </c>
       <c r="B400" s="11" t="s">
         <v>12</v>
@@ -37514,6 +37749,7 @@
     <row r="401" spans="1:23" s="2" customFormat="1" ht="28.5" customHeight="1">
       <c r="A401" s="11" t="str">
         <f t="shared" si="78"/>
+        <v/>
       </c>
       <c r="B401" s="11" t="s">
         <v>10</v>
@@ -37593,6 +37829,7 @@
     <row r="402" spans="1:23" s="2" customFormat="1" ht="28.5" customHeight="1">
       <c r="A402" s="11" t="str">
         <f t="shared" si="78"/>
+        <v/>
       </c>
       <c r="B402" s="11" t="s">
         <v>10</v>
@@ -37672,6 +37909,7 @@
     <row r="403" spans="1:23" s="2" customFormat="1" ht="28.5" customHeight="1">
       <c r="A403" s="11" t="str">
         <f t="shared" si="78"/>
+        <v/>
       </c>
       <c r="B403" s="11" t="s">
         <v>6</v>
@@ -37751,6 +37989,7 @@
     <row r="404" spans="1:23" s="2" customFormat="1" ht="28.5" customHeight="1">
       <c r="A404" s="11" t="str">
         <f t="shared" si="78"/>
+        <v/>
       </c>
       <c r="B404" s="11" t="s">
         <v>8</v>
@@ -37830,6 +38069,7 @@
     <row r="405" spans="1:23" s="7" customFormat="1" ht="28.5" customHeight="1">
       <c r="A405" s="11" t="str">
         <f t="shared" si="78"/>
+        <v/>
       </c>
       <c r="B405" s="11" t="s">
         <v>14</v>
@@ -37909,6 +38149,7 @@
     <row r="406" spans="1:23" s="2" customFormat="1" ht="28.5" customHeight="1">
       <c r="A406" s="11" t="str">
         <f t="shared" si="78"/>
+        <v/>
       </c>
       <c r="B406" s="11" t="s">
         <v>14</v>
@@ -37988,6 +38229,7 @@
     <row r="407" spans="1:23" s="7" customFormat="1" ht="28.5" customHeight="1">
       <c r="A407" s="11" t="str">
         <f t="shared" si="78"/>
+        <v/>
       </c>
       <c r="B407" s="11" t="s">
         <v>14</v>
@@ -38067,6 +38309,7 @@
     <row r="408" spans="1:23" s="2" customFormat="1" ht="28.5" customHeight="1">
       <c r="A408" s="11" t="str">
         <f t="shared" si="78"/>
+        <v/>
       </c>
       <c r="B408" s="11" t="s">
         <v>12</v>
@@ -38146,6 +38389,7 @@
     <row r="409" spans="1:23" s="2" customFormat="1" ht="28.5" customHeight="1">
       <c r="A409" s="11" t="str">
         <f t="shared" si="78"/>
+        <v/>
       </c>
       <c r="B409" s="11" t="s">
         <v>12</v>
@@ -38225,6 +38469,7 @@
     <row r="410" spans="1:23" s="16" customFormat="1" ht="28.5" customHeight="1">
       <c r="A410" s="11" t="str">
         <f t="shared" si="78"/>
+        <v/>
       </c>
       <c r="B410" s="11" t="s">
         <v>12</v>
@@ -38304,6 +38549,7 @@
     <row r="411" spans="1:23" s="2" customFormat="1" ht="28.5" customHeight="1">
       <c r="A411" s="11" t="str">
         <f t="shared" si="78"/>
+        <v/>
       </c>
       <c r="B411" s="11" t="s">
         <v>12</v>
@@ -38383,6 +38629,7 @@
     <row r="412" spans="1:23" s="7" customFormat="1" ht="28.5" customHeight="1">
       <c r="A412" s="11" t="str">
         <f t="shared" si="78"/>
+        <v/>
       </c>
       <c r="B412" s="11" t="s">
         <v>10</v>
@@ -38462,6 +38709,7 @@
     <row r="413" spans="1:23" s="16" customFormat="1" ht="28.5" customHeight="1">
       <c r="A413" s="11" t="str">
         <f t="shared" si="78"/>
+        <v/>
       </c>
       <c r="B413" s="11" t="s">
         <v>10</v>
@@ -38541,6 +38789,7 @@
     <row r="414" spans="1:23" s="16" customFormat="1" ht="28.5" customHeight="1">
       <c r="A414" s="11" t="str">
         <f t="shared" si="78"/>
+        <v/>
       </c>
       <c r="B414" s="11" t="s">
         <v>10</v>
@@ -38620,6 +38869,7 @@
     <row r="415" spans="1:23" s="2" customFormat="1" ht="28.5" customHeight="1">
       <c r="A415" s="11" t="str">
         <f t="shared" si="78"/>
+        <v/>
       </c>
       <c r="B415" s="11" t="s">
         <v>12</v>
@@ -38699,6 +38949,7 @@
     <row r="416" spans="1:23" s="2" customFormat="1" ht="28.5" customHeight="1">
       <c r="A416" s="11" t="str">
         <f t="shared" si="78"/>
+        <v/>
       </c>
       <c r="B416" s="11" t="s">
         <v>18</v>
@@ -38778,6 +39029,7 @@
     <row r="417" spans="1:23" s="2" customFormat="1" ht="28.5" customHeight="1">
       <c r="A417" s="11" t="str">
         <f t="shared" si="78"/>
+        <v/>
       </c>
       <c r="B417" s="11" t="s">
         <v>12</v>
@@ -38857,6 +39109,7 @@
     <row r="418" spans="1:23" s="7" customFormat="1" ht="28.5" customHeight="1">
       <c r="A418" s="11" t="str">
         <f t="shared" si="78"/>
+        <v/>
       </c>
       <c r="B418" s="11" t="s">
         <v>14</v>
@@ -38936,6 +39189,7 @@
     <row r="419" spans="1:23" s="2" customFormat="1" ht="28.5" customHeight="1">
       <c r="A419" s="11" t="str">
         <f t="shared" si="78"/>
+        <v/>
       </c>
       <c r="B419" s="11" t="s">
         <v>10</v>
@@ -39015,6 +39269,7 @@
     <row r="420" spans="1:23" s="2" customFormat="1" ht="28.5" customHeight="1">
       <c r="A420" s="11" t="str">
         <f t="shared" si="78"/>
+        <v/>
       </c>
       <c r="B420" s="11" t="s">
         <v>8</v>
@@ -39094,6 +39349,7 @@
     <row r="421" spans="1:23" s="2" customFormat="1" ht="28.5" customHeight="1">
       <c r="A421" s="11" t="str">
         <f t="shared" si="78"/>
+        <v/>
       </c>
       <c r="B421" s="11" t="s">
         <v>12</v>
@@ -39173,6 +39429,7 @@
     <row r="422" spans="1:23" s="2" customFormat="1" ht="28.5" customHeight="1">
       <c r="A422" s="11" t="str">
         <f t="shared" si="78"/>
+        <v/>
       </c>
       <c r="B422" s="11" t="s">
         <v>12</v>
@@ -39252,6 +39509,7 @@
     <row r="423" spans="1:23" s="7" customFormat="1" ht="28.5" customHeight="1">
       <c r="A423" s="11" t="str">
         <f t="shared" si="78"/>
+        <v/>
       </c>
       <c r="B423" s="11" t="s">
         <v>10</v>
@@ -39331,6 +39589,7 @@
     <row r="424" spans="1:23" s="2" customFormat="1" ht="28.5" customHeight="1">
       <c r="A424" s="11" t="str">
         <f t="shared" si="78"/>
+        <v/>
       </c>
       <c r="B424" s="11" t="s">
         <v>10</v>
@@ -39410,6 +39669,7 @@
     <row r="425" spans="1:23" s="7" customFormat="1" ht="28.5" customHeight="1">
       <c r="A425" s="11" t="str">
         <f t="shared" si="78"/>
+        <v/>
       </c>
       <c r="B425" s="11" t="s">
         <v>10</v>
@@ -39489,6 +39749,7 @@
     <row r="426" spans="1:23" s="2" customFormat="1" ht="28.5" customHeight="1">
       <c r="A426" s="11" t="str">
         <f t="shared" si="78"/>
+        <v/>
       </c>
       <c r="B426" s="11" t="s">
         <v>10</v>
@@ -39568,6 +39829,7 @@
     <row r="427" spans="1:23" s="7" customFormat="1" ht="28.5" customHeight="1">
       <c r="A427" s="11" t="str">
         <f t="shared" si="78"/>
+        <v/>
       </c>
       <c r="B427" s="11" t="s">
         <v>14</v>
@@ -39647,6 +39909,7 @@
     <row r="428" spans="1:23" s="2" customFormat="1" ht="28.5" customHeight="1">
       <c r="A428" s="11" t="str">
         <f t="shared" si="78"/>
+        <v/>
       </c>
       <c r="B428" s="11" t="s">
         <v>10</v>
@@ -39726,6 +39989,7 @@
     <row r="429" spans="1:23" s="2" customFormat="1" ht="28.5" customHeight="1">
       <c r="A429" s="11" t="str">
         <f t="shared" si="78"/>
+        <v/>
       </c>
       <c r="B429" s="11" t="s">
         <v>6</v>
@@ -39805,6 +40069,7 @@
     <row r="430" spans="1:23" s="2" customFormat="1" ht="28.5" customHeight="1">
       <c r="A430" s="11" t="str">
         <f t="shared" si="78"/>
+        <v/>
       </c>
       <c r="B430" s="11" t="s">
         <v>6</v>
@@ -39884,6 +40149,7 @@
     <row r="431" spans="1:23" s="7" customFormat="1" ht="28.5" customHeight="1">
       <c r="A431" s="11" t="str">
         <f t="shared" si="78"/>
+        <v/>
       </c>
       <c r="B431" s="11" t="s">
         <v>14</v>
@@ -39963,6 +40229,7 @@
     <row r="432" spans="1:23" s="16" customFormat="1" ht="28.5" customHeight="1">
       <c r="A432" s="11" t="str">
         <f t="shared" si="78"/>
+        <v/>
       </c>
       <c r="B432" s="11" t="s">
         <v>12</v>
@@ -40042,6 +40309,7 @@
     <row r="433" spans="1:23" s="2" customFormat="1" ht="28.5" customHeight="1">
       <c r="A433" s="11" t="str">
         <f t="shared" si="78"/>
+        <v/>
       </c>
       <c r="B433" s="11" t="s">
         <v>12</v>
@@ -40121,6 +40389,7 @@
     <row r="434" spans="1:23" s="16" customFormat="1" ht="28.5" customHeight="1">
       <c r="A434" s="11" t="str">
         <f t="shared" si="78"/>
+        <v/>
       </c>
       <c r="B434" s="11" t="s">
         <v>10</v>
@@ -40200,6 +40469,7 @@
     <row r="435" spans="1:23" s="7" customFormat="1" ht="28.5" customHeight="1">
       <c r="A435" s="11" t="str">
         <f t="shared" si="78"/>
+        <v/>
       </c>
       <c r="B435" s="11" t="s">
         <v>12</v>
@@ -40277,6 +40547,7 @@
     <row r="436" spans="1:23" s="2" customFormat="1" ht="28.5" customHeight="1">
       <c r="A436" s="11" t="str">
         <f t="shared" si="78"/>
+        <v/>
       </c>
       <c r="B436" s="11" t="s">
         <v>12</v>
@@ -40354,6 +40625,7 @@
     <row r="437" spans="1:23" s="2" customFormat="1" ht="28.5" customHeight="1">
       <c r="A437" s="11" t="str">
         <f t="shared" si="78"/>
+        <v/>
       </c>
       <c r="B437" s="11" t="s">
         <v>12</v>
@@ -40431,6 +40703,7 @@
     <row r="438" spans="1:23" s="2" customFormat="1" ht="28.5" customHeight="1">
       <c r="A438" s="11" t="str">
         <f t="shared" si="78"/>
+        <v/>
       </c>
       <c r="B438" s="11" t="s">
         <v>12</v>
@@ -40508,6 +40781,7 @@
     <row r="439" spans="1:23" s="2" customFormat="1" ht="28.5" customHeight="1">
       <c r="A439" s="11" t="str">
         <f t="shared" si="78"/>
+        <v/>
       </c>
       <c r="B439" s="11" t="s">
         <v>12</v>
@@ -40585,6 +40859,7 @@
     <row r="440" spans="1:23" s="16" customFormat="1" ht="28.5" customHeight="1">
       <c r="A440" s="11" t="str">
         <f t="shared" si="78"/>
+        <v/>
       </c>
       <c r="B440" s="11" t="s">
         <v>12</v>
@@ -40662,6 +40937,7 @@
     <row r="441" spans="1:23" s="2" customFormat="1" ht="28.5" customHeight="1">
       <c r="A441" s="11" t="str">
         <f t="shared" si="78"/>
+        <v/>
       </c>
       <c r="B441" s="11" t="s">
         <v>12</v>
@@ -40739,6 +41015,7 @@
     <row r="442" spans="1:23" s="16" customFormat="1" ht="28.5" customHeight="1">
       <c r="A442" s="11" t="str">
         <f t="shared" si="78"/>
+        <v/>
       </c>
       <c r="B442" s="11" t="s">
         <v>12</v>
@@ -40816,6 +41093,7 @@
     <row r="443" spans="1:23" s="2" customFormat="1" ht="28.5" customHeight="1">
       <c r="A443" s="11" t="str">
         <f t="shared" si="78"/>
+        <v/>
       </c>
       <c r="B443" s="11" t="s">
         <v>12</v>
@@ -40895,6 +41173,7 @@
     <row r="444" spans="1:23" s="2" customFormat="1" ht="28.5" customHeight="1">
       <c r="A444" s="11" t="str">
         <f t="shared" si="78"/>
+        <v/>
       </c>
       <c r="B444" s="11" t="s">
         <v>12</v>
@@ -40972,6 +41251,7 @@
     <row r="445" spans="1:23" s="16" customFormat="1" ht="28.5" customHeight="1">
       <c r="A445" s="11" t="str">
         <f t="shared" si="78"/>
+        <v/>
       </c>
       <c r="B445" s="11" t="s">
         <v>12</v>
@@ -41025,15 +41305,19 @@
       </c>
       <c r="R445" s="13" t="str">
         <f t="shared" si="85"/>
+        <v/>
       </c>
       <c r="S445" s="12" t="str">
         <f t="shared" si="86"/>
+        <v/>
       </c>
       <c r="T445" s="12" t="str">
         <f t="shared" si="87"/>
+        <v/>
       </c>
       <c r="U445" s="12" t="str">
         <f t="shared" si="88"/>
+        <v/>
       </c>
       <c r="V445" s="12" t="str">
         <f t="shared" si="89"/>
@@ -41047,6 +41331,7 @@
     <row r="446" spans="1:23" s="2" customFormat="1" ht="28.5" customHeight="1">
       <c r="A446" s="11" t="str">
         <f t="shared" si="78"/>
+        <v/>
       </c>
       <c r="B446" s="11" t="s">
         <v>12</v>
@@ -41124,6 +41409,7 @@
     <row r="447" spans="1:23" s="2" customFormat="1" ht="28.5" customHeight="1">
       <c r="A447" s="11" t="str">
         <f t="shared" si="78"/>
+        <v/>
       </c>
       <c r="B447" s="11" t="s">
         <v>12</v>
@@ -41201,6 +41487,7 @@
     <row r="448" spans="1:23" s="2" customFormat="1" ht="28.5" customHeight="1">
       <c r="A448" s="11" t="str">
         <f t="shared" si="78"/>
+        <v/>
       </c>
       <c r="B448" s="11" t="s">
         <v>6</v>
@@ -41280,6 +41567,7 @@
     <row r="449" spans="1:23" s="16" customFormat="1" ht="28.5" customHeight="1">
       <c r="A449" s="11" t="str">
         <f t="shared" si="78"/>
+        <v/>
       </c>
       <c r="B449" s="11" t="s">
         <v>12</v>
@@ -41357,6 +41645,7 @@
     <row r="450" spans="1:23" s="2" customFormat="1" ht="28.5" customHeight="1">
       <c r="A450" s="11" t="str">
         <f t="shared" si="78"/>
+        <v/>
       </c>
       <c r="B450" s="11" t="s">
         <v>12</v>
@@ -41434,6 +41723,7 @@
     <row r="451" spans="1:23" s="16" customFormat="1" ht="28.5" customHeight="1">
       <c r="A451" s="11" t="str">
         <f t="shared" si="78"/>
+        <v/>
       </c>
       <c r="B451" s="11" t="s">
         <v>12</v>
@@ -41511,6 +41801,7 @@
     <row r="452" spans="1:23" s="2" customFormat="1" ht="28.5" customHeight="1">
       <c r="A452" s="11" t="str">
         <f t="shared" si="78"/>
+        <v/>
       </c>
       <c r="B452" s="11" t="s">
         <v>12</v>
@@ -41590,6 +41881,7 @@
     <row r="453" spans="1:23" s="2" customFormat="1" ht="28.5" customHeight="1">
       <c r="A453" s="11" t="str">
         <f t="shared" si="78"/>
+        <v/>
       </c>
       <c r="B453" s="11" t="s">
         <v>6</v>
@@ -41667,6 +41959,7 @@
     <row r="454" spans="1:23" s="2" customFormat="1" ht="28.5" customHeight="1">
       <c r="A454" s="11" t="str">
         <f t="shared" si="78"/>
+        <v/>
       </c>
       <c r="B454" s="11" t="s">
         <v>10</v>
@@ -41744,6 +42037,7 @@
     <row r="455" spans="1:23" s="7" customFormat="1" ht="28.5" customHeight="1">
       <c r="A455" s="11" t="str">
         <f t="shared" si="78"/>
+        <v/>
       </c>
       <c r="B455" s="11" t="s">
         <v>6</v>
@@ -41823,6 +42117,7 @@
     <row r="456" spans="1:23" s="2" customFormat="1" ht="28.5" customHeight="1">
       <c r="A456" s="11" t="str">
         <f t="shared" si="78"/>
+        <v/>
       </c>
       <c r="B456" s="11" t="s">
         <v>6</v>
@@ -41900,6 +42195,7 @@
     <row r="457" spans="1:23" s="2" customFormat="1" ht="28.5" customHeight="1">
       <c r="A457" s="11" t="str">
         <f t="shared" si="78"/>
+        <v/>
       </c>
       <c r="B457" s="11" t="s">
         <v>6</v>
@@ -41977,6 +42273,7 @@
     <row r="458" spans="1:23" s="2" customFormat="1" ht="28.5" customHeight="1">
       <c r="A458" s="11" t="str">
         <f t="shared" si="78"/>
+        <v/>
       </c>
       <c r="B458" s="11" t="s">
         <v>6</v>
@@ -42054,6 +42351,7 @@
     <row r="459" spans="1:23" s="2" customFormat="1" ht="28.5" customHeight="1">
       <c r="A459" s="11" t="str">
         <f t="shared" si="78"/>
+        <v/>
       </c>
       <c r="B459" s="11" t="s">
         <v>10</v>
@@ -42131,6 +42429,7 @@
     <row r="460" spans="1:23" s="2" customFormat="1" ht="28.5" customHeight="1">
       <c r="A460" s="11" t="str">
         <f t="shared" si="78"/>
+        <v/>
       </c>
       <c r="B460" s="11" t="s">
         <v>6</v>
@@ -42208,6 +42507,7 @@
     <row r="461" spans="1:23" s="2" customFormat="1" ht="28.5" customHeight="1">
       <c r="A461" s="11" t="str">
         <f t="shared" si="78"/>
+        <v/>
       </c>
       <c r="B461" s="11" t="s">
         <v>6</v>
@@ -42285,6 +42585,7 @@
     <row r="462" spans="1:23" s="2" customFormat="1" ht="28.5" customHeight="1">
       <c r="A462" s="11" t="str">
         <f t="shared" si="78"/>
+        <v/>
       </c>
       <c r="B462" s="11" t="s">
         <v>6</v>
@@ -42362,6 +42663,7 @@
     <row r="463" spans="1:23" s="2" customFormat="1" ht="28.5" customHeight="1">
       <c r="A463" s="11" t="str">
         <f t="shared" ref="A463:A526" si="91">IF($T463="","",1+COUNTIF($W$15:$W$883,"&lt;"&amp;W463))</f>
+        <v/>
       </c>
       <c r="B463" s="11" t="s">
         <v>6</v>
@@ -42439,6 +42741,7 @@
     <row r="464" spans="1:23" s="2" customFormat="1" ht="28.5" customHeight="1">
       <c r="A464" s="11" t="str">
         <f t="shared" si="91"/>
+        <v/>
       </c>
       <c r="B464" s="11" t="s">
         <v>6</v>
@@ -42516,6 +42819,7 @@
     <row r="465" spans="1:23" s="2" customFormat="1" ht="28.5" customHeight="1">
       <c r="A465" s="11" t="str">
         <f t="shared" si="91"/>
+        <v/>
       </c>
       <c r="B465" s="11" t="s">
         <v>6</v>
@@ -42593,6 +42897,7 @@
     <row r="466" spans="1:23" s="2" customFormat="1" ht="28.5" customHeight="1">
       <c r="A466" s="11" t="str">
         <f t="shared" si="91"/>
+        <v/>
       </c>
       <c r="B466" s="11" t="s">
         <v>6</v>
@@ -42670,6 +42975,7 @@
     <row r="467" spans="1:23" s="2" customFormat="1" ht="28.5" customHeight="1">
       <c r="A467" s="11" t="str">
         <f t="shared" si="91"/>
+        <v/>
       </c>
       <c r="B467" s="11" t="s">
         <v>6</v>
@@ -42747,6 +43053,7 @@
     <row r="468" spans="1:23" s="16" customFormat="1" ht="28.5" customHeight="1">
       <c r="A468" s="11" t="str">
         <f t="shared" si="91"/>
+        <v/>
       </c>
       <c r="B468" s="11" t="s">
         <v>6</v>
@@ -42826,6 +43133,7 @@
     <row r="469" spans="1:23" s="16" customFormat="1" ht="28.5" customHeight="1">
       <c r="A469" s="11" t="str">
         <f t="shared" si="91"/>
+        <v/>
       </c>
       <c r="B469" s="11" t="s">
         <v>6</v>
@@ -42905,6 +43213,7 @@
     <row r="470" spans="1:23" s="16" customFormat="1" ht="28.5" customHeight="1">
       <c r="A470" s="11" t="str">
         <f t="shared" si="91"/>
+        <v/>
       </c>
       <c r="B470" s="11" t="s">
         <v>12</v>
@@ -42982,6 +43291,7 @@
     <row r="471" spans="1:23" s="2" customFormat="1" ht="28.5" customHeight="1">
       <c r="A471" s="11" t="str">
         <f t="shared" si="91"/>
+        <v/>
       </c>
       <c r="B471" s="11" t="s">
         <v>6</v>
@@ -43059,6 +43369,7 @@
     <row r="472" spans="1:23" s="16" customFormat="1" ht="28.5" customHeight="1">
       <c r="A472" s="11" t="str">
         <f t="shared" si="91"/>
+        <v/>
       </c>
       <c r="B472" s="11" t="s">
         <v>6</v>
@@ -43138,6 +43449,7 @@
     <row r="473" spans="1:23" s="2" customFormat="1" ht="28.5" customHeight="1">
       <c r="A473" s="11" t="str">
         <f t="shared" si="91"/>
+        <v/>
       </c>
       <c r="B473" s="11" t="s">
         <v>6</v>
@@ -43215,6 +43527,7 @@
     <row r="474" spans="1:23" s="2" customFormat="1" ht="28.5" customHeight="1">
       <c r="A474" s="11" t="str">
         <f t="shared" si="91"/>
+        <v/>
       </c>
       <c r="B474" s="11" t="s">
         <v>6</v>
@@ -43292,6 +43605,7 @@
     <row r="475" spans="1:23" s="2" customFormat="1" ht="28.5" customHeight="1">
       <c r="A475" s="11" t="str">
         <f t="shared" si="91"/>
+        <v/>
       </c>
       <c r="B475" s="11" t="s">
         <v>12</v>
@@ -43369,6 +43683,7 @@
     <row r="476" spans="1:23" s="2" customFormat="1" ht="28.5" customHeight="1">
       <c r="A476" s="11" t="str">
         <f t="shared" si="91"/>
+        <v/>
       </c>
       <c r="B476" s="11" t="s">
         <v>6</v>
@@ -43446,6 +43761,7 @@
     <row r="477" spans="1:23" s="16" customFormat="1" ht="28.5" customHeight="1">
       <c r="A477" s="11" t="str">
         <f t="shared" si="91"/>
+        <v/>
       </c>
       <c r="B477" s="11" t="s">
         <v>6</v>
@@ -43523,6 +43839,7 @@
     <row r="478" spans="1:23" s="7" customFormat="1" ht="28.5" customHeight="1">
       <c r="A478" s="11" t="str">
         <f t="shared" si="91"/>
+        <v/>
       </c>
       <c r="B478" s="11" t="s">
         <v>14</v>
@@ -43600,6 +43917,7 @@
     <row r="479" spans="1:23" s="7" customFormat="1" ht="28.5" customHeight="1">
       <c r="A479" s="11" t="str">
         <f t="shared" si="91"/>
+        <v/>
       </c>
       <c r="B479" s="11" t="s">
         <v>14</v>
@@ -43677,6 +43995,7 @@
     <row r="480" spans="1:23" s="2" customFormat="1" ht="28.5" customHeight="1">
       <c r="A480" s="11" t="str">
         <f t="shared" si="91"/>
+        <v/>
       </c>
       <c r="B480" s="11" t="s">
         <v>14</v>
@@ -43754,6 +44073,7 @@
     <row r="481" spans="1:23" s="2" customFormat="1" ht="28.5" customHeight="1">
       <c r="A481" s="11" t="str">
         <f t="shared" si="91"/>
+        <v/>
       </c>
       <c r="B481" s="11" t="s">
         <v>14</v>
@@ -43831,6 +44151,7 @@
     <row r="482" spans="1:23" s="7" customFormat="1" ht="28.5" customHeight="1">
       <c r="A482" s="11" t="str">
         <f t="shared" si="91"/>
+        <v/>
       </c>
       <c r="B482" s="11" t="s">
         <v>10</v>
@@ -43908,6 +44229,7 @@
     <row r="483" spans="1:23" s="2" customFormat="1" ht="28.5" customHeight="1">
       <c r="A483" s="11" t="str">
         <f t="shared" si="91"/>
+        <v/>
       </c>
       <c r="B483" s="11" t="s">
         <v>12</v>
@@ -43985,6 +44307,7 @@
     <row r="484" spans="1:23" s="16" customFormat="1" ht="28.5" customHeight="1">
       <c r="A484" s="11" t="str">
         <f t="shared" si="91"/>
+        <v/>
       </c>
       <c r="B484" s="11" t="s">
         <v>6</v>
@@ -44062,6 +44385,7 @@
     <row r="485" spans="1:23" s="7" customFormat="1" ht="28.5" customHeight="1">
       <c r="A485" s="11" t="str">
         <f t="shared" si="91"/>
+        <v/>
       </c>
       <c r="B485" s="11" t="s">
         <v>10</v>
@@ -44139,6 +44463,7 @@
     <row r="486" spans="1:23" s="2" customFormat="1" ht="28.5" customHeight="1">
       <c r="A486" s="11" t="str">
         <f t="shared" si="91"/>
+        <v/>
       </c>
       <c r="B486" s="11" t="s">
         <v>6</v>
@@ -44216,6 +44541,7 @@
     <row r="487" spans="1:23" s="2" customFormat="1" ht="28.5" customHeight="1">
       <c r="A487" s="11" t="str">
         <f t="shared" si="91"/>
+        <v/>
       </c>
       <c r="B487" s="11" t="s">
         <v>6</v>
@@ -44293,6 +44619,7 @@
     <row r="488" spans="1:23" s="2" customFormat="1" ht="28.5" customHeight="1">
       <c r="A488" s="11" t="str">
         <f t="shared" si="91"/>
+        <v/>
       </c>
       <c r="B488" s="11" t="s">
         <v>12</v>
@@ -44370,6 +44697,7 @@
     <row r="489" spans="1:23" s="2" customFormat="1" ht="28.5" customHeight="1">
       <c r="A489" s="11" t="str">
         <f t="shared" si="91"/>
+        <v/>
       </c>
       <c r="B489" s="11" t="s">
         <v>6</v>
@@ -44447,6 +44775,7 @@
     <row r="490" spans="1:23" s="16" customFormat="1" ht="28.5" customHeight="1">
       <c r="A490" s="11" t="str">
         <f t="shared" si="91"/>
+        <v/>
       </c>
       <c r="B490" s="11" t="s">
         <v>6</v>
@@ -44524,6 +44853,7 @@
     <row r="491" spans="1:23" s="16" customFormat="1" ht="28.5" customHeight="1">
       <c r="A491" s="11" t="str">
         <f t="shared" si="91"/>
+        <v/>
       </c>
       <c r="B491" s="11" t="s">
         <v>6</v>
@@ -44601,6 +44931,7 @@
     <row r="492" spans="1:23" s="16" customFormat="1" ht="28.5" customHeight="1">
       <c r="A492" s="11" t="str">
         <f t="shared" si="91"/>
+        <v/>
       </c>
       <c r="B492" s="11" t="s">
         <v>12</v>
@@ -44678,6 +45009,7 @@
     <row r="493" spans="1:23" s="2" customFormat="1" ht="28.5" customHeight="1">
       <c r="A493" s="11" t="str">
         <f t="shared" si="91"/>
+        <v/>
       </c>
       <c r="B493" s="11" t="s">
         <v>12</v>
@@ -44755,6 +45087,7 @@
     <row r="494" spans="1:23" s="16" customFormat="1" ht="28.5" customHeight="1">
       <c r="A494" s="11" t="str">
         <f t="shared" si="91"/>
+        <v/>
       </c>
       <c r="B494" s="11" t="s">
         <v>8</v>
@@ -44832,6 +45165,7 @@
     <row r="495" spans="1:23" s="2" customFormat="1" ht="28.5" customHeight="1">
       <c r="A495" s="11" t="str">
         <f t="shared" si="91"/>
+        <v/>
       </c>
       <c r="B495" s="11" t="s">
         <v>12</v>
@@ -44909,6 +45243,7 @@
     <row r="496" spans="1:23" s="2" customFormat="1" ht="28.5" customHeight="1">
       <c r="A496" s="11" t="str">
         <f t="shared" si="91"/>
+        <v/>
       </c>
       <c r="B496" s="11" t="s">
         <v>6</v>
@@ -44986,6 +45321,7 @@
     <row r="497" spans="1:23" s="2" customFormat="1" ht="28.5" customHeight="1">
       <c r="A497" s="11" t="str">
         <f t="shared" si="91"/>
+        <v/>
       </c>
       <c r="B497" s="11" t="s">
         <v>12</v>
@@ -45063,6 +45399,7 @@
     <row r="498" spans="1:23" s="2" customFormat="1" ht="28.5" customHeight="1">
       <c r="A498" s="11" t="str">
         <f t="shared" si="91"/>
+        <v/>
       </c>
       <c r="B498" s="11" t="s">
         <v>6</v>
@@ -45140,6 +45477,7 @@
     <row r="499" spans="1:23" s="2" customFormat="1" ht="28.5" customHeight="1">
       <c r="A499" s="11" t="str">
         <f t="shared" si="91"/>
+        <v/>
       </c>
       <c r="B499" s="11" t="s">
         <v>6</v>
@@ -45217,6 +45555,7 @@
     <row r="500" spans="1:23" s="2" customFormat="1" ht="28.5" customHeight="1">
       <c r="A500" s="11" t="str">
         <f t="shared" si="91"/>
+        <v/>
       </c>
       <c r="B500" s="11" t="s">
         <v>12</v>
@@ -45294,6 +45633,7 @@
     <row r="501" spans="1:23" s="2" customFormat="1" ht="28.5" customHeight="1">
       <c r="A501" s="11" t="str">
         <f t="shared" si="91"/>
+        <v/>
       </c>
       <c r="B501" s="11" t="s">
         <v>12</v>
@@ -45371,6 +45711,7 @@
     <row r="502" spans="1:23" s="7" customFormat="1" ht="28.5" customHeight="1">
       <c r="A502" s="11" t="str">
         <f t="shared" si="91"/>
+        <v/>
       </c>
       <c r="B502" s="11" t="s">
         <v>10</v>
@@ -45448,6 +45789,7 @@
     <row r="503" spans="1:23" s="2" customFormat="1" ht="28.5" customHeight="1">
       <c r="A503" s="11" t="str">
         <f t="shared" si="91"/>
+        <v/>
       </c>
       <c r="B503" s="11" t="s">
         <v>6</v>
@@ -45525,6 +45867,7 @@
     <row r="504" spans="1:23" s="2" customFormat="1" ht="28.5" customHeight="1">
       <c r="A504" s="11" t="str">
         <f t="shared" si="91"/>
+        <v/>
       </c>
       <c r="B504" s="11" t="s">
         <v>6</v>
@@ -45602,6 +45945,7 @@
     <row r="505" spans="1:23" s="2" customFormat="1" ht="28.5" customHeight="1">
       <c r="A505" s="11" t="str">
         <f t="shared" si="91"/>
+        <v/>
       </c>
       <c r="B505" s="11" t="s">
         <v>14</v>
@@ -45679,6 +46023,7 @@
     <row r="506" spans="1:23" s="2" customFormat="1" ht="28.5" customHeight="1">
       <c r="A506" s="11" t="str">
         <f t="shared" si="91"/>
+        <v/>
       </c>
       <c r="B506" s="11" t="s">
         <v>14</v>
@@ -45756,6 +46101,7 @@
     <row r="507" spans="1:23" s="2" customFormat="1" ht="28.5" customHeight="1">
       <c r="A507" s="11" t="str">
         <f t="shared" si="91"/>
+        <v/>
       </c>
       <c r="B507" s="11" t="s">
         <v>10</v>
@@ -45809,15 +46155,19 @@
       </c>
       <c r="R507" s="13" t="str">
         <f t="shared" si="98"/>
+        <v/>
       </c>
       <c r="S507" s="12" t="str">
         <f t="shared" si="99"/>
+        <v/>
       </c>
       <c r="T507" s="12" t="str">
         <f t="shared" si="100"/>
+        <v/>
       </c>
       <c r="U507" s="12" t="str">
         <f t="shared" si="101"/>
+        <v/>
       </c>
       <c r="V507" s="12" t="str">
         <f t="shared" si="102"/>
@@ -45831,6 +46181,7 @@
     <row r="508" spans="1:23" s="7" customFormat="1" ht="28.5" customHeight="1">
       <c r="A508" s="11" t="str">
         <f t="shared" si="91"/>
+        <v/>
       </c>
       <c r="B508" s="11" t="s">
         <v>6</v>
@@ -45908,6 +46259,7 @@
     <row r="509" spans="1:23" s="2" customFormat="1" ht="28.5" customHeight="1">
       <c r="A509" s="11" t="str">
         <f t="shared" si="91"/>
+        <v/>
       </c>
       <c r="B509" s="11" t="s">
         <v>6</v>
@@ -45985,6 +46337,7 @@
     <row r="510" spans="1:23" s="2" customFormat="1" ht="28.5" customHeight="1">
       <c r="A510" s="11" t="str">
         <f t="shared" si="91"/>
+        <v/>
       </c>
       <c r="B510" s="11" t="s">
         <v>12</v>
@@ -46062,6 +46415,7 @@
     <row r="511" spans="1:23" s="2" customFormat="1" ht="28.5" customHeight="1">
       <c r="A511" s="11" t="str">
         <f t="shared" si="91"/>
+        <v/>
       </c>
       <c r="B511" s="11" t="s">
         <v>12</v>
@@ -46139,6 +46493,7 @@
     <row r="512" spans="1:23" s="2" customFormat="1" ht="28.5" customHeight="1">
       <c r="A512" s="11" t="str">
         <f t="shared" si="91"/>
+        <v/>
       </c>
       <c r="B512" s="11" t="s">
         <v>6</v>
@@ -46216,6 +46571,7 @@
     <row r="513" spans="1:23" s="7" customFormat="1" ht="28.5" customHeight="1">
       <c r="A513" s="11" t="str">
         <f t="shared" si="91"/>
+        <v/>
       </c>
       <c r="B513" s="11" t="s">
         <v>6</v>
@@ -46293,6 +46649,7 @@
     <row r="514" spans="1:23" s="2" customFormat="1" ht="28.5" customHeight="1">
       <c r="A514" s="11" t="str">
         <f t="shared" si="91"/>
+        <v/>
       </c>
       <c r="B514" s="11" t="s">
         <v>12</v>
@@ -46370,6 +46727,7 @@
     <row r="515" spans="1:23" s="2" customFormat="1" ht="28.5" customHeight="1">
       <c r="A515" s="11" t="str">
         <f t="shared" si="91"/>
+        <v/>
       </c>
       <c r="B515" s="11" t="s">
         <v>12</v>
@@ -46447,6 +46805,7 @@
     <row r="516" spans="1:23" s="2" customFormat="1" ht="28.5" customHeight="1">
       <c r="A516" s="11" t="str">
         <f t="shared" si="91"/>
+        <v/>
       </c>
       <c r="B516" s="11" t="s">
         <v>12</v>
@@ -46524,6 +46883,7 @@
     <row r="517" spans="1:23" s="2" customFormat="1" ht="28.5" customHeight="1">
       <c r="A517" s="11" t="str">
         <f t="shared" si="91"/>
+        <v/>
       </c>
       <c r="B517" s="11" t="s">
         <v>6</v>
@@ -46601,6 +46961,7 @@
     <row r="518" spans="1:23" s="7" customFormat="1" ht="28.5" customHeight="1">
       <c r="A518" s="11" t="str">
         <f t="shared" si="91"/>
+        <v/>
       </c>
       <c r="B518" s="11" t="s">
         <v>12</v>
@@ -46678,6 +47039,7 @@
     <row r="519" spans="1:23" s="2" customFormat="1" ht="28.5" customHeight="1">
       <c r="A519" s="11" t="str">
         <f t="shared" si="91"/>
+        <v/>
       </c>
       <c r="B519" s="11" t="s">
         <v>14</v>
@@ -46755,6 +47117,7 @@
     <row r="520" spans="1:23" s="16" customFormat="1" ht="28.5" customHeight="1">
       <c r="A520" s="11" t="str">
         <f t="shared" si="91"/>
+        <v/>
       </c>
       <c r="B520" s="11" t="s">
         <v>14</v>
@@ -46832,6 +47195,7 @@
     <row r="521" spans="1:23" s="2" customFormat="1" ht="28.5" customHeight="1">
       <c r="A521" s="11" t="str">
         <f t="shared" si="91"/>
+        <v/>
       </c>
       <c r="B521" s="11" t="s">
         <v>14</v>
@@ -46909,6 +47273,7 @@
     <row r="522" spans="1:23" s="16" customFormat="1" ht="28.5" customHeight="1">
       <c r="A522" s="11" t="str">
         <f t="shared" si="91"/>
+        <v/>
       </c>
       <c r="B522" s="11" t="s">
         <v>14</v>
@@ -46986,6 +47351,7 @@
     <row r="523" spans="1:23" s="2" customFormat="1" ht="28.5" customHeight="1">
       <c r="A523" s="11" t="str">
         <f t="shared" si="91"/>
+        <v/>
       </c>
       <c r="B523" s="11" t="s">
         <v>12</v>
@@ -47063,6 +47429,7 @@
     <row r="524" spans="1:23" s="16" customFormat="1" ht="28.5" customHeight="1">
       <c r="A524" s="11" t="str">
         <f t="shared" si="91"/>
+        <v/>
       </c>
       <c r="B524" s="11" t="s">
         <v>6</v>
@@ -47140,6 +47507,7 @@
     <row r="525" spans="1:23" s="2" customFormat="1" ht="28.5" customHeight="1">
       <c r="A525" s="11" t="str">
         <f t="shared" si="91"/>
+        <v/>
       </c>
       <c r="B525" s="11" t="s">
         <v>6</v>
@@ -47217,6 +47585,7 @@
     <row r="526" spans="1:23" s="2" customFormat="1" ht="28.5" customHeight="1">
       <c r="A526" s="11" t="str">
         <f t="shared" si="91"/>
+        <v/>
       </c>
       <c r="B526" s="11" t="s">
         <v>14</v>
@@ -47294,6 +47663,7 @@
     <row r="527" spans="1:23" s="2" customFormat="1" ht="28.5" customHeight="1">
       <c r="A527" s="11" t="str">
         <f t="shared" ref="A527:A590" si="104">IF($T527="","",1+COUNTIF($W$15:$W$883,"&lt;"&amp;W527))</f>
+        <v/>
       </c>
       <c r="B527" s="11" t="s">
         <v>6</v>
@@ -47371,6 +47741,7 @@
     <row r="528" spans="1:23" s="2" customFormat="1" ht="28.5" customHeight="1">
       <c r="A528" s="11" t="str">
         <f t="shared" si="104"/>
+        <v/>
       </c>
       <c r="B528" s="11" t="s">
         <v>6</v>
@@ -47448,6 +47819,7 @@
     <row r="529" spans="1:23" s="2" customFormat="1" ht="28.5" customHeight="1">
       <c r="A529" s="11" t="str">
         <f t="shared" si="104"/>
+        <v/>
       </c>
       <c r="B529" s="11" t="s">
         <v>18</v>
@@ -47525,6 +47897,7 @@
     <row r="530" spans="1:23" s="16" customFormat="1" ht="28.5" customHeight="1">
       <c r="A530" s="11" t="str">
         <f t="shared" si="104"/>
+        <v/>
       </c>
       <c r="B530" s="11" t="s">
         <v>18</v>
@@ -47602,6 +47975,7 @@
     <row r="531" spans="1:23" s="2" customFormat="1" ht="28.5" customHeight="1">
       <c r="A531" s="11" t="str">
         <f t="shared" si="104"/>
+        <v/>
       </c>
       <c r="B531" s="11" t="s">
         <v>18</v>
@@ -47679,6 +48053,7 @@
     <row r="532" spans="1:23" s="16" customFormat="1" ht="28.5" customHeight="1">
       <c r="A532" s="11" t="str">
         <f t="shared" si="104"/>
+        <v/>
       </c>
       <c r="B532" s="11" t="s">
         <v>18</v>
@@ -47756,6 +48131,7 @@
     <row r="533" spans="1:23" s="2" customFormat="1" ht="28.5" customHeight="1">
       <c r="A533" s="11" t="str">
         <f t="shared" si="104"/>
+        <v/>
       </c>
       <c r="B533" s="11" t="s">
         <v>6</v>
@@ -47833,6 +48209,7 @@
     <row r="534" spans="1:23" s="2" customFormat="1" ht="28.5" customHeight="1">
       <c r="A534" s="11" t="str">
         <f t="shared" si="104"/>
+        <v/>
       </c>
       <c r="B534" s="11" t="s">
         <v>6</v>
@@ -47910,6 +48287,7 @@
     <row r="535" spans="1:23" s="16" customFormat="1" ht="28.5" customHeight="1">
       <c r="A535" s="11" t="str">
         <f t="shared" si="104"/>
+        <v/>
       </c>
       <c r="B535" s="11" t="s">
         <v>12</v>
@@ -47987,6 +48365,7 @@
     <row r="536" spans="1:23" s="2" customFormat="1" ht="28.5" customHeight="1">
       <c r="A536" s="11" t="str">
         <f t="shared" si="104"/>
+        <v/>
       </c>
       <c r="B536" s="11" t="s">
         <v>10</v>
@@ -48064,6 +48443,7 @@
     <row r="537" spans="1:23" s="16" customFormat="1" ht="28.5" customHeight="1">
       <c r="A537" s="11" t="str">
         <f t="shared" si="104"/>
+        <v/>
       </c>
       <c r="B537" s="11" t="s">
         <v>6</v>
@@ -48141,6 +48521,7 @@
     <row r="538" spans="1:23" s="2" customFormat="1" ht="28.5" customHeight="1">
       <c r="A538" s="11" t="str">
         <f t="shared" si="104"/>
+        <v/>
       </c>
       <c r="B538" s="11" t="s">
         <v>10</v>
@@ -48218,6 +48599,7 @@
     <row r="539" spans="1:23" s="2" customFormat="1" ht="28.5" customHeight="1">
       <c r="A539" s="11" t="str">
         <f t="shared" si="104"/>
+        <v/>
       </c>
       <c r="B539" s="11" t="s">
         <v>10</v>
@@ -48295,6 +48677,7 @@
     <row r="540" spans="1:23" s="2" customFormat="1" ht="28.5" customHeight="1">
       <c r="A540" s="11" t="str">
         <f t="shared" si="104"/>
+        <v/>
       </c>
       <c r="B540" s="11" t="s">
         <v>10</v>
@@ -48372,6 +48755,7 @@
     <row r="541" spans="1:23" s="2" customFormat="1" ht="28.5" customHeight="1">
       <c r="A541" s="11" t="str">
         <f t="shared" si="104"/>
+        <v/>
       </c>
       <c r="B541" s="11" t="s">
         <v>10</v>
@@ -48449,6 +48833,7 @@
     <row r="542" spans="1:23" s="2" customFormat="1" ht="28.5" customHeight="1">
       <c r="A542" s="11" t="str">
         <f t="shared" si="104"/>
+        <v/>
       </c>
       <c r="B542" s="11" t="s">
         <v>14</v>
@@ -48526,6 +48911,7 @@
     <row r="543" spans="1:23" s="2" customFormat="1" ht="28.5" customHeight="1">
       <c r="A543" s="11" t="str">
         <f t="shared" si="104"/>
+        <v/>
       </c>
       <c r="B543" s="11" t="s">
         <v>18</v>
@@ -48603,6 +48989,7 @@
     <row r="544" spans="1:23" s="7" customFormat="1" ht="28.5" customHeight="1">
       <c r="A544" s="11" t="str">
         <f t="shared" si="104"/>
+        <v/>
       </c>
       <c r="B544" s="11" t="s">
         <v>6</v>
@@ -48680,6 +49067,7 @@
     <row r="545" spans="1:23" s="2" customFormat="1" ht="28.5" customHeight="1">
       <c r="A545" s="11" t="str">
         <f t="shared" si="104"/>
+        <v/>
       </c>
       <c r="B545" s="11" t="s">
         <v>6</v>
@@ -48757,6 +49145,7 @@
     <row r="546" spans="1:23" s="2" customFormat="1" ht="28.5" customHeight="1">
       <c r="A546" s="11" t="str">
         <f t="shared" si="104"/>
+        <v/>
       </c>
       <c r="B546" s="11" t="s">
         <v>8</v>
@@ -48834,6 +49223,7 @@
     <row r="547" spans="1:23" s="2" customFormat="1" ht="28.5" customHeight="1">
       <c r="A547" s="11" t="str">
         <f t="shared" si="104"/>
+        <v/>
       </c>
       <c r="B547" s="11" t="s">
         <v>6</v>
@@ -48911,6 +49301,7 @@
     <row r="548" spans="1:23" s="7" customFormat="1" ht="28.5" customHeight="1">
       <c r="A548" s="11" t="str">
         <f t="shared" si="104"/>
+        <v/>
       </c>
       <c r="B548" s="11" t="s">
         <v>6</v>
@@ -48988,6 +49379,7 @@
     <row r="549" spans="1:23" s="16" customFormat="1" ht="28.5" customHeight="1">
       <c r="A549" s="11" t="str">
         <f t="shared" si="104"/>
+        <v/>
       </c>
       <c r="B549" s="11" t="s">
         <v>10</v>
@@ -49065,6 +49457,7 @@
     <row r="550" spans="1:23" s="2" customFormat="1" ht="28.5" customHeight="1">
       <c r="A550" s="11" t="str">
         <f t="shared" si="104"/>
+        <v/>
       </c>
       <c r="B550" s="11" t="s">
         <v>18</v>
@@ -49142,6 +49535,7 @@
     <row r="551" spans="1:23" s="2" customFormat="1" ht="28.5" customHeight="1">
       <c r="A551" s="11" t="str">
         <f t="shared" si="104"/>
+        <v/>
       </c>
       <c r="B551" s="11" t="s">
         <v>18</v>
@@ -49219,6 +49613,7 @@
     <row r="552" spans="1:23" s="2" customFormat="1" ht="28.5" customHeight="1">
       <c r="A552" s="11" t="str">
         <f t="shared" si="104"/>
+        <v/>
       </c>
       <c r="B552" s="11" t="s">
         <v>18</v>
@@ -49296,6 +49691,7 @@
     <row r="553" spans="1:23" s="2" customFormat="1" ht="28.5" customHeight="1">
       <c r="A553" s="11" t="str">
         <f t="shared" si="104"/>
+        <v/>
       </c>
       <c r="B553" s="11" t="s">
         <v>18</v>
@@ -49373,6 +49769,7 @@
     <row r="554" spans="1:23" s="2" customFormat="1" ht="28.5" customHeight="1">
       <c r="A554" s="11" t="str">
         <f t="shared" si="104"/>
+        <v/>
       </c>
       <c r="B554" s="11" t="s">
         <v>18</v>
@@ -49450,6 +49847,7 @@
     <row r="555" spans="1:23" s="7" customFormat="1" ht="28.5" customHeight="1">
       <c r="A555" s="11" t="str">
         <f t="shared" si="104"/>
+        <v/>
       </c>
       <c r="B555" s="11" t="s">
         <v>10</v>
@@ -49527,6 +49925,7 @@
     <row r="556" spans="1:23" s="16" customFormat="1" ht="28.5" customHeight="1">
       <c r="A556" s="11" t="str">
         <f t="shared" si="104"/>
+        <v/>
       </c>
       <c r="B556" s="11" t="s">
         <v>6</v>
@@ -49604,6 +50003,7 @@
     <row r="557" spans="1:23" s="16" customFormat="1" ht="28.5" customHeight="1">
       <c r="A557" s="11" t="str">
         <f t="shared" si="104"/>
+        <v/>
       </c>
       <c r="B557" s="11" t="s">
         <v>14</v>
@@ -49681,6 +50081,7 @@
     <row r="558" spans="1:23" s="7" customFormat="1" ht="28.5" customHeight="1">
       <c r="A558" s="11" t="str">
         <f t="shared" si="104"/>
+        <v/>
       </c>
       <c r="B558" s="11" t="s">
         <v>14</v>
@@ -49758,6 +50159,7 @@
     <row r="559" spans="1:23" s="2" customFormat="1" ht="28.5" customHeight="1">
       <c r="A559" s="11" t="str">
         <f t="shared" si="104"/>
+        <v/>
       </c>
       <c r="B559" s="11" t="s">
         <v>10</v>
@@ -49835,6 +50237,7 @@
     <row r="560" spans="1:23" s="2" customFormat="1" ht="28.5" customHeight="1">
       <c r="A560" s="11" t="str">
         <f t="shared" si="104"/>
+        <v/>
       </c>
       <c r="B560" s="11" t="s">
         <v>8</v>
@@ -49914,6 +50317,7 @@
     <row r="561" spans="1:23" s="2" customFormat="1" ht="28.5" customHeight="1">
       <c r="A561" s="11" t="str">
         <f t="shared" si="104"/>
+        <v/>
       </c>
       <c r="B561" s="11" t="s">
         <v>10</v>
@@ -49991,6 +50395,7 @@
     <row r="562" spans="1:23" s="2" customFormat="1" ht="28.5" customHeight="1">
       <c r="A562" s="11" t="str">
         <f t="shared" si="104"/>
+        <v/>
       </c>
       <c r="B562" s="11" t="s">
         <v>10</v>
@@ -50044,15 +50449,19 @@
       </c>
       <c r="R562" s="13" t="str">
         <f t="shared" si="111"/>
+        <v/>
       </c>
       <c r="S562" s="12" t="str">
         <f t="shared" si="112"/>
+        <v/>
       </c>
       <c r="T562" s="12" t="str">
         <f t="shared" si="113"/>
+        <v/>
       </c>
       <c r="U562" s="12" t="str">
         <f t="shared" si="114"/>
+        <v/>
       </c>
       <c r="V562" s="12" t="str">
         <f t="shared" si="115"/>
@@ -50066,6 +50475,7 @@
     <row r="563" spans="1:23" s="2" customFormat="1" ht="28.5" customHeight="1">
       <c r="A563" s="11" t="str">
         <f t="shared" si="104"/>
+        <v/>
       </c>
       <c r="B563" s="11" t="s">
         <v>10</v>
@@ -50143,6 +50553,7 @@
     <row r="564" spans="1:23" s="16" customFormat="1" ht="28.5" customHeight="1">
       <c r="A564" s="11" t="str">
         <f t="shared" si="104"/>
+        <v/>
       </c>
       <c r="B564" s="11" t="s">
         <v>10</v>
@@ -50220,6 +50631,7 @@
     <row r="565" spans="1:23" s="2" customFormat="1" ht="28.5" customHeight="1">
       <c r="A565" s="11" t="str">
         <f t="shared" si="104"/>
+        <v/>
       </c>
       <c r="B565" s="11" t="s">
         <v>10</v>
@@ -50273,15 +50685,19 @@
       </c>
       <c r="R565" s="13" t="str">
         <f t="shared" si="111"/>
+        <v/>
       </c>
       <c r="S565" s="12" t="str">
         <f t="shared" si="112"/>
+        <v/>
       </c>
       <c r="T565" s="12" t="str">
         <f t="shared" si="113"/>
+        <v/>
       </c>
       <c r="U565" s="12" t="str">
         <f t="shared" si="114"/>
+        <v/>
       </c>
       <c r="V565" s="12" t="str">
         <f t="shared" si="115"/>
@@ -50295,6 +50711,7 @@
     <row r="566" spans="1:23" s="16" customFormat="1" ht="28.5" customHeight="1">
       <c r="A566" s="11" t="str">
         <f t="shared" si="104"/>
+        <v/>
       </c>
       <c r="B566" s="11" t="s">
         <v>18</v>
@@ -50372,6 +50789,7 @@
     <row r="567" spans="1:23" s="2" customFormat="1" ht="28.5" customHeight="1">
       <c r="A567" s="11" t="str">
         <f t="shared" si="104"/>
+        <v/>
       </c>
       <c r="B567" s="11" t="s">
         <v>6</v>
@@ -50449,6 +50867,7 @@
     <row r="568" spans="1:23" s="2" customFormat="1" ht="28.5" customHeight="1">
       <c r="A568" s="11" t="str">
         <f t="shared" si="104"/>
+        <v/>
       </c>
       <c r="B568" s="11" t="s">
         <v>6</v>
@@ -50526,6 +50945,7 @@
     <row r="569" spans="1:23" s="16" customFormat="1" ht="28.5" customHeight="1">
       <c r="A569" s="11" t="str">
         <f t="shared" si="104"/>
+        <v/>
       </c>
       <c r="B569" s="11" t="s">
         <v>6</v>
@@ -50603,6 +51023,7 @@
     <row r="570" spans="1:23" s="2" customFormat="1" ht="28.5" customHeight="1">
       <c r="A570" s="11" t="str">
         <f t="shared" si="104"/>
+        <v/>
       </c>
       <c r="B570" s="11" t="s">
         <v>6</v>
@@ -50680,6 +51101,7 @@
     <row r="571" spans="1:23" s="7" customFormat="1" ht="28.5" customHeight="1">
       <c r="A571" s="11" t="str">
         <f t="shared" si="104"/>
+        <v/>
       </c>
       <c r="B571" s="11" t="s">
         <v>6</v>
@@ -50757,6 +51179,7 @@
     <row r="572" spans="1:23" s="2" customFormat="1" ht="28.5" customHeight="1">
       <c r="A572" s="11" t="str">
         <f t="shared" si="104"/>
+        <v/>
       </c>
       <c r="B572" s="11" t="s">
         <v>6</v>
@@ -50834,6 +51257,7 @@
     <row r="573" spans="1:23" s="7" customFormat="1" ht="28.5" customHeight="1">
       <c r="A573" s="11" t="str">
         <f t="shared" si="104"/>
+        <v/>
       </c>
       <c r="B573" s="11" t="s">
         <v>6</v>
@@ -50913,6 +51337,7 @@
     <row r="574" spans="1:23" s="7" customFormat="1" ht="28.5" customHeight="1">
       <c r="A574" s="11" t="str">
         <f t="shared" si="104"/>
+        <v/>
       </c>
       <c r="B574" s="11" t="s">
         <v>6</v>
@@ -50990,6 +51415,7 @@
     <row r="575" spans="1:23" s="2" customFormat="1" ht="28.5" customHeight="1">
       <c r="A575" s="11" t="str">
         <f t="shared" si="104"/>
+        <v/>
       </c>
       <c r="B575" s="11" t="s">
         <v>6</v>
@@ -51067,6 +51493,7 @@
     <row r="576" spans="1:23" s="2" customFormat="1" ht="28.5" customHeight="1">
       <c r="A576" s="11" t="str">
         <f t="shared" si="104"/>
+        <v/>
       </c>
       <c r="B576" s="11" t="s">
         <v>12</v>
@@ -51144,6 +51571,7 @@
     <row r="577" spans="1:23" s="2" customFormat="1" ht="28.5" customHeight="1">
       <c r="A577" s="11" t="str">
         <f t="shared" si="104"/>
+        <v/>
       </c>
       <c r="B577" s="11" t="s">
         <v>10</v>
@@ -51221,6 +51649,7 @@
     <row r="578" spans="1:23" s="2" customFormat="1" ht="28.5" customHeight="1">
       <c r="A578" s="11" t="str">
         <f t="shared" si="104"/>
+        <v/>
       </c>
       <c r="B578" s="11" t="s">
         <v>10</v>
@@ -51298,6 +51727,7 @@
     <row r="579" spans="1:23" s="2" customFormat="1" ht="28.5" customHeight="1">
       <c r="A579" s="11" t="str">
         <f t="shared" si="104"/>
+        <v/>
       </c>
       <c r="B579" s="11" t="s">
         <v>10</v>
@@ -51375,6 +51805,7 @@
     <row r="580" spans="1:23" s="2" customFormat="1" ht="28.5" customHeight="1">
       <c r="A580" s="11" t="str">
         <f t="shared" si="104"/>
+        <v/>
       </c>
       <c r="B580" s="11" t="s">
         <v>6</v>
@@ -51452,6 +51883,7 @@
     <row r="581" spans="1:23" s="2" customFormat="1" ht="28.5" customHeight="1">
       <c r="A581" s="11" t="str">
         <f t="shared" si="104"/>
+        <v/>
       </c>
       <c r="B581" s="11" t="s">
         <v>14</v>
@@ -51529,6 +51961,7 @@
     <row r="582" spans="1:23" s="7" customFormat="1" ht="28.5" customHeight="1">
       <c r="A582" s="11" t="str">
         <f t="shared" si="104"/>
+        <v/>
       </c>
       <c r="B582" s="11" t="s">
         <v>18</v>
@@ -51606,6 +52039,7 @@
     <row r="583" spans="1:23" s="2" customFormat="1" ht="28.5" customHeight="1">
       <c r="A583" s="11" t="str">
         <f t="shared" si="104"/>
+        <v/>
       </c>
       <c r="B583" s="11" t="s">
         <v>12</v>
@@ -51683,6 +52117,7 @@
     <row r="584" spans="1:23" s="2" customFormat="1" ht="28.5" customHeight="1">
       <c r="A584" s="11" t="str">
         <f t="shared" si="104"/>
+        <v/>
       </c>
       <c r="B584" s="11" t="s">
         <v>8</v>
@@ -51760,6 +52195,7 @@
     <row r="585" spans="1:23" s="16" customFormat="1" ht="28.5" customHeight="1">
       <c r="A585" s="11" t="str">
         <f t="shared" si="104"/>
+        <v/>
       </c>
       <c r="B585" s="11" t="s">
         <v>10</v>
@@ -51813,15 +52249,19 @@
       </c>
       <c r="R585" s="13" t="str">
         <f t="shared" si="111"/>
+        <v/>
       </c>
       <c r="S585" s="12" t="str">
         <f t="shared" si="112"/>
+        <v/>
       </c>
       <c r="T585" s="12" t="str">
         <f t="shared" si="113"/>
+        <v/>
       </c>
       <c r="U585" s="12" t="str">
         <f t="shared" si="114"/>
+        <v/>
       </c>
       <c r="V585" s="12" t="str">
         <f t="shared" si="115"/>
@@ -51835,6 +52275,7 @@
     <row r="586" spans="1:23" s="2" customFormat="1" ht="28.5" customHeight="1">
       <c r="A586" s="11" t="str">
         <f t="shared" si="104"/>
+        <v/>
       </c>
       <c r="B586" s="11" t="s">
         <v>6</v>
@@ -51912,6 +52353,7 @@
     <row r="587" spans="1:23" s="2" customFormat="1" ht="28.5" customHeight="1">
       <c r="A587" s="11" t="str">
         <f t="shared" si="104"/>
+        <v/>
       </c>
       <c r="B587" s="11" t="s">
         <v>6</v>
@@ -51989,6 +52431,7 @@
     <row r="588" spans="1:23" s="7" customFormat="1" ht="28.5" customHeight="1">
       <c r="A588" s="11" t="str">
         <f t="shared" si="104"/>
+        <v/>
       </c>
       <c r="B588" s="11" t="s">
         <v>6</v>
@@ -52066,6 +52509,7 @@
     <row r="589" spans="1:23" s="2" customFormat="1" ht="28.5" customHeight="1">
       <c r="A589" s="11" t="str">
         <f t="shared" si="104"/>
+        <v/>
       </c>
       <c r="B589" s="11" t="s">
         <v>6</v>
@@ -52143,6 +52587,7 @@
     <row r="590" spans="1:23" s="2" customFormat="1" ht="28.5" customHeight="1">
       <c r="A590" s="11" t="str">
         <f t="shared" si="104"/>
+        <v/>
       </c>
       <c r="B590" s="11" t="s">
         <v>10</v>
@@ -52220,6 +52665,7 @@
     <row r="591" spans="1:23" s="2" customFormat="1" ht="28.5" customHeight="1">
       <c r="A591" s="11" t="str">
         <f t="shared" ref="A591:A654" si="117">IF($T591="","",1+COUNTIF($W$15:$W$883,"&lt;"&amp;W591))</f>
+        <v/>
       </c>
       <c r="B591" s="11" t="s">
         <v>10</v>
@@ -52297,6 +52743,7 @@
     <row r="592" spans="1:23" s="2" customFormat="1" ht="28.5" customHeight="1">
       <c r="A592" s="11" t="str">
         <f t="shared" si="117"/>
+        <v/>
       </c>
       <c r="B592" s="11" t="s">
         <v>10</v>
@@ -52374,6 +52821,7 @@
     <row r="593" spans="1:23" s="2" customFormat="1" ht="28.5" customHeight="1">
       <c r="A593" s="11" t="str">
         <f t="shared" si="117"/>
+        <v/>
       </c>
       <c r="B593" s="11" t="s">
         <v>10</v>
@@ -52451,6 +52899,7 @@
     <row r="594" spans="1:23" s="2" customFormat="1" ht="28.5" customHeight="1">
       <c r="A594" s="11" t="str">
         <f t="shared" si="117"/>
+        <v/>
       </c>
       <c r="B594" s="11" t="s">
         <v>10</v>
@@ -52528,6 +52977,7 @@
     <row r="595" spans="1:23" s="2" customFormat="1" ht="28.5" customHeight="1">
       <c r="A595" s="11" t="str">
         <f t="shared" si="117"/>
+        <v/>
       </c>
       <c r="B595" s="11" t="s">
         <v>10</v>
@@ -52605,6 +53055,7 @@
     <row r="596" spans="1:23" s="2" customFormat="1" ht="28.5" customHeight="1">
       <c r="A596" s="11" t="str">
         <f t="shared" si="117"/>
+        <v/>
       </c>
       <c r="B596" s="11" t="s">
         <v>10</v>
@@ -52682,6 +53133,7 @@
     <row r="597" spans="1:23" s="2" customFormat="1" ht="28.5" customHeight="1">
       <c r="A597" s="11" t="str">
         <f t="shared" si="117"/>
+        <v/>
       </c>
       <c r="B597" s="11" t="s">
         <v>10</v>
@@ -52759,6 +53211,7 @@
     <row r="598" spans="1:23" s="2" customFormat="1" ht="28.5" customHeight="1">
       <c r="A598" s="11" t="str">
         <f t="shared" si="117"/>
+        <v/>
       </c>
       <c r="B598" s="11" t="s">
         <v>10</v>
@@ -52836,6 +53289,7 @@
     <row r="599" spans="1:23" s="2" customFormat="1" ht="28.5" customHeight="1">
       <c r="A599" s="11" t="str">
         <f t="shared" si="117"/>
+        <v/>
       </c>
       <c r="B599" s="11" t="s">
         <v>10</v>
@@ -52913,6 +53367,7 @@
     <row r="600" spans="1:23" s="16" customFormat="1" ht="28.5" customHeight="1">
       <c r="A600" s="11" t="str">
         <f t="shared" si="117"/>
+        <v/>
       </c>
       <c r="B600" s="11" t="s">
         <v>10</v>
@@ -52990,6 +53445,7 @@
     <row r="601" spans="1:23" s="2" customFormat="1" ht="28.5" customHeight="1">
       <c r="A601" s="11" t="str">
         <f t="shared" si="117"/>
+        <v/>
       </c>
       <c r="B601" s="11" t="s">
         <v>14</v>
@@ -53067,6 +53523,7 @@
     <row r="602" spans="1:23" s="2" customFormat="1" ht="28.5" customHeight="1">
       <c r="A602" s="11" t="str">
         <f t="shared" si="117"/>
+        <v/>
       </c>
       <c r="B602" s="11" t="s">
         <v>14</v>
@@ -53144,6 +53601,7 @@
     <row r="603" spans="1:23" s="2" customFormat="1" ht="28.5" customHeight="1">
       <c r="A603" s="11" t="str">
         <f t="shared" si="117"/>
+        <v/>
       </c>
       <c r="B603" s="11" t="s">
         <v>14</v>
@@ -53221,6 +53679,7 @@
     <row r="604" spans="1:23" s="2" customFormat="1" ht="28.5" customHeight="1">
       <c r="A604" s="11" t="str">
         <f t="shared" si="117"/>
+        <v/>
       </c>
       <c r="B604" s="11" t="s">
         <v>14</v>
@@ -53298,6 +53757,7 @@
     <row r="605" spans="1:23" s="2" customFormat="1" ht="28.5" customHeight="1">
       <c r="A605" s="11" t="str">
         <f t="shared" si="117"/>
+        <v/>
       </c>
       <c r="B605" s="11" t="s">
         <v>10</v>
@@ -53375,6 +53835,7 @@
     <row r="606" spans="1:23" s="2" customFormat="1" ht="28.5" customHeight="1">
       <c r="A606" s="11" t="str">
         <f t="shared" si="117"/>
+        <v/>
       </c>
       <c r="B606" s="11" t="s">
         <v>6</v>
@@ -53452,6 +53913,7 @@
     <row r="607" spans="1:23" s="2" customFormat="1" ht="28.5" customHeight="1">
       <c r="A607" s="11" t="str">
         <f t="shared" si="117"/>
+        <v/>
       </c>
       <c r="B607" s="11" t="s">
         <v>6</v>
@@ -53529,6 +53991,7 @@
     <row r="608" spans="1:23" s="2" customFormat="1" ht="28.5" customHeight="1">
       <c r="A608" s="11" t="str">
         <f t="shared" si="117"/>
+        <v/>
       </c>
       <c r="B608" s="11" t="s">
         <v>8</v>
@@ -53606,6 +54069,7 @@
     <row r="609" spans="1:23" s="2" customFormat="1" ht="28.5" customHeight="1">
       <c r="A609" s="11" t="str">
         <f t="shared" si="117"/>
+        <v/>
       </c>
       <c r="B609" s="11" t="s">
         <v>10</v>
@@ -53683,6 +54147,7 @@
     <row r="610" spans="1:23" s="2" customFormat="1" ht="28.5" customHeight="1">
       <c r="A610" s="11" t="str">
         <f t="shared" si="117"/>
+        <v/>
       </c>
       <c r="B610" s="11" t="s">
         <v>6</v>
@@ -53760,6 +54225,7 @@
     <row r="611" spans="1:23" s="2" customFormat="1" ht="28.5" customHeight="1">
       <c r="A611" s="11" t="str">
         <f t="shared" si="117"/>
+        <v/>
       </c>
       <c r="B611" s="11" t="s">
         <v>8</v>
@@ -53837,6 +54303,7 @@
     <row r="612" spans="1:23" s="2" customFormat="1" ht="28.5" customHeight="1">
       <c r="A612" s="11" t="str">
         <f t="shared" si="117"/>
+        <v/>
       </c>
       <c r="B612" s="11" t="s">
         <v>8</v>
@@ -53914,6 +54381,7 @@
     <row r="613" spans="1:23" s="2" customFormat="1" ht="28.5" customHeight="1">
       <c r="A613" s="11" t="str">
         <f t="shared" si="117"/>
+        <v/>
       </c>
       <c r="B613" s="11" t="s">
         <v>8</v>
@@ -53991,6 +54459,7 @@
     <row r="614" spans="1:23" s="2" customFormat="1" ht="28.5" customHeight="1">
       <c r="A614" s="11" t="str">
         <f t="shared" si="117"/>
+        <v/>
       </c>
       <c r="B614" s="11" t="s">
         <v>12</v>
@@ -54068,6 +54537,7 @@
     <row r="615" spans="1:23" s="2" customFormat="1" ht="28.5" customHeight="1">
       <c r="A615" s="11" t="str">
         <f t="shared" si="117"/>
+        <v/>
       </c>
       <c r="B615" s="11" t="s">
         <v>12</v>
@@ -54145,6 +54615,7 @@
     <row r="616" spans="1:23" s="2" customFormat="1" ht="28.5" customHeight="1">
       <c r="A616" s="11" t="str">
         <f t="shared" si="117"/>
+        <v/>
       </c>
       <c r="B616" s="11" t="s">
         <v>12</v>
@@ -54222,6 +54693,7 @@
     <row r="617" spans="1:23" s="7" customFormat="1" ht="28.5" customHeight="1">
       <c r="A617" s="11" t="str">
         <f t="shared" si="117"/>
+        <v/>
       </c>
       <c r="B617" s="11" t="s">
         <v>10</v>
@@ -54299,6 +54771,7 @@
     <row r="618" spans="1:23" s="2" customFormat="1" ht="28.5" customHeight="1">
       <c r="A618" s="11" t="str">
         <f t="shared" si="117"/>
+        <v/>
       </c>
       <c r="B618" s="11" t="s">
         <v>10</v>
@@ -54376,6 +54849,7 @@
     <row r="619" spans="1:23" s="2" customFormat="1" ht="28.5" customHeight="1">
       <c r="A619" s="11" t="str">
         <f t="shared" si="117"/>
+        <v/>
       </c>
       <c r="B619" s="11" t="s">
         <v>10</v>
@@ -54453,6 +54927,7 @@
     <row r="620" spans="1:23" s="2" customFormat="1" ht="28.5" customHeight="1">
       <c r="A620" s="11" t="str">
         <f t="shared" si="117"/>
+        <v/>
       </c>
       <c r="B620" s="11" t="s">
         <v>10</v>
@@ -54530,6 +55005,7 @@
     <row r="621" spans="1:23" s="2" customFormat="1" ht="28.5" customHeight="1">
       <c r="A621" s="11" t="str">
         <f t="shared" si="117"/>
+        <v/>
       </c>
       <c r="B621" s="11" t="s">
         <v>10</v>
@@ -54607,6 +55083,7 @@
     <row r="622" spans="1:23" s="2" customFormat="1" ht="28.5" customHeight="1">
       <c r="A622" s="11" t="str">
         <f t="shared" si="117"/>
+        <v/>
       </c>
       <c r="B622" s="11" t="s">
         <v>10</v>
@@ -54684,6 +55161,7 @@
     <row r="623" spans="1:23" s="16" customFormat="1" ht="28.5" customHeight="1">
       <c r="A623" s="11" t="str">
         <f t="shared" si="117"/>
+        <v/>
       </c>
       <c r="B623" s="11" t="s">
         <v>8</v>
@@ -54761,6 +55239,7 @@
     <row r="624" spans="1:23" s="2" customFormat="1" ht="28.5" customHeight="1">
       <c r="A624" s="11" t="str">
         <f t="shared" si="117"/>
+        <v/>
       </c>
       <c r="B624" s="11" t="s">
         <v>6</v>
@@ -54838,6 +55317,7 @@
     <row r="625" spans="1:23" s="2" customFormat="1" ht="28.5" customHeight="1">
       <c r="A625" s="11" t="str">
         <f t="shared" si="117"/>
+        <v/>
       </c>
       <c r="B625" s="11" t="s">
         <v>12</v>
@@ -54915,6 +55395,7 @@
     <row r="626" spans="1:23" s="2" customFormat="1" ht="28.5" customHeight="1">
       <c r="A626" s="11" t="str">
         <f t="shared" si="117"/>
+        <v/>
       </c>
       <c r="B626" s="11" t="s">
         <v>10</v>
@@ -54992,6 +55473,7 @@
     <row r="627" spans="1:23" s="16" customFormat="1" ht="28.5" customHeight="1">
       <c r="A627" s="11" t="str">
         <f t="shared" si="117"/>
+        <v/>
       </c>
       <c r="B627" s="11" t="s">
         <v>10</v>
@@ -55069,6 +55551,7 @@
     <row r="628" spans="1:23" s="16" customFormat="1" ht="28.5" customHeight="1">
       <c r="A628" s="11" t="str">
         <f t="shared" si="117"/>
+        <v/>
       </c>
       <c r="B628" s="11" t="s">
         <v>10</v>
@@ -55146,6 +55629,7 @@
     <row r="629" spans="1:23" s="2" customFormat="1" ht="28.5" customHeight="1">
       <c r="A629" s="11" t="str">
         <f t="shared" si="117"/>
+        <v/>
       </c>
       <c r="B629" s="11" t="s">
         <v>16</v>
@@ -55223,6 +55707,7 @@
     <row r="630" spans="1:23" s="16" customFormat="1" ht="28.5" customHeight="1">
       <c r="A630" s="11" t="str">
         <f t="shared" si="117"/>
+        <v/>
       </c>
       <c r="B630" s="11" t="s">
         <v>16</v>
@@ -55300,6 +55785,7 @@
     <row r="631" spans="1:23" s="2" customFormat="1" ht="28.5" customHeight="1">
       <c r="A631" s="11" t="str">
         <f t="shared" si="117"/>
+        <v/>
       </c>
       <c r="B631" s="11" t="s">
         <v>16</v>
@@ -55377,6 +55863,7 @@
     <row r="632" spans="1:23" s="2" customFormat="1" ht="28.5" customHeight="1">
       <c r="A632" s="11" t="str">
         <f t="shared" si="117"/>
+        <v/>
       </c>
       <c r="B632" s="11" t="s">
         <v>10</v>
@@ -55454,6 +55941,7 @@
     <row r="633" spans="1:23" s="16" customFormat="1" ht="28.5" customHeight="1">
       <c r="A633" s="11" t="str">
         <f t="shared" si="117"/>
+        <v/>
       </c>
       <c r="B633" s="11" t="s">
         <v>18</v>
@@ -55531,6 +56019,7 @@
     <row r="634" spans="1:23" s="2" customFormat="1" ht="28.5" customHeight="1">
       <c r="A634" s="11" t="str">
         <f t="shared" si="117"/>
+        <v/>
       </c>
       <c r="B634" s="11" t="s">
         <v>12</v>
@@ -55608,6 +56097,7 @@
     <row r="635" spans="1:23" s="7" customFormat="1" ht="28.5" customHeight="1">
       <c r="A635" s="11" t="str">
         <f t="shared" si="117"/>
+        <v/>
       </c>
       <c r="B635" s="11" t="s">
         <v>18</v>
@@ -55685,6 +56175,7 @@
     <row r="636" spans="1:23" s="2" customFormat="1" ht="28.5" customHeight="1">
       <c r="A636" s="11" t="str">
         <f t="shared" si="117"/>
+        <v/>
       </c>
       <c r="B636" s="11" t="s">
         <v>6</v>
@@ -55762,6 +56253,7 @@
     <row r="637" spans="1:23" s="7" customFormat="1" ht="28.5" customHeight="1">
       <c r="A637" s="11" t="str">
         <f t="shared" si="117"/>
+        <v/>
       </c>
       <c r="B637" s="11" t="s">
         <v>18</v>
@@ -55839,6 +56331,7 @@
     <row r="638" spans="1:23" s="16" customFormat="1" ht="28.5" customHeight="1">
       <c r="A638" s="11" t="str">
         <f t="shared" si="117"/>
+        <v/>
       </c>
       <c r="B638" s="11" t="s">
         <v>14</v>
@@ -55916,6 +56409,7 @@
     <row r="639" spans="1:23" s="2" customFormat="1" ht="28.5" customHeight="1">
       <c r="A639" s="11" t="str">
         <f t="shared" si="117"/>
+        <v/>
       </c>
       <c r="B639" s="11" t="s">
         <v>18</v>
@@ -55995,6 +56489,7 @@
     <row r="640" spans="1:23" s="2" customFormat="1" ht="28.5" customHeight="1">
       <c r="A640" s="11" t="str">
         <f t="shared" si="117"/>
+        <v/>
       </c>
       <c r="B640" s="11" t="s">
         <v>12</v>
@@ -56072,6 +56567,7 @@
     <row r="641" spans="1:23" s="16" customFormat="1" ht="28.5" customHeight="1">
       <c r="A641" s="11" t="str">
         <f t="shared" si="117"/>
+        <v/>
       </c>
       <c r="B641" s="11" t="s">
         <v>12</v>
@@ -56149,6 +56645,7 @@
     <row r="642" spans="1:23" s="16" customFormat="1" ht="28.5" customHeight="1">
       <c r="A642" s="11" t="str">
         <f t="shared" si="117"/>
+        <v/>
       </c>
       <c r="B642" s="11" t="s">
         <v>10</v>
@@ -56226,6 +56723,7 @@
     <row r="643" spans="1:23" s="2" customFormat="1" ht="28.5" customHeight="1">
       <c r="A643" s="11" t="str">
         <f t="shared" si="117"/>
+        <v/>
       </c>
       <c r="B643" s="11" t="s">
         <v>10</v>
@@ -56303,6 +56801,7 @@
     <row r="644" spans="1:23" s="7" customFormat="1" ht="28.5" customHeight="1">
       <c r="A644" s="11" t="str">
         <f t="shared" si="117"/>
+        <v/>
       </c>
       <c r="B644" s="11" t="s">
         <v>10</v>
@@ -56380,6 +56879,7 @@
     <row r="645" spans="1:23" s="2" customFormat="1" ht="28.5" customHeight="1">
       <c r="A645" s="11" t="str">
         <f t="shared" si="117"/>
+        <v/>
       </c>
       <c r="B645" s="11" t="s">
         <v>12</v>
@@ -56457,6 +56957,7 @@
     <row r="646" spans="1:23" s="16" customFormat="1" ht="28.5" customHeight="1">
       <c r="A646" s="11" t="str">
         <f t="shared" si="117"/>
+        <v/>
       </c>
       <c r="B646" s="11" t="s">
         <v>8</v>
@@ -56534,6 +57035,7 @@
     <row r="647" spans="1:23" s="2" customFormat="1" ht="28.5" customHeight="1">
       <c r="A647" s="11" t="str">
         <f t="shared" si="117"/>
+        <v/>
       </c>
       <c r="B647" s="11" t="s">
         <v>8</v>
@@ -56611,6 +57113,7 @@
     <row r="648" spans="1:23" s="2" customFormat="1" ht="28.5" customHeight="1">
       <c r="A648" s="11" t="str">
         <f t="shared" si="117"/>
+        <v/>
       </c>
       <c r="B648" s="11" t="s">
         <v>6</v>
@@ -56688,6 +57191,7 @@
     <row r="649" spans="1:23" s="2" customFormat="1" ht="28.5" customHeight="1">
       <c r="A649" s="11" t="str">
         <f t="shared" si="117"/>
+        <v/>
       </c>
       <c r="B649" s="11" t="s">
         <v>10</v>
@@ -56765,6 +57269,7 @@
     <row r="650" spans="1:23" s="16" customFormat="1" ht="28.5" customHeight="1">
       <c r="A650" s="11" t="str">
         <f t="shared" si="117"/>
+        <v/>
       </c>
       <c r="B650" s="11" t="s">
         <v>14</v>
@@ -56842,6 +57347,7 @@
     <row r="651" spans="1:23" s="2" customFormat="1" ht="28.5" customHeight="1">
       <c r="A651" s="11" t="str">
         <f t="shared" si="117"/>
+        <v/>
       </c>
       <c r="B651" s="11" t="s">
         <v>18</v>
@@ -56919,6 +57425,7 @@
     <row r="652" spans="1:23" s="2" customFormat="1" ht="28.5" customHeight="1">
       <c r="A652" s="11" t="str">
         <f t="shared" si="117"/>
+        <v/>
       </c>
       <c r="B652" s="11" t="s">
         <v>6</v>
@@ -56996,6 +57503,7 @@
     <row r="653" spans="1:23" s="7" customFormat="1" ht="28.5" customHeight="1">
       <c r="A653" s="11" t="str">
         <f t="shared" si="117"/>
+        <v/>
       </c>
       <c r="B653" s="11" t="s">
         <v>10</v>
@@ -57073,6 +57581,7 @@
     <row r="654" spans="1:23" s="16" customFormat="1" ht="28.5" customHeight="1">
       <c r="A654" s="11" t="str">
         <f t="shared" si="117"/>
+        <v/>
       </c>
       <c r="B654" s="11" t="s">
         <v>6</v>
@@ -57150,6 +57659,7 @@
     <row r="655" spans="1:23" s="2" customFormat="1" ht="28.5" customHeight="1">
       <c r="A655" s="11" t="str">
         <f t="shared" ref="A655:A718" si="130">IF($T655="","",1+COUNTIF($W$15:$W$883,"&lt;"&amp;W655))</f>
+        <v/>
       </c>
       <c r="B655" s="11" t="s">
         <v>10</v>
@@ -57227,6 +57737,7 @@
     <row r="656" spans="1:23" s="16" customFormat="1" ht="28.5" customHeight="1">
       <c r="A656" s="11" t="str">
         <f t="shared" si="130"/>
+        <v/>
       </c>
       <c r="B656" s="11" t="s">
         <v>14</v>
@@ -57304,6 +57815,7 @@
     <row r="657" spans="1:23" s="2" customFormat="1" ht="28.5" customHeight="1">
       <c r="A657" s="11" t="str">
         <f t="shared" si="130"/>
+        <v/>
       </c>
       <c r="B657" s="11" t="s">
         <v>10</v>
@@ -57381,6 +57893,7 @@
     <row r="658" spans="1:23" s="2" customFormat="1" ht="28.5" customHeight="1">
       <c r="A658" s="11" t="str">
         <f t="shared" si="130"/>
+        <v/>
       </c>
       <c r="B658" s="11" t="s">
         <v>10</v>
@@ -57458,6 +57971,7 @@
     <row r="659" spans="1:23" s="7" customFormat="1" ht="28.5" customHeight="1">
       <c r="A659" s="11" t="str">
         <f t="shared" si="130"/>
+        <v/>
       </c>
       <c r="B659" s="11" t="s">
         <v>10</v>
@@ -57535,6 +58049,7 @@
     <row r="660" spans="1:23" s="16" customFormat="1" ht="28.5" customHeight="1">
       <c r="A660" s="11" t="str">
         <f t="shared" si="130"/>
+        <v/>
       </c>
       <c r="B660" s="11" t="s">
         <v>10</v>
@@ -57612,6 +58127,7 @@
     <row r="661" spans="1:23" s="7" customFormat="1" ht="28.5" customHeight="1">
       <c r="A661" s="11" t="str">
         <f t="shared" si="130"/>
+        <v/>
       </c>
       <c r="B661" s="11" t="s">
         <v>10</v>
@@ -57689,6 +58205,7 @@
     <row r="662" spans="1:23" s="7" customFormat="1" ht="28.5" customHeight="1">
       <c r="A662" s="11" t="str">
         <f t="shared" si="130"/>
+        <v/>
       </c>
       <c r="B662" s="11" t="s">
         <v>10</v>
@@ -57766,6 +58283,7 @@
     <row r="663" spans="1:23" s="2" customFormat="1" ht="28.5" customHeight="1">
       <c r="A663" s="11" t="str">
         <f t="shared" si="130"/>
+        <v/>
       </c>
       <c r="B663" s="11" t="s">
         <v>18</v>
@@ -57843,6 +58361,7 @@
     <row r="664" spans="1:23" s="16" customFormat="1" ht="28.5" customHeight="1">
       <c r="A664" s="11" t="str">
         <f t="shared" si="130"/>
+        <v/>
       </c>
       <c r="B664" s="11" t="s">
         <v>18</v>
@@ -57920,6 +58439,7 @@
     <row r="665" spans="1:23" s="2" customFormat="1" ht="28.5" customHeight="1">
       <c r="A665" s="11" t="str">
         <f t="shared" si="130"/>
+        <v/>
       </c>
       <c r="B665" s="11" t="s">
         <v>10</v>
@@ -57997,6 +58517,7 @@
     <row r="666" spans="1:23" s="7" customFormat="1" ht="28.5" customHeight="1">
       <c r="A666" s="11" t="str">
         <f t="shared" si="130"/>
+        <v/>
       </c>
       <c r="B666" s="11" t="s">
         <v>10</v>
@@ -58074,6 +58595,7 @@
     <row r="667" spans="1:23" s="16" customFormat="1" ht="28.5" customHeight="1">
       <c r="A667" s="11" t="str">
         <f t="shared" si="130"/>
+        <v/>
       </c>
       <c r="B667" s="11" t="s">
         <v>10</v>
@@ -58151,6 +58673,7 @@
     <row r="668" spans="1:23" s="2" customFormat="1" ht="28.5" customHeight="1">
       <c r="A668" s="11" t="str">
         <f t="shared" si="130"/>
+        <v/>
       </c>
       <c r="B668" s="11" t="s">
         <v>10</v>
@@ -58228,6 +58751,7 @@
     <row r="669" spans="1:23" s="2" customFormat="1" ht="28.5" customHeight="1">
       <c r="A669" s="11" t="str">
         <f t="shared" si="130"/>
+        <v/>
       </c>
       <c r="B669" s="11" t="s">
         <v>6</v>
@@ -58305,6 +58829,7 @@
     <row r="670" spans="1:23" s="2" customFormat="1" ht="28.5" customHeight="1">
       <c r="A670" s="11" t="str">
         <f t="shared" si="130"/>
+        <v/>
       </c>
       <c r="B670" s="11" t="s">
         <v>14</v>
@@ -58382,6 +58907,7 @@
     <row r="671" spans="1:23" s="2" customFormat="1" ht="28.5" customHeight="1">
       <c r="A671" s="11" t="str">
         <f t="shared" si="130"/>
+        <v/>
       </c>
       <c r="B671" s="11" t="s">
         <v>10</v>
@@ -58459,6 +58985,7 @@
     <row r="672" spans="1:23" s="2" customFormat="1" ht="28.5" customHeight="1">
       <c r="A672" s="11" t="str">
         <f t="shared" si="130"/>
+        <v/>
       </c>
       <c r="B672" s="11" t="s">
         <v>10</v>
@@ -58536,6 +59063,7 @@
     <row r="673" spans="1:23" s="16" customFormat="1" ht="28.5" customHeight="1">
       <c r="A673" s="11" t="str">
         <f t="shared" si="130"/>
+        <v/>
       </c>
       <c r="B673" s="11" t="s">
         <v>10</v>
@@ -58613,6 +59141,7 @@
     <row r="674" spans="1:23" s="16" customFormat="1" ht="28.5" customHeight="1">
       <c r="A674" s="11" t="str">
         <f t="shared" si="130"/>
+        <v/>
       </c>
       <c r="B674" s="11" t="s">
         <v>6</v>
@@ -58690,6 +59219,7 @@
     <row r="675" spans="1:23" s="2" customFormat="1" ht="28.5" customHeight="1">
       <c r="A675" s="11" t="str">
         <f t="shared" si="130"/>
+        <v/>
       </c>
       <c r="B675" s="11" t="s">
         <v>16</v>
@@ -58767,6 +59297,7 @@
     <row r="676" spans="1:23" s="2" customFormat="1" ht="28.5" customHeight="1">
       <c r="A676" s="11" t="str">
         <f t="shared" si="130"/>
+        <v/>
       </c>
       <c r="B676" s="11" t="s">
         <v>10</v>
@@ -58820,15 +59351,19 @@
       </c>
       <c r="R676" s="13" t="str">
         <f t="shared" si="137"/>
+        <v/>
       </c>
       <c r="S676" s="12" t="str">
         <f t="shared" si="138"/>
+        <v/>
       </c>
       <c r="T676" s="12" t="str">
         <f t="shared" si="139"/>
+        <v/>
       </c>
       <c r="U676" s="12" t="str">
         <f t="shared" si="140"/>
+        <v/>
       </c>
       <c r="V676" s="12" t="str">
         <f t="shared" si="141"/>
@@ -58842,6 +59377,7 @@
     <row r="677" spans="1:23" s="2" customFormat="1" ht="28.5" customHeight="1">
       <c r="A677" s="11" t="str">
         <f t="shared" si="130"/>
+        <v/>
       </c>
       <c r="B677" s="11" t="s">
         <v>10</v>
@@ -58919,6 +59455,7 @@
     <row r="678" spans="1:23" s="2" customFormat="1" ht="28.5" customHeight="1">
       <c r="A678" s="11" t="str">
         <f t="shared" si="130"/>
+        <v/>
       </c>
       <c r="B678" s="11" t="s">
         <v>6</v>
@@ -58996,6 +59533,7 @@
     <row r="679" spans="1:23" s="2" customFormat="1" ht="28.5" customHeight="1">
       <c r="A679" s="11" t="str">
         <f t="shared" si="130"/>
+        <v/>
       </c>
       <c r="B679" s="11" t="s">
         <v>6</v>
@@ -59073,6 +59611,7 @@
     <row r="680" spans="1:23" s="16" customFormat="1" ht="28.5" customHeight="1">
       <c r="A680" s="11" t="str">
         <f t="shared" si="130"/>
+        <v/>
       </c>
       <c r="B680" s="11" t="s">
         <v>10</v>
@@ -59150,6 +59689,7 @@
     <row r="681" spans="1:23" s="7" customFormat="1" ht="28.5" customHeight="1">
       <c r="A681" s="11" t="str">
         <f t="shared" si="130"/>
+        <v/>
       </c>
       <c r="B681" s="11" t="s">
         <v>10</v>
@@ -59227,6 +59767,7 @@
     <row r="682" spans="1:23" s="7" customFormat="1" ht="28.5" customHeight="1">
       <c r="A682" s="11" t="str">
         <f t="shared" si="130"/>
+        <v/>
       </c>
       <c r="B682" s="11" t="s">
         <v>10</v>
@@ -59304,6 +59845,7 @@
     <row r="683" spans="1:23" s="2" customFormat="1" ht="28.5" customHeight="1">
       <c r="A683" s="11" t="str">
         <f t="shared" si="130"/>
+        <v/>
       </c>
       <c r="B683" s="11" t="s">
         <v>14</v>
@@ -59381,6 +59923,7 @@
     <row r="684" spans="1:23" s="2" customFormat="1" ht="28.5" customHeight="1">
       <c r="A684" s="11" t="str">
         <f t="shared" si="130"/>
+        <v/>
       </c>
       <c r="B684" s="11" t="s">
         <v>10</v>
@@ -59458,6 +60001,7 @@
     <row r="685" spans="1:23" s="2" customFormat="1" ht="28.5" customHeight="1">
       <c r="A685" s="11" t="str">
         <f t="shared" si="130"/>
+        <v/>
       </c>
       <c r="B685" s="11" t="s">
         <v>10</v>
@@ -59511,15 +60055,19 @@
       </c>
       <c r="R685" s="13" t="str">
         <f t="shared" si="137"/>
+        <v/>
       </c>
       <c r="S685" s="12" t="str">
         <f t="shared" si="138"/>
+        <v/>
       </c>
       <c r="T685" s="12" t="str">
         <f t="shared" si="139"/>
+        <v/>
       </c>
       <c r="U685" s="12" t="str">
         <f t="shared" si="140"/>
+        <v/>
       </c>
       <c r="V685" s="12" t="str">
         <f t="shared" si="141"/>
@@ -59533,6 +60081,7 @@
     <row r="686" spans="1:23" s="7" customFormat="1" ht="28.5" customHeight="1">
       <c r="A686" s="11" t="str">
         <f t="shared" si="130"/>
+        <v/>
       </c>
       <c r="B686" s="11" t="s">
         <v>10</v>
@@ -59610,6 +60159,7 @@
     <row r="687" spans="1:23" s="2" customFormat="1" ht="28.5" customHeight="1">
       <c r="A687" s="11" t="str">
         <f t="shared" si="130"/>
+        <v/>
       </c>
       <c r="B687" s="11" t="s">
         <v>8</v>
@@ -59687,6 +60237,7 @@
     <row r="688" spans="1:23" s="7" customFormat="1" ht="28.5" customHeight="1">
       <c r="A688" s="11" t="str">
         <f t="shared" si="130"/>
+        <v/>
       </c>
       <c r="B688" s="11" t="s">
         <v>8</v>
@@ -59764,6 +60315,7 @@
     <row r="689" spans="1:23" s="2" customFormat="1" ht="28.5" customHeight="1">
       <c r="A689" s="11" t="str">
         <f t="shared" si="130"/>
+        <v/>
       </c>
       <c r="B689" s="11" t="s">
         <v>8</v>
@@ -59841,6 +60393,7 @@
     <row r="690" spans="1:23" s="2" customFormat="1" ht="28.5" customHeight="1">
       <c r="A690" s="11" t="str">
         <f t="shared" si="130"/>
+        <v/>
       </c>
       <c r="B690" s="11" t="s">
         <v>8</v>
@@ -59918,6 +60471,7 @@
     <row r="691" spans="1:23" s="16" customFormat="1" ht="28.5" customHeight="1">
       <c r="A691" s="11" t="str">
         <f t="shared" si="130"/>
+        <v/>
       </c>
       <c r="B691" s="11" t="s">
         <v>10</v>
@@ -59995,6 +60549,7 @@
     <row r="692" spans="1:23" s="2" customFormat="1" ht="28.5" customHeight="1">
       <c r="A692" s="11" t="str">
         <f t="shared" si="130"/>
+        <v/>
       </c>
       <c r="B692" s="11" t="s">
         <v>6</v>
@@ -60072,6 +60627,7 @@
     <row r="693" spans="1:23" s="2" customFormat="1" ht="28.5" customHeight="1">
       <c r="A693" s="11" t="str">
         <f t="shared" si="130"/>
+        <v/>
       </c>
       <c r="B693" s="11" t="s">
         <v>8</v>
@@ -60149,6 +60705,7 @@
     <row r="694" spans="1:23" s="2" customFormat="1" ht="28.5" customHeight="1">
       <c r="A694" s="11" t="str">
         <f t="shared" si="130"/>
+        <v/>
       </c>
       <c r="B694" s="11" t="s">
         <v>12</v>
@@ -60226,6 +60783,7 @@
     <row r="695" spans="1:23" s="2" customFormat="1" ht="28.5" customHeight="1">
       <c r="A695" s="11" t="str">
         <f t="shared" si="130"/>
+        <v/>
       </c>
       <c r="B695" s="11" t="s">
         <v>18</v>
@@ -60303,6 +60861,7 @@
     <row r="696" spans="1:23" s="2" customFormat="1" ht="28.5" customHeight="1">
       <c r="A696" s="11" t="str">
         <f t="shared" si="130"/>
+        <v/>
       </c>
       <c r="B696" s="11" t="s">
         <v>8</v>
@@ -60380,6 +60939,7 @@
     <row r="697" spans="1:23" s="7" customFormat="1" ht="28.5" customHeight="1">
       <c r="A697" s="11" t="str">
         <f t="shared" si="130"/>
+        <v/>
       </c>
       <c r="B697" s="11" t="s">
         <v>10</v>
@@ -60457,6 +61017,7 @@
     <row r="698" spans="1:23" s="2" customFormat="1" ht="28.5" customHeight="1">
       <c r="A698" s="11" t="str">
         <f t="shared" si="130"/>
+        <v/>
       </c>
       <c r="B698" s="11" t="s">
         <v>6</v>
@@ -60534,6 +61095,7 @@
     <row r="699" spans="1:23" s="2" customFormat="1" ht="28.5" customHeight="1">
       <c r="A699" s="11" t="str">
         <f t="shared" si="130"/>
+        <v/>
       </c>
       <c r="B699" s="11" t="s">
         <v>6</v>
@@ -60611,6 +61173,7 @@
     <row r="700" spans="1:23" s="2" customFormat="1" ht="28.5" customHeight="1">
       <c r="A700" s="11" t="str">
         <f t="shared" si="130"/>
+        <v/>
       </c>
       <c r="B700" s="11" t="s">
         <v>6</v>
@@ -60688,6 +61251,7 @@
     <row r="701" spans="1:23" s="7" customFormat="1" ht="28.5" customHeight="1">
       <c r="A701" s="11" t="str">
         <f t="shared" si="130"/>
+        <v/>
       </c>
       <c r="B701" s="11" t="s">
         <v>10</v>
@@ -60765,6 +61329,7 @@
     <row r="702" spans="1:23" s="7" customFormat="1" ht="28.5" customHeight="1">
       <c r="A702" s="11" t="str">
         <f t="shared" si="130"/>
+        <v/>
       </c>
       <c r="B702" s="11" t="s">
         <v>18</v>
@@ -60842,6 +61407,7 @@
     <row r="703" spans="1:23" s="2" customFormat="1" ht="28.5" customHeight="1">
       <c r="A703" s="11" t="str">
         <f t="shared" si="130"/>
+        <v/>
       </c>
       <c r="B703" s="11" t="s">
         <v>6</v>
@@ -60919,6 +61485,7 @@
     <row r="704" spans="1:23" s="7" customFormat="1" ht="28.5" customHeight="1">
       <c r="A704" s="11" t="str">
         <f t="shared" si="130"/>
+        <v/>
       </c>
       <c r="B704" s="11" t="s">
         <v>14</v>
@@ -60996,6 +61563,7 @@
     <row r="705" spans="1:23" s="2" customFormat="1" ht="28.5" customHeight="1">
       <c r="A705" s="11" t="str">
         <f t="shared" si="130"/>
+        <v/>
       </c>
       <c r="B705" s="11" t="s">
         <v>12</v>
@@ -61073,6 +61641,7 @@
     <row r="706" spans="1:23" s="2" customFormat="1" ht="28.5" customHeight="1">
       <c r="A706" s="11" t="str">
         <f t="shared" si="130"/>
+        <v/>
       </c>
       <c r="B706" s="11" t="s">
         <v>12</v>
@@ -61150,6 +61719,7 @@
     <row r="707" spans="1:23" s="2" customFormat="1" ht="28.5" customHeight="1">
       <c r="A707" s="11" t="str">
         <f t="shared" si="130"/>
+        <v/>
       </c>
       <c r="B707" s="11" t="s">
         <v>12</v>
@@ -61227,6 +61797,7 @@
     <row r="708" spans="1:23" s="2" customFormat="1" ht="28.5" customHeight="1">
       <c r="A708" s="11" t="str">
         <f t="shared" si="130"/>
+        <v/>
       </c>
       <c r="B708" s="11" t="s">
         <v>12</v>
@@ -61304,6 +61875,7 @@
     <row r="709" spans="1:23" s="2" customFormat="1" ht="28.5" customHeight="1">
       <c r="A709" s="11" t="str">
         <f t="shared" si="130"/>
+        <v/>
       </c>
       <c r="B709" s="11" t="s">
         <v>8</v>
@@ -61381,6 +61953,7 @@
     <row r="710" spans="1:23" s="2" customFormat="1" ht="28.5" customHeight="1">
       <c r="A710" s="11" t="str">
         <f t="shared" si="130"/>
+        <v/>
       </c>
       <c r="B710" s="11" t="s">
         <v>12</v>
@@ -61458,6 +62031,7 @@
     <row r="711" spans="1:23" s="2" customFormat="1" ht="28.5" customHeight="1">
       <c r="A711" s="11" t="str">
         <f t="shared" si="130"/>
+        <v/>
       </c>
       <c r="B711" s="11" t="s">
         <v>14</v>
@@ -61535,6 +62109,7 @@
     <row r="712" spans="1:23" s="2" customFormat="1" ht="28.5" customHeight="1">
       <c r="A712" s="11" t="str">
         <f t="shared" si="130"/>
+        <v/>
       </c>
       <c r="B712" s="11" t="s">
         <v>6</v>
@@ -61612,6 +62187,7 @@
     <row r="713" spans="1:23" s="2" customFormat="1" ht="28.5" customHeight="1">
       <c r="A713" s="11" t="str">
         <f t="shared" si="130"/>
+        <v/>
       </c>
       <c r="B713" s="11" t="s">
         <v>14</v>
@@ -61689,6 +62265,7 @@
     <row r="714" spans="1:23" s="2" customFormat="1" ht="28.5" customHeight="1">
       <c r="A714" s="11" t="str">
         <f t="shared" si="130"/>
+        <v/>
       </c>
       <c r="B714" s="11" t="s">
         <v>8</v>
@@ -61766,6 +62343,7 @@
     <row r="715" spans="1:23" s="2" customFormat="1" ht="28.5" customHeight="1">
       <c r="A715" s="11" t="str">
         <f t="shared" si="130"/>
+        <v/>
       </c>
       <c r="B715" s="11" t="s">
         <v>10</v>
@@ -61843,6 +62421,7 @@
     <row r="716" spans="1:23" s="2" customFormat="1" ht="28.5" customHeight="1">
       <c r="A716" s="11" t="str">
         <f t="shared" si="130"/>
+        <v/>
       </c>
       <c r="B716" s="11" t="s">
         <v>12</v>
@@ -61920,6 +62499,7 @@
     <row r="717" spans="1:23" s="16" customFormat="1" ht="28.5" customHeight="1">
       <c r="A717" s="11" t="str">
         <f t="shared" si="130"/>
+        <v/>
       </c>
       <c r="B717" s="11" t="s">
         <v>12</v>
@@ -61997,6 +62577,7 @@
     <row r="718" spans="1:23" s="2" customFormat="1" ht="28.5" customHeight="1">
       <c r="A718" s="11" t="str">
         <f t="shared" si="130"/>
+        <v/>
       </c>
       <c r="B718" s="11" t="s">
         <v>12</v>
@@ -62074,6 +62655,7 @@
     <row r="719" spans="1:23" s="16" customFormat="1" ht="28.5" customHeight="1">
       <c r="A719" s="11" t="str">
         <f t="shared" ref="A719:A782" si="143">IF($T719="","",1+COUNTIF($W$15:$W$883,"&lt;"&amp;W719))</f>
+        <v/>
       </c>
       <c r="B719" s="11" t="s">
         <v>10</v>
@@ -62151,6 +62733,7 @@
     <row r="720" spans="1:23" s="2" customFormat="1" ht="28.5" customHeight="1">
       <c r="A720" s="11" t="str">
         <f t="shared" si="143"/>
+        <v/>
       </c>
       <c r="B720" s="11" t="s">
         <v>18</v>
@@ -62228,6 +62811,7 @@
     <row r="721" spans="1:23" s="2" customFormat="1" ht="28.5" customHeight="1">
       <c r="A721" s="11" t="str">
         <f t="shared" si="143"/>
+        <v/>
       </c>
       <c r="B721" s="11" t="s">
         <v>14</v>
@@ -62305,6 +62889,7 @@
     <row r="722" spans="1:23" s="2" customFormat="1" ht="28.5" customHeight="1">
       <c r="A722" s="11" t="str">
         <f t="shared" si="143"/>
+        <v/>
       </c>
       <c r="B722" s="11" t="s">
         <v>12</v>
@@ -62382,6 +62967,7 @@
     <row r="723" spans="1:23" s="2" customFormat="1" ht="28.5" customHeight="1">
       <c r="A723" s="11" t="str">
         <f t="shared" si="143"/>
+        <v/>
       </c>
       <c r="B723" s="11" t="s">
         <v>6</v>
@@ -62459,6 +63045,7 @@
     <row r="724" spans="1:23" s="2" customFormat="1" ht="28.5" customHeight="1">
       <c r="A724" s="11" t="str">
         <f t="shared" si="143"/>
+        <v/>
       </c>
       <c r="B724" s="11" t="s">
         <v>6</v>
@@ -62536,6 +63123,7 @@
     <row r="725" spans="1:23" s="2" customFormat="1" ht="28.5" customHeight="1">
       <c r="A725" s="11" t="str">
         <f t="shared" si="143"/>
+        <v/>
       </c>
       <c r="B725" s="11" t="s">
         <v>12</v>
@@ -62613,6 +63201,7 @@
     <row r="726" spans="1:23" s="7" customFormat="1" ht="28.5" customHeight="1">
       <c r="A726" s="11" t="str">
         <f t="shared" si="143"/>
+        <v/>
       </c>
       <c r="B726" s="11" t="s">
         <v>12</v>
@@ -62690,6 +63279,7 @@
     <row r="727" spans="1:23" s="2" customFormat="1" ht="28.5" customHeight="1">
       <c r="A727" s="11" t="str">
         <f t="shared" si="143"/>
+        <v/>
       </c>
       <c r="B727" s="11" t="s">
         <v>10</v>
@@ -62767,6 +63357,7 @@
     <row r="728" spans="1:23" s="2" customFormat="1" ht="28.5" customHeight="1">
       <c r="A728" s="11" t="str">
         <f t="shared" si="143"/>
+        <v/>
       </c>
       <c r="B728" s="11" t="s">
         <v>10</v>
@@ -62844,6 +63435,7 @@
     <row r="729" spans="1:23" s="7" customFormat="1" ht="28.5" customHeight="1">
       <c r="A729" s="11" t="str">
         <f t="shared" si="143"/>
+        <v/>
       </c>
       <c r="B729" s="11" t="s">
         <v>16</v>
@@ -62921,6 +63513,7 @@
     <row r="730" spans="1:23" s="2" customFormat="1" ht="28.5" customHeight="1">
       <c r="A730" s="11" t="str">
         <f t="shared" si="143"/>
+        <v/>
       </c>
       <c r="B730" s="11" t="s">
         <v>10</v>
@@ -62998,6 +63591,7 @@
     <row r="731" spans="1:23" s="7" customFormat="1" ht="28.5" customHeight="1">
       <c r="A731" s="11" t="str">
         <f t="shared" si="143"/>
+        <v/>
       </c>
       <c r="B731" s="11" t="s">
         <v>18</v>
@@ -63074,6 +63668,7 @@
     <row r="732" spans="1:23" s="2" customFormat="1" ht="28.5" customHeight="1">
       <c r="A732" s="11" t="str">
         <f t="shared" si="143"/>
+        <v/>
       </c>
       <c r="B732" s="11" t="s">
         <v>8</v>
@@ -63151,6 +63746,7 @@
     <row r="733" spans="1:23" s="2" customFormat="1" ht="28.5" customHeight="1">
       <c r="A733" s="11" t="str">
         <f t="shared" si="143"/>
+        <v/>
       </c>
       <c r="B733" s="11" t="s">
         <v>8</v>
@@ -63228,6 +63824,7 @@
     <row r="734" spans="1:23" s="2" customFormat="1" ht="28.5" customHeight="1">
       <c r="A734" s="11" t="str">
         <f t="shared" si="143"/>
+        <v/>
       </c>
       <c r="B734" s="11" t="s">
         <v>10</v>
@@ -63305,6 +63902,7 @@
     <row r="735" spans="1:23" s="16" customFormat="1" ht="28.5" customHeight="1">
       <c r="A735" s="11" t="str">
         <f t="shared" si="143"/>
+        <v/>
       </c>
       <c r="B735" s="11" t="s">
         <v>6</v>
@@ -63384,6 +63982,7 @@
     <row r="736" spans="1:23" s="16" customFormat="1" ht="28.5" customHeight="1">
       <c r="A736" s="11" t="str">
         <f t="shared" si="143"/>
+        <v/>
       </c>
       <c r="B736" s="11" t="s">
         <v>12</v>
@@ -63461,6 +64060,7 @@
     <row r="737" spans="1:23" s="2" customFormat="1" ht="28.5" customHeight="1">
       <c r="A737" s="11" t="str">
         <f t="shared" si="143"/>
+        <v/>
       </c>
       <c r="B737" s="11" t="s">
         <v>12</v>
@@ -63538,6 +64138,7 @@
     <row r="738" spans="1:23" s="2" customFormat="1" ht="28.5" customHeight="1">
       <c r="A738" s="11" t="str">
         <f t="shared" si="143"/>
+        <v/>
       </c>
       <c r="B738" s="11" t="s">
         <v>8</v>
@@ -63615,6 +64216,7 @@
     <row r="739" spans="1:23" s="7" customFormat="1" ht="28.5" customHeight="1">
       <c r="A739" s="11" t="str">
         <f t="shared" si="143"/>
+        <v/>
       </c>
       <c r="B739" s="11" t="s">
         <v>12</v>
@@ -63692,6 +64294,7 @@
     <row r="740" spans="1:23" s="2" customFormat="1" ht="28.5" customHeight="1">
       <c r="A740" s="11" t="str">
         <f t="shared" si="143"/>
+        <v/>
       </c>
       <c r="B740" s="11" t="s">
         <v>8</v>
@@ -63769,6 +64372,7 @@
     <row r="741" spans="1:23" s="2" customFormat="1" ht="28.5" customHeight="1">
       <c r="A741" s="11" t="str">
         <f t="shared" si="143"/>
+        <v/>
       </c>
       <c r="B741" s="11" t="s">
         <v>10</v>
@@ -63846,6 +64450,7 @@
     <row r="742" spans="1:23" s="2" customFormat="1" ht="28.5" customHeight="1">
       <c r="A742" s="11" t="str">
         <f t="shared" si="143"/>
+        <v/>
       </c>
       <c r="B742" s="11" t="s">
         <v>10</v>
@@ -63923,6 +64528,7 @@
     <row r="743" spans="1:23" s="2" customFormat="1" ht="28.5" customHeight="1">
       <c r="A743" s="11" t="str">
         <f t="shared" si="143"/>
+        <v/>
       </c>
       <c r="B743" s="11" t="s">
         <v>10</v>
@@ -64000,6 +64606,7 @@
     <row r="744" spans="1:23" s="2" customFormat="1" ht="28.5" customHeight="1">
       <c r="A744" s="11" t="str">
         <f t="shared" si="143"/>
+        <v/>
       </c>
       <c r="B744" s="11" t="s">
         <v>6</v>
@@ -64077,6 +64684,7 @@
     <row r="745" spans="1:23" s="2" customFormat="1" ht="28.5" customHeight="1">
       <c r="A745" s="11" t="str">
         <f t="shared" si="143"/>
+        <v/>
       </c>
       <c r="B745" s="11" t="s">
         <v>14</v>
@@ -64154,6 +64762,7 @@
     <row r="746" spans="1:23" s="16" customFormat="1" ht="28.5" customHeight="1">
       <c r="A746" s="11" t="str">
         <f t="shared" si="143"/>
+        <v/>
       </c>
       <c r="B746" s="11" t="s">
         <v>14</v>
@@ -64231,6 +64840,7 @@
     <row r="747" spans="1:23" s="7" customFormat="1" ht="28.5" customHeight="1">
       <c r="A747" s="11" t="str">
         <f t="shared" si="143"/>
+        <v/>
       </c>
       <c r="B747" s="11" t="s">
         <v>8</v>
@@ -64308,6 +64918,7 @@
     <row r="748" spans="1:23" s="2" customFormat="1" ht="28.5" customHeight="1">
       <c r="A748" s="11" t="str">
         <f t="shared" si="143"/>
+        <v/>
       </c>
       <c r="B748" s="11" t="s">
         <v>18</v>
@@ -64385,6 +64996,7 @@
     <row r="749" spans="1:23" s="2" customFormat="1" ht="28.5" customHeight="1">
       <c r="A749" s="11" t="str">
         <f t="shared" si="143"/>
+        <v/>
       </c>
       <c r="B749" s="11" t="s">
         <v>6</v>
@@ -64462,6 +65074,7 @@
     <row r="750" spans="1:23" s="2" customFormat="1" ht="28.5" customHeight="1">
       <c r="A750" s="11" t="str">
         <f t="shared" si="143"/>
+        <v/>
       </c>
       <c r="B750" s="11" t="s">
         <v>14</v>
@@ -64539,6 +65152,7 @@
     <row r="751" spans="1:23" s="2" customFormat="1" ht="28.5" customHeight="1">
       <c r="A751" s="11" t="str">
         <f t="shared" si="143"/>
+        <v/>
       </c>
       <c r="B751" s="11" t="s">
         <v>8</v>
@@ -64616,6 +65230,7 @@
     <row r="752" spans="1:23" s="2" customFormat="1" ht="28.5" customHeight="1">
       <c r="A752" s="11" t="str">
         <f t="shared" si="143"/>
+        <v/>
       </c>
       <c r="B752" s="11" t="s">
         <v>6</v>
@@ -64693,6 +65308,7 @@
     <row r="753" spans="1:23" s="2" customFormat="1" ht="28.5" customHeight="1">
       <c r="A753" s="11" t="str">
         <f t="shared" si="143"/>
+        <v/>
       </c>
       <c r="B753" s="11" t="s">
         <v>10</v>
@@ -64770,6 +65386,7 @@
     <row r="754" spans="1:23" s="2" customFormat="1" ht="28.5" customHeight="1">
       <c r="A754" s="11" t="str">
         <f t="shared" si="143"/>
+        <v/>
       </c>
       <c r="B754" s="11" t="s">
         <v>10</v>
@@ -64847,6 +65464,7 @@
     <row r="755" spans="1:23" s="7" customFormat="1" ht="28.5" customHeight="1">
       <c r="A755" s="11" t="str">
         <f t="shared" si="143"/>
+        <v/>
       </c>
       <c r="B755" s="11" t="s">
         <v>14</v>
@@ -64924,6 +65542,7 @@
     <row r="756" spans="1:23" s="2" customFormat="1" ht="28.5" customHeight="1">
       <c r="A756" s="11" t="str">
         <f t="shared" si="143"/>
+        <v/>
       </c>
       <c r="B756" s="11" t="s">
         <v>14</v>
@@ -65001,6 +65620,7 @@
     <row r="757" spans="1:23" s="7" customFormat="1" ht="28.5" customHeight="1">
       <c r="A757" s="11" t="str">
         <f t="shared" si="143"/>
+        <v/>
       </c>
       <c r="B757" s="11" t="s">
         <v>8</v>
@@ -65078,6 +65698,7 @@
     <row r="758" spans="1:23" s="7" customFormat="1" ht="28.5" customHeight="1">
       <c r="A758" s="11" t="str">
         <f t="shared" si="143"/>
+        <v/>
       </c>
       <c r="B758" s="11" t="s">
         <v>18</v>
@@ -65155,6 +65776,7 @@
     <row r="759" spans="1:23" s="7" customFormat="1" ht="28.5" customHeight="1">
       <c r="A759" s="11" t="str">
         <f t="shared" si="143"/>
+        <v/>
       </c>
       <c r="B759" s="11" t="s">
         <v>16</v>
@@ -65232,6 +65854,7 @@
     <row r="760" spans="1:23" s="7" customFormat="1" ht="28.5" customHeight="1">
       <c r="A760" s="11" t="str">
         <f t="shared" si="143"/>
+        <v/>
       </c>
       <c r="B760" s="11" t="s">
         <v>6</v>
@@ -65309,6 +65932,7 @@
     <row r="761" spans="1:23" s="2" customFormat="1" ht="28.5" customHeight="1">
       <c r="A761" s="11" t="str">
         <f t="shared" si="143"/>
+        <v/>
       </c>
       <c r="B761" s="11" t="s">
         <v>14</v>
@@ -65386,6 +66010,7 @@
     <row r="762" spans="1:23" s="2" customFormat="1" ht="28.5" customHeight="1">
       <c r="A762" s="11" t="str">
         <f t="shared" si="143"/>
+        <v/>
       </c>
       <c r="B762" s="11" t="s">
         <v>12</v>
@@ -65439,15 +66064,19 @@
       </c>
       <c r="R762" s="13" t="str">
         <f t="shared" si="150"/>
+        <v/>
       </c>
       <c r="S762" s="12" t="str">
         <f t="shared" si="151"/>
+        <v/>
       </c>
       <c r="T762" s="12" t="str">
         <f t="shared" si="152"/>
+        <v/>
       </c>
       <c r="U762" s="12" t="str">
         <f t="shared" si="153"/>
+        <v/>
       </c>
       <c r="V762" s="12" t="str">
         <f t="shared" si="154"/>
@@ -65461,6 +66090,7 @@
     <row r="763" spans="1:23" s="2" customFormat="1" ht="28.5" customHeight="1">
       <c r="A763" s="11" t="str">
         <f t="shared" si="143"/>
+        <v/>
       </c>
       <c r="B763" s="11" t="s">
         <v>12</v>
@@ -65538,6 +66168,7 @@
     <row r="764" spans="1:23" s="2" customFormat="1" ht="28.5" customHeight="1">
       <c r="A764" s="11" t="str">
         <f t="shared" si="143"/>
+        <v/>
       </c>
       <c r="B764" s="11" t="s">
         <v>10</v>
@@ -65615,6 +66246,7 @@
     <row r="765" spans="1:23" s="16" customFormat="1" ht="28.5" customHeight="1">
       <c r="A765" s="11" t="str">
         <f t="shared" si="143"/>
+        <v/>
       </c>
       <c r="B765" s="11" t="s">
         <v>10</v>
@@ -65692,6 +66324,7 @@
     <row r="766" spans="1:23" s="7" customFormat="1" ht="28.5" customHeight="1">
       <c r="A766" s="11" t="str">
         <f t="shared" si="143"/>
+        <v/>
       </c>
       <c r="B766" s="11" t="s">
         <v>10</v>
@@ -65769,6 +66402,7 @@
     <row r="767" spans="1:23" s="2" customFormat="1" ht="28.5" customHeight="1">
       <c r="A767" s="11" t="str">
         <f t="shared" si="143"/>
+        <v/>
       </c>
       <c r="B767" s="11" t="s">
         <v>14</v>
@@ -65846,6 +66480,7 @@
     <row r="768" spans="1:23" s="7" customFormat="1" ht="28.5" customHeight="1">
       <c r="A768" s="11" t="str">
         <f t="shared" si="143"/>
+        <v/>
       </c>
       <c r="B768" s="11" t="s">
         <v>14</v>
@@ -65923,6 +66558,7 @@
     <row r="769" spans="1:23" s="2" customFormat="1" ht="28.5" customHeight="1">
       <c r="A769" s="11" t="str">
         <f t="shared" si="143"/>
+        <v/>
       </c>
       <c r="B769" s="11" t="s">
         <v>16</v>
@@ -66000,6 +66636,7 @@
     <row r="770" spans="1:23" s="2" customFormat="1" ht="28.5" customHeight="1">
       <c r="A770" s="11" t="str">
         <f t="shared" si="143"/>
+        <v/>
       </c>
       <c r="B770" s="11" t="s">
         <v>16</v>
@@ -66077,6 +66714,7 @@
     <row r="771" spans="1:23" s="2" customFormat="1" ht="28.5" customHeight="1">
       <c r="A771" s="11" t="str">
         <f t="shared" si="143"/>
+        <v/>
       </c>
       <c r="B771" s="11" t="s">
         <v>16</v>
@@ -66154,6 +66792,7 @@
     <row r="772" spans="1:23" s="16" customFormat="1" ht="28.5" customHeight="1">
       <c r="A772" s="11" t="str">
         <f t="shared" si="143"/>
+        <v/>
       </c>
       <c r="B772" s="11" t="s">
         <v>16</v>
@@ -66231,6 +66870,7 @@
     <row r="773" spans="1:23" s="2" customFormat="1" ht="28.5" customHeight="1">
       <c r="A773" s="11" t="str">
         <f t="shared" si="143"/>
+        <v/>
       </c>
       <c r="B773" s="11" t="s">
         <v>10</v>
@@ -66307,6 +66947,7 @@
     <row r="774" spans="1:23" s="2" customFormat="1" ht="28.5" customHeight="1">
       <c r="A774" s="11" t="str">
         <f t="shared" si="143"/>
+        <v/>
       </c>
       <c r="B774" s="11" t="s">
         <v>16</v>
@@ -66384,6 +67025,7 @@
     <row r="775" spans="1:23" s="16" customFormat="1" ht="28.5" customHeight="1">
       <c r="A775" s="11" t="str">
         <f t="shared" si="143"/>
+        <v/>
       </c>
       <c r="B775" s="11" t="s">
         <v>18</v>
@@ -66461,6 +67103,7 @@
     <row r="776" spans="1:23" s="2" customFormat="1" ht="28.5" customHeight="1">
       <c r="A776" s="11" t="str">
         <f t="shared" si="143"/>
+        <v/>
       </c>
       <c r="B776" s="11" t="s">
         <v>12</v>
@@ -66538,6 +67181,7 @@
     <row r="777" spans="1:23" s="2" customFormat="1" ht="28.5" customHeight="1">
       <c r="A777" s="11" t="str">
         <f t="shared" si="143"/>
+        <v/>
       </c>
       <c r="B777" s="11" t="s">
         <v>18</v>
@@ -66615,6 +67259,7 @@
     <row r="778" spans="1:23" s="2" customFormat="1" ht="28.5" customHeight="1">
       <c r="A778" s="11" t="str">
         <f t="shared" si="143"/>
+        <v/>
       </c>
       <c r="B778" s="11" t="s">
         <v>16</v>
@@ -66668,15 +67313,19 @@
       </c>
       <c r="R778" s="13" t="str">
         <f t="shared" si="150"/>
+        <v/>
       </c>
       <c r="S778" s="12" t="str">
         <f t="shared" si="151"/>
+        <v/>
       </c>
       <c r="T778" s="12" t="str">
         <f t="shared" si="152"/>
+        <v/>
       </c>
       <c r="U778" s="12" t="str">
         <f t="shared" si="153"/>
+        <v/>
       </c>
       <c r="V778" s="12" t="str">
         <f t="shared" si="154"/>
@@ -66690,6 +67339,7 @@
     <row r="779" spans="1:23" s="7" customFormat="1" ht="28.5" customHeight="1">
       <c r="A779" s="11" t="str">
         <f t="shared" si="143"/>
+        <v/>
       </c>
       <c r="B779" s="11" t="s">
         <v>6</v>
@@ -66766,6 +67416,7 @@
     <row r="780" spans="1:23" s="2" customFormat="1" ht="28.5" customHeight="1">
       <c r="A780" s="11" t="str">
         <f t="shared" si="143"/>
+        <v/>
       </c>
       <c r="B780" s="11" t="s">
         <v>14</v>
@@ -66843,6 +67494,7 @@
     <row r="781" spans="1:23" s="2" customFormat="1" ht="28.5" customHeight="1">
       <c r="A781" s="11" t="str">
         <f t="shared" si="143"/>
+        <v/>
       </c>
       <c r="B781" s="11" t="s">
         <v>12</v>
@@ -66896,15 +67548,19 @@
       </c>
       <c r="R781" s="13" t="str">
         <f t="shared" si="150"/>
+        <v/>
       </c>
       <c r="S781" s="12" t="str">
         <f t="shared" si="151"/>
+        <v/>
       </c>
       <c r="T781" s="12" t="str">
         <f t="shared" si="152"/>
+        <v/>
       </c>
       <c r="U781" s="12" t="str">
         <f t="shared" si="153"/>
+        <v/>
       </c>
       <c r="V781" s="12" t="str">
         <f t="shared" si="154"/>
@@ -66918,6 +67574,7 @@
     <row r="782" spans="1:23" s="2" customFormat="1" ht="28.5" customHeight="1">
       <c r="A782" s="11" t="str">
         <f t="shared" si="143"/>
+        <v/>
       </c>
       <c r="B782" s="11" t="s">
         <v>18</v>
@@ -66995,6 +67652,7 @@
     <row r="783" spans="1:23" s="2" customFormat="1" ht="28.5" customHeight="1">
       <c r="A783" s="11" t="str">
         <f t="shared" ref="A783:A846" si="159">IF($T783="","",1+COUNTIF($W$15:$W$883,"&lt;"&amp;W783))</f>
+        <v/>
       </c>
       <c r="B783" s="11" t="s">
         <v>12</v>
@@ -67072,6 +67730,7 @@
     <row r="784" spans="1:23" s="2" customFormat="1" ht="28.5" customHeight="1">
       <c r="A784" s="11" t="str">
         <f t="shared" si="159"/>
+        <v/>
       </c>
       <c r="B784" s="11" t="s">
         <v>12</v>
@@ -67149,6 +67808,7 @@
     <row r="785" spans="1:23" s="16" customFormat="1" ht="28.5" customHeight="1">
       <c r="A785" s="11" t="str">
         <f t="shared" si="159"/>
+        <v/>
       </c>
       <c r="B785" s="11" t="s">
         <v>18</v>
@@ -67226,6 +67886,7 @@
     <row r="786" spans="1:23" s="2" customFormat="1" ht="28.5" customHeight="1">
       <c r="A786" s="11" t="str">
         <f t="shared" si="159"/>
+        <v/>
       </c>
       <c r="B786" s="11" t="s">
         <v>18</v>
@@ -67303,6 +67964,7 @@
     <row r="787" spans="1:23" s="2" customFormat="1" ht="28.5" customHeight="1">
       <c r="A787" s="11" t="str">
         <f t="shared" si="159"/>
+        <v/>
       </c>
       <c r="B787" s="11" t="s">
         <v>18</v>
@@ -67380,6 +68042,7 @@
     <row r="788" spans="1:23" s="2" customFormat="1" ht="28.5" customHeight="1">
       <c r="A788" s="11" t="str">
         <f t="shared" si="159"/>
+        <v/>
       </c>
       <c r="B788" s="11" t="s">
         <v>18</v>
@@ -67457,6 +68120,7 @@
     <row r="789" spans="1:23" s="16" customFormat="1" ht="28.5" customHeight="1">
       <c r="A789" s="11" t="str">
         <f t="shared" si="159"/>
+        <v/>
       </c>
       <c r="B789" s="11" t="s">
         <v>16</v>
@@ -67534,6 +68198,7 @@
     <row r="790" spans="1:23" s="7" customFormat="1" ht="28.5" customHeight="1">
       <c r="A790" s="11" t="str">
         <f t="shared" si="159"/>
+        <v/>
       </c>
       <c r="B790" s="11" t="s">
         <v>10</v>
@@ -67611,6 +68276,7 @@
     <row r="791" spans="1:23" s="2" customFormat="1" ht="28.5" customHeight="1">
       <c r="A791" s="11" t="str">
         <f t="shared" si="159"/>
+        <v/>
       </c>
       <c r="B791" s="11" t="s">
         <v>14</v>
@@ -67688,6 +68354,7 @@
     <row r="792" spans="1:23" s="2" customFormat="1" ht="28.5" customHeight="1">
       <c r="A792" s="11" t="str">
         <f t="shared" si="159"/>
+        <v/>
       </c>
       <c r="B792" s="11" t="s">
         <v>14</v>
@@ -67765,6 +68432,7 @@
     <row r="793" spans="1:23" s="2" customFormat="1" ht="28.5" customHeight="1">
       <c r="A793" s="11" t="str">
         <f t="shared" si="159"/>
+        <v/>
       </c>
       <c r="B793" s="11" t="s">
         <v>14</v>
@@ -67842,6 +68510,7 @@
     <row r="794" spans="1:23" s="16" customFormat="1" ht="28.5" customHeight="1">
       <c r="A794" s="11" t="str">
         <f t="shared" si="159"/>
+        <v/>
       </c>
       <c r="B794" s="11" t="s">
         <v>16</v>
@@ -67919,6 +68588,7 @@
     <row r="795" spans="1:23" s="16" customFormat="1" ht="28.5" customHeight="1">
       <c r="A795" s="11" t="str">
         <f t="shared" si="159"/>
+        <v/>
       </c>
       <c r="B795" s="11" t="s">
         <v>8</v>
@@ -67996,6 +68666,7 @@
     <row r="796" spans="1:23" s="2" customFormat="1" ht="28.5" customHeight="1">
       <c r="A796" s="11" t="str">
         <f t="shared" si="159"/>
+        <v/>
       </c>
       <c r="B796" s="11" t="s">
         <v>12</v>
@@ -68073,6 +68744,7 @@
     <row r="797" spans="1:23" s="2" customFormat="1" ht="28.5" customHeight="1">
       <c r="A797" s="11" t="str">
         <f t="shared" si="159"/>
+        <v/>
       </c>
       <c r="B797" s="11" t="s">
         <v>10</v>
@@ -68150,6 +68822,7 @@
     <row r="798" spans="1:23" s="2" customFormat="1" ht="28.5" customHeight="1">
       <c r="A798" s="11" t="str">
         <f t="shared" si="159"/>
+        <v/>
       </c>
       <c r="B798" s="11" t="s">
         <v>18</v>
@@ -68227,6 +68900,7 @@
     <row r="799" spans="1:23" s="2" customFormat="1" ht="28.5" customHeight="1">
       <c r="A799" s="11" t="str">
         <f t="shared" si="159"/>
+        <v/>
       </c>
       <c r="B799" s="11" t="s">
         <v>18</v>
@@ -68304,6 +68978,7 @@
     <row r="800" spans="1:23" s="2" customFormat="1" ht="28.5" customHeight="1">
       <c r="A800" s="11" t="str">
         <f t="shared" si="159"/>
+        <v/>
       </c>
       <c r="B800" s="11" t="s">
         <v>6</v>
@@ -68381,6 +69056,7 @@
     <row r="801" spans="1:23" s="2" customFormat="1" ht="28.5" customHeight="1">
       <c r="A801" s="11" t="str">
         <f t="shared" si="159"/>
+        <v/>
       </c>
       <c r="B801" s="11" t="s">
         <v>10</v>
@@ -68457,6 +69133,7 @@
     <row r="802" spans="1:23" s="7" customFormat="1" ht="28.5" customHeight="1">
       <c r="A802" s="11" t="str">
         <f t="shared" si="159"/>
+        <v/>
       </c>
       <c r="B802" s="11" t="s">
         <v>8</v>
@@ -68534,6 +69211,7 @@
     <row r="803" spans="1:23" s="16" customFormat="1" ht="28.5" customHeight="1">
       <c r="A803" s="11" t="str">
         <f t="shared" si="159"/>
+        <v/>
       </c>
       <c r="B803" s="11" t="s">
         <v>8</v>
@@ -68611,6 +69289,7 @@
     <row r="804" spans="1:23" s="16" customFormat="1" ht="28.5" customHeight="1">
       <c r="A804" s="11" t="str">
         <f t="shared" si="159"/>
+        <v/>
       </c>
       <c r="B804" s="11" t="s">
         <v>16</v>
@@ -68688,6 +69367,7 @@
     <row r="805" spans="1:23" s="2" customFormat="1" ht="28.5" customHeight="1">
       <c r="A805" s="11" t="str">
         <f t="shared" si="159"/>
+        <v/>
       </c>
       <c r="B805" s="11" t="s">
         <v>10</v>
@@ -68765,6 +69445,7 @@
     <row r="806" spans="1:23" s="7" customFormat="1" ht="28.5" customHeight="1">
       <c r="A806" s="11" t="str">
         <f t="shared" si="159"/>
+        <v/>
       </c>
       <c r="B806" s="11" t="s">
         <v>14</v>
@@ -68842,6 +69523,7 @@
     <row r="807" spans="1:23" s="2" customFormat="1" ht="28.5" customHeight="1">
       <c r="A807" s="11" t="str">
         <f t="shared" si="159"/>
+        <v/>
       </c>
       <c r="B807" s="11" t="s">
         <v>12</v>
@@ -68918,6 +69600,7 @@
     <row r="808" spans="1:23" s="2" customFormat="1" ht="28.5" customHeight="1">
       <c r="A808" s="11" t="str">
         <f t="shared" si="159"/>
+        <v/>
       </c>
       <c r="B808" s="11" t="s">
         <v>12</v>
@@ -68994,6 +69677,7 @@
     <row r="809" spans="1:23" s="7" customFormat="1" ht="28.5" customHeight="1">
       <c r="A809" s="11" t="str">
         <f t="shared" si="159"/>
+        <v/>
       </c>
       <c r="B809" s="11" t="s">
         <v>12</v>
@@ -69070,6 +69754,7 @@
     <row r="810" spans="1:23" s="2" customFormat="1" ht="28.5" customHeight="1">
       <c r="A810" s="11" t="str">
         <f t="shared" si="159"/>
+        <v/>
       </c>
       <c r="B810" s="11" t="s">
         <v>6</v>
@@ -69147,6 +69832,7 @@
     <row r="811" spans="1:23" s="7" customFormat="1" ht="28.5" customHeight="1">
       <c r="A811" s="11" t="str">
         <f t="shared" si="159"/>
+        <v/>
       </c>
       <c r="B811" s="11" t="s">
         <v>14</v>
@@ -69224,6 +69910,7 @@
     <row r="812" spans="1:23" s="16" customFormat="1" ht="28.5" customHeight="1">
       <c r="A812" s="11" t="str">
         <f t="shared" si="159"/>
+        <v/>
       </c>
       <c r="B812" s="11" t="s">
         <v>14</v>
@@ -69301,6 +69988,7 @@
     <row r="813" spans="1:23" s="2" customFormat="1" ht="28.5" customHeight="1">
       <c r="A813" s="11" t="str">
         <f t="shared" si="159"/>
+        <v/>
       </c>
       <c r="B813" s="11" t="s">
         <v>18</v>
@@ -69380,6 +70068,7 @@
     <row r="814" spans="1:23" s="2" customFormat="1" ht="28.5" customHeight="1">
       <c r="A814" s="11" t="str">
         <f t="shared" si="159"/>
+        <v/>
       </c>
       <c r="B814" s="11" t="s">
         <v>14</v>
@@ -69457,6 +70146,7 @@
     <row r="815" spans="1:23" s="2" customFormat="1" ht="28.5" customHeight="1">
       <c r="A815" s="11" t="str">
         <f t="shared" si="159"/>
+        <v/>
       </c>
       <c r="B815" s="11" t="s">
         <v>14</v>
@@ -69534,6 +70224,7 @@
     <row r="816" spans="1:23" s="2" customFormat="1" ht="28.5" customHeight="1">
       <c r="A816" s="11" t="str">
         <f t="shared" si="159"/>
+        <v/>
       </c>
       <c r="B816" s="11" t="s">
         <v>14</v>
@@ -69611,6 +70302,7 @@
     <row r="817" spans="1:23" s="2" customFormat="1" ht="28.5" customHeight="1">
       <c r="A817" s="11" t="str">
         <f t="shared" si="159"/>
+        <v/>
       </c>
       <c r="B817" s="11" t="s">
         <v>14</v>
@@ -69688,6 +70380,7 @@
     <row r="818" spans="1:23" s="2" customFormat="1" ht="28.5" customHeight="1">
       <c r="A818" s="11" t="str">
         <f t="shared" si="159"/>
+        <v/>
       </c>
       <c r="B818" s="11" t="s">
         <v>12</v>
@@ -69765,6 +70458,7 @@
     <row r="819" spans="1:23" s="7" customFormat="1" ht="28.5" customHeight="1">
       <c r="A819" s="11" t="str">
         <f t="shared" si="159"/>
+        <v/>
       </c>
       <c r="B819" s="11" t="s">
         <v>12</v>
@@ -69842,6 +70536,7 @@
     <row r="820" spans="1:23" s="16" customFormat="1" ht="28.5" customHeight="1">
       <c r="A820" s="11" t="str">
         <f t="shared" si="159"/>
+        <v/>
       </c>
       <c r="B820" s="11" t="s">
         <v>18</v>
@@ -69919,6 +70614,7 @@
     <row r="821" spans="1:23" s="2" customFormat="1" ht="28.5" customHeight="1">
       <c r="A821" s="11" t="str">
         <f t="shared" si="159"/>
+        <v/>
       </c>
       <c r="B821" s="11" t="s">
         <v>8</v>
@@ -69996,6 +70692,7 @@
     <row r="822" spans="1:23" s="2" customFormat="1" ht="28.5" customHeight="1">
       <c r="A822" s="11" t="str">
         <f t="shared" si="159"/>
+        <v/>
       </c>
       <c r="B822" s="11" t="s">
         <v>14</v>
@@ -70073,6 +70770,7 @@
     <row r="823" spans="1:23" s="2" customFormat="1" ht="28.5" customHeight="1">
       <c r="A823" s="11" t="str">
         <f t="shared" si="159"/>
+        <v/>
       </c>
       <c r="B823" s="11" t="s">
         <v>18</v>
@@ -70150,6 +70848,7 @@
     <row r="824" spans="1:23" s="7" customFormat="1" ht="28.5" customHeight="1">
       <c r="A824" s="11" t="str">
         <f t="shared" si="159"/>
+        <v/>
       </c>
       <c r="B824" s="11" t="s">
         <v>10</v>
@@ -70227,6 +70926,7 @@
     <row r="825" spans="1:23" s="7" customFormat="1" ht="28.5" customHeight="1">
       <c r="A825" s="11" t="str">
         <f t="shared" si="159"/>
+        <v/>
       </c>
       <c r="B825" s="11" t="s">
         <v>10</v>
@@ -70304,6 +71004,7 @@
     <row r="826" spans="1:23" s="2" customFormat="1" ht="28.5" customHeight="1">
       <c r="A826" s="11" t="str">
         <f t="shared" si="159"/>
+        <v/>
       </c>
       <c r="B826" s="11" t="s">
         <v>12</v>
@@ -70381,6 +71082,7 @@
     <row r="827" spans="1:23" s="7" customFormat="1" ht="28.5" customHeight="1">
       <c r="A827" s="11" t="str">
         <f t="shared" si="159"/>
+        <v/>
       </c>
       <c r="B827" s="11" t="s">
         <v>14</v>
@@ -70458,6 +71160,7 @@
     <row r="828" spans="1:23" s="2" customFormat="1" ht="28.5" customHeight="1">
       <c r="A828" s="11" t="str">
         <f t="shared" si="159"/>
+        <v/>
       </c>
       <c r="B828" s="11" t="s">
         <v>14</v>
@@ -70535,6 +71238,7 @@
     <row r="829" spans="1:23" s="2" customFormat="1" ht="28.5" customHeight="1">
       <c r="A829" s="11" t="str">
         <f t="shared" si="159"/>
+        <v/>
       </c>
       <c r="B829" s="11" t="s">
         <v>10</v>
@@ -70612,6 +71316,7 @@
     <row r="830" spans="1:23" s="16" customFormat="1" ht="28.5" customHeight="1">
       <c r="A830" s="11" t="str">
         <f t="shared" si="159"/>
+        <v/>
       </c>
       <c r="B830" s="11" t="s">
         <v>10</v>
@@ -70689,6 +71394,7 @@
     <row r="831" spans="1:23" s="2" customFormat="1" ht="28.5" customHeight="1">
       <c r="A831" s="11" t="str">
         <f t="shared" si="159"/>
+        <v/>
       </c>
       <c r="B831" s="11" t="s">
         <v>18</v>
@@ -70766,6 +71472,7 @@
     <row r="832" spans="1:23" s="2" customFormat="1" ht="28.5" customHeight="1">
       <c r="A832" s="11" t="str">
         <f t="shared" si="159"/>
+        <v/>
       </c>
       <c r="B832" s="11" t="s">
         <v>10</v>
@@ -70843,6 +71550,7 @@
     <row r="833" spans="1:23" s="2" customFormat="1" ht="28.5" customHeight="1">
       <c r="A833" s="11" t="str">
         <f t="shared" si="159"/>
+        <v/>
       </c>
       <c r="B833" s="11" t="s">
         <v>18</v>
@@ -70920,6 +71628,7 @@
     <row r="834" spans="1:23" s="2" customFormat="1" ht="28.5" customHeight="1">
       <c r="A834" s="11" t="str">
         <f t="shared" si="159"/>
+        <v/>
       </c>
       <c r="B834" s="11" t="s">
         <v>16</v>
@@ -70997,6 +71706,7 @@
     <row r="835" spans="1:23" s="16" customFormat="1" ht="28.5" customHeight="1">
       <c r="A835" s="11" t="str">
         <f t="shared" si="159"/>
+        <v/>
       </c>
       <c r="B835" s="11" t="s">
         <v>16</v>
@@ -71074,6 +71784,7 @@
     <row r="836" spans="1:23" s="2" customFormat="1" ht="28.5" customHeight="1">
       <c r="A836" s="11" t="str">
         <f t="shared" si="159"/>
+        <v/>
       </c>
       <c r="B836" s="11" t="s">
         <v>16</v>
@@ -71151,6 +71862,7 @@
     <row r="837" spans="1:23" s="2" customFormat="1" ht="28.5" customHeight="1">
       <c r="A837" s="11" t="str">
         <f t="shared" si="159"/>
+        <v/>
       </c>
       <c r="B837" s="11" t="s">
         <v>16</v>
@@ -71228,6 +71940,7 @@
     <row r="838" spans="1:23" s="2" customFormat="1" ht="28.5" customHeight="1">
       <c r="A838" s="11" t="str">
         <f t="shared" si="159"/>
+        <v/>
       </c>
       <c r="B838" s="11" t="s">
         <v>12</v>
@@ -71305,6 +72018,7 @@
     <row r="839" spans="1:23" s="16" customFormat="1" ht="28.5" customHeight="1">
       <c r="A839" s="11" t="str">
         <f t="shared" si="159"/>
+        <v/>
       </c>
       <c r="B839" s="11" t="s">
         <v>6</v>
@@ -71384,6 +72098,7 @@
     <row r="840" spans="1:23" s="2" customFormat="1" ht="28.5" customHeight="1">
       <c r="A840" s="11" t="str">
         <f t="shared" si="159"/>
+        <v/>
       </c>
       <c r="B840" s="11" t="s">
         <v>10</v>
@@ -71461,6 +72176,7 @@
     <row r="841" spans="1:23" s="7" customFormat="1" ht="28.5" customHeight="1">
       <c r="A841" s="11" t="str">
         <f t="shared" si="159"/>
+        <v/>
       </c>
       <c r="B841" s="11" t="s">
         <v>6</v>
@@ -71538,6 +72254,7 @@
     <row r="842" spans="1:23" s="2" customFormat="1" ht="28.5" customHeight="1">
       <c r="A842" s="11" t="str">
         <f t="shared" si="159"/>
+        <v/>
       </c>
       <c r="B842" s="11" t="s">
         <v>16</v>
@@ -71615,6 +72332,7 @@
     <row r="843" spans="1:23" s="7" customFormat="1" ht="28.5" customHeight="1">
       <c r="A843" s="11" t="str">
         <f t="shared" si="159"/>
+        <v/>
       </c>
       <c r="B843" s="11" t="s">
         <v>10</v>
@@ -71692,6 +72410,7 @@
     <row r="844" spans="1:23" s="16" customFormat="1" ht="28.5" customHeight="1">
       <c r="A844" s="11" t="str">
         <f t="shared" si="159"/>
+        <v/>
       </c>
       <c r="B844" s="11" t="s">
         <v>10</v>
@@ -71769,6 +72488,7 @@
     <row r="845" spans="1:23" s="16" customFormat="1" ht="28.5" customHeight="1">
       <c r="A845" s="11" t="str">
         <f t="shared" si="159"/>
+        <v/>
       </c>
       <c r="B845" s="11" t="s">
         <v>12</v>
@@ -71846,6 +72566,7 @@
     <row r="846" spans="1:23" s="7" customFormat="1" ht="28.5" customHeight="1">
       <c r="A846" s="11" t="str">
         <f t="shared" si="159"/>
+        <v/>
       </c>
       <c r="B846" s="11" t="s">
         <v>18</v>
@@ -71923,6 +72644,7 @@
     <row r="847" spans="1:23" s="16" customFormat="1" ht="28.5" customHeight="1">
       <c r="A847" s="11" t="str">
         <f t="shared" ref="A847:A883" si="173">IF($T847="","",1+COUNTIF($W$15:$W$883,"&lt;"&amp;W847))</f>
+        <v/>
       </c>
       <c r="B847" s="11" t="s">
         <v>12</v>
@@ -72000,6 +72722,7 @@
     <row r="848" spans="1:23" s="2" customFormat="1" ht="28.5" customHeight="1">
       <c r="A848" s="11" t="str">
         <f t="shared" si="173"/>
+        <v/>
       </c>
       <c r="B848" s="11" t="s">
         <v>12</v>
@@ -72053,15 +72776,19 @@
       </c>
       <c r="R848" s="13" t="str">
         <f t="shared" si="179"/>
+        <v/>
       </c>
       <c r="S848" s="12" t="str">
         <f t="shared" si="180"/>
+        <v/>
       </c>
       <c r="T848" s="12" t="str">
         <f t="shared" si="181"/>
+        <v/>
       </c>
       <c r="U848" s="12" t="str">
         <f t="shared" si="182"/>
+        <v/>
       </c>
       <c r="V848" s="12" t="str">
         <f t="shared" si="183"/>
@@ -72075,6 +72802,7 @@
     <row r="849" spans="1:23" s="2" customFormat="1" ht="28.5" customHeight="1">
       <c r="A849" s="11" t="str">
         <f t="shared" si="173"/>
+        <v/>
       </c>
       <c r="B849" s="11" t="s">
         <v>14</v>
@@ -72152,6 +72880,7 @@
     <row r="850" spans="1:23" s="2" customFormat="1" ht="28.5" customHeight="1">
       <c r="A850" s="11" t="str">
         <f t="shared" si="173"/>
+        <v/>
       </c>
       <c r="B850" s="11" t="s">
         <v>14</v>
@@ -72229,6 +72958,7 @@
     <row r="851" spans="1:23" s="2" customFormat="1" ht="28.5" customHeight="1">
       <c r="A851" s="11" t="str">
         <f t="shared" si="173"/>
+        <v/>
       </c>
       <c r="B851" s="11" t="s">
         <v>16</v>
@@ -72306,6 +73036,7 @@
     <row r="852" spans="1:23" s="2" customFormat="1" ht="28.5" customHeight="1">
       <c r="A852" s="11" t="str">
         <f t="shared" si="173"/>
+        <v/>
       </c>
       <c r="B852" s="11" t="s">
         <v>8</v>
@@ -72383,6 +73114,7 @@
     <row r="853" spans="1:23" s="7" customFormat="1" ht="28.5" customHeight="1">
       <c r="A853" s="11" t="str">
         <f t="shared" si="173"/>
+        <v/>
       </c>
       <c r="B853" s="11" t="s">
         <v>14</v>
@@ -72460,6 +73192,7 @@
     <row r="854" spans="1:23" s="2" customFormat="1" ht="28.5" customHeight="1">
       <c r="A854" s="11" t="str">
         <f t="shared" si="173"/>
+        <v/>
       </c>
       <c r="B854" s="11" t="s">
         <v>14</v>
@@ -72513,15 +73246,19 @@
       </c>
       <c r="R854" s="13" t="str">
         <f t="shared" si="179"/>
+        <v/>
       </c>
       <c r="S854" s="12" t="str">
         <f t="shared" si="180"/>
+        <v/>
       </c>
       <c r="T854" s="12" t="str">
         <f t="shared" si="181"/>
+        <v/>
       </c>
       <c r="U854" s="12" t="str">
         <f t="shared" si="182"/>
+        <v/>
       </c>
       <c r="V854" s="12" t="str">
         <f t="shared" si="183"/>
@@ -72535,6 +73272,7 @@
     <row r="855" spans="1:23" s="7" customFormat="1" ht="28.5" customHeight="1">
       <c r="A855" s="11" t="str">
         <f t="shared" si="173"/>
+        <v/>
       </c>
       <c r="B855" s="11" t="s">
         <v>6</v>
@@ -72612,6 +73350,7 @@
     <row r="856" spans="1:23" s="2" customFormat="1" ht="28.5" customHeight="1">
       <c r="A856" s="11" t="str">
         <f t="shared" si="173"/>
+        <v/>
       </c>
       <c r="B856" s="11" t="s">
         <v>14</v>
@@ -72689,6 +73428,7 @@
     <row r="857" spans="1:23" s="2" customFormat="1" ht="28.5" customHeight="1">
       <c r="A857" s="11" t="str">
         <f t="shared" si="173"/>
+        <v/>
       </c>
       <c r="B857" s="11" t="s">
         <v>14</v>
@@ -72766,6 +73506,7 @@
     <row r="858" spans="1:23" s="2" customFormat="1" ht="28.5" customHeight="1">
       <c r="A858" s="11" t="str">
         <f t="shared" si="173"/>
+        <v/>
       </c>
       <c r="B858" s="11" t="s">
         <v>14</v>
@@ -72843,6 +73584,7 @@
     <row r="859" spans="1:23" s="2" customFormat="1" ht="28.5" customHeight="1">
       <c r="A859" s="11" t="str">
         <f t="shared" si="173"/>
+        <v/>
       </c>
       <c r="B859" s="11" t="s">
         <v>12</v>
@@ -72920,6 +73662,7 @@
     <row r="860" spans="1:23" s="2" customFormat="1" ht="28.5" customHeight="1">
       <c r="A860" s="11" t="str">
         <f t="shared" si="173"/>
+        <v/>
       </c>
       <c r="B860" s="11" t="s">
         <v>10</v>
@@ -72997,6 +73740,7 @@
     <row r="861" spans="1:23" s="2" customFormat="1" ht="28.5" customHeight="1">
       <c r="A861" s="11" t="str">
         <f t="shared" si="173"/>
+        <v/>
       </c>
       <c r="B861" s="11" t="s">
         <v>10</v>
@@ -73074,6 +73818,7 @@
     <row r="862" spans="1:23" s="2" customFormat="1" ht="28.5" customHeight="1">
       <c r="A862" s="11" t="str">
         <f t="shared" si="173"/>
+        <v/>
       </c>
       <c r="B862" s="11" t="s">
         <v>10</v>
@@ -73151,6 +73896,7 @@
     <row r="863" spans="1:23" s="2" customFormat="1" ht="28.5" customHeight="1">
       <c r="A863" s="11" t="str">
         <f t="shared" si="173"/>
+        <v/>
       </c>
       <c r="B863" s="11" t="s">
         <v>10</v>
@@ -73228,6 +73974,7 @@
     <row r="864" spans="1:23" s="2" customFormat="1" ht="28.5" customHeight="1">
       <c r="A864" s="11" t="str">
         <f t="shared" si="173"/>
+        <v/>
       </c>
       <c r="B864" s="11" t="s">
         <v>10</v>
@@ -73305,6 +74052,7 @@
     <row r="865" spans="1:23" s="2" customFormat="1" ht="28.5" customHeight="1">
       <c r="A865" s="11" t="str">
         <f t="shared" si="173"/>
+        <v/>
       </c>
       <c r="B865" s="11" t="s">
         <v>10</v>
@@ -73382,6 +74130,7 @@
     <row r="866" spans="1:23" s="2" customFormat="1" ht="28.5" customHeight="1">
       <c r="A866" s="11" t="str">
         <f t="shared" si="173"/>
+        <v/>
       </c>
       <c r="B866" s="11" t="s">
         <v>14</v>
@@ -73459,6 +74208,7 @@
     <row r="867" spans="1:23" s="7" customFormat="1" ht="28.5" customHeight="1">
       <c r="A867" s="11" t="str">
         <f t="shared" si="173"/>
+        <v/>
       </c>
       <c r="B867" s="11" t="s">
         <v>12</v>
@@ -73536,6 +74286,7 @@
     <row r="868" spans="1:23" s="7" customFormat="1" ht="28.5" customHeight="1">
       <c r="A868" s="11" t="str">
         <f t="shared" si="173"/>
+        <v/>
       </c>
       <c r="B868" s="11" t="s">
         <v>14</v>
@@ -73613,6 +74364,7 @@
     <row r="869" spans="1:23" s="7" customFormat="1" ht="28.5" customHeight="1">
       <c r="A869" s="11" t="str">
         <f t="shared" si="173"/>
+        <v/>
       </c>
       <c r="B869" s="11" t="s">
         <v>10</v>
@@ -73690,6 +74442,7 @@
     <row r="870" spans="1:23" s="16" customFormat="1" ht="28.5" customHeight="1">
       <c r="A870" s="11" t="str">
         <f t="shared" si="173"/>
+        <v/>
       </c>
       <c r="B870" s="11" t="s">
         <v>12</v>
@@ -73767,6 +74520,7 @@
     <row r="871" spans="1:23" s="16" customFormat="1" ht="28.5" customHeight="1">
       <c r="A871" s="11" t="str">
         <f t="shared" si="173"/>
+        <v/>
       </c>
       <c r="B871" s="11" t="s">
         <v>18</v>
@@ -73844,6 +74598,7 @@
     <row r="872" spans="1:23" s="2" customFormat="1" ht="28.5" customHeight="1">
       <c r="A872" s="11" t="str">
         <f t="shared" si="173"/>
+        <v/>
       </c>
       <c r="B872" s="11" t="s">
         <v>10</v>
@@ -73921,6 +74676,7 @@
     <row r="873" spans="1:23" s="2" customFormat="1" ht="28.5" customHeight="1">
       <c r="A873" s="11" t="str">
         <f t="shared" si="173"/>
+        <v/>
       </c>
       <c r="B873" s="11" t="s">
         <v>10</v>
@@ -73998,6 +74754,7 @@
     <row r="874" spans="1:23" s="2" customFormat="1" ht="28.5" customHeight="1">
       <c r="A874" s="11" t="str">
         <f t="shared" si="173"/>
+        <v/>
       </c>
       <c r="B874" s="11" t="s">
         <v>12</v>
@@ -74051,15 +74808,19 @@
       </c>
       <c r="R874" s="13" t="str">
         <f t="shared" si="179"/>
+        <v/>
       </c>
       <c r="S874" s="12" t="str">
         <f t="shared" si="180"/>
+        <v/>
       </c>
       <c r="T874" s="12" t="str">
         <f t="shared" si="181"/>
+        <v/>
       </c>
       <c r="U874" s="12" t="str">
         <f t="shared" si="182"/>
+        <v/>
       </c>
       <c r="V874" s="12" t="str">
         <f t="shared" si="183"/>
@@ -74073,6 +74834,7 @@
     <row r="875" spans="1:23" s="16" customFormat="1" ht="28.5" customHeight="1">
       <c r="A875" s="11" t="str">
         <f t="shared" si="173"/>
+        <v/>
       </c>
       <c r="B875" s="11" t="s">
         <v>14</v>
@@ -74150,6 +74912,7 @@
     <row r="876" spans="1:23" s="2" customFormat="1" ht="28.5" customHeight="1">
       <c r="A876" s="11" t="str">
         <f t="shared" si="173"/>
+        <v/>
       </c>
       <c r="B876" s="11" t="s">
         <v>14</v>
@@ -74227,6 +74990,7 @@
     <row r="877" spans="1:23" s="2" customFormat="1" ht="28.5" customHeight="1">
       <c r="A877" s="11" t="str">
         <f t="shared" si="173"/>
+        <v/>
       </c>
       <c r="B877" s="11" t="s">
         <v>10</v>
@@ -74280,15 +75044,19 @@
       </c>
       <c r="R877" s="13" t="str">
         <f t="shared" si="179"/>
+        <v/>
       </c>
       <c r="S877" s="12" t="str">
         <f t="shared" si="180"/>
+        <v/>
       </c>
       <c r="T877" s="12" t="str">
         <f t="shared" si="181"/>
+        <v/>
       </c>
       <c r="U877" s="12" t="str">
         <f t="shared" si="182"/>
+        <v/>
       </c>
       <c r="V877" s="12" t="str">
         <f t="shared" si="183"/>
@@ -74302,6 +75070,7 @@
     <row r="878" spans="1:23" s="2" customFormat="1" ht="28.5" customHeight="1">
       <c r="A878" s="11" t="str">
         <f t="shared" si="173"/>
+        <v/>
       </c>
       <c r="B878" s="11" t="s">
         <v>12</v>
@@ -74379,6 +75148,7 @@
     <row r="879" spans="1:23" s="16" customFormat="1" ht="28.5" customHeight="1">
       <c r="A879" s="11" t="str">
         <f t="shared" si="173"/>
+        <v/>
       </c>
       <c r="B879" s="11" t="s">
         <v>14</v>
@@ -74430,15 +75200,19 @@
       <c r="Q879" s="12"/>
       <c r="R879" s="13" t="str">
         <f t="shared" si="179"/>
+        <v/>
       </c>
       <c r="S879" s="12" t="str">
         <f t="shared" si="180"/>
+        <v/>
       </c>
       <c r="T879" s="12" t="str">
         <f t="shared" si="181"/>
+        <v/>
       </c>
       <c r="U879" s="12" t="str">
         <f t="shared" si="182"/>
+        <v/>
       </c>
       <c r="V879" s="12" t="str">
         <f t="shared" si="183"/>
@@ -74452,6 +75226,7 @@
     <row r="880" spans="1:23" s="2" customFormat="1" ht="28.5" customHeight="1">
       <c r="A880" s="11" t="str">
         <f t="shared" si="173"/>
+        <v/>
       </c>
       <c r="B880" s="11" t="s">
         <v>10</v>
@@ -74529,6 +75304,7 @@
     <row r="881" spans="1:23" s="2" customFormat="1" ht="28.5" customHeight="1">
       <c r="A881" s="11" t="str">
         <f t="shared" si="173"/>
+        <v/>
       </c>
       <c r="B881" s="11" t="s">
         <v>6</v>
@@ -74606,6 +75382,7 @@
     <row r="882" spans="1:23" s="2" customFormat="1" ht="28.5" customHeight="1">
       <c r="A882" s="11" t="str">
         <f t="shared" si="173"/>
+        <v/>
       </c>
       <c r="B882" s="11" t="s">
         <v>14</v>
@@ -74681,6 +75458,7 @@
     <row r="883" spans="1:23" s="2" customFormat="1" ht="28.5" customHeight="1">
       <c r="A883" s="11" t="str">
         <f t="shared" si="173"/>
+        <v/>
       </c>
       <c r="B883" s="11" t="s">
         <v>10</v>

--- a/fuel_cost_chungcheong.xlsx
+++ b/fuel_cost_chungcheong.xlsx
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4866" uniqueCount="1765">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4719" uniqueCount="1763">
   <si>
     <t>유류비 계산(혼유, 지역화폐 등)</t>
   </si>
@@ -5342,9 +5342,6 @@
     <t>세종 금남면 용포로 109</t>
   </si>
   <si>
-    <t>가격변동</t>
-  </si>
-  <si>
     <t>CJ대한통운㈜ 아산마루주유소</t>
   </si>
   <si>
@@ -5378,16 +5375,13 @@
     <t>충북 청주시 상당구 영운로 71 (영운동)</t>
   </si>
   <si>
-    <t>현행화 일자: 2026-10-13</t>
-  </si>
-  <si>
     <t>만수르기름창고㈜</t>
   </si>
   <si>
     <t>충남 아산시 탕정면 이순신대로 695-5</t>
   </si>
   <si>
-    <t>신규</t>
+    <t>현행화 일자: 2026-10-14</t>
   </si>
 </sst>
 </file>
@@ -8425,29 +8419,29 @@
         <v>21</v>
       </c>
       <c r="B35" s="11" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="C35" s="11" t="s">
-        <v>1722</v>
+        <v>1760</v>
       </c>
       <c r="D35" s="11" t="s">
-        <v>45</v>
+        <v>57</v>
       </c>
       <c r="E35" s="11" t="s">
         <v>26</v>
       </c>
       <c r="F35" s="11" t="s">
-        <v>1723</v>
+        <v>1761</v>
       </c>
       <c r="G35" s="12">
-        <v>1829</v>
+        <v>1799</v>
       </c>
       <c r="H35" s="12">
-        <v>2385</v>
+        <v>2415</v>
       </c>
       <c r="I35" s="12"/>
       <c r="J35" s="12">
-        <v>1815</v>
+        <v>1798</v>
       </c>
       <c r="K35" s="12">
         <f t="shared" si="1"/>
@@ -8455,23 +8449,23 @@
       </c>
       <c r="L35" s="12">
         <f t="shared" si="2"/>
-        <v>1829</v>
+        <v>1799</v>
       </c>
       <c r="M35" s="12">
         <f t="shared" si="3"/>
-        <v>2385</v>
+        <v>2415</v>
       </c>
       <c r="N35" s="12">
         <f t="shared" si="4"/>
-        <v>1815</v>
+        <v>1798</v>
       </c>
       <c r="O35" s="12" t="str">
         <f t="shared" si="5"/>
-        <v>휘발유 45,725원 / 고급유 47,700원</v>
+        <v>휘발유 44,975원 / 고급유 48,300원</v>
       </c>
       <c r="P35" s="12">
         <f t="shared" si="6"/>
-        <v>93425</v>
+        <v>93275</v>
       </c>
       <c r="Q35" s="12" t="s">
         <v>61</v>
@@ -8482,23 +8476,23 @@
       </c>
       <c r="S35" s="12">
         <f t="shared" si="8"/>
-        <v>9342</v>
+        <v>9327</v>
       </c>
       <c r="T35" s="12">
         <f t="shared" si="9"/>
-        <v>84083</v>
+        <v>83948</v>
       </c>
       <c r="U35" s="12">
         <f t="shared" si="10"/>
-        <v>1868.5111111111112</v>
+        <v>1865.5111111111112</v>
       </c>
       <c r="V35" s="12">
         <f t="shared" si="11"/>
-        <v>2076.1111111111113</v>
+        <v>2072.7777777777778</v>
       </c>
       <c r="W35" s="14">
         <f t="shared" si="12"/>
-        <v>84083</v>
+        <v>83948</v>
       </c>
     </row>
     <row r="36" spans="1:23" s="2" customFormat="1" ht="28.5" customHeight="1">
@@ -8507,10 +8501,10 @@
         <v>22</v>
       </c>
       <c r="B36" s="11" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="C36" s="11" t="s">
-        <v>1738</v>
+        <v>1722</v>
       </c>
       <c r="D36" s="11" t="s">
         <v>45</v>
@@ -8519,17 +8513,17 @@
         <v>26</v>
       </c>
       <c r="F36" s="11" t="s">
-        <v>1739</v>
+        <v>1723</v>
       </c>
       <c r="G36" s="12">
-        <v>1804</v>
+        <v>1829</v>
       </c>
       <c r="H36" s="12">
-        <v>2419</v>
+        <v>2385</v>
       </c>
       <c r="I36" s="12"/>
       <c r="J36" s="12">
-        <v>1792</v>
+        <v>1815</v>
       </c>
       <c r="K36" s="12">
         <f t="shared" si="1"/>
@@ -8537,23 +8531,23 @@
       </c>
       <c r="L36" s="12">
         <f t="shared" si="2"/>
-        <v>1804</v>
+        <v>1829</v>
       </c>
       <c r="M36" s="12">
         <f t="shared" si="3"/>
-        <v>2419</v>
+        <v>2385</v>
       </c>
       <c r="N36" s="12">
         <f t="shared" si="4"/>
-        <v>1792</v>
+        <v>1815</v>
       </c>
       <c r="O36" s="12" t="str">
         <f t="shared" si="5"/>
-        <v>휘발유 45,100원 / 고급유 48,380원</v>
+        <v>휘발유 45,725원 / 고급유 47,700원</v>
       </c>
       <c r="P36" s="12">
         <f t="shared" si="6"/>
-        <v>93480</v>
+        <v>93425</v>
       </c>
       <c r="Q36" s="12" t="s">
         <v>61</v>
@@ -8564,23 +8558,23 @@
       </c>
       <c r="S36" s="12">
         <f t="shared" si="8"/>
-        <v>9348</v>
+        <v>9342</v>
       </c>
       <c r="T36" s="12">
         <f t="shared" si="9"/>
-        <v>84132</v>
+        <v>84083</v>
       </c>
       <c r="U36" s="12">
         <f t="shared" si="10"/>
-        <v>1869.6</v>
+        <v>1868.5111111111112</v>
       </c>
       <c r="V36" s="12">
         <f t="shared" si="11"/>
-        <v>2077.3333333333335</v>
+        <v>2076.1111111111113</v>
       </c>
       <c r="W36" s="14">
         <f t="shared" si="12"/>
-        <v>84132</v>
+        <v>84083</v>
       </c>
     </row>
     <row r="37" spans="1:23" s="2" customFormat="1" ht="28.5" customHeight="1">
@@ -8592,26 +8586,26 @@
         <v>6</v>
       </c>
       <c r="C37" s="11" t="s">
-        <v>994</v>
-      </c>
-      <c r="D37" s="15" t="s">
-        <v>78</v>
+        <v>1738</v>
+      </c>
+      <c r="D37" s="11" t="s">
+        <v>45</v>
       </c>
       <c r="E37" s="11" t="s">
         <v>26</v>
       </c>
       <c r="F37" s="11" t="s">
-        <v>995</v>
+        <v>1739</v>
       </c>
       <c r="G37" s="12">
-        <v>1826</v>
+        <v>1804</v>
       </c>
       <c r="H37" s="12">
-        <v>2392</v>
+        <v>2419</v>
       </c>
       <c r="I37" s="12"/>
       <c r="J37" s="12">
-        <v>1818</v>
+        <v>1792</v>
       </c>
       <c r="K37" s="12">
         <f t="shared" si="1"/>
@@ -8619,23 +8613,23 @@
       </c>
       <c r="L37" s="12">
         <f t="shared" si="2"/>
-        <v>1826</v>
+        <v>1804</v>
       </c>
       <c r="M37" s="12">
         <f t="shared" si="3"/>
-        <v>2392</v>
+        <v>2419</v>
       </c>
       <c r="N37" s="12">
         <f t="shared" si="4"/>
-        <v>1818</v>
+        <v>1792</v>
       </c>
       <c r="O37" s="12" t="str">
         <f t="shared" si="5"/>
-        <v>휘발유 45,650원 / 고급유 47,840원</v>
+        <v>휘발유 45,100원 / 고급유 48,380원</v>
       </c>
       <c r="P37" s="12">
         <f t="shared" si="6"/>
-        <v>93490</v>
+        <v>93480</v>
       </c>
       <c r="Q37" s="12" t="s">
         <v>61</v>
@@ -8646,23 +8640,23 @@
       </c>
       <c r="S37" s="12">
         <f t="shared" si="8"/>
-        <v>9349</v>
+        <v>9348</v>
       </c>
       <c r="T37" s="12">
         <f t="shared" si="9"/>
-        <v>84141</v>
+        <v>84132</v>
       </c>
       <c r="U37" s="12">
         <f t="shared" si="10"/>
-        <v>1869.8</v>
+        <v>1869.6</v>
       </c>
       <c r="V37" s="12">
         <f t="shared" si="11"/>
-        <v>2077.5555555555557</v>
+        <v>2077.3333333333335</v>
       </c>
       <c r="W37" s="14">
         <f t="shared" si="12"/>
-        <v>84141</v>
+        <v>84132</v>
       </c>
     </row>
     <row r="38" spans="1:23" s="2" customFormat="1" ht="28.5" customHeight="1">
@@ -8674,26 +8668,26 @@
         <v>6</v>
       </c>
       <c r="C38" s="11" t="s">
-        <v>1441</v>
+        <v>994</v>
       </c>
       <c r="D38" s="15" t="s">
-        <v>59</v>
+        <v>78</v>
       </c>
       <c r="E38" s="11" t="s">
         <v>26</v>
       </c>
       <c r="F38" s="11" t="s">
-        <v>1442</v>
+        <v>995</v>
       </c>
       <c r="G38" s="12">
-        <v>1824</v>
+        <v>1826</v>
       </c>
       <c r="H38" s="12">
-        <v>2397</v>
+        <v>2392</v>
       </c>
       <c r="I38" s="12"/>
       <c r="J38" s="12">
-        <v>1833</v>
+        <v>1818</v>
       </c>
       <c r="K38" s="12">
         <f t="shared" si="1"/>
@@ -8701,23 +8695,23 @@
       </c>
       <c r="L38" s="12">
         <f t="shared" si="2"/>
-        <v>1824</v>
+        <v>1826</v>
       </c>
       <c r="M38" s="12">
         <f t="shared" si="3"/>
-        <v>2397</v>
+        <v>2392</v>
       </c>
       <c r="N38" s="12">
         <f t="shared" si="4"/>
-        <v>1833</v>
+        <v>1818</v>
       </c>
       <c r="O38" s="12" t="str">
         <f t="shared" si="5"/>
-        <v>휘발유 45,600원 / 고급유 47,940원</v>
+        <v>휘발유 45,650원 / 고급유 47,840원</v>
       </c>
       <c r="P38" s="12">
         <f t="shared" si="6"/>
-        <v>93540</v>
+        <v>93490</v>
       </c>
       <c r="Q38" s="12" t="s">
         <v>61</v>
@@ -8728,23 +8722,23 @@
       </c>
       <c r="S38" s="12">
         <f t="shared" si="8"/>
-        <v>9354</v>
+        <v>9349</v>
       </c>
       <c r="T38" s="12">
         <f t="shared" si="9"/>
-        <v>84186</v>
+        <v>84141</v>
       </c>
       <c r="U38" s="12">
         <f t="shared" si="10"/>
-        <v>1870.8</v>
+        <v>1869.8</v>
       </c>
       <c r="V38" s="12">
         <f t="shared" si="11"/>
-        <v>2078.6666666666665</v>
+        <v>2077.5555555555557</v>
       </c>
       <c r="W38" s="14">
         <f t="shared" si="12"/>
-        <v>84186</v>
+        <v>84141</v>
       </c>
     </row>
     <row r="39" spans="1:23" s="2" customFormat="1" ht="28.5" customHeight="1">
@@ -8756,7 +8750,7 @@
         <v>6</v>
       </c>
       <c r="C39" s="11" t="s">
-        <v>1341</v>
+        <v>1441</v>
       </c>
       <c r="D39" s="15" t="s">
         <v>59</v>
@@ -8765,17 +8759,17 @@
         <v>26</v>
       </c>
       <c r="F39" s="11" t="s">
-        <v>1342</v>
+        <v>1442</v>
       </c>
       <c r="G39" s="12">
-        <v>1829</v>
+        <v>1824</v>
       </c>
       <c r="H39" s="12">
-        <v>2395</v>
+        <v>2397</v>
       </c>
       <c r="I39" s="12"/>
       <c r="J39" s="12">
-        <v>1814</v>
+        <v>1833</v>
       </c>
       <c r="K39" s="12">
         <f t="shared" si="1"/>
@@ -8783,23 +8777,23 @@
       </c>
       <c r="L39" s="12">
         <f t="shared" si="2"/>
-        <v>1829</v>
+        <v>1824</v>
       </c>
       <c r="M39" s="12">
         <f t="shared" si="3"/>
-        <v>2395</v>
+        <v>2397</v>
       </c>
       <c r="N39" s="12">
         <f t="shared" si="4"/>
-        <v>1814</v>
+        <v>1833</v>
       </c>
       <c r="O39" s="12" t="str">
         <f t="shared" si="5"/>
-        <v>휘발유 45,725원 / 고급유 47,900원</v>
+        <v>휘발유 45,600원 / 고급유 47,940원</v>
       </c>
       <c r="P39" s="12">
         <f t="shared" si="6"/>
-        <v>93625</v>
+        <v>93540</v>
       </c>
       <c r="Q39" s="12" t="s">
         <v>61</v>
@@ -8810,35 +8804,35 @@
       </c>
       <c r="S39" s="12">
         <f t="shared" si="8"/>
-        <v>9362</v>
+        <v>9354</v>
       </c>
       <c r="T39" s="12">
         <f t="shared" si="9"/>
-        <v>84263</v>
+        <v>84186</v>
       </c>
       <c r="U39" s="12">
         <f t="shared" si="10"/>
-        <v>1872.5111111111112</v>
+        <v>1870.8</v>
       </c>
       <c r="V39" s="12">
         <f t="shared" si="11"/>
-        <v>2080.5555555555557</v>
+        <v>2078.6666666666665</v>
       </c>
       <c r="W39" s="14">
         <f t="shared" si="12"/>
-        <v>84263</v>
-      </c>
-    </row>
-    <row r="40" spans="1:23" s="7" customFormat="1" ht="28.5" customHeight="1">
+        <v>84186</v>
+      </c>
+    </row>
+    <row r="40" spans="1:23" s="2" customFormat="1" ht="28.5" customHeight="1">
       <c r="A40" s="11">
         <f t="shared" si="0"/>
         <v>26</v>
       </c>
       <c r="B40" s="11" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="C40" s="11" t="s">
-        <v>1067</v>
+        <v>1341</v>
       </c>
       <c r="D40" s="15" t="s">
         <v>59</v>
@@ -8847,17 +8841,17 @@
         <v>26</v>
       </c>
       <c r="F40" s="11" t="s">
-        <v>1068</v>
+        <v>1342</v>
       </c>
       <c r="G40" s="12">
-        <v>1847</v>
+        <v>1829</v>
       </c>
       <c r="H40" s="12">
         <v>2395</v>
       </c>
       <c r="I40" s="12"/>
       <c r="J40" s="12">
-        <v>1847</v>
+        <v>1814</v>
       </c>
       <c r="K40" s="12">
         <f t="shared" si="1"/>
@@ -8865,7 +8859,7 @@
       </c>
       <c r="L40" s="12">
         <f t="shared" si="2"/>
-        <v>1847</v>
+        <v>1829</v>
       </c>
       <c r="M40" s="12">
         <f t="shared" si="3"/>
@@ -8873,15 +8867,15 @@
       </c>
       <c r="N40" s="12">
         <f t="shared" si="4"/>
-        <v>1847</v>
+        <v>1814</v>
       </c>
       <c r="O40" s="12" t="str">
         <f t="shared" si="5"/>
-        <v>휘발유 46,175원 / 고급유 47,900원</v>
+        <v>휘발유 45,725원 / 고급유 47,900원</v>
       </c>
       <c r="P40" s="12">
         <f t="shared" si="6"/>
-        <v>94075</v>
+        <v>93625</v>
       </c>
       <c r="Q40" s="12" t="s">
         <v>61</v>
@@ -8892,26 +8886,26 @@
       </c>
       <c r="S40" s="12">
         <f t="shared" si="8"/>
-        <v>9407</v>
+        <v>9362</v>
       </c>
       <c r="T40" s="12">
         <f t="shared" si="9"/>
-        <v>84668</v>
+        <v>84263</v>
       </c>
       <c r="U40" s="12">
         <f t="shared" si="10"/>
-        <v>1881.5111111111112</v>
+        <v>1872.5111111111112</v>
       </c>
       <c r="V40" s="12">
         <f t="shared" si="11"/>
-        <v>2090.5555555555557</v>
+        <v>2080.5555555555557</v>
       </c>
       <c r="W40" s="14">
         <f t="shared" si="12"/>
-        <v>84668</v>
-      </c>
-    </row>
-    <row r="41" spans="1:23" s="2" customFormat="1" ht="28.5" customHeight="1">
+        <v>84263</v>
+      </c>
+    </row>
+    <row r="41" spans="1:23" s="7" customFormat="1" ht="28.5" customHeight="1">
       <c r="A41" s="11">
         <f t="shared" si="0"/>
         <v>27</v>
@@ -8920,26 +8914,26 @@
         <v>10</v>
       </c>
       <c r="C41" s="11" t="s">
-        <v>875</v>
+        <v>1067</v>
       </c>
       <c r="D41" s="15" t="s">
-        <v>45</v>
+        <v>59</v>
       </c>
       <c r="E41" s="11" t="s">
         <v>26</v>
       </c>
       <c r="F41" s="11" t="s">
-        <v>876</v>
+        <v>1068</v>
       </c>
       <c r="G41" s="12">
-        <v>1830</v>
+        <v>1847</v>
       </c>
       <c r="H41" s="12">
-        <v>2419</v>
+        <v>2395</v>
       </c>
       <c r="I41" s="12"/>
       <c r="J41" s="12">
-        <v>1810</v>
+        <v>1847</v>
       </c>
       <c r="K41" s="12">
         <f t="shared" si="1"/>
@@ -8947,23 +8941,23 @@
       </c>
       <c r="L41" s="12">
         <f t="shared" si="2"/>
-        <v>1830</v>
+        <v>1847</v>
       </c>
       <c r="M41" s="12">
         <f t="shared" si="3"/>
-        <v>2419</v>
+        <v>2395</v>
       </c>
       <c r="N41" s="12">
         <f t="shared" si="4"/>
-        <v>1810</v>
+        <v>1847</v>
       </c>
       <c r="O41" s="12" t="str">
         <f t="shared" si="5"/>
-        <v>휘발유 45,750원 / 고급유 48,380원</v>
+        <v>휘발유 46,175원 / 고급유 47,900원</v>
       </c>
       <c r="P41" s="12">
         <f t="shared" si="6"/>
-        <v>94130</v>
+        <v>94075</v>
       </c>
       <c r="Q41" s="12" t="s">
         <v>61</v>
@@ -8974,35 +8968,35 @@
       </c>
       <c r="S41" s="12">
         <f t="shared" si="8"/>
-        <v>9413</v>
+        <v>9407</v>
       </c>
       <c r="T41" s="12">
         <f t="shared" si="9"/>
-        <v>84717</v>
+        <v>84668</v>
       </c>
       <c r="U41" s="12">
         <f t="shared" si="10"/>
-        <v>1882.6</v>
+        <v>1881.5111111111112</v>
       </c>
       <c r="V41" s="12">
         <f t="shared" si="11"/>
-        <v>2091.7777777777778</v>
+        <v>2090.5555555555557</v>
       </c>
       <c r="W41" s="14">
         <f t="shared" si="12"/>
-        <v>84717</v>
-      </c>
-    </row>
-    <row r="42" spans="1:23" s="7" customFormat="1" ht="28.5" customHeight="1">
+        <v>84668</v>
+      </c>
+    </row>
+    <row r="42" spans="1:23" s="2" customFormat="1" ht="28.5" customHeight="1">
       <c r="A42" s="11">
         <f t="shared" si="0"/>
         <v>28</v>
       </c>
       <c r="B42" s="11" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="C42" s="11" t="s">
-        <v>449</v>
+        <v>875</v>
       </c>
       <c r="D42" s="15" t="s">
         <v>45</v>
@@ -9011,17 +9005,17 @@
         <v>26</v>
       </c>
       <c r="F42" s="11" t="s">
-        <v>450</v>
+        <v>876</v>
       </c>
       <c r="G42" s="12">
-        <v>1853</v>
+        <v>1830</v>
       </c>
       <c r="H42" s="12">
-        <v>2395</v>
+        <v>2419</v>
       </c>
       <c r="I42" s="12"/>
       <c r="J42" s="12">
-        <v>1823</v>
+        <v>1810</v>
       </c>
       <c r="K42" s="12">
         <f t="shared" si="1"/>
@@ -9029,23 +9023,23 @@
       </c>
       <c r="L42" s="12">
         <f t="shared" si="2"/>
-        <v>1853</v>
+        <v>1830</v>
       </c>
       <c r="M42" s="12">
         <f t="shared" si="3"/>
-        <v>2395</v>
+        <v>2419</v>
       </c>
       <c r="N42" s="12">
         <f t="shared" si="4"/>
-        <v>1823</v>
+        <v>1810</v>
       </c>
       <c r="O42" s="12" t="str">
         <f t="shared" si="5"/>
-        <v>휘발유 46,325원 / 고급유 47,900원</v>
+        <v>휘발유 45,750원 / 고급유 48,380원</v>
       </c>
       <c r="P42" s="12">
         <f t="shared" si="6"/>
-        <v>94225</v>
+        <v>94130</v>
       </c>
       <c r="Q42" s="12" t="s">
         <v>61</v>
@@ -9056,54 +9050,54 @@
       </c>
       <c r="S42" s="12">
         <f t="shared" si="8"/>
-        <v>9422</v>
+        <v>9413</v>
       </c>
       <c r="T42" s="12">
         <f t="shared" si="9"/>
-        <v>84803</v>
+        <v>84717</v>
       </c>
       <c r="U42" s="12">
         <f t="shared" si="10"/>
-        <v>1884.5111111111112</v>
+        <v>1882.6</v>
       </c>
       <c r="V42" s="12">
         <f t="shared" si="11"/>
-        <v>2093.8888888888887</v>
+        <v>2091.7777777777778</v>
       </c>
       <c r="W42" s="14">
         <f t="shared" si="12"/>
-        <v>84803</v>
-      </c>
-    </row>
-    <row r="43" spans="1:23" s="16" customFormat="1" ht="28.5" customHeight="1">
+        <v>84717</v>
+      </c>
+    </row>
+    <row r="43" spans="1:23" s="7" customFormat="1" ht="28.5" customHeight="1">
       <c r="A43" s="11">
         <f t="shared" si="0"/>
         <v>29</v>
       </c>
       <c r="B43" s="11" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="C43" s="11" t="s">
-        <v>654</v>
+        <v>449</v>
       </c>
       <c r="D43" s="15" t="s">
-        <v>78</v>
+        <v>45</v>
       </c>
       <c r="E43" s="11" t="s">
         <v>26</v>
       </c>
       <c r="F43" s="11" t="s">
-        <v>655</v>
+        <v>450</v>
       </c>
       <c r="G43" s="12">
-        <v>1862</v>
+        <v>1853</v>
       </c>
       <c r="H43" s="12">
         <v>2395</v>
       </c>
       <c r="I43" s="12"/>
       <c r="J43" s="12">
-        <v>1812</v>
+        <v>1823</v>
       </c>
       <c r="K43" s="12">
         <f t="shared" si="1"/>
@@ -9111,7 +9105,7 @@
       </c>
       <c r="L43" s="12">
         <f t="shared" si="2"/>
-        <v>1862</v>
+        <v>1853</v>
       </c>
       <c r="M43" s="12">
         <f t="shared" si="3"/>
@@ -9119,15 +9113,15 @@
       </c>
       <c r="N43" s="12">
         <f t="shared" si="4"/>
-        <v>1812</v>
+        <v>1823</v>
       </c>
       <c r="O43" s="12" t="str">
         <f t="shared" si="5"/>
-        <v>휘발유 46,550원 / 고급유 47,900원</v>
+        <v>휘발유 46,325원 / 고급유 47,900원</v>
       </c>
       <c r="P43" s="12">
         <f t="shared" si="6"/>
-        <v>94450</v>
+        <v>94225</v>
       </c>
       <c r="Q43" s="12" t="s">
         <v>61</v>
@@ -9138,35 +9132,35 @@
       </c>
       <c r="S43" s="12">
         <f t="shared" si="8"/>
-        <v>9445</v>
+        <v>9422</v>
       </c>
       <c r="T43" s="12">
         <f t="shared" si="9"/>
-        <v>85005</v>
+        <v>84803</v>
       </c>
       <c r="U43" s="12">
         <f t="shared" si="10"/>
-        <v>1889</v>
+        <v>1884.5111111111112</v>
       </c>
       <c r="V43" s="12">
         <f t="shared" si="11"/>
-        <v>2098.8888888888887</v>
+        <v>2093.8888888888887</v>
       </c>
       <c r="W43" s="14">
         <f t="shared" si="12"/>
-        <v>85005</v>
-      </c>
-    </row>
-    <row r="44" spans="1:23" s="7" customFormat="1" ht="28.5" customHeight="1">
+        <v>84803</v>
+      </c>
+    </row>
+    <row r="44" spans="1:23" s="16" customFormat="1" ht="28.5" customHeight="1">
       <c r="A44" s="11">
         <f t="shared" si="0"/>
         <v>30</v>
       </c>
       <c r="B44" s="11" t="s">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="C44" s="11" t="s">
-        <v>1277</v>
+        <v>654</v>
       </c>
       <c r="D44" s="15" t="s">
         <v>78</v>
@@ -9175,17 +9169,17 @@
         <v>26</v>
       </c>
       <c r="F44" s="11" t="s">
-        <v>1278</v>
+        <v>655</v>
       </c>
       <c r="G44" s="12">
-        <v>1819</v>
+        <v>1862</v>
       </c>
       <c r="H44" s="12">
-        <v>2459</v>
+        <v>2395</v>
       </c>
       <c r="I44" s="12"/>
       <c r="J44" s="12">
-        <v>1849</v>
+        <v>1812</v>
       </c>
       <c r="K44" s="12">
         <f t="shared" si="1"/>
@@ -9193,23 +9187,23 @@
       </c>
       <c r="L44" s="12">
         <f t="shared" si="2"/>
-        <v>1819</v>
+        <v>1862</v>
       </c>
       <c r="M44" s="12">
         <f t="shared" si="3"/>
-        <v>2459</v>
+        <v>2395</v>
       </c>
       <c r="N44" s="12">
         <f t="shared" si="4"/>
-        <v>1849</v>
+        <v>1812</v>
       </c>
       <c r="O44" s="12" t="str">
         <f t="shared" si="5"/>
-        <v>휘발유 45,475원 / 고급유 49,180원</v>
+        <v>휘발유 46,550원 / 고급유 47,900원</v>
       </c>
       <c r="P44" s="12">
         <f t="shared" si="6"/>
-        <v>94655</v>
+        <v>94450</v>
       </c>
       <c r="Q44" s="12" t="s">
         <v>61</v>
@@ -9220,54 +9214,54 @@
       </c>
       <c r="S44" s="12">
         <f t="shared" si="8"/>
-        <v>9465</v>
+        <v>9445</v>
       </c>
       <c r="T44" s="12">
         <f t="shared" si="9"/>
-        <v>85190</v>
+        <v>85005</v>
       </c>
       <c r="U44" s="12">
         <f t="shared" si="10"/>
-        <v>1893.1111111111111</v>
+        <v>1889</v>
       </c>
       <c r="V44" s="12">
         <f t="shared" si="11"/>
-        <v>2103.4444444444443</v>
+        <v>2098.8888888888887</v>
       </c>
       <c r="W44" s="14">
         <f t="shared" si="12"/>
-        <v>85190</v>
-      </c>
-    </row>
-    <row r="45" spans="1:23" s="16" customFormat="1" ht="28.5" customHeight="1">
+        <v>85005</v>
+      </c>
+    </row>
+    <row r="45" spans="1:23" s="7" customFormat="1" ht="28.5" customHeight="1">
       <c r="A45" s="11">
         <f t="shared" si="0"/>
         <v>31</v>
       </c>
       <c r="B45" s="11" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="C45" s="11" t="s">
-        <v>1594</v>
+        <v>1277</v>
       </c>
       <c r="D45" s="15" t="s">
-        <v>59</v>
+        <v>78</v>
       </c>
       <c r="E45" s="11" t="s">
         <v>26</v>
       </c>
       <c r="F45" s="11" t="s">
-        <v>1595</v>
+        <v>1278</v>
       </c>
       <c r="G45" s="12">
-        <v>1879</v>
+        <v>1819</v>
       </c>
       <c r="H45" s="12">
-        <v>2390</v>
+        <v>2459</v>
       </c>
       <c r="I45" s="12"/>
       <c r="J45" s="12">
-        <v>1879</v>
+        <v>1849</v>
       </c>
       <c r="K45" s="12">
         <f t="shared" si="1"/>
@@ -9275,23 +9269,23 @@
       </c>
       <c r="L45" s="12">
         <f t="shared" si="2"/>
-        <v>1879</v>
+        <v>1819</v>
       </c>
       <c r="M45" s="12">
         <f t="shared" si="3"/>
-        <v>2390</v>
+        <v>2459</v>
       </c>
       <c r="N45" s="12">
         <f t="shared" si="4"/>
-        <v>1879</v>
+        <v>1849</v>
       </c>
       <c r="O45" s="12" t="str">
         <f t="shared" si="5"/>
-        <v>휘발유 46,975원 / 고급유 47,800원</v>
+        <v>휘발유 45,475원 / 고급유 49,180원</v>
       </c>
       <c r="P45" s="12">
         <f t="shared" si="6"/>
-        <v>94775</v>
+        <v>94655</v>
       </c>
       <c r="Q45" s="12" t="s">
         <v>61</v>
@@ -9302,23 +9296,23 @@
       </c>
       <c r="S45" s="12">
         <f t="shared" si="8"/>
-        <v>9477</v>
+        <v>9465</v>
       </c>
       <c r="T45" s="12">
         <f t="shared" si="9"/>
-        <v>85298</v>
+        <v>85190</v>
       </c>
       <c r="U45" s="12">
         <f t="shared" si="10"/>
-        <v>1895.5111111111112</v>
+        <v>1893.1111111111111</v>
       </c>
       <c r="V45" s="12">
         <f t="shared" si="11"/>
-        <v>2106.1111111111113</v>
+        <v>2103.4444444444443</v>
       </c>
       <c r="W45" s="14">
         <f t="shared" si="12"/>
-        <v>85298</v>
+        <v>85190</v>
       </c>
     </row>
     <row r="46" spans="1:23" s="16" customFormat="1" ht="28.5" customHeight="1">
@@ -9327,10 +9321,10 @@
         <v>32</v>
       </c>
       <c r="B46" s="11" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="C46" s="11" t="s">
-        <v>1000</v>
+        <v>1594</v>
       </c>
       <c r="D46" s="15" t="s">
         <v>59</v>
@@ -9339,17 +9333,17 @@
         <v>26</v>
       </c>
       <c r="F46" s="11" t="s">
-        <v>1001</v>
+        <v>1595</v>
       </c>
       <c r="G46" s="12">
-        <v>1895</v>
+        <v>1879</v>
       </c>
       <c r="H46" s="12">
-        <v>2495</v>
+        <v>2390</v>
       </c>
       <c r="I46" s="12"/>
       <c r="J46" s="12">
-        <v>1885</v>
+        <v>1879</v>
       </c>
       <c r="K46" s="12">
         <f t="shared" si="1"/>
@@ -9357,62 +9351,62 @@
       </c>
       <c r="L46" s="12">
         <f t="shared" si="2"/>
-        <v>1895</v>
+        <v>1879</v>
       </c>
       <c r="M46" s="12">
         <f t="shared" si="3"/>
-        <v>2495</v>
+        <v>2390</v>
       </c>
       <c r="N46" s="12">
         <f t="shared" si="4"/>
-        <v>1885</v>
+        <v>1879</v>
       </c>
       <c r="O46" s="12" t="str">
         <f t="shared" si="5"/>
-        <v>휘발유 47,375원 / 고급유 49,900원</v>
+        <v>휘발유 46,975원 / 고급유 47,800원</v>
       </c>
       <c r="P46" s="12">
         <f t="shared" si="6"/>
-        <v>97275</v>
+        <v>94775</v>
       </c>
       <c r="Q46" s="12" t="s">
         <v>61</v>
       </c>
       <c r="R46" s="13">
         <f t="shared" si="7"/>
-        <v>0.12</v>
+        <v>0.1</v>
       </c>
       <c r="S46" s="12">
         <f t="shared" si="8"/>
-        <v>11673</v>
+        <v>9477</v>
       </c>
       <c r="T46" s="12">
         <f t="shared" si="9"/>
-        <v>85602</v>
+        <v>85298</v>
       </c>
       <c r="U46" s="12">
         <f t="shared" si="10"/>
-        <v>1902.2666666666667</v>
+        <v>1895.5111111111112</v>
       </c>
       <c r="V46" s="12">
         <f t="shared" si="11"/>
-        <v>2161.6666666666665</v>
+        <v>2106.1111111111113</v>
       </c>
       <c r="W46" s="14">
         <f t="shared" si="12"/>
-        <v>85602</v>
-      </c>
-    </row>
-    <row r="47" spans="1:23" s="2" customFormat="1" ht="28.5" customHeight="1">
+        <v>85298</v>
+      </c>
+    </row>
+    <row r="47" spans="1:23" s="16" customFormat="1" ht="28.5" customHeight="1">
       <c r="A47" s="11">
         <f t="shared" si="0"/>
         <v>33</v>
       </c>
       <c r="B47" s="11" t="s">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="C47" s="11" t="s">
-        <v>1453</v>
+        <v>1000</v>
       </c>
       <c r="D47" s="15" t="s">
         <v>59</v>
@@ -9421,17 +9415,17 @@
         <v>26</v>
       </c>
       <c r="F47" s="11" t="s">
-        <v>1454</v>
+        <v>1001</v>
       </c>
       <c r="G47" s="12">
-        <v>1898</v>
+        <v>1895</v>
       </c>
       <c r="H47" s="12">
-        <v>2388</v>
+        <v>2495</v>
       </c>
       <c r="I47" s="12"/>
       <c r="J47" s="12">
-        <v>1888</v>
+        <v>1885</v>
       </c>
       <c r="K47" s="12">
         <f t="shared" si="1"/>
@@ -9439,50 +9433,50 @@
       </c>
       <c r="L47" s="12">
         <f t="shared" si="2"/>
-        <v>1898</v>
+        <v>1895</v>
       </c>
       <c r="M47" s="12">
         <f t="shared" si="3"/>
-        <v>2388</v>
+        <v>2495</v>
       </c>
       <c r="N47" s="12">
         <f t="shared" si="4"/>
-        <v>1888</v>
+        <v>1885</v>
       </c>
       <c r="O47" s="12" t="str">
         <f t="shared" si="5"/>
-        <v>휘발유 47,450원 / 고급유 47,760원</v>
+        <v>휘발유 47,375원 / 고급유 49,900원</v>
       </c>
       <c r="P47" s="12">
         <f t="shared" si="6"/>
-        <v>95210</v>
+        <v>97275</v>
       </c>
       <c r="Q47" s="12" t="s">
         <v>61</v>
       </c>
       <c r="R47" s="13">
         <f t="shared" si="7"/>
-        <v>0.1</v>
+        <v>0.12</v>
       </c>
       <c r="S47" s="12">
         <f t="shared" si="8"/>
-        <v>9521</v>
+        <v>11673</v>
       </c>
       <c r="T47" s="12">
         <f t="shared" si="9"/>
-        <v>85689</v>
+        <v>85602</v>
       </c>
       <c r="U47" s="12">
         <f t="shared" si="10"/>
-        <v>1904.2</v>
+        <v>1902.2666666666667</v>
       </c>
       <c r="V47" s="12">
         <f t="shared" si="11"/>
-        <v>2115.7777777777778</v>
+        <v>2161.6666666666665</v>
       </c>
       <c r="W47" s="14">
         <f t="shared" si="12"/>
-        <v>85689</v>
+        <v>85602</v>
       </c>
     </row>
     <row r="48" spans="1:23" s="2" customFormat="1" ht="28.5" customHeight="1">
@@ -9491,29 +9485,29 @@
         <v>34</v>
       </c>
       <c r="B48" s="11" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="C48" s="11" t="s">
-        <v>985</v>
+        <v>1453</v>
       </c>
       <c r="D48" s="15" t="s">
-        <v>45</v>
+        <v>59</v>
       </c>
       <c r="E48" s="11" t="s">
         <v>26</v>
       </c>
       <c r="F48" s="11" t="s">
-        <v>986</v>
+        <v>1454</v>
       </c>
       <c r="G48" s="12">
-        <v>1879</v>
+        <v>1898</v>
       </c>
       <c r="H48" s="12">
-        <v>2415</v>
+        <v>2388</v>
       </c>
       <c r="I48" s="12"/>
       <c r="J48" s="12">
-        <v>1865</v>
+        <v>1888</v>
       </c>
       <c r="K48" s="12">
         <f t="shared" si="1"/>
@@ -9521,23 +9515,23 @@
       </c>
       <c r="L48" s="12">
         <f t="shared" si="2"/>
-        <v>1879</v>
+        <v>1898</v>
       </c>
       <c r="M48" s="12">
         <f t="shared" si="3"/>
-        <v>2415</v>
+        <v>2388</v>
       </c>
       <c r="N48" s="12">
         <f t="shared" si="4"/>
-        <v>1865</v>
+        <v>1888</v>
       </c>
       <c r="O48" s="12" t="str">
         <f t="shared" si="5"/>
-        <v>휘발유 46,975원 / 고급유 48,300원</v>
+        <v>휘발유 47,450원 / 고급유 47,760원</v>
       </c>
       <c r="P48" s="12">
         <f t="shared" si="6"/>
-        <v>95275</v>
+        <v>95210</v>
       </c>
       <c r="Q48" s="12" t="s">
         <v>61</v>
@@ -9548,54 +9542,54 @@
       </c>
       <c r="S48" s="12">
         <f t="shared" si="8"/>
-        <v>9527</v>
+        <v>9521</v>
       </c>
       <c r="T48" s="12">
         <f t="shared" si="9"/>
-        <v>85748</v>
+        <v>85689</v>
       </c>
       <c r="U48" s="12">
         <f t="shared" si="10"/>
-        <v>1905.5111111111112</v>
+        <v>1904.2</v>
       </c>
       <c r="V48" s="12">
         <f t="shared" si="11"/>
-        <v>2117.2222222222222</v>
+        <v>2115.7777777777778</v>
       </c>
       <c r="W48" s="14">
         <f t="shared" si="12"/>
-        <v>85748</v>
-      </c>
-    </row>
-    <row r="49" spans="1:23" s="7" customFormat="1" ht="28.5" customHeight="1">
+        <v>85689</v>
+      </c>
+    </row>
+    <row r="49" spans="1:23" s="2" customFormat="1" ht="28.5" customHeight="1">
       <c r="A49" s="11">
         <f t="shared" si="0"/>
         <v>35</v>
       </c>
       <c r="B49" s="11" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="C49" s="11" t="s">
-        <v>1374</v>
+        <v>985</v>
       </c>
       <c r="D49" s="15" t="s">
-        <v>59</v>
+        <v>45</v>
       </c>
       <c r="E49" s="11" t="s">
-        <v>60</v>
+        <v>26</v>
       </c>
       <c r="F49" s="11" t="s">
-        <v>1375</v>
+        <v>986</v>
       </c>
       <c r="G49" s="12">
-        <v>1898</v>
+        <v>1879</v>
       </c>
       <c r="H49" s="12">
-        <v>2398</v>
+        <v>2415</v>
       </c>
       <c r="I49" s="12"/>
       <c r="J49" s="12">
-        <v>1878</v>
+        <v>1865</v>
       </c>
       <c r="K49" s="12">
         <f t="shared" si="1"/>
@@ -9603,23 +9597,23 @@
       </c>
       <c r="L49" s="12">
         <f t="shared" si="2"/>
-        <v>1898</v>
+        <v>1879</v>
       </c>
       <c r="M49" s="12">
         <f t="shared" si="3"/>
-        <v>2398</v>
+        <v>2415</v>
       </c>
       <c r="N49" s="12">
         <f t="shared" si="4"/>
-        <v>1878</v>
+        <v>1865</v>
       </c>
       <c r="O49" s="12" t="str">
         <f t="shared" si="5"/>
-        <v>휘발유 47,450원 / 고급유 47,960원</v>
+        <v>휘발유 46,975원 / 고급유 48,300원</v>
       </c>
       <c r="P49" s="12">
         <f t="shared" si="6"/>
-        <v>95410</v>
+        <v>95275</v>
       </c>
       <c r="Q49" s="12" t="s">
         <v>61</v>
@@ -9630,54 +9624,54 @@
       </c>
       <c r="S49" s="12">
         <f t="shared" si="8"/>
-        <v>9541</v>
+        <v>9527</v>
       </c>
       <c r="T49" s="12">
         <f t="shared" si="9"/>
-        <v>85869</v>
+        <v>85748</v>
       </c>
       <c r="U49" s="12">
         <f t="shared" si="10"/>
-        <v>1908.2</v>
+        <v>1905.5111111111112</v>
       </c>
       <c r="V49" s="12">
         <f t="shared" si="11"/>
-        <v>2120.2222222222222</v>
+        <v>2117.2222222222222</v>
       </c>
       <c r="W49" s="14">
         <f t="shared" si="12"/>
-        <v>85869</v>
-      </c>
-    </row>
-    <row r="50" spans="1:23" s="16" customFormat="1" ht="28.5" customHeight="1">
+        <v>85748</v>
+      </c>
+    </row>
+    <row r="50" spans="1:23" s="7" customFormat="1" ht="28.5" customHeight="1">
       <c r="A50" s="11">
         <f t="shared" si="0"/>
         <v>36</v>
       </c>
       <c r="B50" s="11" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="C50" s="11" t="s">
-        <v>1315</v>
+        <v>1374</v>
       </c>
       <c r="D50" s="15" t="s">
-        <v>78</v>
+        <v>59</v>
       </c>
       <c r="E50" s="11" t="s">
-        <v>26</v>
+        <v>60</v>
       </c>
       <c r="F50" s="11" t="s">
-        <v>1316</v>
+        <v>1375</v>
       </c>
       <c r="G50" s="12">
-        <v>1865</v>
+        <v>1898</v>
       </c>
       <c r="H50" s="12">
-        <v>2459</v>
+        <v>2398</v>
       </c>
       <c r="I50" s="12"/>
       <c r="J50" s="12">
-        <v>1849</v>
+        <v>1878</v>
       </c>
       <c r="K50" s="12">
         <f t="shared" si="1"/>
@@ -9685,23 +9679,23 @@
       </c>
       <c r="L50" s="12">
         <f t="shared" si="2"/>
-        <v>1865</v>
+        <v>1898</v>
       </c>
       <c r="M50" s="12">
         <f t="shared" si="3"/>
-        <v>2459</v>
+        <v>2398</v>
       </c>
       <c r="N50" s="12">
         <f t="shared" si="4"/>
-        <v>1849</v>
+        <v>1878</v>
       </c>
       <c r="O50" s="12" t="str">
         <f t="shared" si="5"/>
-        <v>휘발유 46,625원 / 고급유 49,180원</v>
+        <v>휘발유 47,450원 / 고급유 47,960원</v>
       </c>
       <c r="P50" s="12">
         <f t="shared" si="6"/>
-        <v>95805</v>
+        <v>95410</v>
       </c>
       <c r="Q50" s="12" t="s">
         <v>61</v>
@@ -9712,35 +9706,35 @@
       </c>
       <c r="S50" s="12">
         <f t="shared" si="8"/>
-        <v>9580</v>
+        <v>9541</v>
       </c>
       <c r="T50" s="12">
         <f t="shared" si="9"/>
-        <v>86225</v>
+        <v>85869</v>
       </c>
       <c r="U50" s="12">
         <f t="shared" si="10"/>
-        <v>1916.1111111111111</v>
+        <v>1908.2</v>
       </c>
       <c r="V50" s="12">
         <f t="shared" si="11"/>
-        <v>2129</v>
+        <v>2120.2222222222222</v>
       </c>
       <c r="W50" s="14">
         <f t="shared" si="12"/>
-        <v>86225</v>
-      </c>
-    </row>
-    <row r="51" spans="1:23" s="2" customFormat="1" ht="28.5" customHeight="1">
+        <v>85869</v>
+      </c>
+    </row>
+    <row r="51" spans="1:23" s="16" customFormat="1" ht="28.5" customHeight="1">
       <c r="A51" s="11">
         <f t="shared" si="0"/>
         <v>37</v>
       </c>
       <c r="B51" s="11" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="C51" s="11" t="s">
-        <v>462</v>
+        <v>1315</v>
       </c>
       <c r="D51" s="15" t="s">
         <v>78</v>
@@ -9749,17 +9743,17 @@
         <v>26</v>
       </c>
       <c r="F51" s="11" t="s">
-        <v>463</v>
+        <v>1316</v>
       </c>
       <c r="G51" s="12">
-        <v>1850</v>
+        <v>1865</v>
       </c>
       <c r="H51" s="12">
-        <v>2480</v>
+        <v>2459</v>
       </c>
       <c r="I51" s="12"/>
       <c r="J51" s="12">
-        <v>1820</v>
+        <v>1849</v>
       </c>
       <c r="K51" s="12">
         <f t="shared" si="1"/>
@@ -9767,23 +9761,23 @@
       </c>
       <c r="L51" s="12">
         <f t="shared" si="2"/>
-        <v>1850</v>
+        <v>1865</v>
       </c>
       <c r="M51" s="12">
         <f t="shared" si="3"/>
-        <v>2480</v>
+        <v>2459</v>
       </c>
       <c r="N51" s="12">
         <f t="shared" si="4"/>
-        <v>1820</v>
+        <v>1849</v>
       </c>
       <c r="O51" s="12" t="str">
         <f t="shared" si="5"/>
-        <v>휘발유 46,250원 / 고급유 49,600원</v>
+        <v>휘발유 46,625원 / 고급유 49,180원</v>
       </c>
       <c r="P51" s="12">
         <f t="shared" si="6"/>
-        <v>95850</v>
+        <v>95805</v>
       </c>
       <c r="Q51" s="12" t="s">
         <v>61</v>
@@ -9794,23 +9788,23 @@
       </c>
       <c r="S51" s="12">
         <f t="shared" si="8"/>
-        <v>9585</v>
+        <v>9580</v>
       </c>
       <c r="T51" s="12">
         <f t="shared" si="9"/>
-        <v>86265</v>
+        <v>86225</v>
       </c>
       <c r="U51" s="12">
         <f t="shared" si="10"/>
-        <v>1917</v>
+        <v>1916.1111111111111</v>
       </c>
       <c r="V51" s="12">
         <f t="shared" si="11"/>
-        <v>2130</v>
+        <v>2129</v>
       </c>
       <c r="W51" s="14">
         <f t="shared" si="12"/>
-        <v>86265</v>
+        <v>86225</v>
       </c>
     </row>
     <row r="52" spans="1:23" s="2" customFormat="1" ht="28.5" customHeight="1">
@@ -9819,10 +9813,10 @@
         <v>38</v>
       </c>
       <c r="B52" s="11" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="C52" s="11" t="s">
-        <v>412</v>
+        <v>462</v>
       </c>
       <c r="D52" s="15" t="s">
         <v>78</v>
@@ -9831,17 +9825,17 @@
         <v>26</v>
       </c>
       <c r="F52" s="11" t="s">
-        <v>413</v>
+        <v>463</v>
       </c>
       <c r="G52" s="12">
-        <v>1887</v>
+        <v>1850</v>
       </c>
       <c r="H52" s="12">
-        <v>2567</v>
+        <v>2480</v>
       </c>
       <c r="I52" s="12"/>
       <c r="J52" s="12">
-        <v>1877</v>
+        <v>1820</v>
       </c>
       <c r="K52" s="12">
         <f t="shared" si="1"/>
@@ -9849,23 +9843,23 @@
       </c>
       <c r="L52" s="12">
         <f t="shared" si="2"/>
-        <v>1887</v>
+        <v>1850</v>
       </c>
       <c r="M52" s="12">
         <f t="shared" si="3"/>
-        <v>2567</v>
+        <v>2480</v>
       </c>
       <c r="N52" s="12">
         <f t="shared" si="4"/>
-        <v>1877</v>
+        <v>1820</v>
       </c>
       <c r="O52" s="12" t="str">
         <f t="shared" si="5"/>
-        <v>휘발유 47,175원 / 고급유 51,340원</v>
+        <v>휘발유 46,250원 / 고급유 49,600원</v>
       </c>
       <c r="P52" s="12">
         <f t="shared" si="6"/>
-        <v>98515</v>
+        <v>95850</v>
       </c>
       <c r="Q52" s="12" t="s">
         <v>61</v>
@@ -9876,23 +9870,23 @@
       </c>
       <c r="S52" s="12">
         <f t="shared" si="8"/>
-        <v>9851</v>
+        <v>9585</v>
       </c>
       <c r="T52" s="12">
         <f t="shared" si="9"/>
-        <v>88664</v>
+        <v>86265</v>
       </c>
       <c r="U52" s="12">
         <f t="shared" si="10"/>
-        <v>1970.3111111111111</v>
+        <v>1917</v>
       </c>
       <c r="V52" s="12">
         <f t="shared" si="11"/>
-        <v>2189.2222222222222</v>
+        <v>2130</v>
       </c>
       <c r="W52" s="14">
         <f t="shared" si="12"/>
-        <v>88664</v>
+        <v>86265</v>
       </c>
     </row>
     <row r="53" spans="1:23" s="2" customFormat="1" ht="28.5" customHeight="1">
@@ -9901,10 +9895,10 @@
         <v>39</v>
       </c>
       <c r="B53" s="11" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="C53" s="11" t="s">
-        <v>1271</v>
+        <v>412</v>
       </c>
       <c r="D53" s="15" t="s">
         <v>78</v>
@@ -9913,17 +9907,17 @@
         <v>26</v>
       </c>
       <c r="F53" s="11" t="s">
-        <v>1272</v>
+        <v>413</v>
       </c>
       <c r="G53" s="12">
-        <v>1805</v>
+        <v>1887</v>
       </c>
       <c r="H53" s="12">
-        <v>2250</v>
+        <v>2567</v>
       </c>
       <c r="I53" s="12"/>
       <c r="J53" s="12">
-        <v>1793</v>
+        <v>1877</v>
       </c>
       <c r="K53" s="12">
         <f t="shared" si="1"/>
@@ -9931,51 +9925,53 @@
       </c>
       <c r="L53" s="12">
         <f t="shared" si="2"/>
-        <v>1805</v>
+        <v>1887</v>
       </c>
       <c r="M53" s="12">
         <f t="shared" si="3"/>
-        <v>2250</v>
+        <v>2567</v>
       </c>
       <c r="N53" s="12">
         <f t="shared" si="4"/>
-        <v>1793</v>
+        <v>1877</v>
       </c>
       <c r="O53" s="12" t="str">
         <f t="shared" si="5"/>
-        <v>휘발유 45,125원 / 고급유 45,000원</v>
+        <v>휘발유 47,175원 / 고급유 51,340원</v>
       </c>
       <c r="P53" s="12">
         <f t="shared" si="6"/>
-        <v>90125</v>
-      </c>
-      <c r="Q53" s="12"/>
+        <v>98515</v>
+      </c>
+      <c r="Q53" s="12" t="s">
+        <v>61</v>
+      </c>
       <c r="R53" s="13">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="S53" s="12">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>9851</v>
       </c>
       <c r="T53" s="12">
         <f t="shared" si="9"/>
-        <v>90125</v>
+        <v>88664</v>
       </c>
       <c r="U53" s="12">
         <f t="shared" si="10"/>
-        <v>2002.7777777777778</v>
+        <v>1970.3111111111111</v>
       </c>
       <c r="V53" s="12">
         <f t="shared" si="11"/>
-        <v>2002.7777777777778</v>
+        <v>2189.2222222222222</v>
       </c>
       <c r="W53" s="14">
         <f t="shared" si="12"/>
-        <v>90125</v>
-      </c>
-    </row>
-    <row r="54" spans="1:23" s="16" customFormat="1" ht="28.5" customHeight="1">
+        <v>88664</v>
+      </c>
+    </row>
+    <row r="54" spans="1:23" s="2" customFormat="1" ht="28.5" customHeight="1">
       <c r="A54" s="11">
         <f t="shared" si="0"/>
         <v>40</v>
@@ -9984,26 +9980,26 @@
         <v>6</v>
       </c>
       <c r="C54" s="11" t="s">
-        <v>697</v>
+        <v>1271</v>
       </c>
       <c r="D54" s="15" t="s">
-        <v>45</v>
+        <v>78</v>
       </c>
       <c r="E54" s="11" t="s">
         <v>26</v>
       </c>
       <c r="F54" s="11" t="s">
-        <v>698</v>
+        <v>1272</v>
       </c>
       <c r="G54" s="12">
-        <v>1810</v>
+        <v>1805</v>
       </c>
       <c r="H54" s="12">
-        <v>2269</v>
+        <v>2250</v>
       </c>
       <c r="I54" s="12"/>
       <c r="J54" s="12">
-        <v>1795</v>
+        <v>1793</v>
       </c>
       <c r="K54" s="12">
         <f t="shared" si="1"/>
@@ -10011,23 +10007,23 @@
       </c>
       <c r="L54" s="12">
         <f t="shared" si="2"/>
-        <v>1810</v>
+        <v>1805</v>
       </c>
       <c r="M54" s="12">
         <f t="shared" si="3"/>
-        <v>2269</v>
+        <v>2250</v>
       </c>
       <c r="N54" s="12">
         <f t="shared" si="4"/>
-        <v>1795</v>
+        <v>1793</v>
       </c>
       <c r="O54" s="12" t="str">
         <f t="shared" si="5"/>
-        <v>휘발유 45,250원 / 고급유 45,380원</v>
+        <v>휘발유 45,125원 / 고급유 45,000원</v>
       </c>
       <c r="P54" s="12">
         <f t="shared" si="6"/>
-        <v>90630</v>
+        <v>90125</v>
       </c>
       <c r="Q54" s="12"/>
       <c r="R54" s="13">
@@ -10040,50 +10036,50 @@
       </c>
       <c r="T54" s="12">
         <f t="shared" si="9"/>
-        <v>90630</v>
+        <v>90125</v>
       </c>
       <c r="U54" s="12">
         <f t="shared" si="10"/>
-        <v>2014</v>
+        <v>2002.7777777777778</v>
       </c>
       <c r="V54" s="12">
         <f t="shared" si="11"/>
-        <v>2014</v>
+        <v>2002.7777777777778</v>
       </c>
       <c r="W54" s="14">
         <f t="shared" si="12"/>
-        <v>90630</v>
-      </c>
-    </row>
-    <row r="55" spans="1:23" s="2" customFormat="1" ht="28.5" customHeight="1">
+        <v>90125</v>
+      </c>
+    </row>
+    <row r="55" spans="1:23" s="16" customFormat="1" ht="28.5" customHeight="1">
       <c r="A55" s="11">
         <f t="shared" si="0"/>
         <v>41</v>
       </c>
       <c r="B55" s="11" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="C55" s="11" t="s">
-        <v>799</v>
+        <v>697</v>
       </c>
       <c r="D55" s="15" t="s">
-        <v>78</v>
+        <v>45</v>
       </c>
       <c r="E55" s="11" t="s">
         <v>26</v>
       </c>
       <c r="F55" s="11" t="s">
-        <v>800</v>
+        <v>698</v>
       </c>
       <c r="G55" s="12">
-        <v>1827</v>
+        <v>1810</v>
       </c>
       <c r="H55" s="12">
-        <v>2270</v>
+        <v>2269</v>
       </c>
       <c r="I55" s="12"/>
       <c r="J55" s="12">
-        <v>1809</v>
+        <v>1795</v>
       </c>
       <c r="K55" s="12">
         <f t="shared" si="1"/>
@@ -10091,23 +10087,23 @@
       </c>
       <c r="L55" s="12">
         <f t="shared" si="2"/>
-        <v>1827</v>
+        <v>1810</v>
       </c>
       <c r="M55" s="12">
         <f t="shared" si="3"/>
-        <v>2270</v>
+        <v>2269</v>
       </c>
       <c r="N55" s="12">
         <f t="shared" si="4"/>
-        <v>1809</v>
+        <v>1795</v>
       </c>
       <c r="O55" s="12" t="str">
         <f t="shared" si="5"/>
-        <v>휘발유 45,675원 / 고급유 45,400원</v>
+        <v>휘발유 45,250원 / 고급유 45,380원</v>
       </c>
       <c r="P55" s="12">
         <f t="shared" si="6"/>
-        <v>91075</v>
+        <v>90630</v>
       </c>
       <c r="Q55" s="12"/>
       <c r="R55" s="13">
@@ -10120,19 +10116,19 @@
       </c>
       <c r="T55" s="12">
         <f t="shared" si="9"/>
-        <v>91075</v>
+        <v>90630</v>
       </c>
       <c r="U55" s="12">
         <f t="shared" si="10"/>
-        <v>2023.8888888888889</v>
+        <v>2014</v>
       </c>
       <c r="V55" s="12">
         <f t="shared" si="11"/>
-        <v>2023.8888888888889</v>
+        <v>2014</v>
       </c>
       <c r="W55" s="14">
         <f t="shared" si="12"/>
-        <v>91075</v>
+        <v>90630</v>
       </c>
     </row>
     <row r="56" spans="1:23" s="2" customFormat="1" ht="28.5" customHeight="1">
@@ -10141,29 +10137,29 @@
         <v>42</v>
       </c>
       <c r="B56" s="11" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="C56" s="11" t="s">
-        <v>122</v>
-      </c>
-      <c r="D56" s="11" t="s">
-        <v>48</v>
+        <v>799</v>
+      </c>
+      <c r="D56" s="15" t="s">
+        <v>78</v>
       </c>
       <c r="E56" s="11" t="s">
         <v>26</v>
       </c>
       <c r="F56" s="11" t="s">
-        <v>123</v>
+        <v>800</v>
       </c>
       <c r="G56" s="12">
-        <v>1814</v>
+        <v>1827</v>
       </c>
       <c r="H56" s="12">
-        <v>2289</v>
+        <v>2270</v>
       </c>
       <c r="I56" s="12"/>
       <c r="J56" s="12">
-        <v>1792</v>
+        <v>1809</v>
       </c>
       <c r="K56" s="12">
         <f t="shared" si="1"/>
@@ -10171,23 +10167,23 @@
       </c>
       <c r="L56" s="12">
         <f t="shared" si="2"/>
-        <v>1814</v>
+        <v>1827</v>
       </c>
       <c r="M56" s="12">
         <f t="shared" si="3"/>
-        <v>2289</v>
+        <v>2270</v>
       </c>
       <c r="N56" s="12">
         <f t="shared" si="4"/>
-        <v>1792</v>
+        <v>1809</v>
       </c>
       <c r="O56" s="12" t="str">
         <f t="shared" si="5"/>
-        <v>휘발유 45,350원 / 고급유 45,780원</v>
+        <v>휘발유 45,675원 / 고급유 45,400원</v>
       </c>
       <c r="P56" s="12">
         <f t="shared" si="6"/>
-        <v>91130</v>
+        <v>91075</v>
       </c>
       <c r="Q56" s="12"/>
       <c r="R56" s="13">
@@ -10200,19 +10196,19 @@
       </c>
       <c r="T56" s="12">
         <f t="shared" si="9"/>
-        <v>91130</v>
+        <v>91075</v>
       </c>
       <c r="U56" s="12">
         <f t="shared" si="10"/>
-        <v>2025.1111111111111</v>
+        <v>2023.8888888888889</v>
       </c>
       <c r="V56" s="12">
         <f t="shared" si="11"/>
-        <v>2025.1111111111111</v>
+        <v>2023.8888888888889</v>
       </c>
       <c r="W56" s="14">
         <f t="shared" si="12"/>
-        <v>91130</v>
+        <v>91075</v>
       </c>
     </row>
     <row r="57" spans="1:23" s="2" customFormat="1" ht="28.5" customHeight="1">
@@ -10221,29 +10217,29 @@
         <v>43</v>
       </c>
       <c r="B57" s="11" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="C57" s="11" t="s">
-        <v>80</v>
-      </c>
-      <c r="D57" s="15" t="s">
-        <v>59</v>
+        <v>122</v>
+      </c>
+      <c r="D57" s="11" t="s">
+        <v>48</v>
       </c>
       <c r="E57" s="11" t="s">
         <v>26</v>
       </c>
       <c r="F57" s="11" t="s">
-        <v>81</v>
+        <v>123</v>
       </c>
       <c r="G57" s="12">
-        <v>1788</v>
+        <v>1814</v>
       </c>
       <c r="H57" s="12">
-        <v>2325</v>
+        <v>2289</v>
       </c>
       <c r="I57" s="12"/>
       <c r="J57" s="12">
-        <v>1795</v>
+        <v>1792</v>
       </c>
       <c r="K57" s="12">
         <f t="shared" si="1"/>
@@ -10251,23 +10247,23 @@
       </c>
       <c r="L57" s="12">
         <f t="shared" si="2"/>
-        <v>1788</v>
+        <v>1814</v>
       </c>
       <c r="M57" s="12">
         <f t="shared" si="3"/>
-        <v>2325</v>
+        <v>2289</v>
       </c>
       <c r="N57" s="12">
         <f t="shared" si="4"/>
-        <v>1795</v>
+        <v>1792</v>
       </c>
       <c r="O57" s="12" t="str">
         <f t="shared" si="5"/>
-        <v>휘발유 44,700원 / 고급유 46,500원</v>
+        <v>휘발유 45,350원 / 고급유 45,780원</v>
       </c>
       <c r="P57" s="12">
         <f t="shared" si="6"/>
-        <v>91200</v>
+        <v>91130</v>
       </c>
       <c r="Q57" s="12"/>
       <c r="R57" s="13">
@@ -10280,19 +10276,19 @@
       </c>
       <c r="T57" s="12">
         <f t="shared" si="9"/>
-        <v>91200</v>
+        <v>91130</v>
       </c>
       <c r="U57" s="12">
         <f t="shared" si="10"/>
-        <v>2026.6666666666667</v>
+        <v>2025.1111111111111</v>
       </c>
       <c r="V57" s="12">
         <f t="shared" si="11"/>
-        <v>2026.6666666666667</v>
+        <v>2025.1111111111111</v>
       </c>
       <c r="W57" s="14">
         <f t="shared" si="12"/>
-        <v>91200</v>
+        <v>91130</v>
       </c>
     </row>
     <row r="58" spans="1:23" s="2" customFormat="1" ht="28.5" customHeight="1">
@@ -10301,29 +10297,29 @@
         <v>44</v>
       </c>
       <c r="B58" s="11" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="C58" s="11" t="s">
-        <v>568</v>
+        <v>80</v>
       </c>
       <c r="D58" s="15" t="s">
-        <v>78</v>
+        <v>59</v>
       </c>
       <c r="E58" s="11" t="s">
         <v>26</v>
       </c>
       <c r="F58" s="11" t="s">
-        <v>569</v>
+        <v>81</v>
       </c>
       <c r="G58" s="12">
-        <v>1822</v>
+        <v>1788</v>
       </c>
       <c r="H58" s="12">
-        <v>2287</v>
+        <v>2325</v>
       </c>
       <c r="I58" s="12"/>
       <c r="J58" s="12">
-        <v>1802</v>
+        <v>1795</v>
       </c>
       <c r="K58" s="12">
         <f t="shared" si="1"/>
@@ -10331,23 +10327,23 @@
       </c>
       <c r="L58" s="12">
         <f t="shared" si="2"/>
-        <v>1822</v>
+        <v>1788</v>
       </c>
       <c r="M58" s="12">
         <f t="shared" si="3"/>
-        <v>2287</v>
+        <v>2325</v>
       </c>
       <c r="N58" s="12">
         <f t="shared" si="4"/>
-        <v>1802</v>
+        <v>1795</v>
       </c>
       <c r="O58" s="12" t="str">
         <f t="shared" si="5"/>
-        <v>휘발유 45,550원 / 고급유 45,740원</v>
+        <v>휘발유 44,700원 / 고급유 46,500원</v>
       </c>
       <c r="P58" s="12">
         <f t="shared" si="6"/>
-        <v>91290</v>
+        <v>91200</v>
       </c>
       <c r="Q58" s="12"/>
       <c r="R58" s="13">
@@ -10360,50 +10356,50 @@
       </c>
       <c r="T58" s="12">
         <f t="shared" si="9"/>
-        <v>91290</v>
+        <v>91200</v>
       </c>
       <c r="U58" s="12">
         <f t="shared" si="10"/>
-        <v>2028.6666666666667</v>
+        <v>2026.6666666666667</v>
       </c>
       <c r="V58" s="12">
         <f t="shared" si="11"/>
-        <v>2028.6666666666667</v>
+        <v>2026.6666666666667</v>
       </c>
       <c r="W58" s="14">
         <f t="shared" si="12"/>
-        <v>91290</v>
-      </c>
-    </row>
-    <row r="59" spans="1:23" s="16" customFormat="1" ht="28.5" customHeight="1">
+        <v>91200</v>
+      </c>
+    </row>
+    <row r="59" spans="1:23" s="2" customFormat="1" ht="28.5" customHeight="1">
       <c r="A59" s="11">
         <f t="shared" si="0"/>
         <v>45</v>
       </c>
       <c r="B59" s="11" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="C59" s="11" t="s">
-        <v>1538</v>
+        <v>568</v>
       </c>
       <c r="D59" s="15" t="s">
-        <v>59</v>
+        <v>78</v>
       </c>
       <c r="E59" s="11" t="s">
         <v>26</v>
       </c>
       <c r="F59" s="11" t="s">
-        <v>1539</v>
+        <v>569</v>
       </c>
       <c r="G59" s="12">
-        <v>1809</v>
+        <v>1822</v>
       </c>
       <c r="H59" s="12">
-        <v>2309</v>
+        <v>2287</v>
       </c>
       <c r="I59" s="12"/>
       <c r="J59" s="12">
-        <v>1809</v>
+        <v>1802</v>
       </c>
       <c r="K59" s="12">
         <f t="shared" si="1"/>
@@ -10411,23 +10407,23 @@
       </c>
       <c r="L59" s="12">
         <f t="shared" si="2"/>
-        <v>1809</v>
+        <v>1822</v>
       </c>
       <c r="M59" s="12">
         <f t="shared" si="3"/>
-        <v>2309</v>
+        <v>2287</v>
       </c>
       <c r="N59" s="12">
         <f t="shared" si="4"/>
-        <v>1809</v>
+        <v>1802</v>
       </c>
       <c r="O59" s="12" t="str">
         <f t="shared" si="5"/>
-        <v>휘발유 45,225원 / 고급유 46,180원</v>
+        <v>휘발유 45,550원 / 고급유 45,740원</v>
       </c>
       <c r="P59" s="12">
         <f t="shared" si="6"/>
-        <v>91405</v>
+        <v>91290</v>
       </c>
       <c r="Q59" s="12"/>
       <c r="R59" s="13">
@@ -10440,22 +10436,22 @@
       </c>
       <c r="T59" s="12">
         <f t="shared" si="9"/>
-        <v>91405</v>
+        <v>91290</v>
       </c>
       <c r="U59" s="12">
         <f t="shared" si="10"/>
-        <v>2031.2222222222222</v>
+        <v>2028.6666666666667</v>
       </c>
       <c r="V59" s="12">
         <f t="shared" si="11"/>
-        <v>2031.2222222222222</v>
+        <v>2028.6666666666667</v>
       </c>
       <c r="W59" s="14">
         <f t="shared" si="12"/>
-        <v>91405</v>
-      </c>
-    </row>
-    <row r="60" spans="1:23" s="7" customFormat="1" ht="28.5" customHeight="1">
+        <v>91290</v>
+      </c>
+    </row>
+    <row r="60" spans="1:23" s="16" customFormat="1" ht="28.5" customHeight="1">
       <c r="A60" s="11">
         <f t="shared" si="0"/>
         <v>46</v>
@@ -10464,7 +10460,7 @@
         <v>10</v>
       </c>
       <c r="C60" s="11" t="s">
-        <v>793</v>
+        <v>1538</v>
       </c>
       <c r="D60" s="15" t="s">
         <v>59</v>
@@ -10473,17 +10469,17 @@
         <v>26</v>
       </c>
       <c r="F60" s="11" t="s">
-        <v>794</v>
+        <v>1539</v>
       </c>
       <c r="G60" s="12">
-        <v>1810</v>
+        <v>1809</v>
       </c>
       <c r="H60" s="12">
-        <v>2310</v>
+        <v>2309</v>
       </c>
       <c r="I60" s="12"/>
       <c r="J60" s="12">
-        <v>1795</v>
+        <v>1809</v>
       </c>
       <c r="K60" s="12">
         <f t="shared" si="1"/>
@@ -10491,23 +10487,23 @@
       </c>
       <c r="L60" s="12">
         <f t="shared" si="2"/>
-        <v>1810</v>
+        <v>1809</v>
       </c>
       <c r="M60" s="12">
         <f t="shared" si="3"/>
-        <v>2310</v>
+        <v>2309</v>
       </c>
       <c r="N60" s="12">
         <f t="shared" si="4"/>
-        <v>1795</v>
+        <v>1809</v>
       </c>
       <c r="O60" s="12" t="str">
         <f t="shared" si="5"/>
-        <v>휘발유 45,250원 / 고급유 46,200원</v>
+        <v>휘발유 45,225원 / 고급유 46,180원</v>
       </c>
       <c r="P60" s="12">
         <f t="shared" si="6"/>
-        <v>91450</v>
+        <v>91405</v>
       </c>
       <c r="Q60" s="12"/>
       <c r="R60" s="13">
@@ -10520,31 +10516,31 @@
       </c>
       <c r="T60" s="12">
         <f t="shared" si="9"/>
-        <v>91450</v>
+        <v>91405</v>
       </c>
       <c r="U60" s="12">
         <f t="shared" si="10"/>
-        <v>2032.2222222222222</v>
+        <v>2031.2222222222222</v>
       </c>
       <c r="V60" s="12">
         <f t="shared" si="11"/>
-        <v>2032.2222222222222</v>
+        <v>2031.2222222222222</v>
       </c>
       <c r="W60" s="14">
         <f t="shared" si="12"/>
-        <v>91450</v>
+        <v>91405</v>
       </c>
     </row>
     <row r="61" spans="1:23" s="7" customFormat="1" ht="28.5" customHeight="1">
       <c r="A61" s="11">
         <f t="shared" si="0"/>
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B61" s="11" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="C61" s="11" t="s">
-        <v>1378</v>
+        <v>793</v>
       </c>
       <c r="D61" s="15" t="s">
         <v>59</v>
@@ -10553,7 +10549,7 @@
         <v>26</v>
       </c>
       <c r="F61" s="11" t="s">
-        <v>1379</v>
+        <v>794</v>
       </c>
       <c r="G61" s="12">
         <v>1810</v>
@@ -10563,7 +10559,7 @@
       </c>
       <c r="I61" s="12"/>
       <c r="J61" s="12">
-        <v>1800</v>
+        <v>1795</v>
       </c>
       <c r="K61" s="12">
         <f t="shared" si="1"/>
@@ -10579,7 +10575,7 @@
       </c>
       <c r="N61" s="12">
         <f t="shared" si="4"/>
-        <v>1800</v>
+        <v>1795</v>
       </c>
       <c r="O61" s="12" t="str">
         <f t="shared" si="5"/>
@@ -10615,35 +10611,35 @@
         <v>91450</v>
       </c>
     </row>
-    <row r="62" spans="1:23" s="16" customFormat="1" ht="28.5" customHeight="1">
+    <row r="62" spans="1:23" s="7" customFormat="1" ht="28.5" customHeight="1">
       <c r="A62" s="11">
         <f t="shared" si="0"/>
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B62" s="11" t="s">
         <v>6</v>
       </c>
       <c r="C62" s="11" t="s">
-        <v>830</v>
+        <v>1378</v>
       </c>
       <c r="D62" s="15" t="s">
-        <v>78</v>
+        <v>59</v>
       </c>
       <c r="E62" s="11" t="s">
         <v>26</v>
       </c>
       <c r="F62" s="11" t="s">
-        <v>831</v>
+        <v>1379</v>
       </c>
       <c r="G62" s="12">
-        <v>1828</v>
+        <v>1810</v>
       </c>
       <c r="H62" s="12">
-        <v>2290</v>
+        <v>2310</v>
       </c>
       <c r="I62" s="12"/>
       <c r="J62" s="12">
-        <v>1819</v>
+        <v>1800</v>
       </c>
       <c r="K62" s="12">
         <f t="shared" si="1"/>
@@ -10651,23 +10647,23 @@
       </c>
       <c r="L62" s="12">
         <f t="shared" si="2"/>
-        <v>1828</v>
+        <v>1810</v>
       </c>
       <c r="M62" s="12">
         <f t="shared" si="3"/>
-        <v>2290</v>
+        <v>2310</v>
       </c>
       <c r="N62" s="12">
         <f t="shared" si="4"/>
-        <v>1819</v>
+        <v>1800</v>
       </c>
       <c r="O62" s="12" t="str">
         <f t="shared" si="5"/>
-        <v>휘발유 45,700원 / 고급유 45,800원</v>
+        <v>휘발유 45,250원 / 고급유 46,200원</v>
       </c>
       <c r="P62" s="12">
         <f t="shared" si="6"/>
-        <v>91500</v>
+        <v>91450</v>
       </c>
       <c r="Q62" s="12"/>
       <c r="R62" s="13">
@@ -10680,50 +10676,50 @@
       </c>
       <c r="T62" s="12">
         <f t="shared" si="9"/>
-        <v>91500</v>
+        <v>91450</v>
       </c>
       <c r="U62" s="12">
         <f t="shared" si="10"/>
-        <v>2033.3333333333333</v>
+        <v>2032.2222222222222</v>
       </c>
       <c r="V62" s="12">
         <f t="shared" si="11"/>
-        <v>2033.3333333333333</v>
+        <v>2032.2222222222222</v>
       </c>
       <c r="W62" s="14">
         <f t="shared" si="12"/>
-        <v>91500</v>
-      </c>
-    </row>
-    <row r="63" spans="1:23" s="2" customFormat="1" ht="28.5" customHeight="1">
+        <v>91450</v>
+      </c>
+    </row>
+    <row r="63" spans="1:23" s="16" customFormat="1" ht="28.5" customHeight="1">
       <c r="A63" s="11">
         <f t="shared" si="0"/>
         <v>49</v>
       </c>
       <c r="B63" s="11" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="C63" s="11" t="s">
-        <v>730</v>
-      </c>
-      <c r="D63" s="11" t="s">
-        <v>57</v>
+        <v>830</v>
+      </c>
+      <c r="D63" s="15" t="s">
+        <v>78</v>
       </c>
       <c r="E63" s="11" t="s">
         <v>26</v>
       </c>
       <c r="F63" s="11" t="s">
-        <v>731</v>
+        <v>831</v>
       </c>
       <c r="G63" s="12">
-        <v>1829</v>
+        <v>1828</v>
       </c>
       <c r="H63" s="12">
-        <v>2289</v>
+        <v>2290</v>
       </c>
       <c r="I63" s="12"/>
       <c r="J63" s="12">
-        <v>1809</v>
+        <v>1819</v>
       </c>
       <c r="K63" s="12">
         <f t="shared" si="1"/>
@@ -10731,23 +10727,23 @@
       </c>
       <c r="L63" s="12">
         <f t="shared" si="2"/>
-        <v>1829</v>
+        <v>1828</v>
       </c>
       <c r="M63" s="12">
         <f t="shared" si="3"/>
-        <v>2289</v>
+        <v>2290</v>
       </c>
       <c r="N63" s="12">
         <f t="shared" si="4"/>
-        <v>1809</v>
+        <v>1819</v>
       </c>
       <c r="O63" s="12" t="str">
         <f t="shared" si="5"/>
-        <v>휘발유 45,725원 / 고급유 45,780원</v>
+        <v>휘발유 45,700원 / 고급유 45,800원</v>
       </c>
       <c r="P63" s="12">
         <f t="shared" si="6"/>
-        <v>91505</v>
+        <v>91500</v>
       </c>
       <c r="Q63" s="12"/>
       <c r="R63" s="13">
@@ -10760,22 +10756,22 @@
       </c>
       <c r="T63" s="12">
         <f t="shared" si="9"/>
-        <v>91505</v>
+        <v>91500</v>
       </c>
       <c r="U63" s="12">
         <f t="shared" si="10"/>
-        <v>2033.4444444444443</v>
+        <v>2033.3333333333333</v>
       </c>
       <c r="V63" s="12">
         <f t="shared" si="11"/>
-        <v>2033.4444444444443</v>
+        <v>2033.3333333333333</v>
       </c>
       <c r="W63" s="14">
         <f t="shared" si="12"/>
-        <v>91505</v>
-      </c>
-    </row>
-    <row r="64" spans="1:23" s="16" customFormat="1" ht="28.5" customHeight="1">
+        <v>91500</v>
+      </c>
+    </row>
+    <row r="64" spans="1:23" s="2" customFormat="1" ht="28.5" customHeight="1">
       <c r="A64" s="11">
         <f t="shared" si="0"/>
         <v>50</v>
@@ -10784,26 +10780,26 @@
         <v>10</v>
       </c>
       <c r="C64" s="11" t="s">
-        <v>1392</v>
-      </c>
-      <c r="D64" s="15" t="s">
-        <v>59</v>
+        <v>730</v>
+      </c>
+      <c r="D64" s="11" t="s">
+        <v>57</v>
       </c>
       <c r="E64" s="11" t="s">
         <v>26</v>
       </c>
       <c r="F64" s="11" t="s">
-        <v>1393</v>
+        <v>731</v>
       </c>
       <c r="G64" s="12">
-        <v>1815</v>
+        <v>1829</v>
       </c>
       <c r="H64" s="12">
-        <v>2310</v>
+        <v>2289</v>
       </c>
       <c r="I64" s="12"/>
       <c r="J64" s="12">
-        <v>1805</v>
+        <v>1809</v>
       </c>
       <c r="K64" s="12">
         <f t="shared" si="1"/>
@@ -10811,23 +10807,23 @@
       </c>
       <c r="L64" s="12">
         <f t="shared" si="2"/>
-        <v>1815</v>
+        <v>1829</v>
       </c>
       <c r="M64" s="12">
         <f t="shared" si="3"/>
-        <v>2310</v>
+        <v>2289</v>
       </c>
       <c r="N64" s="12">
         <f t="shared" si="4"/>
-        <v>1805</v>
+        <v>1809</v>
       </c>
       <c r="O64" s="12" t="str">
         <f t="shared" si="5"/>
-        <v>휘발유 45,375원 / 고급유 46,200원</v>
+        <v>휘발유 45,725원 / 고급유 45,780원</v>
       </c>
       <c r="P64" s="12">
         <f t="shared" si="6"/>
-        <v>91575</v>
+        <v>91505</v>
       </c>
       <c r="Q64" s="12"/>
       <c r="R64" s="13">
@@ -10840,31 +10836,31 @@
       </c>
       <c r="T64" s="12">
         <f t="shared" si="9"/>
-        <v>91575</v>
+        <v>91505</v>
       </c>
       <c r="U64" s="12">
         <f t="shared" si="10"/>
-        <v>2035</v>
+        <v>2033.4444444444443</v>
       </c>
       <c r="V64" s="12">
         <f t="shared" si="11"/>
-        <v>2035</v>
+        <v>2033.4444444444443</v>
       </c>
       <c r="W64" s="14">
         <f t="shared" si="12"/>
-        <v>91575</v>
-      </c>
-    </row>
-    <row r="65" spans="1:23" s="7" customFormat="1" ht="28.5" customHeight="1">
+        <v>91505</v>
+      </c>
+    </row>
+    <row r="65" spans="1:23" s="16" customFormat="1" ht="28.5" customHeight="1">
       <c r="A65" s="11">
         <f t="shared" si="0"/>
         <v>51</v>
       </c>
       <c r="B65" s="11" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="C65" s="11" t="s">
-        <v>1002</v>
+        <v>1392</v>
       </c>
       <c r="D65" s="15" t="s">
         <v>59</v>
@@ -10873,17 +10869,17 @@
         <v>26</v>
       </c>
       <c r="F65" s="11" t="s">
-        <v>1003</v>
+        <v>1393</v>
       </c>
       <c r="G65" s="12">
-        <v>1805</v>
+        <v>1815</v>
       </c>
       <c r="H65" s="12">
-        <v>2325</v>
+        <v>2310</v>
       </c>
       <c r="I65" s="12"/>
       <c r="J65" s="12">
-        <v>1795</v>
+        <v>1805</v>
       </c>
       <c r="K65" s="12">
         <f t="shared" si="1"/>
@@ -10891,23 +10887,23 @@
       </c>
       <c r="L65" s="12">
         <f t="shared" si="2"/>
-        <v>1805</v>
+        <v>1815</v>
       </c>
       <c r="M65" s="12">
         <f t="shared" si="3"/>
-        <v>2325</v>
+        <v>2310</v>
       </c>
       <c r="N65" s="12">
         <f t="shared" si="4"/>
-        <v>1795</v>
+        <v>1805</v>
       </c>
       <c r="O65" s="12" t="str">
         <f t="shared" si="5"/>
-        <v>휘발유 45,125원 / 고급유 46,500원</v>
+        <v>휘발유 45,375원 / 고급유 46,200원</v>
       </c>
       <c r="P65" s="12">
         <f t="shared" si="6"/>
-        <v>91625</v>
+        <v>91575</v>
       </c>
       <c r="Q65" s="12"/>
       <c r="R65" s="13">
@@ -10920,50 +10916,50 @@
       </c>
       <c r="T65" s="12">
         <f t="shared" si="9"/>
-        <v>91625</v>
+        <v>91575</v>
       </c>
       <c r="U65" s="12">
         <f t="shared" si="10"/>
-        <v>2036.1111111111111</v>
+        <v>2035</v>
       </c>
       <c r="V65" s="12">
         <f t="shared" si="11"/>
-        <v>2036.1111111111111</v>
+        <v>2035</v>
       </c>
       <c r="W65" s="14">
         <f t="shared" si="12"/>
-        <v>91625</v>
-      </c>
-    </row>
-    <row r="66" spans="1:23" s="2" customFormat="1" ht="28.5" customHeight="1">
+        <v>91575</v>
+      </c>
+    </row>
+    <row r="66" spans="1:23" s="7" customFormat="1" ht="28.5" customHeight="1">
       <c r="A66" s="11">
         <f t="shared" si="0"/>
         <v>52</v>
       </c>
       <c r="B66" s="11" t="s">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="C66" s="11" t="s">
-        <v>586</v>
+        <v>1002</v>
       </c>
       <c r="D66" s="15" t="s">
-        <v>78</v>
+        <v>59</v>
       </c>
       <c r="E66" s="11" t="s">
         <v>26</v>
       </c>
       <c r="F66" s="11" t="s">
-        <v>587</v>
+        <v>1003</v>
       </c>
       <c r="G66" s="12">
-        <v>1828</v>
+        <v>1805</v>
       </c>
       <c r="H66" s="12">
-        <v>2298</v>
+        <v>2325</v>
       </c>
       <c r="I66" s="12"/>
       <c r="J66" s="12">
-        <v>1811</v>
+        <v>1795</v>
       </c>
       <c r="K66" s="12">
         <f t="shared" si="1"/>
@@ -10971,23 +10967,23 @@
       </c>
       <c r="L66" s="12">
         <f t="shared" si="2"/>
-        <v>1828</v>
+        <v>1805</v>
       </c>
       <c r="M66" s="12">
         <f t="shared" si="3"/>
-        <v>2298</v>
+        <v>2325</v>
       </c>
       <c r="N66" s="12">
         <f t="shared" si="4"/>
-        <v>1811</v>
+        <v>1795</v>
       </c>
       <c r="O66" s="12" t="str">
         <f t="shared" si="5"/>
-        <v>휘발유 45,700원 / 고급유 45,960원</v>
+        <v>휘발유 45,125원 / 고급유 46,500원</v>
       </c>
       <c r="P66" s="12">
         <f t="shared" si="6"/>
-        <v>91660</v>
+        <v>91625</v>
       </c>
       <c r="Q66" s="12"/>
       <c r="R66" s="13">
@@ -11000,19 +10996,19 @@
       </c>
       <c r="T66" s="12">
         <f t="shared" si="9"/>
-        <v>91660</v>
+        <v>91625</v>
       </c>
       <c r="U66" s="12">
         <f t="shared" si="10"/>
-        <v>2036.8888888888889</v>
+        <v>2036.1111111111111</v>
       </c>
       <c r="V66" s="12">
         <f t="shared" si="11"/>
-        <v>2036.8888888888889</v>
+        <v>2036.1111111111111</v>
       </c>
       <c r="W66" s="14">
         <f t="shared" si="12"/>
-        <v>91660</v>
+        <v>91625</v>
       </c>
     </row>
     <row r="67" spans="1:23" s="2" customFormat="1" ht="28.5" customHeight="1">
@@ -11024,26 +11020,26 @@
         <v>6</v>
       </c>
       <c r="C67" s="11" t="s">
-        <v>1384</v>
+        <v>586</v>
       </c>
       <c r="D67" s="15" t="s">
-        <v>59</v>
+        <v>78</v>
       </c>
       <c r="E67" s="11" t="s">
-        <v>60</v>
+        <v>26</v>
       </c>
       <c r="F67" s="11" t="s">
-        <v>1385</v>
+        <v>587</v>
       </c>
       <c r="G67" s="12">
-        <v>1800</v>
+        <v>1828</v>
       </c>
       <c r="H67" s="12">
-        <v>2335</v>
+        <v>2298</v>
       </c>
       <c r="I67" s="12"/>
       <c r="J67" s="12">
-        <v>1795</v>
+        <v>1811</v>
       </c>
       <c r="K67" s="12">
         <f t="shared" si="1"/>
@@ -11051,23 +11047,23 @@
       </c>
       <c r="L67" s="12">
         <f t="shared" si="2"/>
-        <v>1800</v>
+        <v>1828</v>
       </c>
       <c r="M67" s="12">
         <f t="shared" si="3"/>
-        <v>2335</v>
+        <v>2298</v>
       </c>
       <c r="N67" s="12">
         <f t="shared" si="4"/>
-        <v>1795</v>
+        <v>1811</v>
       </c>
       <c r="O67" s="12" t="str">
         <f t="shared" si="5"/>
-        <v>휘발유 45,000원 / 고급유 46,700원</v>
+        <v>휘발유 45,700원 / 고급유 45,960원</v>
       </c>
       <c r="P67" s="12">
         <f t="shared" si="6"/>
-        <v>91700</v>
+        <v>91660</v>
       </c>
       <c r="Q67" s="12"/>
       <c r="R67" s="13">
@@ -11080,50 +11076,50 @@
       </c>
       <c r="T67" s="12">
         <f t="shared" si="9"/>
-        <v>91700</v>
+        <v>91660</v>
       </c>
       <c r="U67" s="12">
         <f t="shared" si="10"/>
-        <v>2037.7777777777778</v>
+        <v>2036.8888888888889</v>
       </c>
       <c r="V67" s="12">
         <f t="shared" si="11"/>
-        <v>2037.7777777777778</v>
+        <v>2036.8888888888889</v>
       </c>
       <c r="W67" s="14">
         <f t="shared" si="12"/>
-        <v>91700</v>
-      </c>
-    </row>
-    <row r="68" spans="1:23" s="7" customFormat="1" ht="28.5" customHeight="1">
+        <v>91660</v>
+      </c>
+    </row>
+    <row r="68" spans="1:23" s="2" customFormat="1" ht="28.5" customHeight="1">
       <c r="A68" s="11">
         <f t="shared" si="0"/>
         <v>54</v>
       </c>
       <c r="B68" s="11" t="s">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="C68" s="11" t="s">
-        <v>1390</v>
+        <v>1384</v>
       </c>
       <c r="D68" s="15" t="s">
         <v>59</v>
       </c>
       <c r="E68" s="11" t="s">
-        <v>26</v>
+        <v>60</v>
       </c>
       <c r="F68" s="11" t="s">
-        <v>1391</v>
+        <v>1385</v>
       </c>
       <c r="G68" s="12">
-        <v>1825</v>
+        <v>1800</v>
       </c>
       <c r="H68" s="12">
-        <v>2305</v>
+        <v>2335</v>
       </c>
       <c r="I68" s="12"/>
       <c r="J68" s="12">
-        <v>1815</v>
+        <v>1795</v>
       </c>
       <c r="K68" s="12">
         <f t="shared" si="1"/>
@@ -11131,23 +11127,23 @@
       </c>
       <c r="L68" s="12">
         <f t="shared" si="2"/>
-        <v>1825</v>
+        <v>1800</v>
       </c>
       <c r="M68" s="12">
         <f t="shared" si="3"/>
-        <v>2305</v>
+        <v>2335</v>
       </c>
       <c r="N68" s="12">
         <f t="shared" si="4"/>
-        <v>1815</v>
+        <v>1795</v>
       </c>
       <c r="O68" s="12" t="str">
         <f t="shared" si="5"/>
-        <v>휘발유 45,625원 / 고급유 46,100원</v>
+        <v>휘발유 45,000원 / 고급유 46,700원</v>
       </c>
       <c r="P68" s="12">
         <f t="shared" si="6"/>
-        <v>91725</v>
+        <v>91700</v>
       </c>
       <c r="Q68" s="12"/>
       <c r="R68" s="13">
@@ -11160,19 +11156,19 @@
       </c>
       <c r="T68" s="12">
         <f t="shared" si="9"/>
-        <v>91725</v>
+        <v>91700</v>
       </c>
       <c r="U68" s="12">
         <f t="shared" si="10"/>
-        <v>2038.3333333333333</v>
+        <v>2037.7777777777778</v>
       </c>
       <c r="V68" s="12">
         <f t="shared" si="11"/>
-        <v>2038.3333333333333</v>
+        <v>2037.7777777777778</v>
       </c>
       <c r="W68" s="14">
         <f t="shared" si="12"/>
-        <v>91725</v>
+        <v>91700</v>
       </c>
     </row>
     <row r="69" spans="1:23" s="7" customFormat="1" ht="28.5" customHeight="1">
@@ -11181,29 +11177,29 @@
         <v>55</v>
       </c>
       <c r="B69" s="11" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="C69" s="11" t="s">
-        <v>1516</v>
-      </c>
-      <c r="D69" s="11" t="s">
-        <v>69</v>
+        <v>1390</v>
+      </c>
+      <c r="D69" s="15" t="s">
+        <v>59</v>
       </c>
       <c r="E69" s="11" t="s">
         <v>26</v>
       </c>
       <c r="F69" s="11" t="s">
-        <v>1517</v>
+        <v>1391</v>
       </c>
       <c r="G69" s="12">
-        <v>1819</v>
+        <v>1825</v>
       </c>
       <c r="H69" s="12">
-        <v>2318</v>
+        <v>2305</v>
       </c>
       <c r="I69" s="12"/>
       <c r="J69" s="12">
-        <v>1799</v>
+        <v>1815</v>
       </c>
       <c r="K69" s="12">
         <f t="shared" si="1"/>
@@ -11211,23 +11207,23 @@
       </c>
       <c r="L69" s="12">
         <f t="shared" si="2"/>
-        <v>1819</v>
+        <v>1825</v>
       </c>
       <c r="M69" s="12">
         <f t="shared" si="3"/>
-        <v>2318</v>
+        <v>2305</v>
       </c>
       <c r="N69" s="12">
         <f t="shared" si="4"/>
-        <v>1799</v>
+        <v>1815</v>
       </c>
       <c r="O69" s="12" t="str">
         <f t="shared" si="5"/>
-        <v>휘발유 45,475원 / 고급유 46,360원</v>
+        <v>휘발유 45,625원 / 고급유 46,100원</v>
       </c>
       <c r="P69" s="12">
         <f t="shared" si="6"/>
-        <v>91835</v>
+        <v>91725</v>
       </c>
       <c r="Q69" s="12"/>
       <c r="R69" s="13">
@@ -11240,22 +11236,22 @@
       </c>
       <c r="T69" s="12">
         <f t="shared" si="9"/>
-        <v>91835</v>
+        <v>91725</v>
       </c>
       <c r="U69" s="12">
         <f t="shared" si="10"/>
-        <v>2040.7777777777778</v>
+        <v>2038.3333333333333</v>
       </c>
       <c r="V69" s="12">
         <f t="shared" si="11"/>
-        <v>2040.7777777777778</v>
+        <v>2038.3333333333333</v>
       </c>
       <c r="W69" s="14">
         <f t="shared" si="12"/>
-        <v>91835</v>
-      </c>
-    </row>
-    <row r="70" spans="1:23" s="16" customFormat="1" ht="28.5" customHeight="1">
+        <v>91725</v>
+      </c>
+    </row>
+    <row r="70" spans="1:23" s="7" customFormat="1" ht="28.5" customHeight="1">
       <c r="A70" s="11">
         <f t="shared" si="0"/>
         <v>56</v>
@@ -11264,26 +11260,26 @@
         <v>10</v>
       </c>
       <c r="C70" s="11" t="s">
-        <v>1317</v>
+        <v>1516</v>
       </c>
       <c r="D70" s="11" t="s">
-        <v>48</v>
+        <v>69</v>
       </c>
       <c r="E70" s="11" t="s">
         <v>26</v>
       </c>
       <c r="F70" s="11" t="s">
-        <v>1318</v>
+        <v>1517</v>
       </c>
       <c r="G70" s="12">
-        <v>1829</v>
+        <v>1819</v>
       </c>
       <c r="H70" s="12">
-        <v>2309</v>
+        <v>2318</v>
       </c>
       <c r="I70" s="12"/>
       <c r="J70" s="12">
-        <v>1797</v>
+        <v>1799</v>
       </c>
       <c r="K70" s="12">
         <f t="shared" si="1"/>
@@ -11291,23 +11287,23 @@
       </c>
       <c r="L70" s="12">
         <f t="shared" si="2"/>
-        <v>1829</v>
+        <v>1819</v>
       </c>
       <c r="M70" s="12">
         <f t="shared" si="3"/>
-        <v>2309</v>
+        <v>2318</v>
       </c>
       <c r="N70" s="12">
         <f t="shared" si="4"/>
-        <v>1797</v>
+        <v>1799</v>
       </c>
       <c r="O70" s="12" t="str">
         <f t="shared" si="5"/>
-        <v>휘발유 45,725원 / 고급유 46,180원</v>
+        <v>휘발유 45,475원 / 고급유 46,360원</v>
       </c>
       <c r="P70" s="12">
         <f t="shared" si="6"/>
-        <v>91905</v>
+        <v>91835</v>
       </c>
       <c r="Q70" s="12"/>
       <c r="R70" s="13">
@@ -11320,50 +11316,50 @@
       </c>
       <c r="T70" s="12">
         <f t="shared" si="9"/>
-        <v>91905</v>
+        <v>91835</v>
       </c>
       <c r="U70" s="12">
         <f t="shared" si="10"/>
-        <v>2042.3333333333333</v>
+        <v>2040.7777777777778</v>
       </c>
       <c r="V70" s="12">
         <f t="shared" si="11"/>
-        <v>2042.3333333333333</v>
+        <v>2040.7777777777778</v>
       </c>
       <c r="W70" s="14">
         <f t="shared" si="12"/>
-        <v>91905</v>
-      </c>
-    </row>
-    <row r="71" spans="1:23" s="2" customFormat="1" ht="28.5" customHeight="1">
+        <v>91835</v>
+      </c>
+    </row>
+    <row r="71" spans="1:23" s="16" customFormat="1" ht="28.5" customHeight="1">
       <c r="A71" s="11">
         <f t="shared" si="0"/>
         <v>57</v>
       </c>
       <c r="B71" s="11" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="C71" s="11" t="s">
-        <v>1388</v>
-      </c>
-      <c r="D71" s="15" t="s">
-        <v>59</v>
+        <v>1317</v>
+      </c>
+      <c r="D71" s="11" t="s">
+        <v>48</v>
       </c>
       <c r="E71" s="11" t="s">
         <v>26</v>
       </c>
       <c r="F71" s="11" t="s">
-        <v>1389</v>
+        <v>1318</v>
       </c>
       <c r="G71" s="12">
-        <v>1810</v>
+        <v>1829</v>
       </c>
       <c r="H71" s="12">
-        <v>2335</v>
+        <v>2309</v>
       </c>
       <c r="I71" s="12"/>
       <c r="J71" s="12">
-        <v>1800</v>
+        <v>1797</v>
       </c>
       <c r="K71" s="12">
         <f t="shared" si="1"/>
@@ -11371,23 +11367,23 @@
       </c>
       <c r="L71" s="12">
         <f t="shared" si="2"/>
-        <v>1810</v>
+        <v>1829</v>
       </c>
       <c r="M71" s="12">
         <f t="shared" si="3"/>
-        <v>2335</v>
+        <v>2309</v>
       </c>
       <c r="N71" s="12">
         <f t="shared" si="4"/>
-        <v>1800</v>
+        <v>1797</v>
       </c>
       <c r="O71" s="12" t="str">
         <f t="shared" si="5"/>
-        <v>휘발유 45,250원 / 고급유 46,700원</v>
+        <v>휘발유 45,725원 / 고급유 46,180원</v>
       </c>
       <c r="P71" s="12">
         <f t="shared" si="6"/>
-        <v>91950</v>
+        <v>91905</v>
       </c>
       <c r="Q71" s="12"/>
       <c r="R71" s="13">
@@ -11400,19 +11396,19 @@
       </c>
       <c r="T71" s="12">
         <f t="shared" si="9"/>
-        <v>91950</v>
+        <v>91905</v>
       </c>
       <c r="U71" s="12">
         <f t="shared" si="10"/>
-        <v>2043.3333333333333</v>
+        <v>2042.3333333333333</v>
       </c>
       <c r="V71" s="12">
         <f t="shared" si="11"/>
-        <v>2043.3333333333333</v>
+        <v>2042.3333333333333</v>
       </c>
       <c r="W71" s="14">
         <f t="shared" si="12"/>
-        <v>91950</v>
+        <v>91905</v>
       </c>
     </row>
     <row r="72" spans="1:23" s="2" customFormat="1" ht="28.5" customHeight="1">
@@ -11424,26 +11420,26 @@
         <v>6</v>
       </c>
       <c r="C72" s="11" t="s">
-        <v>52</v>
+        <v>1388</v>
       </c>
       <c r="D72" s="15" t="s">
-        <v>45</v>
+        <v>59</v>
       </c>
       <c r="E72" s="11" t="s">
         <v>26</v>
       </c>
       <c r="F72" s="11" t="s">
-        <v>53</v>
+        <v>1389</v>
       </c>
       <c r="G72" s="12">
-        <v>1811</v>
+        <v>1810</v>
       </c>
       <c r="H72" s="12">
-        <v>2338</v>
+        <v>2335</v>
       </c>
       <c r="I72" s="12"/>
       <c r="J72" s="12">
-        <v>1798</v>
+        <v>1800</v>
       </c>
       <c r="K72" s="12">
         <f t="shared" si="1"/>
@@ -11451,23 +11447,23 @@
       </c>
       <c r="L72" s="12">
         <f t="shared" si="2"/>
-        <v>1811</v>
+        <v>1810</v>
       </c>
       <c r="M72" s="12">
         <f t="shared" si="3"/>
-        <v>2338</v>
+        <v>2335</v>
       </c>
       <c r="N72" s="12">
         <f t="shared" si="4"/>
-        <v>1798</v>
+        <v>1800</v>
       </c>
       <c r="O72" s="12" t="str">
         <f t="shared" si="5"/>
-        <v>휘발유 45,275원 / 고급유 46,760원</v>
+        <v>휘발유 45,250원 / 고급유 46,700원</v>
       </c>
       <c r="P72" s="12">
         <f t="shared" si="6"/>
-        <v>92035</v>
+        <v>91950</v>
       </c>
       <c r="Q72" s="12"/>
       <c r="R72" s="13">
@@ -11480,19 +11476,19 @@
       </c>
       <c r="T72" s="12">
         <f t="shared" si="9"/>
-        <v>92035</v>
+        <v>91950</v>
       </c>
       <c r="U72" s="12">
         <f t="shared" si="10"/>
-        <v>2045.2222222222222</v>
+        <v>2043.3333333333333</v>
       </c>
       <c r="V72" s="12">
         <f t="shared" si="11"/>
-        <v>2045.2222222222222</v>
+        <v>2043.3333333333333</v>
       </c>
       <c r="W72" s="14">
         <f t="shared" si="12"/>
-        <v>92035</v>
+        <v>91950</v>
       </c>
     </row>
     <row r="73" spans="1:23" s="2" customFormat="1" ht="28.5" customHeight="1">
@@ -11504,7 +11500,7 @@
         <v>6</v>
       </c>
       <c r="C73" s="11" t="s">
-        <v>236</v>
+        <v>52</v>
       </c>
       <c r="D73" s="15" t="s">
         <v>45</v>
@@ -11513,17 +11509,17 @@
         <v>26</v>
       </c>
       <c r="F73" s="11" t="s">
-        <v>237</v>
+        <v>53</v>
       </c>
       <c r="G73" s="12">
-        <v>1806</v>
+        <v>1811</v>
       </c>
       <c r="H73" s="12">
-        <v>2345</v>
+        <v>2338</v>
       </c>
       <c r="I73" s="12"/>
       <c r="J73" s="12">
-        <v>1792</v>
+        <v>1798</v>
       </c>
       <c r="K73" s="12">
         <f t="shared" si="1"/>
@@ -11531,23 +11527,23 @@
       </c>
       <c r="L73" s="12">
         <f t="shared" si="2"/>
-        <v>1806</v>
+        <v>1811</v>
       </c>
       <c r="M73" s="12">
         <f t="shared" si="3"/>
-        <v>2345</v>
+        <v>2338</v>
       </c>
       <c r="N73" s="12">
         <f t="shared" si="4"/>
-        <v>1792</v>
+        <v>1798</v>
       </c>
       <c r="O73" s="12" t="str">
         <f t="shared" si="5"/>
-        <v>휘발유 45,150원 / 고급유 46,900원</v>
+        <v>휘발유 45,275원 / 고급유 46,760원</v>
       </c>
       <c r="P73" s="12">
         <f t="shared" si="6"/>
-        <v>92050</v>
+        <v>92035</v>
       </c>
       <c r="Q73" s="12"/>
       <c r="R73" s="13">
@@ -11560,50 +11556,50 @@
       </c>
       <c r="T73" s="12">
         <f t="shared" si="9"/>
-        <v>92050</v>
+        <v>92035</v>
       </c>
       <c r="U73" s="12">
         <f t="shared" si="10"/>
-        <v>2045.5555555555557</v>
+        <v>2045.2222222222222</v>
       </c>
       <c r="V73" s="12">
         <f t="shared" si="11"/>
-        <v>2045.5555555555557</v>
+        <v>2045.2222222222222</v>
       </c>
       <c r="W73" s="14">
         <f t="shared" si="12"/>
-        <v>92050</v>
+        <v>92035</v>
       </c>
     </row>
     <row r="74" spans="1:23" s="2" customFormat="1" ht="28.5" customHeight="1">
       <c r="A74" s="11">
         <f t="shared" si="0"/>
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="B74" s="11" t="s">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="C74" s="11" t="s">
-        <v>1152</v>
+        <v>236</v>
       </c>
       <c r="D74" s="15" t="s">
-        <v>59</v>
+        <v>45</v>
       </c>
       <c r="E74" s="11" t="s">
         <v>26</v>
       </c>
       <c r="F74" s="11" t="s">
-        <v>1153</v>
+        <v>237</v>
       </c>
       <c r="G74" s="12">
-        <v>1850</v>
+        <v>1806</v>
       </c>
       <c r="H74" s="12">
-        <v>2290</v>
+        <v>2345</v>
       </c>
       <c r="I74" s="12"/>
       <c r="J74" s="12">
-        <v>1810</v>
+        <v>1792</v>
       </c>
       <c r="K74" s="12">
         <f t="shared" si="1"/>
@@ -11611,19 +11607,19 @@
       </c>
       <c r="L74" s="12">
         <f t="shared" si="2"/>
-        <v>1850</v>
+        <v>1806</v>
       </c>
       <c r="M74" s="12">
         <f t="shared" si="3"/>
-        <v>2290</v>
+        <v>2345</v>
       </c>
       <c r="N74" s="12">
         <f t="shared" si="4"/>
-        <v>1810</v>
+        <v>1792</v>
       </c>
       <c r="O74" s="12" t="str">
         <f t="shared" si="5"/>
-        <v>휘발유 46,250원 / 고급유 45,800원</v>
+        <v>휘발유 45,150원 / 고급유 46,900원</v>
       </c>
       <c r="P74" s="12">
         <f t="shared" si="6"/>
@@ -11658,32 +11654,32 @@
     <row r="75" spans="1:23" s="2" customFormat="1" ht="28.5" customHeight="1">
       <c r="A75" s="11">
         <f t="shared" si="0"/>
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B75" s="11" t="s">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="C75" s="11" t="s">
-        <v>234</v>
+        <v>1152</v>
       </c>
       <c r="D75" s="15" t="s">
-        <v>78</v>
+        <v>59</v>
       </c>
       <c r="E75" s="11" t="s">
         <v>26</v>
       </c>
       <c r="F75" s="11" t="s">
-        <v>235</v>
+        <v>1153</v>
       </c>
       <c r="G75" s="12">
-        <v>1815</v>
+        <v>1850</v>
       </c>
       <c r="H75" s="12">
-        <v>2335</v>
+        <v>2290</v>
       </c>
       <c r="I75" s="12"/>
       <c r="J75" s="12">
-        <v>1825</v>
+        <v>1810</v>
       </c>
       <c r="K75" s="12">
         <f t="shared" si="1"/>
@@ -11691,23 +11687,23 @@
       </c>
       <c r="L75" s="12">
         <f t="shared" si="2"/>
-        <v>1815</v>
+        <v>1850</v>
       </c>
       <c r="M75" s="12">
         <f t="shared" si="3"/>
-        <v>2335</v>
+        <v>2290</v>
       </c>
       <c r="N75" s="12">
         <f t="shared" si="4"/>
-        <v>1825</v>
+        <v>1810</v>
       </c>
       <c r="O75" s="12" t="str">
         <f t="shared" si="5"/>
-        <v>휘발유 45,375원 / 고급유 46,700원</v>
+        <v>휘발유 46,250원 / 고급유 45,800원</v>
       </c>
       <c r="P75" s="12">
         <f t="shared" si="6"/>
-        <v>92075</v>
+        <v>92050</v>
       </c>
       <c r="Q75" s="12"/>
       <c r="R75" s="13">
@@ -11720,50 +11716,50 @@
       </c>
       <c r="T75" s="12">
         <f t="shared" si="9"/>
-        <v>92075</v>
+        <v>92050</v>
       </c>
       <c r="U75" s="12">
         <f t="shared" si="10"/>
-        <v>2046.1111111111111</v>
+        <v>2045.5555555555557</v>
       </c>
       <c r="V75" s="12">
         <f t="shared" si="11"/>
-        <v>2046.1111111111111</v>
+        <v>2045.5555555555557</v>
       </c>
       <c r="W75" s="14">
         <f t="shared" si="12"/>
-        <v>92075</v>
-      </c>
-    </row>
-    <row r="76" spans="1:23" s="7" customFormat="1" ht="28.5" customHeight="1">
+        <v>92050</v>
+      </c>
+    </row>
+    <row r="76" spans="1:23" s="2" customFormat="1" ht="28.5" customHeight="1">
       <c r="A76" s="11">
         <f t="shared" si="0"/>
         <v>62</v>
       </c>
       <c r="B76" s="11" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="C76" s="11" t="s">
-        <v>280</v>
+        <v>234</v>
       </c>
       <c r="D76" s="15" t="s">
-        <v>45</v>
+        <v>78</v>
       </c>
       <c r="E76" s="11" t="s">
         <v>26</v>
       </c>
       <c r="F76" s="11" t="s">
-        <v>281</v>
+        <v>235</v>
       </c>
       <c r="G76" s="12">
-        <v>1808</v>
+        <v>1815</v>
       </c>
       <c r="H76" s="12">
-        <v>2345</v>
+        <v>2335</v>
       </c>
       <c r="I76" s="12"/>
       <c r="J76" s="12">
-        <v>1794</v>
+        <v>1825</v>
       </c>
       <c r="K76" s="12">
         <f t="shared" si="1"/>
@@ -11771,23 +11767,23 @@
       </c>
       <c r="L76" s="12">
         <f t="shared" si="2"/>
-        <v>1808</v>
+        <v>1815</v>
       </c>
       <c r="M76" s="12">
         <f t="shared" si="3"/>
-        <v>2345</v>
+        <v>2335</v>
       </c>
       <c r="N76" s="12">
         <f t="shared" si="4"/>
-        <v>1794</v>
+        <v>1825</v>
       </c>
       <c r="O76" s="12" t="str">
         <f t="shared" si="5"/>
-        <v>휘발유 45,200원 / 고급유 46,900원</v>
+        <v>휘발유 45,375원 / 고급유 46,700원</v>
       </c>
       <c r="P76" s="12">
         <f t="shared" si="6"/>
-        <v>92100</v>
+        <v>92075</v>
       </c>
       <c r="Q76" s="12"/>
       <c r="R76" s="13">
@@ -11800,19 +11796,19 @@
       </c>
       <c r="T76" s="12">
         <f t="shared" si="9"/>
-        <v>92100</v>
+        <v>92075</v>
       </c>
       <c r="U76" s="12">
         <f t="shared" si="10"/>
-        <v>2046.6666666666667</v>
+        <v>2046.1111111111111</v>
       </c>
       <c r="V76" s="12">
         <f t="shared" si="11"/>
-        <v>2046.6666666666667</v>
+        <v>2046.1111111111111</v>
       </c>
       <c r="W76" s="14">
         <f t="shared" si="12"/>
-        <v>92100</v>
+        <v>92075</v>
       </c>
     </row>
     <row r="77" spans="1:23" s="7" customFormat="1" ht="28.5" customHeight="1">
@@ -11821,10 +11817,10 @@
         <v>63</v>
       </c>
       <c r="B77" s="11" t="s">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="C77" s="11" t="s">
-        <v>877</v>
+        <v>280</v>
       </c>
       <c r="D77" s="15" t="s">
         <v>45</v>
@@ -11833,17 +11829,17 @@
         <v>26</v>
       </c>
       <c r="F77" s="11" t="s">
-        <v>878</v>
+        <v>281</v>
       </c>
       <c r="G77" s="12">
-        <v>1825</v>
+        <v>1808</v>
       </c>
       <c r="H77" s="12">
-        <v>2325</v>
+        <v>2345</v>
       </c>
       <c r="I77" s="12"/>
       <c r="J77" s="12">
-        <v>1815</v>
+        <v>1794</v>
       </c>
       <c r="K77" s="12">
         <f t="shared" si="1"/>
@@ -11851,23 +11847,23 @@
       </c>
       <c r="L77" s="12">
         <f t="shared" si="2"/>
-        <v>1825</v>
+        <v>1808</v>
       </c>
       <c r="M77" s="12">
         <f t="shared" si="3"/>
-        <v>2325</v>
+        <v>2345</v>
       </c>
       <c r="N77" s="12">
         <f t="shared" si="4"/>
-        <v>1815</v>
+        <v>1794</v>
       </c>
       <c r="O77" s="12" t="str">
         <f t="shared" si="5"/>
-        <v>휘발유 45,625원 / 고급유 46,500원</v>
+        <v>휘발유 45,200원 / 고급유 46,900원</v>
       </c>
       <c r="P77" s="12">
         <f t="shared" si="6"/>
-        <v>92125</v>
+        <v>92100</v>
       </c>
       <c r="Q77" s="12"/>
       <c r="R77" s="13">
@@ -11880,22 +11876,22 @@
       </c>
       <c r="T77" s="12">
         <f t="shared" si="9"/>
-        <v>92125</v>
+        <v>92100</v>
       </c>
       <c r="U77" s="12">
         <f t="shared" si="10"/>
-        <v>2047.2222222222222</v>
+        <v>2046.6666666666667</v>
       </c>
       <c r="V77" s="12">
         <f t="shared" si="11"/>
-        <v>2047.2222222222222</v>
+        <v>2046.6666666666667</v>
       </c>
       <c r="W77" s="14">
         <f t="shared" si="12"/>
-        <v>92125</v>
-      </c>
-    </row>
-    <row r="78" spans="1:23" s="2" customFormat="1" ht="28.5" customHeight="1">
+        <v>92100</v>
+      </c>
+    </row>
+    <row r="78" spans="1:23" s="7" customFormat="1" ht="28.5" customHeight="1">
       <c r="A78" s="11">
         <f t="shared" si="0"/>
         <v>64</v>
@@ -11904,26 +11900,26 @@
         <v>12</v>
       </c>
       <c r="C78" s="11" t="s">
-        <v>314</v>
+        <v>877</v>
       </c>
       <c r="D78" s="15" t="s">
-        <v>59</v>
+        <v>45</v>
       </c>
       <c r="E78" s="11" t="s">
         <v>26</v>
       </c>
       <c r="F78" s="11" t="s">
-        <v>315</v>
+        <v>878</v>
       </c>
       <c r="G78" s="12">
-        <v>1798</v>
+        <v>1825</v>
       </c>
       <c r="H78" s="12">
-        <v>2359</v>
+        <v>2325</v>
       </c>
       <c r="I78" s="12"/>
       <c r="J78" s="12">
-        <v>1794</v>
+        <v>1815</v>
       </c>
       <c r="K78" s="12">
         <f t="shared" si="1"/>
@@ -11931,23 +11927,23 @@
       </c>
       <c r="L78" s="12">
         <f t="shared" si="2"/>
-        <v>1798</v>
+        <v>1825</v>
       </c>
       <c r="M78" s="12">
         <f t="shared" si="3"/>
-        <v>2359</v>
+        <v>2325</v>
       </c>
       <c r="N78" s="12">
         <f t="shared" si="4"/>
-        <v>1794</v>
+        <v>1815</v>
       </c>
       <c r="O78" s="12" t="str">
         <f t="shared" si="5"/>
-        <v>휘발유 44,950원 / 고급유 47,180원</v>
+        <v>휘발유 45,625원 / 고급유 46,500원</v>
       </c>
       <c r="P78" s="12">
         <f t="shared" si="6"/>
-        <v>92130</v>
+        <v>92125</v>
       </c>
       <c r="Q78" s="12"/>
       <c r="R78" s="13">
@@ -11960,40 +11956,40 @@
       </c>
       <c r="T78" s="12">
         <f t="shared" si="9"/>
-        <v>92130</v>
+        <v>92125</v>
       </c>
       <c r="U78" s="12">
         <f t="shared" si="10"/>
-        <v>2047.3333333333333</v>
+        <v>2047.2222222222222</v>
       </c>
       <c r="V78" s="12">
         <f t="shared" si="11"/>
-        <v>2047.3333333333333</v>
+        <v>2047.2222222222222</v>
       </c>
       <c r="W78" s="14">
         <f t="shared" si="12"/>
-        <v>92130</v>
+        <v>92125</v>
       </c>
     </row>
     <row r="79" spans="1:23" s="2" customFormat="1" ht="28.5" customHeight="1">
       <c r="A79" s="11">
         <f t="shared" ref="A79:A142" si="13">IF($T79="","",1+COUNTIF($W$15:$W$882,"&lt;"&amp;W79))</f>
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="B79" s="11" t="s">
         <v>12</v>
       </c>
       <c r="C79" s="11" t="s">
-        <v>1206</v>
+        <v>314</v>
       </c>
       <c r="D79" s="15" t="s">
-        <v>45</v>
+        <v>59</v>
       </c>
       <c r="E79" s="11" t="s">
         <v>26</v>
       </c>
       <c r="F79" s="11" t="s">
-        <v>1207</v>
+        <v>315</v>
       </c>
       <c r="G79" s="12">
         <v>1798</v>
@@ -12003,7 +11999,7 @@
       </c>
       <c r="I79" s="12"/>
       <c r="J79" s="12">
-        <v>1839</v>
+        <v>1794</v>
       </c>
       <c r="K79" s="12">
         <f t="shared" ref="K79:K142" si="14">IF(AND(IFERROR(SEARCH("현대오일뱅크",$C79),0)&gt;0,IFERROR(SEARCH("직영",$C79),0)&gt;0),$B$13,0)</f>
@@ -12019,7 +12015,7 @@
       </c>
       <c r="N79" s="12">
         <f t="shared" ref="N79:N142" si="17">IF($J79="","",$J79+$K79)</f>
-        <v>1839</v>
+        <v>1794</v>
       </c>
       <c r="O79" s="12" t="str">
         <f t="shared" ref="O79:O142" si="18">IF($B$10=0,"",IFERROR(IF($B$4&gt;0,"휘발유 "&amp;TEXT(IF($L79="",1/0,$L79*$B$4),"#,##0")&amp;"원","")&amp;IF($B$5&gt;0,IF($B$4&gt;0," / ","")&amp;"고급유 "&amp;TEXT(IF($M79="",1/0,$M79*$B$5),"#,##0")&amp;"원","")&amp;IF($B$6&gt;0,IF(OR($B$4&gt;0,$B$5&gt;0)," / ","")&amp;"경유 "&amp;TEXT(IF($N79="",1/0,$N79*$B$6),"#,##0")&amp;"원",""),""))</f>
@@ -12058,13 +12054,13 @@
     <row r="80" spans="1:23" s="2" customFormat="1" ht="28.5" customHeight="1">
       <c r="A80" s="11">
         <f t="shared" si="13"/>
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B80" s="11" t="s">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="C80" s="11" t="s">
-        <v>1174</v>
+        <v>1206</v>
       </c>
       <c r="D80" s="15" t="s">
         <v>45</v>
@@ -12073,17 +12069,17 @@
         <v>26</v>
       </c>
       <c r="F80" s="11" t="s">
-        <v>1175</v>
+        <v>1207</v>
       </c>
       <c r="G80" s="12">
-        <v>1809</v>
+        <v>1798</v>
       </c>
       <c r="H80" s="12">
-        <v>2346</v>
+        <v>2359</v>
       </c>
       <c r="I80" s="12"/>
       <c r="J80" s="12">
-        <v>1798</v>
+        <v>1839</v>
       </c>
       <c r="K80" s="12">
         <f t="shared" si="14"/>
@@ -12091,23 +12087,23 @@
       </c>
       <c r="L80" s="12">
         <f t="shared" si="15"/>
-        <v>1809</v>
+        <v>1798</v>
       </c>
       <c r="M80" s="12">
         <f t="shared" si="16"/>
-        <v>2346</v>
+        <v>2359</v>
       </c>
       <c r="N80" s="12">
         <f t="shared" si="17"/>
-        <v>1798</v>
+        <v>1839</v>
       </c>
       <c r="O80" s="12" t="str">
         <f t="shared" si="18"/>
-        <v>휘발유 45,225원 / 고급유 46,920원</v>
+        <v>휘발유 44,950원 / 고급유 47,180원</v>
       </c>
       <c r="P80" s="12">
         <f t="shared" si="19"/>
-        <v>92145</v>
+        <v>92130</v>
       </c>
       <c r="Q80" s="12"/>
       <c r="R80" s="13">
@@ -12120,19 +12116,19 @@
       </c>
       <c r="T80" s="12">
         <f t="shared" si="22"/>
-        <v>92145</v>
+        <v>92130</v>
       </c>
       <c r="U80" s="12">
         <f t="shared" si="23"/>
-        <v>2047.6666666666667</v>
+        <v>2047.3333333333333</v>
       </c>
       <c r="V80" s="12">
         <f t="shared" si="24"/>
-        <v>2047.6666666666667</v>
+        <v>2047.3333333333333</v>
       </c>
       <c r="W80" s="14">
         <f t="shared" si="25"/>
-        <v>92145</v>
+        <v>92130</v>
       </c>
     </row>
     <row r="81" spans="1:23" s="2" customFormat="1" ht="28.5" customHeight="1">
@@ -12141,29 +12137,29 @@
         <v>67</v>
       </c>
       <c r="B81" s="11" t="s">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="C81" s="11" t="s">
-        <v>238</v>
+        <v>1174</v>
       </c>
       <c r="D81" s="15" t="s">
-        <v>59</v>
+        <v>45</v>
       </c>
       <c r="E81" s="11" t="s">
         <v>26</v>
       </c>
       <c r="F81" s="11" t="s">
-        <v>239</v>
+        <v>1175</v>
       </c>
       <c r="G81" s="12">
-        <v>1850</v>
+        <v>1809</v>
       </c>
       <c r="H81" s="12">
-        <v>2300</v>
+        <v>2346</v>
       </c>
       <c r="I81" s="12"/>
       <c r="J81" s="12">
-        <v>1835</v>
+        <v>1798</v>
       </c>
       <c r="K81" s="12">
         <f t="shared" si="14"/>
@@ -12171,23 +12167,23 @@
       </c>
       <c r="L81" s="12">
         <f t="shared" si="15"/>
-        <v>1850</v>
+        <v>1809</v>
       </c>
       <c r="M81" s="12">
         <f t="shared" si="16"/>
-        <v>2300</v>
+        <v>2346</v>
       </c>
       <c r="N81" s="12">
         <f t="shared" si="17"/>
-        <v>1835</v>
+        <v>1798</v>
       </c>
       <c r="O81" s="12" t="str">
         <f t="shared" si="18"/>
-        <v>휘발유 46,250원 / 고급유 46,000원</v>
+        <v>휘발유 45,225원 / 고급유 46,920원</v>
       </c>
       <c r="P81" s="12">
         <f t="shared" si="19"/>
-        <v>92250</v>
+        <v>92145</v>
       </c>
       <c r="Q81" s="12"/>
       <c r="R81" s="13">
@@ -12200,50 +12196,50 @@
       </c>
       <c r="T81" s="12">
         <f t="shared" si="22"/>
-        <v>92250</v>
+        <v>92145</v>
       </c>
       <c r="U81" s="12">
         <f t="shared" si="23"/>
-        <v>2050</v>
+        <v>2047.6666666666667</v>
       </c>
       <c r="V81" s="12">
         <f t="shared" si="24"/>
-        <v>2050</v>
+        <v>2047.6666666666667</v>
       </c>
       <c r="W81" s="14">
         <f t="shared" si="25"/>
-        <v>92250</v>
-      </c>
-    </row>
-    <row r="82" spans="1:23" s="7" customFormat="1" ht="28.5" customHeight="1">
+        <v>92145</v>
+      </c>
+    </row>
+    <row r="82" spans="1:23" s="2" customFormat="1" ht="28.5" customHeight="1">
       <c r="A82" s="11">
         <f t="shared" si="13"/>
         <v>68</v>
       </c>
       <c r="B82" s="11" t="s">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="C82" s="11" t="s">
-        <v>1114</v>
+        <v>238</v>
       </c>
       <c r="D82" s="15" t="s">
-        <v>45</v>
+        <v>59</v>
       </c>
       <c r="E82" s="11" t="s">
         <v>26</v>
       </c>
       <c r="F82" s="11" t="s">
-        <v>1115</v>
+        <v>239</v>
       </c>
       <c r="G82" s="12">
-        <v>1804</v>
+        <v>1850</v>
       </c>
       <c r="H82" s="12">
-        <v>2358</v>
+        <v>2300</v>
       </c>
       <c r="I82" s="12"/>
       <c r="J82" s="12">
-        <v>1792</v>
+        <v>1835</v>
       </c>
       <c r="K82" s="12">
         <f t="shared" si="14"/>
@@ -12251,23 +12247,23 @@
       </c>
       <c r="L82" s="12">
         <f t="shared" si="15"/>
-        <v>1804</v>
+        <v>1850</v>
       </c>
       <c r="M82" s="12">
         <f t="shared" si="16"/>
-        <v>2358</v>
+        <v>2300</v>
       </c>
       <c r="N82" s="12">
         <f t="shared" si="17"/>
-        <v>1792</v>
+        <v>1835</v>
       </c>
       <c r="O82" s="12" t="str">
         <f t="shared" si="18"/>
-        <v>휘발유 45,100원 / 고급유 47,160원</v>
+        <v>휘발유 46,250원 / 고급유 46,000원</v>
       </c>
       <c r="P82" s="12">
         <f t="shared" si="19"/>
-        <v>92260</v>
+        <v>92250</v>
       </c>
       <c r="Q82" s="12"/>
       <c r="R82" s="13">
@@ -12280,22 +12276,22 @@
       </c>
       <c r="T82" s="12">
         <f t="shared" si="22"/>
-        <v>92260</v>
+        <v>92250</v>
       </c>
       <c r="U82" s="12">
         <f t="shared" si="23"/>
-        <v>2050.2222222222222</v>
+        <v>2050</v>
       </c>
       <c r="V82" s="12">
         <f t="shared" si="24"/>
-        <v>2050.2222222222222</v>
+        <v>2050</v>
       </c>
       <c r="W82" s="14">
         <f t="shared" si="25"/>
-        <v>92260</v>
-      </c>
-    </row>
-    <row r="83" spans="1:23" s="2" customFormat="1" ht="28.5" customHeight="1">
+        <v>92250</v>
+      </c>
+    </row>
+    <row r="83" spans="1:23" s="7" customFormat="1" ht="28.5" customHeight="1">
       <c r="A83" s="11">
         <f t="shared" si="13"/>
         <v>69</v>
@@ -12304,26 +12300,26 @@
         <v>6</v>
       </c>
       <c r="C83" s="11" t="s">
-        <v>1613</v>
+        <v>1114</v>
       </c>
       <c r="D83" s="15" t="s">
-        <v>78</v>
+        <v>45</v>
       </c>
       <c r="E83" s="11" t="s">
         <v>26</v>
       </c>
       <c r="F83" s="11" t="s">
-        <v>1614</v>
+        <v>1115</v>
       </c>
       <c r="G83" s="12">
-        <v>1815</v>
+        <v>1804</v>
       </c>
       <c r="H83" s="12">
-        <v>2345</v>
+        <v>2358</v>
       </c>
       <c r="I83" s="12"/>
       <c r="J83" s="12">
-        <v>1799</v>
+        <v>1792</v>
       </c>
       <c r="K83" s="12">
         <f t="shared" si="14"/>
@@ -12331,23 +12327,23 @@
       </c>
       <c r="L83" s="12">
         <f t="shared" si="15"/>
-        <v>1815</v>
+        <v>1804</v>
       </c>
       <c r="M83" s="12">
         <f t="shared" si="16"/>
-        <v>2345</v>
+        <v>2358</v>
       </c>
       <c r="N83" s="12">
         <f t="shared" si="17"/>
-        <v>1799</v>
+        <v>1792</v>
       </c>
       <c r="O83" s="12" t="str">
         <f t="shared" si="18"/>
-        <v>휘발유 45,375원 / 고급유 46,900원</v>
+        <v>휘발유 45,100원 / 고급유 47,160원</v>
       </c>
       <c r="P83" s="12">
         <f t="shared" si="19"/>
-        <v>92275</v>
+        <v>92260</v>
       </c>
       <c r="Q83" s="12"/>
       <c r="R83" s="13">
@@ -12360,19 +12356,19 @@
       </c>
       <c r="T83" s="12">
         <f t="shared" si="22"/>
-        <v>92275</v>
+        <v>92260</v>
       </c>
       <c r="U83" s="12">
         <f t="shared" si="23"/>
-        <v>2050.5555555555557</v>
+        <v>2050.2222222222222</v>
       </c>
       <c r="V83" s="12">
         <f t="shared" si="24"/>
-        <v>2050.5555555555557</v>
+        <v>2050.2222222222222</v>
       </c>
       <c r="W83" s="14">
         <f t="shared" si="25"/>
-        <v>92275</v>
+        <v>92260</v>
       </c>
     </row>
     <row r="84" spans="1:23" s="2" customFormat="1" ht="28.5" customHeight="1">
@@ -12381,29 +12377,29 @@
         <v>70</v>
       </c>
       <c r="B84" s="11" t="s">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="C84" s="11" t="s">
-        <v>166</v>
-      </c>
-      <c r="D84" s="11" t="s">
-        <v>57</v>
+        <v>1613</v>
+      </c>
+      <c r="D84" s="15" t="s">
+        <v>78</v>
       </c>
       <c r="E84" s="11" t="s">
         <v>26</v>
       </c>
       <c r="F84" s="11" t="s">
-        <v>167</v>
+        <v>1614</v>
       </c>
       <c r="G84" s="12">
-        <v>1829</v>
+        <v>1815</v>
       </c>
       <c r="H84" s="12">
-        <v>2329</v>
+        <v>2345</v>
       </c>
       <c r="I84" s="12"/>
       <c r="J84" s="12">
-        <v>1809</v>
+        <v>1799</v>
       </c>
       <c r="K84" s="12">
         <f t="shared" si="14"/>
@@ -12411,23 +12407,23 @@
       </c>
       <c r="L84" s="12">
         <f t="shared" si="15"/>
-        <v>1829</v>
+        <v>1815</v>
       </c>
       <c r="M84" s="12">
         <f t="shared" si="16"/>
-        <v>2329</v>
+        <v>2345</v>
       </c>
       <c r="N84" s="12">
         <f t="shared" si="17"/>
-        <v>1809</v>
+        <v>1799</v>
       </c>
       <c r="O84" s="12" t="str">
         <f t="shared" si="18"/>
-        <v>휘발유 45,725원 / 고급유 46,580원</v>
+        <v>휘발유 45,375원 / 고급유 46,900원</v>
       </c>
       <c r="P84" s="12">
         <f t="shared" si="19"/>
-        <v>92305</v>
+        <v>92275</v>
       </c>
       <c r="Q84" s="12"/>
       <c r="R84" s="13">
@@ -12440,19 +12436,19 @@
       </c>
       <c r="T84" s="12">
         <f t="shared" si="22"/>
-        <v>92305</v>
+        <v>92275</v>
       </c>
       <c r="U84" s="12">
         <f t="shared" si="23"/>
-        <v>2051.2222222222222</v>
+        <v>2050.5555555555557</v>
       </c>
       <c r="V84" s="12">
         <f t="shared" si="24"/>
-        <v>2051.2222222222222</v>
+        <v>2050.5555555555557</v>
       </c>
       <c r="W84" s="14">
         <f t="shared" si="25"/>
-        <v>92305</v>
+        <v>92275</v>
       </c>
     </row>
     <row r="85" spans="1:23" s="2" customFormat="1" ht="28.5" customHeight="1">
@@ -12461,10 +12457,10 @@
         <v>71</v>
       </c>
       <c r="B85" s="11" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="C85" s="11" t="s">
-        <v>1548</v>
+        <v>166</v>
       </c>
       <c r="D85" s="11" t="s">
         <v>57</v>
@@ -12473,17 +12469,17 @@
         <v>26</v>
       </c>
       <c r="F85" s="11" t="s">
-        <v>1549</v>
+        <v>167</v>
       </c>
       <c r="G85" s="12">
         <v>1829</v>
       </c>
       <c r="H85" s="12">
-        <v>2330</v>
+        <v>2329</v>
       </c>
       <c r="I85" s="12"/>
       <c r="J85" s="12">
-        <v>1815</v>
+        <v>1809</v>
       </c>
       <c r="K85" s="12">
         <f t="shared" si="14"/>
@@ -12495,19 +12491,19 @@
       </c>
       <c r="M85" s="12">
         <f t="shared" si="16"/>
-        <v>2330</v>
+        <v>2329</v>
       </c>
       <c r="N85" s="12">
         <f t="shared" si="17"/>
-        <v>1815</v>
+        <v>1809</v>
       </c>
       <c r="O85" s="12" t="str">
         <f t="shared" si="18"/>
-        <v>휘발유 45,725원 / 고급유 46,600원</v>
+        <v>휘발유 45,725원 / 고급유 46,580원</v>
       </c>
       <c r="P85" s="12">
         <f t="shared" si="19"/>
-        <v>92325</v>
+        <v>92305</v>
       </c>
       <c r="Q85" s="12"/>
       <c r="R85" s="13">
@@ -12520,19 +12516,19 @@
       </c>
       <c r="T85" s="12">
         <f t="shared" si="22"/>
-        <v>92325</v>
+        <v>92305</v>
       </c>
       <c r="U85" s="12">
         <f t="shared" si="23"/>
-        <v>2051.6666666666665</v>
+        <v>2051.2222222222222</v>
       </c>
       <c r="V85" s="12">
         <f t="shared" si="24"/>
-        <v>2051.6666666666665</v>
+        <v>2051.2222222222222</v>
       </c>
       <c r="W85" s="14">
         <f t="shared" si="25"/>
-        <v>92325</v>
+        <v>92305</v>
       </c>
     </row>
     <row r="86" spans="1:23" s="2" customFormat="1" ht="28.5" customHeight="1">
@@ -12544,26 +12540,26 @@
         <v>10</v>
       </c>
       <c r="C86" s="11" t="s">
-        <v>1757</v>
+        <v>1548</v>
       </c>
       <c r="D86" s="11" t="s">
-        <v>78</v>
+        <v>57</v>
       </c>
       <c r="E86" s="11" t="s">
         <v>26</v>
       </c>
       <c r="F86" s="11" t="s">
-        <v>1758</v>
+        <v>1549</v>
       </c>
       <c r="G86" s="12">
-        <v>1855</v>
+        <v>1829</v>
       </c>
       <c r="H86" s="12">
-        <v>2300</v>
+        <v>2330</v>
       </c>
       <c r="I86" s="12"/>
       <c r="J86" s="12">
-        <v>1855</v>
+        <v>1815</v>
       </c>
       <c r="K86" s="12">
         <f t="shared" si="14"/>
@@ -12571,23 +12567,23 @@
       </c>
       <c r="L86" s="12">
         <f t="shared" si="15"/>
-        <v>1855</v>
+        <v>1829</v>
       </c>
       <c r="M86" s="12">
         <f t="shared" si="16"/>
-        <v>2300</v>
+        <v>2330</v>
       </c>
       <c r="N86" s="12">
         <f t="shared" si="17"/>
-        <v>1855</v>
+        <v>1815</v>
       </c>
       <c r="O86" s="12" t="str">
         <f t="shared" si="18"/>
-        <v>휘발유 46,375원 / 고급유 46,000원</v>
+        <v>휘발유 45,725원 / 고급유 46,600원</v>
       </c>
       <c r="P86" s="12">
         <f t="shared" si="19"/>
-        <v>92375</v>
+        <v>92325</v>
       </c>
       <c r="Q86" s="12"/>
       <c r="R86" s="13">
@@ -12600,19 +12596,19 @@
       </c>
       <c r="T86" s="12">
         <f t="shared" si="22"/>
-        <v>92375</v>
+        <v>92325</v>
       </c>
       <c r="U86" s="12">
         <f t="shared" si="23"/>
-        <v>2052.7777777777778</v>
+        <v>2051.6666666666665</v>
       </c>
       <c r="V86" s="12">
         <f t="shared" si="24"/>
-        <v>2052.7777777777778</v>
+        <v>2051.6666666666665</v>
       </c>
       <c r="W86" s="14">
         <f t="shared" si="25"/>
-        <v>92375</v>
+        <v>92325</v>
       </c>
     </row>
     <row r="87" spans="1:23" s="2" customFormat="1" ht="28.5" customHeight="1">
@@ -12621,53 +12617,53 @@
         <v>73</v>
       </c>
       <c r="B87" s="11" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="C87" s="11" t="s">
-        <v>192</v>
-      </c>
-      <c r="D87" s="15" t="s">
-        <v>45</v>
+        <v>1756</v>
+      </c>
+      <c r="D87" s="11" t="s">
+        <v>78</v>
       </c>
       <c r="E87" s="11" t="s">
         <v>26</v>
       </c>
       <c r="F87" s="11" t="s">
-        <v>193</v>
+        <v>1757</v>
       </c>
       <c r="G87" s="12">
-        <v>1852</v>
+        <v>1855</v>
       </c>
       <c r="H87" s="12">
-        <v>2328</v>
+        <v>2300</v>
       </c>
       <c r="I87" s="12"/>
       <c r="J87" s="12">
-        <v>1844</v>
+        <v>1855</v>
       </c>
       <c r="K87" s="12">
         <f t="shared" si="14"/>
-        <v>-10</v>
+        <v>0</v>
       </c>
       <c r="L87" s="12">
         <f t="shared" si="15"/>
-        <v>1842</v>
+        <v>1855</v>
       </c>
       <c r="M87" s="12">
         <f t="shared" si="16"/>
-        <v>2318</v>
+        <v>2300</v>
       </c>
       <c r="N87" s="12">
         <f t="shared" si="17"/>
-        <v>1834</v>
+        <v>1855</v>
       </c>
       <c r="O87" s="12" t="str">
         <f t="shared" si="18"/>
-        <v>휘발유 46,050원 / 고급유 46,360원</v>
+        <v>휘발유 46,375원 / 고급유 46,000원</v>
       </c>
       <c r="P87" s="12">
         <f t="shared" si="19"/>
-        <v>92410</v>
+        <v>92375</v>
       </c>
       <c r="Q87" s="12"/>
       <c r="R87" s="13">
@@ -12680,31 +12676,31 @@
       </c>
       <c r="T87" s="12">
         <f t="shared" si="22"/>
-        <v>92410</v>
+        <v>92375</v>
       </c>
       <c r="U87" s="12">
         <f t="shared" si="23"/>
-        <v>2053.5555555555557</v>
+        <v>2052.7777777777778</v>
       </c>
       <c r="V87" s="12">
         <f t="shared" si="24"/>
-        <v>2053.5555555555557</v>
+        <v>2052.7777777777778</v>
       </c>
       <c r="W87" s="14">
         <f t="shared" si="25"/>
-        <v>92410</v>
-      </c>
-    </row>
-    <row r="88" spans="1:23" s="7" customFormat="1" ht="28.5" customHeight="1">
+        <v>92375</v>
+      </c>
+    </row>
+    <row r="88" spans="1:23" s="2" customFormat="1" ht="28.5" customHeight="1">
       <c r="A88" s="11">
         <f t="shared" si="13"/>
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="B88" s="11" t="s">
         <v>12</v>
       </c>
       <c r="C88" s="11" t="s">
-        <v>206</v>
+        <v>192</v>
       </c>
       <c r="D88" s="15" t="s">
         <v>45</v>
@@ -12713,7 +12709,7 @@
         <v>26</v>
       </c>
       <c r="F88" s="11" t="s">
-        <v>207</v>
+        <v>193</v>
       </c>
       <c r="G88" s="12">
         <v>1852</v>
@@ -12775,59 +12771,59 @@
         <v>92410</v>
       </c>
     </row>
-    <row r="89" spans="1:23" s="2" customFormat="1" ht="28.5" customHeight="1">
+    <row r="89" spans="1:23" s="7" customFormat="1" ht="28.5" customHeight="1">
       <c r="A89" s="11">
         <f t="shared" si="13"/>
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B89" s="11" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="C89" s="11" t="s">
-        <v>1464</v>
-      </c>
-      <c r="D89" s="11" t="s">
-        <v>48</v>
+        <v>206</v>
+      </c>
+      <c r="D89" s="15" t="s">
+        <v>45</v>
       </c>
       <c r="E89" s="11" t="s">
         <v>26</v>
       </c>
       <c r="F89" s="11" t="s">
-        <v>1465</v>
+        <v>207</v>
       </c>
       <c r="G89" s="12">
-        <v>1819</v>
+        <v>1852</v>
       </c>
       <c r="H89" s="12">
-        <v>2349</v>
+        <v>2328</v>
       </c>
       <c r="I89" s="12"/>
       <c r="J89" s="12">
-        <v>1818</v>
+        <v>1844</v>
       </c>
       <c r="K89" s="12">
         <f t="shared" si="14"/>
-        <v>0</v>
+        <v>-10</v>
       </c>
       <c r="L89" s="12">
         <f t="shared" si="15"/>
-        <v>1819</v>
+        <v>1842</v>
       </c>
       <c r="M89" s="12">
         <f t="shared" si="16"/>
-        <v>2349</v>
+        <v>2318</v>
       </c>
       <c r="N89" s="12">
         <f t="shared" si="17"/>
-        <v>1818</v>
+        <v>1834</v>
       </c>
       <c r="O89" s="12" t="str">
         <f t="shared" si="18"/>
-        <v>휘발유 45,475원 / 고급유 46,980원</v>
+        <v>휘발유 46,050원 / 고급유 46,360원</v>
       </c>
       <c r="P89" s="12">
         <f t="shared" si="19"/>
-        <v>92455</v>
+        <v>92410</v>
       </c>
       <c r="Q89" s="12"/>
       <c r="R89" s="13">
@@ -12840,19 +12836,19 @@
       </c>
       <c r="T89" s="12">
         <f t="shared" si="22"/>
-        <v>92455</v>
+        <v>92410</v>
       </c>
       <c r="U89" s="12">
         <f t="shared" si="23"/>
-        <v>2054.5555555555557</v>
+        <v>2053.5555555555557</v>
       </c>
       <c r="V89" s="12">
         <f t="shared" si="24"/>
-        <v>2054.5555555555557</v>
+        <v>2053.5555555555557</v>
       </c>
       <c r="W89" s="14">
         <f t="shared" si="25"/>
-        <v>92455</v>
+        <v>92410</v>
       </c>
     </row>
     <row r="90" spans="1:23" s="2" customFormat="1" ht="28.5" customHeight="1">
@@ -12861,29 +12857,29 @@
         <v>76</v>
       </c>
       <c r="B90" s="11" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="C90" s="11" t="s">
-        <v>1580</v>
-      </c>
-      <c r="D90" s="15" t="s">
-        <v>78</v>
+        <v>1464</v>
+      </c>
+      <c r="D90" s="11" t="s">
+        <v>48</v>
       </c>
       <c r="E90" s="11" t="s">
         <v>26</v>
       </c>
       <c r="F90" s="11" t="s">
-        <v>1581</v>
+        <v>1465</v>
       </c>
       <c r="G90" s="12">
-        <v>1820</v>
+        <v>1819</v>
       </c>
       <c r="H90" s="12">
-        <v>2350</v>
+        <v>2349</v>
       </c>
       <c r="I90" s="12"/>
       <c r="J90" s="12">
-        <v>1810</v>
+        <v>1818</v>
       </c>
       <c r="K90" s="12">
         <f t="shared" si="14"/>
@@ -12891,23 +12887,23 @@
       </c>
       <c r="L90" s="12">
         <f t="shared" si="15"/>
-        <v>1820</v>
+        <v>1819</v>
       </c>
       <c r="M90" s="12">
         <f t="shared" si="16"/>
-        <v>2350</v>
+        <v>2349</v>
       </c>
       <c r="N90" s="12">
         <f t="shared" si="17"/>
-        <v>1810</v>
+        <v>1818</v>
       </c>
       <c r="O90" s="12" t="str">
         <f t="shared" si="18"/>
-        <v>휘발유 45,500원 / 고급유 47,000원</v>
+        <v>휘발유 45,475원 / 고급유 46,980원</v>
       </c>
       <c r="P90" s="12">
         <f t="shared" si="19"/>
-        <v>92500</v>
+        <v>92455</v>
       </c>
       <c r="Q90" s="12"/>
       <c r="R90" s="13">
@@ -12920,19 +12916,19 @@
       </c>
       <c r="T90" s="12">
         <f t="shared" si="22"/>
-        <v>92500</v>
+        <v>92455</v>
       </c>
       <c r="U90" s="12">
         <f t="shared" si="23"/>
-        <v>2055.5555555555557</v>
+        <v>2054.5555555555557</v>
       </c>
       <c r="V90" s="12">
         <f t="shared" si="24"/>
-        <v>2055.5555555555557</v>
+        <v>2054.5555555555557</v>
       </c>
       <c r="W90" s="14">
         <f t="shared" si="25"/>
-        <v>92500</v>
+        <v>92455</v>
       </c>
     </row>
     <row r="91" spans="1:23" s="2" customFormat="1" ht="28.5" customHeight="1">
@@ -12941,29 +12937,29 @@
         <v>77</v>
       </c>
       <c r="B91" s="11" t="s">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="C91" s="11" t="s">
-        <v>1752</v>
-      </c>
-      <c r="D91" s="11" t="s">
-        <v>45</v>
+        <v>1580</v>
+      </c>
+      <c r="D91" s="15" t="s">
+        <v>78</v>
       </c>
       <c r="E91" s="11" t="s">
         <v>26</v>
       </c>
       <c r="F91" s="11" t="s">
-        <v>1753</v>
+        <v>1581</v>
       </c>
       <c r="G91" s="12">
-        <v>1815</v>
+        <v>1820</v>
       </c>
       <c r="H91" s="12">
-        <v>2357</v>
+        <v>2350</v>
       </c>
       <c r="I91" s="12"/>
       <c r="J91" s="12">
-        <v>1808</v>
+        <v>1810</v>
       </c>
       <c r="K91" s="12">
         <f t="shared" si="14"/>
@@ -12971,23 +12967,23 @@
       </c>
       <c r="L91" s="12">
         <f t="shared" si="15"/>
-        <v>1815</v>
+        <v>1820</v>
       </c>
       <c r="M91" s="12">
         <f t="shared" si="16"/>
-        <v>2357</v>
+        <v>2350</v>
       </c>
       <c r="N91" s="12">
         <f t="shared" si="17"/>
-        <v>1808</v>
+        <v>1810</v>
       </c>
       <c r="O91" s="12" t="str">
         <f t="shared" si="18"/>
-        <v>휘발유 45,375원 / 고급유 47,140원</v>
+        <v>휘발유 45,500원 / 고급유 47,000원</v>
       </c>
       <c r="P91" s="12">
         <f t="shared" si="19"/>
-        <v>92515</v>
+        <v>92500</v>
       </c>
       <c r="Q91" s="12"/>
       <c r="R91" s="13">
@@ -13000,40 +12996,40 @@
       </c>
       <c r="T91" s="12">
         <f t="shared" si="22"/>
-        <v>92515</v>
+        <v>92500</v>
       </c>
       <c r="U91" s="12">
         <f t="shared" si="23"/>
-        <v>2055.8888888888887</v>
+        <v>2055.5555555555557</v>
       </c>
       <c r="V91" s="12">
         <f t="shared" si="24"/>
-        <v>2055.8888888888887</v>
+        <v>2055.5555555555557</v>
       </c>
       <c r="W91" s="14">
         <f t="shared" si="25"/>
-        <v>92515</v>
+        <v>92500</v>
       </c>
     </row>
     <row r="92" spans="1:23" s="2" customFormat="1" ht="28.5" customHeight="1">
       <c r="A92" s="11">
         <f t="shared" si="13"/>
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="B92" s="11" t="s">
         <v>14</v>
       </c>
       <c r="C92" s="11" t="s">
-        <v>1750</v>
+        <v>1751</v>
       </c>
       <c r="D92" s="11" t="s">
-        <v>59</v>
+        <v>45</v>
       </c>
       <c r="E92" s="11" t="s">
         <v>26</v>
       </c>
       <c r="F92" s="11" t="s">
-        <v>1751</v>
+        <v>1752</v>
       </c>
       <c r="G92" s="12">
         <v>1815</v>
@@ -13043,7 +13039,7 @@
       </c>
       <c r="I92" s="12"/>
       <c r="J92" s="12">
-        <v>1819</v>
+        <v>1808</v>
       </c>
       <c r="K92" s="12">
         <f t="shared" si="14"/>
@@ -13059,7 +13055,7 @@
       </c>
       <c r="N92" s="12">
         <f t="shared" si="17"/>
-        <v>1819</v>
+        <v>1808</v>
       </c>
       <c r="O92" s="12" t="str">
         <f t="shared" si="18"/>
@@ -13095,35 +13091,35 @@
         <v>92515</v>
       </c>
     </row>
-    <row r="93" spans="1:23" s="16" customFormat="1" ht="28.5" customHeight="1">
+    <row r="93" spans="1:23" s="2" customFormat="1" ht="28.5" customHeight="1">
       <c r="A93" s="11">
         <f t="shared" si="13"/>
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="B93" s="11" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="C93" s="11" t="s">
-        <v>677</v>
-      </c>
-      <c r="D93" s="15" t="s">
+        <v>1749</v>
+      </c>
+      <c r="D93" s="11" t="s">
         <v>59</v>
       </c>
       <c r="E93" s="11" t="s">
         <v>26</v>
       </c>
       <c r="F93" s="11" t="s">
-        <v>678</v>
+        <v>1750</v>
       </c>
       <c r="G93" s="12">
-        <v>1814</v>
+        <v>1815</v>
       </c>
       <c r="H93" s="12">
-        <v>2359</v>
+        <v>2357</v>
       </c>
       <c r="I93" s="12"/>
       <c r="J93" s="12">
-        <v>1804</v>
+        <v>1819</v>
       </c>
       <c r="K93" s="12">
         <f t="shared" si="14"/>
@@ -13131,23 +13127,23 @@
       </c>
       <c r="L93" s="12">
         <f t="shared" si="15"/>
-        <v>1814</v>
+        <v>1815</v>
       </c>
       <c r="M93" s="12">
         <f t="shared" si="16"/>
-        <v>2359</v>
+        <v>2357</v>
       </c>
       <c r="N93" s="12">
         <f t="shared" si="17"/>
-        <v>1804</v>
+        <v>1819</v>
       </c>
       <c r="O93" s="12" t="str">
         <f t="shared" si="18"/>
-        <v>휘발유 45,350원 / 고급유 47,180원</v>
+        <v>휘발유 45,375원 / 고급유 47,140원</v>
       </c>
       <c r="P93" s="12">
         <f t="shared" si="19"/>
-        <v>92530</v>
+        <v>92515</v>
       </c>
       <c r="Q93" s="12"/>
       <c r="R93" s="13">
@@ -13160,50 +13156,50 @@
       </c>
       <c r="T93" s="12">
         <f t="shared" si="22"/>
-        <v>92530</v>
+        <v>92515</v>
       </c>
       <c r="U93" s="12">
         <f t="shared" si="23"/>
-        <v>2056.2222222222222</v>
+        <v>2055.8888888888887</v>
       </c>
       <c r="V93" s="12">
         <f t="shared" si="24"/>
-        <v>2056.2222222222222</v>
+        <v>2055.8888888888887</v>
       </c>
       <c r="W93" s="14">
         <f t="shared" si="25"/>
-        <v>92530</v>
-      </c>
-    </row>
-    <row r="94" spans="1:23" s="7" customFormat="1" ht="28.5" customHeight="1">
+        <v>92515</v>
+      </c>
+    </row>
+    <row r="94" spans="1:23" s="16" customFormat="1" ht="28.5" customHeight="1">
       <c r="A94" s="11">
         <f t="shared" si="13"/>
         <v>80</v>
       </c>
       <c r="B94" s="11" t="s">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="C94" s="11" t="s">
-        <v>541</v>
+        <v>677</v>
       </c>
       <c r="D94" s="15" t="s">
-        <v>45</v>
+        <v>59</v>
       </c>
       <c r="E94" s="11" t="s">
         <v>26</v>
       </c>
       <c r="F94" s="11" t="s">
-        <v>542</v>
+        <v>678</v>
       </c>
       <c r="G94" s="12">
-        <v>1828</v>
+        <v>1814</v>
       </c>
       <c r="H94" s="12">
-        <v>2349</v>
+        <v>2359</v>
       </c>
       <c r="I94" s="12"/>
       <c r="J94" s="12">
-        <v>1813</v>
+        <v>1804</v>
       </c>
       <c r="K94" s="12">
         <f t="shared" si="14"/>
@@ -13211,23 +13207,23 @@
       </c>
       <c r="L94" s="12">
         <f t="shared" si="15"/>
-        <v>1828</v>
+        <v>1814</v>
       </c>
       <c r="M94" s="12">
         <f t="shared" si="16"/>
-        <v>2349</v>
+        <v>2359</v>
       </c>
       <c r="N94" s="12">
         <f t="shared" si="17"/>
-        <v>1813</v>
+        <v>1804</v>
       </c>
       <c r="O94" s="12" t="str">
         <f t="shared" si="18"/>
-        <v>휘발유 45,700원 / 고급유 46,980원</v>
+        <v>휘발유 45,350원 / 고급유 47,180원</v>
       </c>
       <c r="P94" s="12">
         <f t="shared" si="19"/>
-        <v>92680</v>
+        <v>92530</v>
       </c>
       <c r="Q94" s="12"/>
       <c r="R94" s="13">
@@ -13240,22 +13236,22 @@
       </c>
       <c r="T94" s="12">
         <f t="shared" si="22"/>
-        <v>92680</v>
+        <v>92530</v>
       </c>
       <c r="U94" s="12">
         <f t="shared" si="23"/>
-        <v>2059.5555555555557</v>
+        <v>2056.2222222222222</v>
       </c>
       <c r="V94" s="12">
         <f t="shared" si="24"/>
-        <v>2059.5555555555557</v>
+        <v>2056.2222222222222</v>
       </c>
       <c r="W94" s="14">
         <f t="shared" si="25"/>
-        <v>92680</v>
-      </c>
-    </row>
-    <row r="95" spans="1:23" s="16" customFormat="1" ht="28.5" customHeight="1">
+        <v>92530</v>
+      </c>
+    </row>
+    <row r="95" spans="1:23" s="7" customFormat="1" ht="28.5" customHeight="1">
       <c r="A95" s="11">
         <f t="shared" si="13"/>
         <v>81</v>
@@ -13264,7 +13260,7 @@
         <v>6</v>
       </c>
       <c r="C95" s="11" t="s">
-        <v>1685</v>
+        <v>541</v>
       </c>
       <c r="D95" s="15" t="s">
         <v>45</v>
@@ -13273,17 +13269,17 @@
         <v>26</v>
       </c>
       <c r="F95" s="11" t="s">
-        <v>1686</v>
+        <v>542</v>
       </c>
       <c r="G95" s="12">
-        <v>1825</v>
+        <v>1828</v>
       </c>
       <c r="H95" s="12">
-        <v>2355</v>
+        <v>2349</v>
       </c>
       <c r="I95" s="12"/>
       <c r="J95" s="12">
-        <v>1810</v>
+        <v>1813</v>
       </c>
       <c r="K95" s="12">
         <f t="shared" si="14"/>
@@ -13291,23 +13287,23 @@
       </c>
       <c r="L95" s="12">
         <f t="shared" si="15"/>
-        <v>1825</v>
+        <v>1828</v>
       </c>
       <c r="M95" s="12">
         <f t="shared" si="16"/>
-        <v>2355</v>
+        <v>2349</v>
       </c>
       <c r="N95" s="12">
         <f t="shared" si="17"/>
-        <v>1810</v>
+        <v>1813</v>
       </c>
       <c r="O95" s="12" t="str">
         <f t="shared" si="18"/>
-        <v>휘발유 45,625원 / 고급유 47,100원</v>
+        <v>휘발유 45,700원 / 고급유 46,980원</v>
       </c>
       <c r="P95" s="12">
         <f t="shared" si="19"/>
-        <v>92725</v>
+        <v>92680</v>
       </c>
       <c r="Q95" s="12"/>
       <c r="R95" s="13">
@@ -13320,50 +13316,50 @@
       </c>
       <c r="T95" s="12">
         <f t="shared" si="22"/>
-        <v>92725</v>
+        <v>92680</v>
       </c>
       <c r="U95" s="12">
         <f t="shared" si="23"/>
-        <v>2060.5555555555557</v>
+        <v>2059.5555555555557</v>
       </c>
       <c r="V95" s="12">
         <f t="shared" si="24"/>
-        <v>2060.5555555555557</v>
+        <v>2059.5555555555557</v>
       </c>
       <c r="W95" s="14">
         <f t="shared" si="25"/>
-        <v>92725</v>
-      </c>
-    </row>
-    <row r="96" spans="1:23" s="2" customFormat="1" ht="28.5" customHeight="1">
+        <v>92680</v>
+      </c>
+    </row>
+    <row r="96" spans="1:23" s="16" customFormat="1" ht="28.5" customHeight="1">
       <c r="A96" s="11">
         <f t="shared" si="13"/>
         <v>82</v>
       </c>
       <c r="B96" s="11" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="C96" s="11" t="s">
-        <v>248</v>
+        <v>1685</v>
       </c>
       <c r="D96" s="15" t="s">
-        <v>78</v>
+        <v>45</v>
       </c>
       <c r="E96" s="11" t="s">
         <v>26</v>
       </c>
       <c r="F96" s="11" t="s">
-        <v>249</v>
+        <v>1686</v>
       </c>
       <c r="G96" s="12">
-        <v>1839</v>
+        <v>1825</v>
       </c>
       <c r="H96" s="12">
-        <v>2339</v>
+        <v>2355</v>
       </c>
       <c r="I96" s="12"/>
       <c r="J96" s="12">
-        <v>1843</v>
+        <v>1810</v>
       </c>
       <c r="K96" s="12">
         <f t="shared" si="14"/>
@@ -13371,23 +13367,23 @@
       </c>
       <c r="L96" s="12">
         <f t="shared" si="15"/>
-        <v>1839</v>
+        <v>1825</v>
       </c>
       <c r="M96" s="12">
         <f t="shared" si="16"/>
-        <v>2339</v>
+        <v>2355</v>
       </c>
       <c r="N96" s="12">
         <f t="shared" si="17"/>
-        <v>1843</v>
+        <v>1810</v>
       </c>
       <c r="O96" s="12" t="str">
         <f t="shared" si="18"/>
-        <v>휘발유 45,975원 / 고급유 46,780원</v>
+        <v>휘발유 45,625원 / 고급유 47,100원</v>
       </c>
       <c r="P96" s="12">
         <f t="shared" si="19"/>
-        <v>92755</v>
+        <v>92725</v>
       </c>
       <c r="Q96" s="12"/>
       <c r="R96" s="13">
@@ -13400,19 +13396,19 @@
       </c>
       <c r="T96" s="12">
         <f t="shared" si="22"/>
-        <v>92755</v>
+        <v>92725</v>
       </c>
       <c r="U96" s="12">
         <f t="shared" si="23"/>
-        <v>2061.2222222222222</v>
+        <v>2060.5555555555557</v>
       </c>
       <c r="V96" s="12">
         <f t="shared" si="24"/>
-        <v>2061.2222222222222</v>
+        <v>2060.5555555555557</v>
       </c>
       <c r="W96" s="14">
         <f t="shared" si="25"/>
-        <v>92755</v>
+        <v>92725</v>
       </c>
     </row>
     <row r="97" spans="1:23" s="2" customFormat="1" ht="28.5" customHeight="1">
@@ -13421,29 +13417,29 @@
         <v>83</v>
       </c>
       <c r="B97" s="11" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="C97" s="11" t="s">
-        <v>1609</v>
+        <v>248</v>
       </c>
       <c r="D97" s="15" t="s">
-        <v>59</v>
+        <v>78</v>
       </c>
       <c r="E97" s="11" t="s">
         <v>26</v>
       </c>
       <c r="F97" s="11" t="s">
-        <v>1610</v>
+        <v>249</v>
       </c>
       <c r="G97" s="12">
-        <v>1825</v>
+        <v>1839</v>
       </c>
       <c r="H97" s="12">
-        <v>2359</v>
+        <v>2339</v>
       </c>
       <c r="I97" s="12"/>
       <c r="J97" s="12">
-        <v>1815</v>
+        <v>1843</v>
       </c>
       <c r="K97" s="12">
         <f t="shared" si="14"/>
@@ -13451,23 +13447,23 @@
       </c>
       <c r="L97" s="12">
         <f t="shared" si="15"/>
-        <v>1825</v>
+        <v>1839</v>
       </c>
       <c r="M97" s="12">
         <f t="shared" si="16"/>
-        <v>2359</v>
+        <v>2339</v>
       </c>
       <c r="N97" s="12">
         <f t="shared" si="17"/>
-        <v>1815</v>
+        <v>1843</v>
       </c>
       <c r="O97" s="12" t="str">
         <f t="shared" si="18"/>
-        <v>휘발유 45,625원 / 고급유 47,180원</v>
+        <v>휘발유 45,975원 / 고급유 46,780원</v>
       </c>
       <c r="P97" s="12">
         <f t="shared" si="19"/>
-        <v>92805</v>
+        <v>92755</v>
       </c>
       <c r="Q97" s="12"/>
       <c r="R97" s="13">
@@ -13480,50 +13476,50 @@
       </c>
       <c r="T97" s="12">
         <f t="shared" si="22"/>
-        <v>92805</v>
+        <v>92755</v>
       </c>
       <c r="U97" s="12">
         <f t="shared" si="23"/>
-        <v>2062.3333333333335</v>
+        <v>2061.2222222222222</v>
       </c>
       <c r="V97" s="12">
         <f t="shared" si="24"/>
-        <v>2062.3333333333335</v>
+        <v>2061.2222222222222</v>
       </c>
       <c r="W97" s="14">
         <f t="shared" si="25"/>
-        <v>92805</v>
+        <v>92755</v>
       </c>
     </row>
     <row r="98" spans="1:23" s="2" customFormat="1" ht="28.5" customHeight="1">
       <c r="A98" s="11">
         <f t="shared" si="13"/>
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="B98" s="11" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="C98" s="11" t="s">
-        <v>883</v>
-      </c>
-      <c r="D98" s="11" t="s">
-        <v>57</v>
+        <v>1609</v>
+      </c>
+      <c r="D98" s="15" t="s">
+        <v>59</v>
       </c>
       <c r="E98" s="11" t="s">
         <v>26</v>
       </c>
       <c r="F98" s="11" t="s">
-        <v>884</v>
+        <v>1610</v>
       </c>
       <c r="G98" s="12">
-        <v>1849</v>
+        <v>1825</v>
       </c>
       <c r="H98" s="12">
-        <v>2329</v>
+        <v>2359</v>
       </c>
       <c r="I98" s="12"/>
       <c r="J98" s="12">
-        <v>1839</v>
+        <v>1815</v>
       </c>
       <c r="K98" s="12">
         <f t="shared" si="14"/>
@@ -13531,19 +13527,19 @@
       </c>
       <c r="L98" s="12">
         <f t="shared" si="15"/>
-        <v>1849</v>
+        <v>1825</v>
       </c>
       <c r="M98" s="12">
         <f t="shared" si="16"/>
-        <v>2329</v>
+        <v>2359</v>
       </c>
       <c r="N98" s="12">
         <f t="shared" si="17"/>
-        <v>1839</v>
+        <v>1815</v>
       </c>
       <c r="O98" s="12" t="str">
         <f t="shared" si="18"/>
-        <v>휘발유 46,225원 / 고급유 46,580원</v>
+        <v>휘발유 45,625원 / 고급유 47,180원</v>
       </c>
       <c r="P98" s="12">
         <f t="shared" si="19"/>
@@ -13578,32 +13574,32 @@
     <row r="99" spans="1:23" s="2" customFormat="1" ht="28.5" customHeight="1">
       <c r="A99" s="11">
         <f t="shared" si="13"/>
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="B99" s="11" t="s">
         <v>10</v>
       </c>
       <c r="C99" s="11" t="s">
-        <v>626</v>
-      </c>
-      <c r="D99" s="15" t="s">
-        <v>59</v>
+        <v>883</v>
+      </c>
+      <c r="D99" s="11" t="s">
+        <v>57</v>
       </c>
       <c r="E99" s="11" t="s">
         <v>26</v>
       </c>
       <c r="F99" s="11" t="s">
-        <v>627</v>
+        <v>884</v>
       </c>
       <c r="G99" s="12">
-        <v>1857</v>
+        <v>1849</v>
       </c>
       <c r="H99" s="12">
-        <v>2319</v>
+        <v>2329</v>
       </c>
       <c r="I99" s="12"/>
       <c r="J99" s="12">
-        <v>1834</v>
+        <v>1839</v>
       </c>
       <c r="K99" s="12">
         <f t="shared" si="14"/>
@@ -13611,19 +13607,19 @@
       </c>
       <c r="L99" s="12">
         <f t="shared" si="15"/>
-        <v>1857</v>
+        <v>1849</v>
       </c>
       <c r="M99" s="12">
         <f t="shared" si="16"/>
-        <v>2319</v>
+        <v>2329</v>
       </c>
       <c r="N99" s="12">
         <f t="shared" si="17"/>
-        <v>1834</v>
+        <v>1839</v>
       </c>
       <c r="O99" s="12" t="str">
         <f t="shared" si="18"/>
-        <v>휘발유 46,425원 / 고급유 46,380원</v>
+        <v>휘발유 46,225원 / 고급유 46,580원</v>
       </c>
       <c r="P99" s="12">
         <f t="shared" si="19"/>
@@ -13655,35 +13651,35 @@
         <v>92805</v>
       </c>
     </row>
-    <row r="100" spans="1:23" s="7" customFormat="1" ht="28.5" customHeight="1">
+    <row r="100" spans="1:23" s="2" customFormat="1" ht="28.5" customHeight="1">
       <c r="A100" s="11">
         <f t="shared" si="13"/>
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="B100" s="11" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="C100" s="11" t="s">
-        <v>106</v>
-      </c>
-      <c r="D100" s="11" t="s">
-        <v>57</v>
+        <v>626</v>
+      </c>
+      <c r="D100" s="15" t="s">
+        <v>59</v>
       </c>
       <c r="E100" s="11" t="s">
         <v>26</v>
       </c>
       <c r="F100" s="11" t="s">
-        <v>107</v>
+        <v>627</v>
       </c>
       <c r="G100" s="12">
-        <v>1819</v>
+        <v>1857</v>
       </c>
       <c r="H100" s="12">
-        <v>2368</v>
+        <v>2319</v>
       </c>
       <c r="I100" s="12"/>
       <c r="J100" s="12">
-        <v>1809</v>
+        <v>1834</v>
       </c>
       <c r="K100" s="12">
         <f t="shared" si="14"/>
@@ -13691,23 +13687,23 @@
       </c>
       <c r="L100" s="12">
         <f t="shared" si="15"/>
-        <v>1819</v>
+        <v>1857</v>
       </c>
       <c r="M100" s="12">
         <f t="shared" si="16"/>
-        <v>2368</v>
+        <v>2319</v>
       </c>
       <c r="N100" s="12">
         <f t="shared" si="17"/>
-        <v>1809</v>
+        <v>1834</v>
       </c>
       <c r="O100" s="12" t="str">
         <f t="shared" si="18"/>
-        <v>휘발유 45,475원 / 고급유 47,360원</v>
+        <v>휘발유 46,425원 / 고급유 46,380원</v>
       </c>
       <c r="P100" s="12">
         <f t="shared" si="19"/>
-        <v>92835</v>
+        <v>92805</v>
       </c>
       <c r="Q100" s="12"/>
       <c r="R100" s="13">
@@ -13720,50 +13716,50 @@
       </c>
       <c r="T100" s="12">
         <f t="shared" si="22"/>
-        <v>92835</v>
+        <v>92805</v>
       </c>
       <c r="U100" s="12">
         <f t="shared" si="23"/>
-        <v>2063</v>
+        <v>2062.3333333333335</v>
       </c>
       <c r="V100" s="12">
         <f t="shared" si="24"/>
-        <v>2063</v>
+        <v>2062.3333333333335</v>
       </c>
       <c r="W100" s="14">
         <f t="shared" si="25"/>
-        <v>92835</v>
-      </c>
-    </row>
-    <row r="101" spans="1:23" s="2" customFormat="1" ht="28.5" customHeight="1">
+        <v>92805</v>
+      </c>
+    </row>
+    <row r="101" spans="1:23" s="7" customFormat="1" ht="28.5" customHeight="1">
       <c r="A101" s="11">
         <f t="shared" si="13"/>
         <v>87</v>
       </c>
       <c r="B101" s="11" t="s">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="C101" s="11" t="s">
-        <v>642</v>
-      </c>
-      <c r="D101" s="15" t="s">
+        <v>106</v>
+      </c>
+      <c r="D101" s="11" t="s">
         <v>57</v>
       </c>
       <c r="E101" s="11" t="s">
         <v>26</v>
       </c>
       <c r="F101" s="11" t="s">
-        <v>643</v>
+        <v>107</v>
       </c>
       <c r="G101" s="12">
-        <v>1829</v>
+        <v>1819</v>
       </c>
       <c r="H101" s="12">
-        <v>2359</v>
+        <v>2368</v>
       </c>
       <c r="I101" s="12"/>
       <c r="J101" s="12">
-        <v>1819</v>
+        <v>1809</v>
       </c>
       <c r="K101" s="12">
         <f t="shared" si="14"/>
@@ -13771,23 +13767,23 @@
       </c>
       <c r="L101" s="12">
         <f t="shared" si="15"/>
-        <v>1829</v>
+        <v>1819</v>
       </c>
       <c r="M101" s="12">
         <f t="shared" si="16"/>
-        <v>2359</v>
+        <v>2368</v>
       </c>
       <c r="N101" s="12">
         <f t="shared" si="17"/>
-        <v>1819</v>
+        <v>1809</v>
       </c>
       <c r="O101" s="12" t="str">
         <f t="shared" si="18"/>
-        <v>휘발유 45,725원 / 고급유 47,180원</v>
+        <v>휘발유 45,475원 / 고급유 47,360원</v>
       </c>
       <c r="P101" s="12">
         <f t="shared" si="19"/>
-        <v>92905</v>
+        <v>92835</v>
       </c>
       <c r="Q101" s="12"/>
       <c r="R101" s="13">
@@ -13800,50 +13796,50 @@
       </c>
       <c r="T101" s="12">
         <f t="shared" si="22"/>
-        <v>92905</v>
+        <v>92835</v>
       </c>
       <c r="U101" s="12">
         <f t="shared" si="23"/>
-        <v>2064.5555555555557</v>
+        <v>2063</v>
       </c>
       <c r="V101" s="12">
         <f t="shared" si="24"/>
-        <v>2064.5555555555557</v>
+        <v>2063</v>
       </c>
       <c r="W101" s="14">
         <f t="shared" si="25"/>
-        <v>92905</v>
-      </c>
-    </row>
-    <row r="102" spans="1:23" s="16" customFormat="1" ht="28.5" customHeight="1">
+        <v>92835</v>
+      </c>
+    </row>
+    <row r="102" spans="1:23" s="2" customFormat="1" ht="28.5" customHeight="1">
       <c r="A102" s="11">
         <f t="shared" si="13"/>
         <v>88</v>
       </c>
       <c r="B102" s="11" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="C102" s="11" t="s">
-        <v>246</v>
+        <v>642</v>
       </c>
       <c r="D102" s="15" t="s">
-        <v>78</v>
+        <v>57</v>
       </c>
       <c r="E102" s="11" t="s">
         <v>26</v>
       </c>
       <c r="F102" s="11" t="s">
-        <v>247</v>
+        <v>643</v>
       </c>
       <c r="G102" s="12">
-        <v>1848</v>
+        <v>1829</v>
       </c>
       <c r="H102" s="12">
-        <v>2339</v>
+        <v>2359</v>
       </c>
       <c r="I102" s="12"/>
       <c r="J102" s="12">
-        <v>1843</v>
+        <v>1819</v>
       </c>
       <c r="K102" s="12">
         <f t="shared" si="14"/>
@@ -13851,23 +13847,23 @@
       </c>
       <c r="L102" s="12">
         <f t="shared" si="15"/>
-        <v>1848</v>
+        <v>1829</v>
       </c>
       <c r="M102" s="12">
         <f t="shared" si="16"/>
-        <v>2339</v>
+        <v>2359</v>
       </c>
       <c r="N102" s="12">
         <f t="shared" si="17"/>
-        <v>1843</v>
+        <v>1819</v>
       </c>
       <c r="O102" s="12" t="str">
         <f t="shared" si="18"/>
-        <v>휘발유 46,200원 / 고급유 46,780원</v>
+        <v>휘발유 45,725원 / 고급유 47,180원</v>
       </c>
       <c r="P102" s="12">
         <f t="shared" si="19"/>
-        <v>92980</v>
+        <v>92905</v>
       </c>
       <c r="Q102" s="12"/>
       <c r="R102" s="13">
@@ -13880,50 +13876,50 @@
       </c>
       <c r="T102" s="12">
         <f t="shared" si="22"/>
-        <v>92980</v>
+        <v>92905</v>
       </c>
       <c r="U102" s="12">
         <f t="shared" si="23"/>
-        <v>2066.2222222222222</v>
+        <v>2064.5555555555557</v>
       </c>
       <c r="V102" s="12">
         <f t="shared" si="24"/>
-        <v>2066.2222222222222</v>
+        <v>2064.5555555555557</v>
       </c>
       <c r="W102" s="14">
         <f t="shared" si="25"/>
-        <v>92980</v>
-      </c>
-    </row>
-    <row r="103" spans="1:23" s="2" customFormat="1" ht="28.5" customHeight="1">
+        <v>92905</v>
+      </c>
+    </row>
+    <row r="103" spans="1:23" s="16" customFormat="1" ht="28.5" customHeight="1">
       <c r="A103" s="11">
         <f t="shared" si="13"/>
         <v>89</v>
       </c>
       <c r="B103" s="11" t="s">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="C103" s="11" t="s">
-        <v>380</v>
+        <v>246</v>
       </c>
       <c r="D103" s="15" t="s">
-        <v>59</v>
+        <v>78</v>
       </c>
       <c r="E103" s="11" t="s">
         <v>26</v>
       </c>
       <c r="F103" s="11" t="s">
-        <v>381</v>
+        <v>247</v>
       </c>
       <c r="G103" s="12">
-        <v>1819</v>
+        <v>1848</v>
       </c>
       <c r="H103" s="12">
-        <v>2379</v>
+        <v>2339</v>
       </c>
       <c r="I103" s="12"/>
       <c r="J103" s="12">
-        <v>1809</v>
+        <v>1843</v>
       </c>
       <c r="K103" s="12">
         <f t="shared" si="14"/>
@@ -13931,23 +13927,23 @@
       </c>
       <c r="L103" s="12">
         <f t="shared" si="15"/>
-        <v>1819</v>
+        <v>1848</v>
       </c>
       <c r="M103" s="12">
         <f t="shared" si="16"/>
-        <v>2379</v>
+        <v>2339</v>
       </c>
       <c r="N103" s="12">
         <f t="shared" si="17"/>
-        <v>1809</v>
+        <v>1843</v>
       </c>
       <c r="O103" s="12" t="str">
         <f t="shared" si="18"/>
-        <v>휘발유 45,475원 / 고급유 47,580원</v>
+        <v>휘발유 46,200원 / 고급유 46,780원</v>
       </c>
       <c r="P103" s="12">
         <f t="shared" si="19"/>
-        <v>93055</v>
+        <v>92980</v>
       </c>
       <c r="Q103" s="12"/>
       <c r="R103" s="13">
@@ -13960,19 +13956,19 @@
       </c>
       <c r="T103" s="12">
         <f t="shared" si="22"/>
-        <v>93055</v>
+        <v>92980</v>
       </c>
       <c r="U103" s="12">
         <f t="shared" si="23"/>
-        <v>2067.8888888888887</v>
+        <v>2066.2222222222222</v>
       </c>
       <c r="V103" s="12">
         <f t="shared" si="24"/>
-        <v>2067.8888888888887</v>
+        <v>2066.2222222222222</v>
       </c>
       <c r="W103" s="14">
         <f t="shared" si="25"/>
-        <v>93055</v>
+        <v>92980</v>
       </c>
     </row>
     <row r="104" spans="1:23" s="2" customFormat="1" ht="28.5" customHeight="1">
@@ -13981,29 +13977,29 @@
         <v>90</v>
       </c>
       <c r="B104" s="11" t="s">
-        <v>6</v>
+        <v>18</v>
       </c>
       <c r="C104" s="11" t="s">
-        <v>401</v>
-      </c>
-      <c r="D104" s="11" t="s">
-        <v>57</v>
+        <v>380</v>
+      </c>
+      <c r="D104" s="15" t="s">
+        <v>59</v>
       </c>
       <c r="E104" s="11" t="s">
-        <v>60</v>
+        <v>26</v>
       </c>
       <c r="F104" s="11" t="s">
-        <v>402</v>
+        <v>381</v>
       </c>
       <c r="G104" s="12">
-        <v>1979</v>
+        <v>1819</v>
       </c>
       <c r="H104" s="12">
-        <v>2698</v>
+        <v>2379</v>
       </c>
       <c r="I104" s="12"/>
       <c r="J104" s="12">
-        <v>1979</v>
+        <v>1809</v>
       </c>
       <c r="K104" s="12">
         <f t="shared" si="14"/>
@@ -14011,50 +14007,48 @@
       </c>
       <c r="L104" s="12">
         <f t="shared" si="15"/>
-        <v>1979</v>
+        <v>1819</v>
       </c>
       <c r="M104" s="12">
         <f t="shared" si="16"/>
-        <v>2698</v>
+        <v>2379</v>
       </c>
       <c r="N104" s="12">
         <f t="shared" si="17"/>
-        <v>1979</v>
+        <v>1809</v>
       </c>
       <c r="O104" s="12" t="str">
         <f t="shared" si="18"/>
-        <v>휘발유 49,475원 / 고급유 53,960원</v>
+        <v>휘발유 45,475원 / 고급유 47,580원</v>
       </c>
       <c r="P104" s="12">
         <f t="shared" si="19"/>
-        <v>103435</v>
-      </c>
-      <c r="Q104" s="12" t="s">
-        <v>61</v>
-      </c>
+        <v>93055</v>
+      </c>
+      <c r="Q104" s="12"/>
       <c r="R104" s="13">
         <f t="shared" si="20"/>
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="S104" s="12">
         <f t="shared" si="21"/>
-        <v>10343</v>
+        <v>0</v>
       </c>
       <c r="T104" s="12">
         <f t="shared" si="22"/>
-        <v>93092</v>
+        <v>93055</v>
       </c>
       <c r="U104" s="12">
         <f t="shared" si="23"/>
-        <v>2068.7111111111112</v>
+        <v>2067.8888888888887</v>
       </c>
       <c r="V104" s="12">
         <f t="shared" si="24"/>
-        <v>2298.5555555555557</v>
+        <v>2067.8888888888887</v>
       </c>
       <c r="W104" s="14">
         <f t="shared" si="25"/>
-        <v>93092</v>
+        <v>93055</v>
       </c>
     </row>
     <row r="105" spans="1:23" s="2" customFormat="1" ht="28.5" customHeight="1">
@@ -14063,29 +14057,29 @@
         <v>91</v>
       </c>
       <c r="B105" s="11" t="s">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="C105" s="11" t="s">
-        <v>576</v>
-      </c>
-      <c r="D105" s="15" t="s">
-        <v>45</v>
+        <v>401</v>
+      </c>
+      <c r="D105" s="11" t="s">
+        <v>57</v>
       </c>
       <c r="E105" s="11" t="s">
-        <v>26</v>
+        <v>60</v>
       </c>
       <c r="F105" s="11" t="s">
-        <v>577</v>
+        <v>402</v>
       </c>
       <c r="G105" s="12">
-        <v>1845</v>
+        <v>1979</v>
       </c>
       <c r="H105" s="12">
-        <v>2349</v>
+        <v>2698</v>
       </c>
       <c r="I105" s="12"/>
       <c r="J105" s="12">
-        <v>1835</v>
+        <v>1979</v>
       </c>
       <c r="K105" s="12">
         <f t="shared" si="14"/>
@@ -14093,79 +14087,81 @@
       </c>
       <c r="L105" s="12">
         <f t="shared" si="15"/>
-        <v>1845</v>
+        <v>1979</v>
       </c>
       <c r="M105" s="12">
         <f t="shared" si="16"/>
-        <v>2349</v>
+        <v>2698</v>
       </c>
       <c r="N105" s="12">
         <f t="shared" si="17"/>
-        <v>1835</v>
+        <v>1979</v>
       </c>
       <c r="O105" s="12" t="str">
         <f t="shared" si="18"/>
-        <v>휘발유 46,125원 / 고급유 46,980원</v>
+        <v>휘발유 49,475원 / 고급유 53,960원</v>
       </c>
       <c r="P105" s="12">
         <f t="shared" si="19"/>
-        <v>93105</v>
-      </c>
-      <c r="Q105" s="12"/>
+        <v>103435</v>
+      </c>
+      <c r="Q105" s="12" t="s">
+        <v>61</v>
+      </c>
       <c r="R105" s="13">
         <f t="shared" si="20"/>
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="S105" s="12">
         <f t="shared" si="21"/>
-        <v>0</v>
+        <v>10343</v>
       </c>
       <c r="T105" s="12">
         <f t="shared" si="22"/>
-        <v>93105</v>
+        <v>93092</v>
       </c>
       <c r="U105" s="12">
         <f t="shared" si="23"/>
-        <v>2069</v>
+        <v>2068.7111111111112</v>
       </c>
       <c r="V105" s="12">
         <f t="shared" si="24"/>
-        <v>2069</v>
+        <v>2298.5555555555557</v>
       </c>
       <c r="W105" s="14">
         <f t="shared" si="25"/>
-        <v>93105</v>
-      </c>
-    </row>
-    <row r="106" spans="1:23" s="7" customFormat="1" ht="28.5" customHeight="1">
+        <v>93092</v>
+      </c>
+    </row>
+    <row r="106" spans="1:23" s="2" customFormat="1" ht="28.5" customHeight="1">
       <c r="A106" s="11">
         <f t="shared" si="13"/>
         <v>92</v>
       </c>
       <c r="B106" s="11" t="s">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="C106" s="11" t="s">
-        <v>326</v>
+        <v>576</v>
       </c>
       <c r="D106" s="15" t="s">
-        <v>59</v>
+        <v>45</v>
       </c>
       <c r="E106" s="11" t="s">
         <v>26</v>
       </c>
       <c r="F106" s="11" t="s">
-        <v>327</v>
+        <v>577</v>
       </c>
       <c r="G106" s="12">
-        <v>1810</v>
+        <v>1845</v>
       </c>
       <c r="H106" s="12">
-        <v>2395</v>
+        <v>2349</v>
       </c>
       <c r="I106" s="12"/>
       <c r="J106" s="12">
-        <v>1815</v>
+        <v>1835</v>
       </c>
       <c r="K106" s="12">
         <f t="shared" si="14"/>
@@ -14173,23 +14169,23 @@
       </c>
       <c r="L106" s="12">
         <f t="shared" si="15"/>
-        <v>1810</v>
+        <v>1845</v>
       </c>
       <c r="M106" s="12">
         <f t="shared" si="16"/>
-        <v>2395</v>
+        <v>2349</v>
       </c>
       <c r="N106" s="12">
         <f t="shared" si="17"/>
-        <v>1815</v>
+        <v>1835</v>
       </c>
       <c r="O106" s="12" t="str">
         <f t="shared" si="18"/>
-        <v>휘발유 45,250원 / 고급유 47,900원</v>
+        <v>휘발유 46,125원 / 고급유 46,980원</v>
       </c>
       <c r="P106" s="12">
         <f t="shared" si="19"/>
-        <v>93150</v>
+        <v>93105</v>
       </c>
       <c r="Q106" s="12"/>
       <c r="R106" s="13">
@@ -14202,50 +14198,50 @@
       </c>
       <c r="T106" s="12">
         <f t="shared" si="22"/>
-        <v>93150</v>
+        <v>93105</v>
       </c>
       <c r="U106" s="12">
         <f t="shared" si="23"/>
-        <v>2070</v>
+        <v>2069</v>
       </c>
       <c r="V106" s="12">
         <f t="shared" si="24"/>
-        <v>2070</v>
+        <v>2069</v>
       </c>
       <c r="W106" s="14">
         <f t="shared" si="25"/>
-        <v>93150</v>
-      </c>
-    </row>
-    <row r="107" spans="1:23" s="2" customFormat="1" ht="28.5" customHeight="1">
+        <v>93105</v>
+      </c>
+    </row>
+    <row r="107" spans="1:23" s="7" customFormat="1" ht="28.5" customHeight="1">
       <c r="A107" s="11">
         <f t="shared" si="13"/>
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="B107" s="11" t="s">
         <v>6</v>
       </c>
       <c r="C107" s="11" t="s">
-        <v>308</v>
+        <v>326</v>
       </c>
       <c r="D107" s="15" t="s">
-        <v>45</v>
+        <v>59</v>
       </c>
       <c r="E107" s="11" t="s">
         <v>26</v>
       </c>
       <c r="F107" s="11" t="s">
-        <v>309</v>
+        <v>327</v>
       </c>
       <c r="G107" s="12">
-        <v>1814</v>
+        <v>1810</v>
       </c>
       <c r="H107" s="12">
-        <v>2390</v>
+        <v>2395</v>
       </c>
       <c r="I107" s="12"/>
       <c r="J107" s="12">
-        <v>1809</v>
+        <v>1815</v>
       </c>
       <c r="K107" s="12">
         <f t="shared" si="14"/>
@@ -14253,19 +14249,19 @@
       </c>
       <c r="L107" s="12">
         <f t="shared" si="15"/>
-        <v>1814</v>
+        <v>1810</v>
       </c>
       <c r="M107" s="12">
         <f t="shared" si="16"/>
-        <v>2390</v>
+        <v>2395</v>
       </c>
       <c r="N107" s="12">
         <f t="shared" si="17"/>
-        <v>1809</v>
+        <v>1815</v>
       </c>
       <c r="O107" s="12" t="str">
         <f t="shared" si="18"/>
-        <v>휘발유 45,350원 / 고급유 47,800원</v>
+        <v>휘발유 45,250원 / 고급유 47,900원</v>
       </c>
       <c r="P107" s="12">
         <f t="shared" si="19"/>
@@ -14297,16 +14293,16 @@
         <v>93150</v>
       </c>
     </row>
-    <row r="108" spans="1:23" s="7" customFormat="1" ht="28.5" customHeight="1">
+    <row r="108" spans="1:23" s="2" customFormat="1" ht="28.5" customHeight="1">
       <c r="A108" s="11">
         <f t="shared" si="13"/>
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="B108" s="11" t="s">
         <v>6</v>
       </c>
       <c r="C108" s="11" t="s">
-        <v>1313</v>
+        <v>308</v>
       </c>
       <c r="D108" s="15" t="s">
         <v>45</v>
@@ -14315,7 +14311,7 @@
         <v>26</v>
       </c>
       <c r="F108" s="11" t="s">
-        <v>1314</v>
+        <v>309</v>
       </c>
       <c r="G108" s="12">
         <v>1814</v>
@@ -14377,16 +14373,16 @@
         <v>93150</v>
       </c>
     </row>
-    <row r="109" spans="1:23" s="2" customFormat="1" ht="28.5" customHeight="1">
+    <row r="109" spans="1:23" s="7" customFormat="1" ht="28.5" customHeight="1">
       <c r="A109" s="11">
         <f t="shared" si="13"/>
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="B109" s="11" t="s">
         <v>6</v>
       </c>
       <c r="C109" s="11" t="s">
-        <v>1490</v>
+        <v>1313</v>
       </c>
       <c r="D109" s="15" t="s">
         <v>45</v>
@@ -14395,7 +14391,7 @@
         <v>26</v>
       </c>
       <c r="F109" s="11" t="s">
-        <v>1491</v>
+        <v>1314</v>
       </c>
       <c r="G109" s="12">
         <v>1814</v>
@@ -14457,25 +14453,25 @@
         <v>93150</v>
       </c>
     </row>
-    <row r="110" spans="1:23" s="7" customFormat="1" ht="28.5" customHeight="1">
+    <row r="110" spans="1:23" s="2" customFormat="1" ht="28.5" customHeight="1">
       <c r="A110" s="11">
         <f t="shared" si="13"/>
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="B110" s="11" t="s">
         <v>6</v>
       </c>
       <c r="C110" s="11" t="s">
-        <v>1020</v>
-      </c>
-      <c r="D110" s="11" t="s">
-        <v>57</v>
+        <v>1490</v>
+      </c>
+      <c r="D110" s="15" t="s">
+        <v>45</v>
       </c>
       <c r="E110" s="11" t="s">
         <v>26</v>
       </c>
       <c r="F110" s="11" t="s">
-        <v>1021</v>
+        <v>1491</v>
       </c>
       <c r="G110" s="12">
         <v>1814</v>
@@ -14485,7 +14481,7 @@
       </c>
       <c r="I110" s="12"/>
       <c r="J110" s="12">
-        <v>1814</v>
+        <v>1809</v>
       </c>
       <c r="K110" s="12">
         <f t="shared" si="14"/>
@@ -14501,7 +14497,7 @@
       </c>
       <c r="N110" s="12">
         <f t="shared" si="17"/>
-        <v>1814</v>
+        <v>1809</v>
       </c>
       <c r="O110" s="12" t="str">
         <f t="shared" si="18"/>
@@ -14537,35 +14533,35 @@
         <v>93150</v>
       </c>
     </row>
-    <row r="111" spans="1:23" s="2" customFormat="1" ht="28.5" customHeight="1">
+    <row r="111" spans="1:23" s="7" customFormat="1" ht="28.5" customHeight="1">
       <c r="A111" s="11">
         <f t="shared" si="13"/>
-        <v>97</v>
+        <v>93</v>
       </c>
       <c r="B111" s="11" t="s">
         <v>6</v>
       </c>
       <c r="C111" s="11" t="s">
-        <v>312</v>
-      </c>
-      <c r="D111" s="15" t="s">
-        <v>59</v>
+        <v>1020</v>
+      </c>
+      <c r="D111" s="11" t="s">
+        <v>57</v>
       </c>
       <c r="E111" s="11" t="s">
         <v>26</v>
       </c>
       <c r="F111" s="11" t="s">
-        <v>313</v>
+        <v>1021</v>
       </c>
       <c r="G111" s="12">
-        <v>1815</v>
+        <v>1814</v>
       </c>
       <c r="H111" s="12">
         <v>2390</v>
       </c>
       <c r="I111" s="12"/>
       <c r="J111" s="12">
-        <v>1809</v>
+        <v>1814</v>
       </c>
       <c r="K111" s="12">
         <f t="shared" si="14"/>
@@ -14573,7 +14569,7 @@
       </c>
       <c r="L111" s="12">
         <f t="shared" si="15"/>
-        <v>1815</v>
+        <v>1814</v>
       </c>
       <c r="M111" s="12">
         <f t="shared" si="16"/>
@@ -14581,15 +14577,15 @@
       </c>
       <c r="N111" s="12">
         <f t="shared" si="17"/>
-        <v>1809</v>
+        <v>1814</v>
       </c>
       <c r="O111" s="12" t="str">
         <f t="shared" si="18"/>
-        <v>휘발유 45,375원 / 고급유 47,800원</v>
+        <v>휘발유 45,350원 / 고급유 47,800원</v>
       </c>
       <c r="P111" s="12">
         <f t="shared" si="19"/>
-        <v>93175</v>
+        <v>93150</v>
       </c>
       <c r="Q111" s="12"/>
       <c r="R111" s="13">
@@ -14602,50 +14598,50 @@
       </c>
       <c r="T111" s="12">
         <f t="shared" si="22"/>
-        <v>93175</v>
+        <v>93150</v>
       </c>
       <c r="U111" s="12">
         <f t="shared" si="23"/>
-        <v>2070.5555555555557</v>
+        <v>2070</v>
       </c>
       <c r="V111" s="12">
         <f t="shared" si="24"/>
-        <v>2070.5555555555557</v>
+        <v>2070</v>
       </c>
       <c r="W111" s="14">
         <f t="shared" si="25"/>
-        <v>93175</v>
-      </c>
-    </row>
-    <row r="112" spans="1:23" s="16" customFormat="1" ht="28.5" customHeight="1">
+        <v>93150</v>
+      </c>
+    </row>
+    <row r="112" spans="1:23" s="2" customFormat="1" ht="28.5" customHeight="1">
       <c r="A112" s="11">
         <f t="shared" si="13"/>
         <v>98</v>
       </c>
       <c r="B112" s="11" t="s">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="C112" s="11" t="s">
-        <v>636</v>
-      </c>
-      <c r="D112" s="11" t="s">
-        <v>57</v>
+        <v>312</v>
+      </c>
+      <c r="D112" s="15" t="s">
+        <v>59</v>
       </c>
       <c r="E112" s="11" t="s">
         <v>26</v>
       </c>
       <c r="F112" s="11" t="s">
-        <v>637</v>
+        <v>313</v>
       </c>
       <c r="G112" s="12">
-        <v>1849</v>
+        <v>1815</v>
       </c>
       <c r="H112" s="12">
-        <v>2350</v>
+        <v>2390</v>
       </c>
       <c r="I112" s="12"/>
       <c r="J112" s="12">
-        <v>1819</v>
+        <v>1809</v>
       </c>
       <c r="K112" s="12">
         <f t="shared" si="14"/>
@@ -14653,23 +14649,23 @@
       </c>
       <c r="L112" s="12">
         <f t="shared" si="15"/>
-        <v>1849</v>
+        <v>1815</v>
       </c>
       <c r="M112" s="12">
         <f t="shared" si="16"/>
-        <v>2350</v>
+        <v>2390</v>
       </c>
       <c r="N112" s="12">
         <f t="shared" si="17"/>
-        <v>1819</v>
+        <v>1809</v>
       </c>
       <c r="O112" s="12" t="str">
         <f t="shared" si="18"/>
-        <v>휘발유 46,225원 / 고급유 47,000원</v>
+        <v>휘발유 45,375원 / 고급유 47,800원</v>
       </c>
       <c r="P112" s="12">
         <f t="shared" si="19"/>
-        <v>93225</v>
+        <v>93175</v>
       </c>
       <c r="Q112" s="12"/>
       <c r="R112" s="13">
@@ -14682,50 +14678,50 @@
       </c>
       <c r="T112" s="12">
         <f t="shared" si="22"/>
-        <v>93225</v>
+        <v>93175</v>
       </c>
       <c r="U112" s="12">
         <f t="shared" si="23"/>
-        <v>2071.6666666666665</v>
+        <v>2070.5555555555557</v>
       </c>
       <c r="V112" s="12">
         <f t="shared" si="24"/>
-        <v>2071.6666666666665</v>
+        <v>2070.5555555555557</v>
       </c>
       <c r="W112" s="14">
         <f t="shared" si="25"/>
-        <v>93225</v>
-      </c>
-    </row>
-    <row r="113" spans="1:23" s="2" customFormat="1" ht="28.5" customHeight="1">
+        <v>93175</v>
+      </c>
+    </row>
+    <row r="113" spans="1:23" s="16" customFormat="1" ht="28.5" customHeight="1">
       <c r="A113" s="11">
         <f t="shared" si="13"/>
         <v>99</v>
       </c>
       <c r="B113" s="11" t="s">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="C113" s="11" t="s">
-        <v>1524</v>
+        <v>636</v>
       </c>
       <c r="D113" s="11" t="s">
-        <v>78</v>
+        <v>57</v>
       </c>
       <c r="E113" s="11" t="s">
         <v>26</v>
       </c>
       <c r="F113" s="11" t="s">
-        <v>1525</v>
+        <v>637</v>
       </c>
       <c r="G113" s="12">
-        <v>1810</v>
+        <v>1849</v>
       </c>
       <c r="H113" s="12">
-        <v>2399</v>
+        <v>2350</v>
       </c>
       <c r="I113" s="12"/>
       <c r="J113" s="12">
-        <v>1789</v>
+        <v>1819</v>
       </c>
       <c r="K113" s="12">
         <f t="shared" si="14"/>
@@ -14733,23 +14729,23 @@
       </c>
       <c r="L113" s="12">
         <f t="shared" si="15"/>
-        <v>1810</v>
+        <v>1849</v>
       </c>
       <c r="M113" s="12">
         <f t="shared" si="16"/>
-        <v>2399</v>
+        <v>2350</v>
       </c>
       <c r="N113" s="12">
         <f t="shared" si="17"/>
-        <v>1789</v>
+        <v>1819</v>
       </c>
       <c r="O113" s="12" t="str">
         <f t="shared" si="18"/>
-        <v>휘발유 45,250원 / 고급유 47,980원</v>
+        <v>휘발유 46,225원 / 고급유 47,000원</v>
       </c>
       <c r="P113" s="12">
         <f t="shared" si="19"/>
-        <v>93230</v>
+        <v>93225</v>
       </c>
       <c r="Q113" s="12"/>
       <c r="R113" s="13">
@@ -14762,40 +14758,40 @@
       </c>
       <c r="T113" s="12">
         <f t="shared" si="22"/>
-        <v>93230</v>
+        <v>93225</v>
       </c>
       <c r="U113" s="12">
         <f t="shared" si="23"/>
-        <v>2071.7777777777778</v>
+        <v>2071.6666666666665</v>
       </c>
       <c r="V113" s="12">
         <f t="shared" si="24"/>
-        <v>2071.7777777777778</v>
+        <v>2071.6666666666665</v>
       </c>
       <c r="W113" s="14">
         <f t="shared" si="25"/>
-        <v>93230</v>
+        <v>93225</v>
       </c>
     </row>
     <row r="114" spans="1:23" s="2" customFormat="1" ht="28.5" customHeight="1">
       <c r="A114" s="11">
         <f t="shared" si="13"/>
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="B114" s="11" t="s">
         <v>10</v>
       </c>
       <c r="C114" s="11" t="s">
-        <v>1532</v>
-      </c>
-      <c r="D114" s="15" t="s">
+        <v>1524</v>
+      </c>
+      <c r="D114" s="11" t="s">
         <v>78</v>
       </c>
       <c r="E114" s="11" t="s">
         <v>26</v>
       </c>
       <c r="F114" s="11" t="s">
-        <v>1533</v>
+        <v>1525</v>
       </c>
       <c r="G114" s="12">
         <v>1810</v>
@@ -14805,7 +14801,7 @@
       </c>
       <c r="I114" s="12"/>
       <c r="J114" s="12">
-        <v>1795</v>
+        <v>1789</v>
       </c>
       <c r="K114" s="12">
         <f t="shared" si="14"/>
@@ -14821,7 +14817,7 @@
       </c>
       <c r="N114" s="12">
         <f t="shared" si="17"/>
-        <v>1795</v>
+        <v>1789</v>
       </c>
       <c r="O114" s="12" t="str">
         <f t="shared" si="18"/>
@@ -14860,32 +14856,32 @@
     <row r="115" spans="1:23" s="2" customFormat="1" ht="28.5" customHeight="1">
       <c r="A115" s="11">
         <f t="shared" si="13"/>
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="B115" s="11" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="C115" s="11" t="s">
-        <v>1024</v>
+        <v>1532</v>
       </c>
       <c r="D115" s="15" t="s">
-        <v>45</v>
+        <v>78</v>
       </c>
       <c r="E115" s="11" t="s">
         <v>26</v>
       </c>
       <c r="F115" s="11" t="s">
-        <v>1025</v>
+        <v>1533</v>
       </c>
       <c r="G115" s="12">
-        <v>1814</v>
+        <v>1810</v>
       </c>
       <c r="H115" s="12">
-        <v>2395</v>
+        <v>2399</v>
       </c>
       <c r="I115" s="12"/>
       <c r="J115" s="12">
-        <v>1809</v>
+        <v>1795</v>
       </c>
       <c r="K115" s="12">
         <f t="shared" si="14"/>
@@ -14893,23 +14889,23 @@
       </c>
       <c r="L115" s="12">
         <f t="shared" si="15"/>
-        <v>1814</v>
+        <v>1810</v>
       </c>
       <c r="M115" s="12">
         <f t="shared" si="16"/>
-        <v>2395</v>
+        <v>2399</v>
       </c>
       <c r="N115" s="12">
         <f t="shared" si="17"/>
-        <v>1809</v>
+        <v>1795</v>
       </c>
       <c r="O115" s="12" t="str">
         <f t="shared" si="18"/>
-        <v>휘발유 45,350원 / 고급유 47,900원</v>
+        <v>휘발유 45,250원 / 고급유 47,980원</v>
       </c>
       <c r="P115" s="12">
         <f t="shared" si="19"/>
-        <v>93250</v>
+        <v>93230</v>
       </c>
       <c r="Q115" s="12"/>
       <c r="R115" s="13">
@@ -14922,31 +14918,31 @@
       </c>
       <c r="T115" s="12">
         <f t="shared" si="22"/>
-        <v>93250</v>
+        <v>93230</v>
       </c>
       <c r="U115" s="12">
         <f t="shared" si="23"/>
-        <v>2072.2222222222222</v>
+        <v>2071.7777777777778</v>
       </c>
       <c r="V115" s="12">
         <f t="shared" si="24"/>
-        <v>2072.2222222222222</v>
+        <v>2071.7777777777778</v>
       </c>
       <c r="W115" s="14">
         <f t="shared" si="25"/>
-        <v>93250</v>
-      </c>
-    </row>
-    <row r="116" spans="1:23" s="16" customFormat="1" ht="28.5" customHeight="1">
+        <v>93230</v>
+      </c>
+    </row>
+    <row r="116" spans="1:23" s="2" customFormat="1" ht="28.5" customHeight="1">
       <c r="A116" s="11">
         <f t="shared" si="13"/>
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="B116" s="11" t="s">
         <v>6</v>
       </c>
       <c r="C116" s="11" t="s">
-        <v>871</v>
+        <v>1024</v>
       </c>
       <c r="D116" s="15" t="s">
         <v>45</v>
@@ -14955,17 +14951,17 @@
         <v>26</v>
       </c>
       <c r="F116" s="11" t="s">
-        <v>872</v>
+        <v>1025</v>
       </c>
       <c r="G116" s="12">
-        <v>1818</v>
+        <v>1814</v>
       </c>
       <c r="H116" s="12">
-        <v>2390</v>
+        <v>2395</v>
       </c>
       <c r="I116" s="12"/>
       <c r="J116" s="12">
-        <v>1799</v>
+        <v>1809</v>
       </c>
       <c r="K116" s="12">
         <f t="shared" si="14"/>
@@ -14973,19 +14969,19 @@
       </c>
       <c r="L116" s="12">
         <f t="shared" si="15"/>
-        <v>1818</v>
+        <v>1814</v>
       </c>
       <c r="M116" s="12">
         <f t="shared" si="16"/>
-        <v>2390</v>
+        <v>2395</v>
       </c>
       <c r="N116" s="12">
         <f t="shared" si="17"/>
-        <v>1799</v>
+        <v>1809</v>
       </c>
       <c r="O116" s="12" t="str">
         <f t="shared" si="18"/>
-        <v>휘발유 45,450원 / 고급유 47,800원</v>
+        <v>휘발유 45,350원 / 고급유 47,900원</v>
       </c>
       <c r="P116" s="12">
         <f t="shared" si="19"/>
@@ -15020,32 +15016,32 @@
     <row r="117" spans="1:23" s="16" customFormat="1" ht="28.5" customHeight="1">
       <c r="A117" s="11">
         <f t="shared" si="13"/>
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="B117" s="11" t="s">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="C117" s="11" t="s">
-        <v>1425</v>
+        <v>871</v>
       </c>
       <c r="D117" s="15" t="s">
-        <v>59</v>
+        <v>45</v>
       </c>
       <c r="E117" s="11" t="s">
         <v>26</v>
       </c>
       <c r="F117" s="11" t="s">
-        <v>1426</v>
+        <v>872</v>
       </c>
       <c r="G117" s="12">
-        <v>1845</v>
+        <v>1818</v>
       </c>
       <c r="H117" s="12">
-        <v>2357</v>
+        <v>2390</v>
       </c>
       <c r="I117" s="12"/>
       <c r="J117" s="12">
-        <v>1849</v>
+        <v>1799</v>
       </c>
       <c r="K117" s="12">
         <f t="shared" si="14"/>
@@ -15053,23 +15049,23 @@
       </c>
       <c r="L117" s="12">
         <f t="shared" si="15"/>
-        <v>1845</v>
+        <v>1818</v>
       </c>
       <c r="M117" s="12">
         <f t="shared" si="16"/>
-        <v>2357</v>
+        <v>2390</v>
       </c>
       <c r="N117" s="12">
         <f t="shared" si="17"/>
-        <v>1849</v>
+        <v>1799</v>
       </c>
       <c r="O117" s="12" t="str">
         <f t="shared" si="18"/>
-        <v>휘발유 46,125원 / 고급유 47,140원</v>
+        <v>휘발유 45,450원 / 고급유 47,800원</v>
       </c>
       <c r="P117" s="12">
         <f t="shared" si="19"/>
-        <v>93265</v>
+        <v>93250</v>
       </c>
       <c r="Q117" s="12"/>
       <c r="R117" s="13">
@@ -15082,22 +15078,22 @@
       </c>
       <c r="T117" s="12">
         <f t="shared" si="22"/>
-        <v>93265</v>
+        <v>93250</v>
       </c>
       <c r="U117" s="12">
         <f t="shared" si="23"/>
-        <v>2072.5555555555557</v>
+        <v>2072.2222222222222</v>
       </c>
       <c r="V117" s="12">
         <f t="shared" si="24"/>
-        <v>2072.5555555555557</v>
+        <v>2072.2222222222222</v>
       </c>
       <c r="W117" s="14">
         <f t="shared" si="25"/>
-        <v>93265</v>
-      </c>
-    </row>
-    <row r="118" spans="1:23" s="2" customFormat="1" ht="28.5" customHeight="1">
+        <v>93250</v>
+      </c>
+    </row>
+    <row r="118" spans="1:23" s="16" customFormat="1" ht="28.5" customHeight="1">
       <c r="A118" s="11">
         <f t="shared" si="13"/>
         <v>104</v>
@@ -15106,26 +15102,26 @@
         <v>14</v>
       </c>
       <c r="C118" s="11" t="s">
-        <v>1762</v>
-      </c>
-      <c r="D118" s="11" t="s">
-        <v>57</v>
+        <v>1425</v>
+      </c>
+      <c r="D118" s="15" t="s">
+        <v>59</v>
       </c>
       <c r="E118" s="11" t="s">
         <v>26</v>
       </c>
       <c r="F118" s="11" t="s">
-        <v>1763</v>
+        <v>1426</v>
       </c>
       <c r="G118" s="12">
-        <v>1799</v>
+        <v>1845</v>
       </c>
       <c r="H118" s="12">
-        <v>2415</v>
+        <v>2357</v>
       </c>
       <c r="I118" s="12"/>
       <c r="J118" s="12">
-        <v>1798</v>
+        <v>1849</v>
       </c>
       <c r="K118" s="12">
         <f t="shared" si="14"/>
@@ -15133,23 +15129,23 @@
       </c>
       <c r="L118" s="12">
         <f t="shared" si="15"/>
-        <v>1799</v>
+        <v>1845</v>
       </c>
       <c r="M118" s="12">
         <f t="shared" si="16"/>
-        <v>2415</v>
+        <v>2357</v>
       </c>
       <c r="N118" s="12">
         <f t="shared" si="17"/>
-        <v>1798</v>
+        <v>1849</v>
       </c>
       <c r="O118" s="12" t="str">
         <f t="shared" si="18"/>
-        <v>휘발유 44,975원 / 고급유 48,300원</v>
+        <v>휘발유 46,125원 / 고급유 47,140원</v>
       </c>
       <c r="P118" s="12">
         <f t="shared" si="19"/>
-        <v>93275</v>
+        <v>93265</v>
       </c>
       <c r="Q118" s="12"/>
       <c r="R118" s="13">
@@ -15162,19 +15158,19 @@
       </c>
       <c r="T118" s="12">
         <f t="shared" si="22"/>
-        <v>93275</v>
+        <v>93265</v>
       </c>
       <c r="U118" s="12">
         <f t="shared" si="23"/>
-        <v>2072.7777777777778</v>
+        <v>2072.5555555555557</v>
       </c>
       <c r="V118" s="12">
         <f t="shared" si="24"/>
-        <v>2072.7777777777778</v>
+        <v>2072.5555555555557</v>
       </c>
       <c r="W118" s="14">
         <f t="shared" si="25"/>
-        <v>93275</v>
+        <v>93265</v>
       </c>
     </row>
     <row r="119" spans="1:23" s="2" customFormat="1" ht="28.5" customHeight="1">
@@ -18706,7 +18702,7 @@
         <v>14</v>
       </c>
       <c r="C163" s="11" t="s">
-        <v>1755</v>
+        <v>1754</v>
       </c>
       <c r="D163" s="11" t="s">
         <v>78</v>
@@ -18715,7 +18711,7 @@
         <v>26</v>
       </c>
       <c r="F163" s="11" t="s">
-        <v>1756</v>
+        <v>1755</v>
       </c>
       <c r="G163" s="12">
         <v>1833</v>
@@ -57760,7 +57756,7 @@
         <v>14</v>
       </c>
       <c r="C656" s="11" t="s">
-        <v>1754</v>
+        <v>1753</v>
       </c>
       <c r="D656" s="11" t="s">
         <v>57</v>
@@ -66105,7 +66101,7 @@
         <v>10</v>
       </c>
       <c r="C763" s="11" t="s">
-        <v>1759</v>
+        <v>1758</v>
       </c>
       <c r="D763" s="11" t="s">
         <v>45</v>
@@ -66114,7 +66110,7 @@
         <v>26</v>
       </c>
       <c r="F763" s="11" t="s">
-        <v>1760</v>
+        <v>1759</v>
       </c>
       <c r="G763" s="12">
         <v>1858</v>
@@ -75508,7 +75504,7 @@
     </row>
     <row r="2" spans="1:13" s="16" customFormat="1" ht="21" customHeight="1">
       <c r="A2" s="18" t="s">
-        <v>1761</v>
+        <v>1762</v>
       </c>
     </row>
     <row r="3" spans="1:13" s="16" customFormat="1" ht="27.75" customHeight="1">
@@ -75553,1506 +75549,559 @@
       </c>
     </row>
     <row r="4" spans="1:13" s="16" customFormat="1" ht="25.5" customHeight="1">
-      <c r="A4" s="19" t="s">
-        <v>14</v>
-      </c>
-      <c r="B4" s="20" t="s">
-        <v>1558</v>
-      </c>
-      <c r="C4" s="20" t="s">
-        <v>1559</v>
-      </c>
-      <c r="D4" s="20" t="s">
-        <v>1749</v>
-      </c>
-      <c r="E4" s="26">
-        <v>1829</v>
-      </c>
-      <c r="F4" s="26">
-        <v>1829</v>
-      </c>
-      <c r="G4" s="26">
-        <f t="shared" ref="G4:G40" si="0">IF(OR(E4="",F4=""),"",F4-E4)</f>
-        <v>0</v>
-      </c>
-      <c r="H4" s="26">
-        <v>2329</v>
-      </c>
-      <c r="I4" s="26">
-        <v>2359</v>
-      </c>
-      <c r="J4" s="26">
-        <f t="shared" ref="J4:J40" si="1">IF(OR(H4="",I4=""),"",I4-H4)</f>
-        <v>30</v>
-      </c>
-      <c r="K4" s="26">
-        <v>1809</v>
-      </c>
-      <c r="L4" s="26">
-        <v>1809</v>
-      </c>
-      <c r="M4" s="26">
-        <f t="shared" ref="M4:M40" si="2">IF(OR(K4="",L4=""),"",L4-K4)</f>
-        <v>0</v>
-      </c>
+      <c r="A4" s="19"/>
+      <c r="B4" s="20"/>
+      <c r="C4" s="20"/>
+      <c r="D4" s="20"/>
+      <c r="E4" s="26"/>
+      <c r="F4" s="26"/>
+      <c r="G4" s="26"/>
+      <c r="H4" s="26"/>
+      <c r="I4" s="26"/>
+      <c r="J4" s="26"/>
+      <c r="K4" s="26"/>
+      <c r="L4" s="26"/>
+      <c r="M4" s="26"/>
     </row>
     <row r="5" spans="1:13" s="16" customFormat="1" ht="25.5" customHeight="1">
-      <c r="A5" s="19" t="s">
-        <v>12</v>
-      </c>
-      <c r="B5" s="20" t="s">
-        <v>1277</v>
-      </c>
-      <c r="C5" s="20" t="s">
-        <v>1278</v>
-      </c>
-      <c r="D5" s="20" t="s">
-        <v>1749</v>
-      </c>
-      <c r="E5" s="26">
-        <v>1819</v>
-      </c>
-      <c r="F5" s="26">
-        <v>1819</v>
-      </c>
-      <c r="G5" s="26">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="H5" s="26">
-        <v>2459</v>
-      </c>
-      <c r="I5" s="26">
-        <v>2459</v>
-      </c>
-      <c r="J5" s="26">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="K5" s="26">
-        <v>1819</v>
-      </c>
-      <c r="L5" s="26">
-        <v>1849</v>
-      </c>
-      <c r="M5" s="26">
-        <f t="shared" si="2"/>
-        <v>30</v>
-      </c>
+      <c r="A5" s="19"/>
+      <c r="B5" s="20"/>
+      <c r="C5" s="20"/>
+      <c r="D5" s="20"/>
+      <c r="E5" s="26"/>
+      <c r="F5" s="26"/>
+      <c r="G5" s="26"/>
+      <c r="H5" s="26"/>
+      <c r="I5" s="26"/>
+      <c r="J5" s="26"/>
+      <c r="K5" s="26"/>
+      <c r="L5" s="26"/>
+      <c r="M5" s="26"/>
     </row>
     <row r="6" spans="1:13" s="16" customFormat="1" ht="25.5" customHeight="1">
-      <c r="A6" s="19" t="s">
-        <v>10</v>
-      </c>
-      <c r="B6" s="20" t="s">
-        <v>1453</v>
-      </c>
-      <c r="C6" s="20" t="s">
-        <v>1454</v>
-      </c>
-      <c r="D6" s="20" t="s">
-        <v>1749</v>
-      </c>
-      <c r="E6" s="26">
-        <v>1898</v>
-      </c>
-      <c r="F6" s="26">
-        <v>1898</v>
-      </c>
-      <c r="G6" s="26">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="H6" s="26">
-        <v>2388</v>
-      </c>
-      <c r="I6" s="26">
-        <v>2388</v>
-      </c>
-      <c r="J6" s="26">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="K6" s="26">
-        <v>1858</v>
-      </c>
-      <c r="L6" s="26">
-        <v>1888</v>
-      </c>
-      <c r="M6" s="26">
-        <f t="shared" si="2"/>
-        <v>30</v>
-      </c>
+      <c r="A6" s="19"/>
+      <c r="B6" s="20"/>
+      <c r="C6" s="20"/>
+      <c r="D6" s="20"/>
+      <c r="E6" s="26"/>
+      <c r="F6" s="26"/>
+      <c r="G6" s="26"/>
+      <c r="H6" s="26"/>
+      <c r="I6" s="26"/>
+      <c r="J6" s="26"/>
+      <c r="K6" s="26"/>
+      <c r="L6" s="26"/>
+      <c r="M6" s="26"/>
     </row>
     <row r="7" spans="1:13" s="16" customFormat="1" ht="25.5" customHeight="1">
-      <c r="A7" s="19" t="s">
-        <v>8</v>
-      </c>
-      <c r="B7" s="20" t="s">
-        <v>602</v>
-      </c>
-      <c r="C7" s="20" t="s">
-        <v>1748</v>
-      </c>
-      <c r="D7" s="20" t="s">
-        <v>1749</v>
-      </c>
-      <c r="E7" s="26">
-        <v>1829</v>
-      </c>
-      <c r="F7" s="26">
-        <v>1829</v>
-      </c>
-      <c r="G7" s="26">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="H7" s="26">
-        <v>2289</v>
-      </c>
-      <c r="I7" s="26">
-        <v>2399</v>
-      </c>
-      <c r="J7" s="26">
-        <f t="shared" si="1"/>
-        <v>110</v>
-      </c>
-      <c r="K7" s="26">
-        <v>1815</v>
-      </c>
-      <c r="L7" s="26">
-        <v>1815</v>
-      </c>
-      <c r="M7" s="26">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
+      <c r="A7" s="19"/>
+      <c r="B7" s="20"/>
+      <c r="C7" s="20"/>
+      <c r="D7" s="20"/>
+      <c r="E7" s="26"/>
+      <c r="F7" s="26"/>
+      <c r="G7" s="26"/>
+      <c r="H7" s="26"/>
+      <c r="I7" s="26"/>
+      <c r="J7" s="26"/>
+      <c r="K7" s="26"/>
+      <c r="L7" s="26"/>
+      <c r="M7" s="26"/>
     </row>
     <row r="8" spans="1:13" s="16" customFormat="1" ht="25.5" customHeight="1">
-      <c r="A8" s="19" t="s">
-        <v>6</v>
-      </c>
-      <c r="B8" s="20" t="s">
-        <v>871</v>
-      </c>
-      <c r="C8" s="20" t="s">
-        <v>872</v>
-      </c>
-      <c r="D8" s="20" t="s">
-        <v>1749</v>
-      </c>
-      <c r="E8" s="26">
-        <v>1818</v>
-      </c>
-      <c r="F8" s="26">
-        <v>1818</v>
-      </c>
-      <c r="G8" s="26">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="H8" s="26">
-        <v>2329</v>
-      </c>
-      <c r="I8" s="26">
-        <v>2390</v>
-      </c>
-      <c r="J8" s="26">
-        <f t="shared" si="1"/>
-        <v>61</v>
-      </c>
-      <c r="K8" s="26">
-        <v>1799</v>
-      </c>
-      <c r="L8" s="26">
-        <v>1799</v>
-      </c>
-      <c r="M8" s="26">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
+      <c r="A8" s="19"/>
+      <c r="B8" s="20"/>
+      <c r="C8" s="20"/>
+      <c r="D8" s="20"/>
+      <c r="E8" s="26"/>
+      <c r="F8" s="26"/>
+      <c r="G8" s="26"/>
+      <c r="H8" s="26"/>
+      <c r="I8" s="26"/>
+      <c r="J8" s="26"/>
+      <c r="K8" s="26"/>
+      <c r="L8" s="26"/>
+      <c r="M8" s="26"/>
     </row>
     <row r="9" spans="1:13" s="16" customFormat="1" ht="25.5" customHeight="1">
-      <c r="A9" s="19" t="s">
-        <v>16</v>
-      </c>
-      <c r="B9" s="20" t="s">
-        <v>600</v>
-      </c>
-      <c r="C9" s="20" t="s">
-        <v>601</v>
-      </c>
-      <c r="D9" s="20" t="s">
-        <v>1749</v>
-      </c>
-      <c r="E9" s="26">
-        <v>1865</v>
-      </c>
-      <c r="F9" s="26">
-        <v>1865</v>
-      </c>
-      <c r="G9" s="26">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="H9" s="26">
-        <v>2350</v>
-      </c>
-      <c r="I9" s="26">
-        <v>2350</v>
-      </c>
-      <c r="J9" s="26">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="K9" s="26">
-        <v>1855</v>
-      </c>
-      <c r="L9" s="26">
-        <v>1875</v>
-      </c>
-      <c r="M9" s="26">
-        <f t="shared" si="2"/>
-        <v>20</v>
-      </c>
+      <c r="A9" s="19"/>
+      <c r="B9" s="20"/>
+      <c r="C9" s="20"/>
+      <c r="D9" s="20"/>
+      <c r="E9" s="26"/>
+      <c r="F9" s="26"/>
+      <c r="G9" s="26"/>
+      <c r="H9" s="26"/>
+      <c r="I9" s="26"/>
+      <c r="J9" s="26"/>
+      <c r="K9" s="26"/>
+      <c r="L9" s="26"/>
+      <c r="M9" s="26"/>
     </row>
     <row r="10" spans="1:13" s="16" customFormat="1" ht="25.5" customHeight="1">
-      <c r="A10" s="19" t="s">
-        <v>18</v>
-      </c>
-      <c r="B10" s="20" t="s">
-        <v>405</v>
-      </c>
-      <c r="C10" s="20" t="s">
-        <v>406</v>
-      </c>
-      <c r="D10" s="20" t="s">
-        <v>1749</v>
-      </c>
-      <c r="E10" s="26">
-        <v>1839</v>
-      </c>
-      <c r="F10" s="26">
-        <v>1839</v>
-      </c>
-      <c r="G10" s="26">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
+      <c r="A10" s="19"/>
+      <c r="B10" s="20"/>
+      <c r="C10" s="20"/>
+      <c r="D10" s="20"/>
+      <c r="E10" s="26"/>
+      <c r="F10" s="26"/>
+      <c r="G10" s="26"/>
       <c r="H10" s="26"/>
       <c r="I10" s="26"/>
-      <c r="J10" s="26" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K10" s="26">
-        <v>1809</v>
-      </c>
-      <c r="L10" s="26">
-        <v>1812</v>
-      </c>
-      <c r="M10" s="26">
-        <f t="shared" si="2"/>
-        <v>3</v>
-      </c>
+      <c r="J10" s="26"/>
+      <c r="K10" s="26"/>
+      <c r="L10" s="26"/>
+      <c r="M10" s="26"/>
     </row>
     <row r="11" spans="1:13" s="16" customFormat="1" ht="25.5" customHeight="1">
-      <c r="A11" s="19" t="s">
-        <v>16</v>
-      </c>
-      <c r="B11" s="20" t="s">
-        <v>468</v>
-      </c>
-      <c r="C11" s="20" t="s">
-        <v>469</v>
-      </c>
-      <c r="D11" s="20" t="s">
-        <v>1749</v>
-      </c>
-      <c r="E11" s="26">
-        <v>1840</v>
-      </c>
-      <c r="F11" s="26">
-        <v>1840</v>
-      </c>
-      <c r="G11" s="26">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
+      <c r="A11" s="19"/>
+      <c r="B11" s="20"/>
+      <c r="C11" s="20"/>
+      <c r="D11" s="20"/>
+      <c r="E11" s="26"/>
+      <c r="F11" s="26"/>
+      <c r="G11" s="26"/>
       <c r="H11" s="26"/>
       <c r="I11" s="26"/>
-      <c r="J11" s="26" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K11" s="26">
-        <v>1837</v>
-      </c>
-      <c r="L11" s="26">
-        <v>1817</v>
-      </c>
-      <c r="M11" s="26">
-        <f t="shared" si="2"/>
-        <v>-20</v>
-      </c>
+      <c r="J11" s="26"/>
+      <c r="K11" s="26"/>
+      <c r="L11" s="26"/>
+      <c r="M11" s="26"/>
     </row>
     <row r="12" spans="1:13" s="16" customFormat="1" ht="25.5" customHeight="1">
-      <c r="A12" s="19" t="s">
-        <v>16</v>
-      </c>
-      <c r="B12" s="20" t="s">
-        <v>885</v>
-      </c>
-      <c r="C12" s="20" t="s">
-        <v>886</v>
-      </c>
-      <c r="D12" s="20" t="s">
-        <v>1749</v>
-      </c>
-      <c r="E12" s="26">
-        <v>1859</v>
-      </c>
-      <c r="F12" s="26">
-        <v>1859</v>
-      </c>
-      <c r="G12" s="26">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
+      <c r="A12" s="19"/>
+      <c r="B12" s="20"/>
+      <c r="C12" s="20"/>
+      <c r="D12" s="20"/>
+      <c r="E12" s="26"/>
+      <c r="F12" s="26"/>
+      <c r="G12" s="26"/>
       <c r="H12" s="26"/>
       <c r="I12" s="26"/>
-      <c r="J12" s="26" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K12" s="26">
-        <v>1829</v>
-      </c>
-      <c r="L12" s="26">
-        <v>1814</v>
-      </c>
-      <c r="M12" s="26">
-        <f t="shared" si="2"/>
-        <v>-15</v>
-      </c>
+      <c r="J12" s="26"/>
+      <c r="K12" s="26"/>
+      <c r="L12" s="26"/>
+      <c r="M12" s="26"/>
     </row>
     <row r="13" spans="1:13" s="16" customFormat="1" ht="25.5" customHeight="1">
-      <c r="A13" s="19" t="s">
-        <v>16</v>
-      </c>
-      <c r="B13" s="20" t="s">
-        <v>1631</v>
-      </c>
-      <c r="C13" s="20" t="s">
-        <v>1632</v>
-      </c>
-      <c r="D13" s="20" t="s">
-        <v>1749</v>
-      </c>
-      <c r="E13" s="26">
-        <v>1869</v>
-      </c>
-      <c r="F13" s="26">
-        <v>1899</v>
-      </c>
-      <c r="G13" s="26">
-        <f t="shared" si="0"/>
-        <v>30</v>
-      </c>
+      <c r="A13" s="19"/>
+      <c r="B13" s="20"/>
+      <c r="C13" s="20"/>
+      <c r="D13" s="20"/>
+      <c r="E13" s="26"/>
+      <c r="F13" s="26"/>
+      <c r="G13" s="26"/>
       <c r="H13" s="26"/>
       <c r="I13" s="26"/>
-      <c r="J13" s="26" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K13" s="26">
-        <v>1849</v>
-      </c>
-      <c r="L13" s="26">
-        <v>1854</v>
-      </c>
-      <c r="M13" s="26">
-        <f t="shared" si="2"/>
-        <v>5</v>
-      </c>
+      <c r="J13" s="26"/>
+      <c r="K13" s="26"/>
+      <c r="L13" s="26"/>
+      <c r="M13" s="26"/>
     </row>
     <row r="14" spans="1:13" s="16" customFormat="1" ht="25.5" customHeight="1">
-      <c r="A14" s="19" t="s">
-        <v>16</v>
-      </c>
-      <c r="B14" s="20" t="s">
-        <v>1346</v>
-      </c>
-      <c r="C14" s="20" t="s">
-        <v>1347</v>
-      </c>
-      <c r="D14" s="20" t="s">
-        <v>1749</v>
-      </c>
-      <c r="E14" s="26">
-        <v>1870</v>
-      </c>
-      <c r="F14" s="26">
-        <v>1850</v>
-      </c>
-      <c r="G14" s="26">
-        <f t="shared" si="0"/>
-        <v>-20</v>
-      </c>
+      <c r="A14" s="19"/>
+      <c r="B14" s="20"/>
+      <c r="C14" s="20"/>
+      <c r="D14" s="20"/>
+      <c r="E14" s="26"/>
+      <c r="F14" s="26"/>
+      <c r="G14" s="26"/>
       <c r="H14" s="26"/>
       <c r="I14" s="26"/>
-      <c r="J14" s="26" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K14" s="26">
-        <v>1840</v>
-      </c>
-      <c r="L14" s="26">
-        <v>1820</v>
-      </c>
-      <c r="M14" s="26">
-        <f t="shared" si="2"/>
-        <v>-20</v>
-      </c>
+      <c r="J14" s="26"/>
+      <c r="K14" s="26"/>
+      <c r="L14" s="26"/>
+      <c r="M14" s="26"/>
     </row>
     <row r="15" spans="1:13" s="16" customFormat="1" ht="25.5" customHeight="1">
-      <c r="A15" s="19" t="s">
-        <v>10</v>
-      </c>
-      <c r="B15" s="20" t="s">
-        <v>1140</v>
-      </c>
-      <c r="C15" s="20" t="s">
-        <v>1141</v>
-      </c>
-      <c r="D15" s="20" t="s">
-        <v>1749</v>
-      </c>
-      <c r="E15" s="26">
-        <v>1829</v>
-      </c>
-      <c r="F15" s="26">
-        <v>1829</v>
-      </c>
-      <c r="G15" s="26">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
+      <c r="A15" s="19"/>
+      <c r="B15" s="20"/>
+      <c r="C15" s="20"/>
+      <c r="D15" s="20"/>
+      <c r="E15" s="26"/>
+      <c r="F15" s="26"/>
+      <c r="G15" s="26"/>
       <c r="H15" s="26"/>
       <c r="I15" s="26"/>
-      <c r="J15" s="26" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K15" s="26">
-        <v>1819</v>
-      </c>
-      <c r="L15" s="26">
-        <v>1859</v>
-      </c>
-      <c r="M15" s="26">
-        <f t="shared" si="2"/>
-        <v>40</v>
-      </c>
+      <c r="J15" s="26"/>
+      <c r="K15" s="26"/>
+      <c r="L15" s="26"/>
+      <c r="M15" s="26"/>
     </row>
     <row r="16" spans="1:13" s="16" customFormat="1" ht="25.5" customHeight="1">
-      <c r="A16" s="19" t="s">
-        <v>10</v>
-      </c>
-      <c r="B16" s="20" t="s">
-        <v>951</v>
-      </c>
-      <c r="C16" s="20" t="s">
-        <v>952</v>
-      </c>
-      <c r="D16" s="20" t="s">
-        <v>1749</v>
-      </c>
-      <c r="E16" s="26">
-        <v>1838</v>
-      </c>
-      <c r="F16" s="26">
-        <v>1838</v>
-      </c>
-      <c r="G16" s="26">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
+      <c r="A16" s="19"/>
+      <c r="B16" s="20"/>
+      <c r="C16" s="20"/>
+      <c r="D16" s="20"/>
+      <c r="E16" s="26"/>
+      <c r="F16" s="26"/>
+      <c r="G16" s="26"/>
       <c r="H16" s="26"/>
       <c r="I16" s="26"/>
-      <c r="J16" s="26" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K16" s="26">
-        <v>1828</v>
-      </c>
-      <c r="L16" s="26">
-        <v>1978</v>
-      </c>
-      <c r="M16" s="26">
-        <f t="shared" si="2"/>
-        <v>150</v>
-      </c>
+      <c r="J16" s="26"/>
+      <c r="K16" s="26"/>
+      <c r="L16" s="26"/>
+      <c r="M16" s="26"/>
     </row>
     <row r="17" spans="1:13" s="16" customFormat="1" ht="25.5" customHeight="1">
-      <c r="A17" s="19" t="s">
-        <v>14</v>
-      </c>
-      <c r="B17" s="20" t="s">
-        <v>1247</v>
-      </c>
-      <c r="C17" s="20" t="s">
-        <v>1248</v>
-      </c>
-      <c r="D17" s="20" t="s">
-        <v>1749</v>
-      </c>
-      <c r="E17" s="26">
-        <v>1858</v>
-      </c>
-      <c r="F17" s="26">
-        <v>1868</v>
-      </c>
-      <c r="G17" s="26">
-        <f t="shared" si="0"/>
-        <v>10</v>
-      </c>
+      <c r="A17" s="19"/>
+      <c r="B17" s="20"/>
+      <c r="C17" s="20"/>
+      <c r="D17" s="20"/>
+      <c r="E17" s="26"/>
+      <c r="F17" s="26"/>
+      <c r="G17" s="26"/>
       <c r="H17" s="26"/>
       <c r="I17" s="26"/>
-      <c r="J17" s="26" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K17" s="26">
-        <v>1848</v>
-      </c>
-      <c r="L17" s="26">
-        <v>1848</v>
-      </c>
-      <c r="M17" s="26">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
+      <c r="J17" s="26"/>
+      <c r="K17" s="26"/>
+      <c r="L17" s="26"/>
+      <c r="M17" s="26"/>
     </row>
     <row r="18" spans="1:13" s="16" customFormat="1" ht="25.5" customHeight="1">
-      <c r="A18" s="19" t="s">
-        <v>12</v>
-      </c>
-      <c r="B18" s="20" t="s">
-        <v>715</v>
-      </c>
-      <c r="C18" s="20" t="s">
-        <v>716</v>
-      </c>
-      <c r="D18" s="20" t="s">
-        <v>1749</v>
-      </c>
-      <c r="E18" s="26">
-        <v>1867</v>
-      </c>
-      <c r="F18" s="26">
-        <v>1867</v>
-      </c>
-      <c r="G18" s="26">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
+      <c r="A18" s="19"/>
+      <c r="B18" s="20"/>
+      <c r="C18" s="20"/>
+      <c r="D18" s="20"/>
+      <c r="E18" s="26"/>
+      <c r="F18" s="26"/>
+      <c r="G18" s="26"/>
       <c r="H18" s="26"/>
       <c r="I18" s="26"/>
-      <c r="J18" s="26" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K18" s="26">
-        <v>1847</v>
-      </c>
-      <c r="L18" s="26">
-        <v>1860</v>
-      </c>
-      <c r="M18" s="26">
-        <f t="shared" si="2"/>
-        <v>13</v>
-      </c>
+      <c r="J18" s="26"/>
+      <c r="K18" s="26"/>
+      <c r="L18" s="26"/>
+      <c r="M18" s="26"/>
     </row>
     <row r="19" spans="1:13" s="16" customFormat="1" ht="25.5" customHeight="1">
-      <c r="A19" s="19" t="s">
-        <v>14</v>
-      </c>
-      <c r="B19" s="20" t="s">
-        <v>439</v>
-      </c>
-      <c r="C19" s="20" t="s">
-        <v>440</v>
-      </c>
-      <c r="D19" s="20" t="s">
-        <v>1749</v>
-      </c>
-      <c r="E19" s="26">
-        <v>1869</v>
-      </c>
-      <c r="F19" s="26">
-        <v>1869</v>
-      </c>
-      <c r="G19" s="26">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
+      <c r="A19" s="19"/>
+      <c r="B19" s="20"/>
+      <c r="C19" s="20"/>
+      <c r="D19" s="20"/>
+      <c r="E19" s="26"/>
+      <c r="F19" s="26"/>
+      <c r="G19" s="26"/>
       <c r="H19" s="26"/>
       <c r="I19" s="26"/>
-      <c r="J19" s="26" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K19" s="26">
-        <v>1839</v>
-      </c>
-      <c r="L19" s="26">
-        <v>1824</v>
-      </c>
-      <c r="M19" s="26">
-        <f t="shared" si="2"/>
-        <v>-15</v>
-      </c>
+      <c r="J19" s="26"/>
+      <c r="K19" s="26"/>
+      <c r="L19" s="26"/>
+      <c r="M19" s="26"/>
     </row>
     <row r="20" spans="1:13" s="16" customFormat="1" ht="25.5" customHeight="1">
-      <c r="A20" s="19" t="s">
-        <v>14</v>
-      </c>
-      <c r="B20" s="20" t="s">
-        <v>1295</v>
-      </c>
-      <c r="C20" s="20" t="s">
-        <v>1296</v>
-      </c>
-      <c r="D20" s="20" t="s">
-        <v>1749</v>
-      </c>
-      <c r="E20" s="26">
-        <v>1879</v>
-      </c>
-      <c r="F20" s="26">
-        <v>1879</v>
-      </c>
-      <c r="G20" s="26">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
+      <c r="A20" s="19"/>
+      <c r="B20" s="20"/>
+      <c r="C20" s="20"/>
+      <c r="D20" s="20"/>
+      <c r="E20" s="26"/>
+      <c r="F20" s="26"/>
+      <c r="G20" s="26"/>
       <c r="H20" s="26"/>
       <c r="I20" s="26"/>
-      <c r="J20" s="26" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K20" s="26">
-        <v>1843</v>
-      </c>
-      <c r="L20" s="26">
-        <v>1858</v>
-      </c>
-      <c r="M20" s="26">
-        <f t="shared" si="2"/>
-        <v>15</v>
-      </c>
+      <c r="J20" s="26"/>
+      <c r="K20" s="26"/>
+      <c r="L20" s="26"/>
+      <c r="M20" s="26"/>
     </row>
     <row r="21" spans="1:13" s="16" customFormat="1" ht="25.5" customHeight="1">
-      <c r="A21" s="19" t="s">
-        <v>14</v>
-      </c>
-      <c r="B21" s="20" t="s">
-        <v>386</v>
-      </c>
-      <c r="C21" s="20" t="s">
-        <v>387</v>
-      </c>
-      <c r="D21" s="20" t="s">
-        <v>1749</v>
-      </c>
-      <c r="E21" s="26">
-        <v>1897</v>
-      </c>
-      <c r="F21" s="26">
-        <v>1878</v>
-      </c>
-      <c r="G21" s="26">
-        <f t="shared" si="0"/>
-        <v>-19</v>
-      </c>
+      <c r="A21" s="19"/>
+      <c r="B21" s="20"/>
+      <c r="C21" s="20"/>
+      <c r="D21" s="20"/>
+      <c r="E21" s="26"/>
+      <c r="F21" s="26"/>
+      <c r="G21" s="26"/>
       <c r="H21" s="26"/>
       <c r="I21" s="26"/>
-      <c r="J21" s="26" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K21" s="26">
-        <v>1807</v>
-      </c>
-      <c r="L21" s="26">
-        <v>1817</v>
-      </c>
-      <c r="M21" s="26">
-        <f t="shared" si="2"/>
-        <v>10</v>
-      </c>
+      <c r="J21" s="26"/>
+      <c r="K21" s="26"/>
+      <c r="L21" s="26"/>
+      <c r="M21" s="26"/>
     </row>
     <row r="22" spans="1:13" s="16" customFormat="1" ht="25.5" customHeight="1">
-      <c r="A22" s="19" t="s">
-        <v>6</v>
-      </c>
-      <c r="B22" s="20" t="s">
-        <v>1504</v>
-      </c>
-      <c r="C22" s="20" t="s">
-        <v>1505</v>
-      </c>
-      <c r="D22" s="20" t="s">
-        <v>1749</v>
-      </c>
-      <c r="E22" s="26">
-        <v>1899</v>
-      </c>
-      <c r="F22" s="26">
-        <v>1830</v>
-      </c>
-      <c r="G22" s="26">
-        <f t="shared" si="0"/>
-        <v>-69</v>
-      </c>
+      <c r="A22" s="19"/>
+      <c r="B22" s="20"/>
+      <c r="C22" s="20"/>
+      <c r="D22" s="20"/>
+      <c r="E22" s="26"/>
+      <c r="F22" s="26"/>
+      <c r="G22" s="26"/>
       <c r="H22" s="26"/>
       <c r="I22" s="26"/>
-      <c r="J22" s="26" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K22" s="26">
-        <v>1839</v>
-      </c>
-      <c r="L22" s="26">
-        <v>1816</v>
-      </c>
-      <c r="M22" s="26">
-        <f t="shared" si="2"/>
-        <v>-23</v>
-      </c>
+      <c r="J22" s="26"/>
+      <c r="K22" s="26"/>
+      <c r="L22" s="26"/>
+      <c r="M22" s="26"/>
     </row>
     <row r="23" spans="1:13" s="16" customFormat="1" ht="25.5" customHeight="1">
-      <c r="A23" s="19" t="s">
-        <v>10</v>
-      </c>
-      <c r="B23" s="20" t="s">
-        <v>1202</v>
-      </c>
-      <c r="C23" s="20" t="s">
-        <v>1203</v>
-      </c>
-      <c r="D23" s="20" t="s">
-        <v>1749</v>
-      </c>
-      <c r="E23" s="26">
-        <v>1938</v>
-      </c>
-      <c r="F23" s="26">
-        <v>1908</v>
-      </c>
-      <c r="G23" s="26">
-        <f t="shared" si="0"/>
-        <v>-30</v>
-      </c>
+      <c r="A23" s="19"/>
+      <c r="B23" s="20"/>
+      <c r="C23" s="20"/>
+      <c r="D23" s="20"/>
+      <c r="E23" s="26"/>
+      <c r="F23" s="26"/>
+      <c r="G23" s="26"/>
       <c r="H23" s="26"/>
       <c r="I23" s="26"/>
-      <c r="J23" s="26" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K23" s="26">
-        <v>1898</v>
-      </c>
-      <c r="L23" s="26">
-        <v>1898</v>
-      </c>
-      <c r="M23" s="26">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
+      <c r="J23" s="26"/>
+      <c r="K23" s="26"/>
+      <c r="L23" s="26"/>
+      <c r="M23" s="26"/>
     </row>
     <row r="24" spans="1:13" s="16" customFormat="1" ht="25.5" customHeight="1">
-      <c r="A24" s="19" t="s">
-        <v>16</v>
-      </c>
-      <c r="B24" s="20" t="s">
-        <v>1647</v>
-      </c>
-      <c r="C24" s="20" t="s">
-        <v>1648</v>
-      </c>
-      <c r="D24" s="20" t="s">
-        <v>1749</v>
-      </c>
-      <c r="E24" s="26">
-        <v>1989</v>
-      </c>
-      <c r="F24" s="26">
-        <v>1865</v>
-      </c>
-      <c r="G24" s="26">
-        <f t="shared" si="0"/>
-        <v>-124</v>
-      </c>
+      <c r="A24" s="19"/>
+      <c r="B24" s="20"/>
+      <c r="C24" s="20"/>
+      <c r="D24" s="20"/>
+      <c r="E24" s="26"/>
+      <c r="F24" s="26"/>
+      <c r="G24" s="26"/>
       <c r="H24" s="26"/>
       <c r="I24" s="26"/>
-      <c r="J24" s="26" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K24" s="26">
-        <v>1825</v>
-      </c>
-      <c r="L24" s="26">
-        <v>1825</v>
-      </c>
-      <c r="M24" s="26">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
+      <c r="J24" s="26"/>
+      <c r="K24" s="26"/>
+      <c r="L24" s="26"/>
+      <c r="M24" s="26"/>
     </row>
     <row r="25" spans="1:13" s="16" customFormat="1" ht="25.5" customHeight="1">
-      <c r="A25" s="19" t="s">
-        <v>12</v>
-      </c>
-      <c r="B25" s="20" t="s">
-        <v>1570</v>
-      </c>
-      <c r="C25" s="20" t="s">
-        <v>1571</v>
-      </c>
-      <c r="D25" s="20" t="s">
-        <v>1749</v>
-      </c>
-      <c r="E25" s="26">
-        <v>1824</v>
-      </c>
-      <c r="F25" s="26">
-        <v>1797</v>
-      </c>
-      <c r="G25" s="26">
-        <f t="shared" si="0"/>
-        <v>-27</v>
-      </c>
+      <c r="A25" s="19"/>
+      <c r="B25" s="20"/>
+      <c r="C25" s="20"/>
+      <c r="D25" s="20"/>
+      <c r="E25" s="26"/>
+      <c r="F25" s="26"/>
+      <c r="G25" s="26"/>
       <c r="H25" s="26"/>
       <c r="I25" s="26"/>
-      <c r="J25" s="26" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K25" s="26">
-        <v>1812</v>
-      </c>
-      <c r="L25" s="26">
-        <v>1792</v>
-      </c>
-      <c r="M25" s="26">
-        <f t="shared" si="2"/>
-        <v>-20</v>
-      </c>
+      <c r="J25" s="26"/>
+      <c r="K25" s="26"/>
+      <c r="L25" s="26"/>
+      <c r="M25" s="26"/>
     </row>
     <row r="26" spans="1:13" s="16" customFormat="1" ht="25.5" customHeight="1">
-      <c r="A26" s="19" t="s">
-        <v>10</v>
-      </c>
-      <c r="B26" s="20" t="s">
-        <v>1186</v>
-      </c>
-      <c r="C26" s="20" t="s">
-        <v>1187</v>
-      </c>
-      <c r="D26" s="20" t="s">
-        <v>1749</v>
-      </c>
-      <c r="E26" s="26">
-        <v>1824</v>
-      </c>
-      <c r="F26" s="26">
-        <v>1826</v>
-      </c>
-      <c r="G26" s="26">
-        <f t="shared" si="0"/>
-        <v>2</v>
-      </c>
+      <c r="A26" s="19"/>
+      <c r="B26" s="20"/>
+      <c r="C26" s="20"/>
+      <c r="D26" s="20"/>
+      <c r="E26" s="26"/>
+      <c r="F26" s="26"/>
+      <c r="G26" s="26"/>
       <c r="H26" s="26"/>
       <c r="I26" s="26"/>
-      <c r="J26" s="26" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K26" s="26">
-        <v>1813</v>
-      </c>
-      <c r="L26" s="26">
-        <v>1813</v>
-      </c>
-      <c r="M26" s="26">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
+      <c r="J26" s="26"/>
+      <c r="K26" s="26"/>
+      <c r="L26" s="26"/>
+      <c r="M26" s="26"/>
     </row>
     <row r="27" spans="1:13" s="16" customFormat="1" ht="25.5" customHeight="1">
-      <c r="A27" s="19" t="s">
-        <v>6</v>
-      </c>
-      <c r="B27" s="20" t="s">
-        <v>1249</v>
-      </c>
-      <c r="C27" s="20" t="s">
-        <v>1250</v>
-      </c>
-      <c r="D27" s="20" t="s">
-        <v>1749</v>
-      </c>
-      <c r="E27" s="26">
-        <v>1825</v>
-      </c>
-      <c r="F27" s="26">
-        <v>1815</v>
-      </c>
-      <c r="G27" s="26">
-        <f t="shared" si="0"/>
-        <v>-10</v>
-      </c>
+      <c r="A27" s="19"/>
+      <c r="B27" s="20"/>
+      <c r="C27" s="20"/>
+      <c r="D27" s="20"/>
+      <c r="E27" s="26"/>
+      <c r="F27" s="26"/>
+      <c r="G27" s="26"/>
       <c r="H27" s="26"/>
       <c r="I27" s="26"/>
-      <c r="J27" s="26" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K27" s="26">
-        <v>1795</v>
-      </c>
-      <c r="L27" s="26">
-        <v>1795</v>
-      </c>
-      <c r="M27" s="26">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
+      <c r="J27" s="26"/>
+      <c r="K27" s="26"/>
+      <c r="L27" s="26"/>
+      <c r="M27" s="26"/>
     </row>
     <row r="28" spans="1:13" s="16" customFormat="1" ht="25.5" customHeight="1">
-      <c r="A28" s="19" t="s">
-        <v>10</v>
-      </c>
-      <c r="B28" s="20" t="s">
-        <v>742</v>
-      </c>
-      <c r="C28" s="20" t="s">
-        <v>743</v>
-      </c>
-      <c r="D28" s="20" t="s">
-        <v>1749</v>
-      </c>
-      <c r="E28" s="26">
-        <v>1829</v>
-      </c>
-      <c r="F28" s="26">
-        <v>1839</v>
-      </c>
-      <c r="G28" s="26">
-        <f t="shared" si="0"/>
-        <v>10</v>
-      </c>
+      <c r="A28" s="19"/>
+      <c r="B28" s="20"/>
+      <c r="C28" s="20"/>
+      <c r="D28" s="20"/>
+      <c r="E28" s="26"/>
+      <c r="F28" s="26"/>
+      <c r="G28" s="26"/>
       <c r="H28" s="26"/>
       <c r="I28" s="26"/>
-      <c r="J28" s="26" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K28" s="26">
-        <v>1819</v>
-      </c>
-      <c r="L28" s="26">
-        <v>1819</v>
-      </c>
-      <c r="M28" s="26">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
+      <c r="J28" s="26"/>
+      <c r="K28" s="26"/>
+      <c r="L28" s="26"/>
+      <c r="M28" s="26"/>
     </row>
     <row r="29" spans="1:13" s="16" customFormat="1" ht="25.5" customHeight="1">
-      <c r="A29" s="19" t="s">
-        <v>6</v>
-      </c>
-      <c r="B29" s="20" t="s">
-        <v>128</v>
-      </c>
-      <c r="C29" s="20" t="s">
-        <v>129</v>
-      </c>
-      <c r="D29" s="20" t="s">
-        <v>1749</v>
-      </c>
-      <c r="E29" s="26">
-        <v>1842</v>
-      </c>
-      <c r="F29" s="26">
-        <v>1812</v>
-      </c>
-      <c r="G29" s="26">
-        <f t="shared" si="0"/>
-        <v>-30</v>
-      </c>
+      <c r="A29" s="19"/>
+      <c r="B29" s="20"/>
+      <c r="C29" s="20"/>
+      <c r="D29" s="20"/>
+      <c r="E29" s="26"/>
+      <c r="F29" s="26"/>
+      <c r="G29" s="26"/>
       <c r="H29" s="26"/>
       <c r="I29" s="26"/>
-      <c r="J29" s="26" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K29" s="26">
-        <v>1792</v>
-      </c>
-      <c r="L29" s="26">
-        <v>1797</v>
-      </c>
-      <c r="M29" s="26">
-        <f t="shared" si="2"/>
-        <v>5</v>
-      </c>
+      <c r="J29" s="26"/>
+      <c r="K29" s="26"/>
+      <c r="L29" s="26"/>
+      <c r="M29" s="26"/>
     </row>
     <row r="30" spans="1:13" s="16" customFormat="1" ht="25.5" customHeight="1">
-      <c r="A30" s="19" t="s">
-        <v>6</v>
-      </c>
-      <c r="B30" s="20" t="s">
-        <v>1693</v>
-      </c>
-      <c r="C30" s="20" t="s">
-        <v>1694</v>
-      </c>
-      <c r="D30" s="20" t="s">
-        <v>1749</v>
-      </c>
-      <c r="E30" s="26">
-        <v>1842</v>
-      </c>
-      <c r="F30" s="26">
-        <v>1829</v>
-      </c>
-      <c r="G30" s="26">
-        <f t="shared" si="0"/>
-        <v>-13</v>
-      </c>
+      <c r="A30" s="19"/>
+      <c r="B30" s="20"/>
+      <c r="C30" s="20"/>
+      <c r="D30" s="20"/>
+      <c r="E30" s="26"/>
+      <c r="F30" s="26"/>
+      <c r="G30" s="26"/>
       <c r="H30" s="26"/>
       <c r="I30" s="26"/>
-      <c r="J30" s="26" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K30" s="26">
-        <v>1829</v>
-      </c>
-      <c r="L30" s="26">
-        <v>1822</v>
-      </c>
-      <c r="M30" s="26">
-        <f t="shared" si="2"/>
-        <v>-7</v>
-      </c>
+      <c r="J30" s="26"/>
+      <c r="K30" s="26"/>
+      <c r="L30" s="26"/>
+      <c r="M30" s="26"/>
     </row>
     <row r="31" spans="1:13" s="16" customFormat="1" ht="25.5" customHeight="1">
-      <c r="A31" s="19" t="s">
-        <v>12</v>
-      </c>
-      <c r="B31" s="20" t="s">
-        <v>1582</v>
-      </c>
-      <c r="C31" s="20" t="s">
-        <v>1583</v>
-      </c>
-      <c r="D31" s="20" t="s">
-        <v>1749</v>
-      </c>
-      <c r="E31" s="26">
-        <v>1848</v>
-      </c>
-      <c r="F31" s="26">
-        <v>1848</v>
-      </c>
-      <c r="G31" s="26">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
+      <c r="A31" s="19"/>
+      <c r="B31" s="20"/>
+      <c r="C31" s="20"/>
+      <c r="D31" s="20"/>
+      <c r="E31" s="26"/>
+      <c r="F31" s="26"/>
+      <c r="G31" s="26"/>
       <c r="H31" s="26"/>
       <c r="I31" s="26"/>
-      <c r="J31" s="26" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K31" s="26">
-        <v>1823</v>
-      </c>
-      <c r="L31" s="26">
-        <v>1838</v>
-      </c>
-      <c r="M31" s="26">
-        <f t="shared" si="2"/>
-        <v>15</v>
-      </c>
+      <c r="J31" s="26"/>
+      <c r="K31" s="26"/>
+      <c r="L31" s="26"/>
+      <c r="M31" s="26"/>
     </row>
     <row r="32" spans="1:13" s="16" customFormat="1" ht="25.5" customHeight="1">
-      <c r="A32" s="19" t="s">
-        <v>10</v>
-      </c>
-      <c r="B32" s="20" t="s">
-        <v>859</v>
-      </c>
-      <c r="C32" s="20" t="s">
-        <v>860</v>
-      </c>
-      <c r="D32" s="20" t="s">
-        <v>1749</v>
-      </c>
-      <c r="E32" s="26">
-        <v>1855</v>
-      </c>
-      <c r="F32" s="26">
-        <v>1855</v>
-      </c>
-      <c r="G32" s="26">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
+      <c r="A32" s="19"/>
+      <c r="B32" s="20"/>
+      <c r="C32" s="20"/>
+      <c r="D32" s="20"/>
+      <c r="E32" s="26"/>
+      <c r="F32" s="26"/>
+      <c r="G32" s="26"/>
       <c r="H32" s="26"/>
       <c r="I32" s="26"/>
-      <c r="J32" s="26" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K32" s="26">
-        <v>1825</v>
-      </c>
-      <c r="L32" s="26">
-        <v>1875</v>
-      </c>
-      <c r="M32" s="26">
-        <f t="shared" si="2"/>
-        <v>50</v>
-      </c>
+      <c r="J32" s="26"/>
+      <c r="K32" s="26"/>
+      <c r="L32" s="26"/>
+      <c r="M32" s="26"/>
     </row>
     <row r="33" spans="1:13" s="16" customFormat="1" ht="25.5" customHeight="1">
-      <c r="A33" s="19" t="s">
-        <v>14</v>
-      </c>
-      <c r="B33" s="20" t="s">
-        <v>1327</v>
-      </c>
-      <c r="C33" s="20" t="s">
-        <v>1328</v>
-      </c>
-      <c r="D33" s="20" t="s">
-        <v>1749</v>
-      </c>
-      <c r="E33" s="26">
-        <v>1858</v>
-      </c>
-      <c r="F33" s="26">
-        <v>1858</v>
-      </c>
-      <c r="G33" s="26">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
+      <c r="A33" s="19"/>
+      <c r="B33" s="20"/>
+      <c r="C33" s="20"/>
+      <c r="D33" s="20"/>
+      <c r="E33" s="26"/>
+      <c r="F33" s="26"/>
+      <c r="G33" s="26"/>
       <c r="H33" s="26"/>
       <c r="I33" s="26"/>
-      <c r="J33" s="26" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K33" s="26">
-        <v>1877</v>
-      </c>
-      <c r="L33" s="26">
-        <v>1857</v>
-      </c>
-      <c r="M33" s="26">
-        <f t="shared" si="2"/>
-        <v>-20</v>
-      </c>
+      <c r="J33" s="26"/>
+      <c r="K33" s="26"/>
+      <c r="L33" s="26"/>
+      <c r="M33" s="26"/>
     </row>
     <row r="34" spans="1:13" s="16" customFormat="1" ht="25.5" customHeight="1">
-      <c r="A34" s="19" t="s">
-        <v>16</v>
-      </c>
-      <c r="B34" s="20" t="s">
-        <v>1466</v>
-      </c>
-      <c r="C34" s="20" t="s">
-        <v>1467</v>
-      </c>
-      <c r="D34" s="20" t="s">
-        <v>1749</v>
-      </c>
-      <c r="E34" s="26">
-        <v>1860</v>
-      </c>
-      <c r="F34" s="26">
-        <v>1860</v>
-      </c>
-      <c r="G34" s="26">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
+      <c r="A34" s="19"/>
+      <c r="B34" s="20"/>
+      <c r="C34" s="20"/>
+      <c r="D34" s="20"/>
+      <c r="E34" s="26"/>
+      <c r="F34" s="26"/>
+      <c r="G34" s="26"/>
       <c r="H34" s="26"/>
       <c r="I34" s="26"/>
-      <c r="J34" s="26" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K34" s="26">
-        <v>1820</v>
-      </c>
-      <c r="L34" s="26">
-        <v>1840</v>
-      </c>
-      <c r="M34" s="26">
-        <f t="shared" si="2"/>
-        <v>20</v>
-      </c>
+      <c r="J34" s="26"/>
+      <c r="K34" s="26"/>
+      <c r="L34" s="26"/>
+      <c r="M34" s="26"/>
     </row>
     <row r="35" spans="1:13" s="16" customFormat="1" ht="25.5" customHeight="1">
-      <c r="A35" s="19" t="s">
-        <v>14</v>
-      </c>
-      <c r="B35" s="20" t="s">
-        <v>773</v>
-      </c>
-      <c r="C35" s="20" t="s">
-        <v>774</v>
-      </c>
-      <c r="D35" s="20" t="s">
-        <v>1749</v>
-      </c>
-      <c r="E35" s="26">
-        <v>1869</v>
-      </c>
-      <c r="F35" s="26">
-        <v>1869</v>
-      </c>
-      <c r="G35" s="26">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
+      <c r="A35" s="19"/>
+      <c r="B35" s="20"/>
+      <c r="C35" s="20"/>
+      <c r="D35" s="20"/>
+      <c r="E35" s="26"/>
+      <c r="F35" s="26"/>
+      <c r="G35" s="26"/>
       <c r="H35" s="26"/>
       <c r="I35" s="26"/>
-      <c r="J35" s="26" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K35" s="26">
-        <v>1834</v>
-      </c>
-      <c r="L35" s="26">
-        <v>1839</v>
-      </c>
-      <c r="M35" s="26">
-        <f t="shared" si="2"/>
-        <v>5</v>
-      </c>
+      <c r="J35" s="26"/>
+      <c r="K35" s="26"/>
+      <c r="L35" s="26"/>
+      <c r="M35" s="26"/>
     </row>
     <row r="36" spans="1:13" s="16" customFormat="1" ht="25.5" customHeight="1">
-      <c r="A36" s="19" t="s">
-        <v>10</v>
-      </c>
-      <c r="B36" s="20" t="s">
-        <v>447</v>
-      </c>
-      <c r="C36" s="20" t="s">
-        <v>448</v>
-      </c>
-      <c r="D36" s="20" t="s">
-        <v>1749</v>
-      </c>
-      <c r="E36" s="26">
-        <v>1870</v>
-      </c>
-      <c r="F36" s="26">
-        <v>1870</v>
-      </c>
-      <c r="G36" s="26">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
+      <c r="A36" s="19"/>
+      <c r="B36" s="20"/>
+      <c r="C36" s="20"/>
+      <c r="D36" s="20"/>
+      <c r="E36" s="26"/>
+      <c r="F36" s="26"/>
+      <c r="G36" s="26"/>
       <c r="H36" s="26"/>
       <c r="I36" s="26"/>
-      <c r="J36" s="26" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K36" s="26">
-        <v>1840</v>
-      </c>
-      <c r="L36" s="26">
-        <v>1860</v>
-      </c>
-      <c r="M36" s="26">
-        <f t="shared" si="2"/>
-        <v>20</v>
-      </c>
+      <c r="J36" s="26"/>
+      <c r="K36" s="26"/>
+      <c r="L36" s="26"/>
+      <c r="M36" s="26"/>
     </row>
     <row r="37" spans="1:13" s="16" customFormat="1" ht="25.5" customHeight="1">
-      <c r="A37" s="19" t="s">
-        <v>14</v>
-      </c>
-      <c r="B37" s="20" t="s">
-        <v>1645</v>
-      </c>
-      <c r="C37" s="20" t="s">
-        <v>1646</v>
-      </c>
-      <c r="D37" s="20" t="s">
-        <v>1749</v>
-      </c>
-      <c r="E37" s="26">
-        <v>1879</v>
-      </c>
-      <c r="F37" s="26">
-        <v>1879</v>
-      </c>
-      <c r="G37" s="26">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
+      <c r="A37" s="19"/>
+      <c r="B37" s="20"/>
+      <c r="C37" s="20"/>
+      <c r="D37" s="20"/>
+      <c r="E37" s="26"/>
+      <c r="F37" s="26"/>
+      <c r="G37" s="26"/>
       <c r="H37" s="26"/>
       <c r="I37" s="26"/>
-      <c r="J37" s="26" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K37" s="26">
-        <v>1909</v>
-      </c>
-      <c r="L37" s="26">
-        <v>1889</v>
-      </c>
-      <c r="M37" s="26">
-        <f t="shared" si="2"/>
-        <v>-20</v>
-      </c>
+      <c r="J37" s="26"/>
+      <c r="K37" s="26"/>
+      <c r="L37" s="26"/>
+      <c r="M37" s="26"/>
     </row>
     <row r="38" spans="1:13" s="16" customFormat="1" ht="25.5" customHeight="1">
-      <c r="A38" s="19" t="s">
-        <v>14</v>
-      </c>
-      <c r="B38" s="20" t="s">
-        <v>834</v>
-      </c>
-      <c r="C38" s="20" t="s">
-        <v>835</v>
-      </c>
-      <c r="D38" s="20" t="s">
-        <v>1749</v>
-      </c>
-      <c r="E38" s="26">
-        <v>1929</v>
-      </c>
-      <c r="F38" s="26">
-        <v>1899</v>
-      </c>
-      <c r="G38" s="26">
-        <f t="shared" si="0"/>
-        <v>-30</v>
-      </c>
+      <c r="A38" s="19"/>
+      <c r="B38" s="20"/>
+      <c r="C38" s="20"/>
+      <c r="D38" s="20"/>
+      <c r="E38" s="26"/>
+      <c r="F38" s="26"/>
+      <c r="G38" s="26"/>
       <c r="H38" s="26"/>
       <c r="I38" s="26"/>
-      <c r="J38" s="26" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K38" s="26">
-        <v>1889</v>
-      </c>
-      <c r="L38" s="26">
-        <v>1889</v>
-      </c>
-      <c r="M38" s="26">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
+      <c r="J38" s="26"/>
+      <c r="K38" s="26"/>
+      <c r="L38" s="26"/>
+      <c r="M38" s="26"/>
     </row>
     <row r="39" spans="1:13" s="16" customFormat="1" ht="25.5" customHeight="1">
-      <c r="A39" s="19" t="s">
-        <v>6</v>
-      </c>
-      <c r="B39" s="20" t="s">
-        <v>771</v>
-      </c>
-      <c r="C39" s="20" t="s">
-        <v>772</v>
-      </c>
-      <c r="D39" s="20" t="s">
-        <v>1749</v>
-      </c>
-      <c r="E39" s="26">
-        <v>2199</v>
-      </c>
-      <c r="F39" s="26">
-        <v>1829</v>
-      </c>
-      <c r="G39" s="26">
-        <f t="shared" si="0"/>
-        <v>-370</v>
-      </c>
+      <c r="A39" s="19"/>
+      <c r="B39" s="20"/>
+      <c r="C39" s="20"/>
+      <c r="D39" s="20"/>
+      <c r="E39" s="26"/>
+      <c r="F39" s="26"/>
+      <c r="G39" s="26"/>
       <c r="H39" s="26"/>
       <c r="I39" s="26"/>
-      <c r="J39" s="26" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K39" s="26">
-        <v>2199</v>
-      </c>
-      <c r="L39" s="26">
-        <v>1819</v>
-      </c>
-      <c r="M39" s="26">
-        <f t="shared" si="2"/>
-        <v>-380</v>
-      </c>
+      <c r="J39" s="26"/>
+      <c r="K39" s="26"/>
+      <c r="L39" s="26"/>
+      <c r="M39" s="26"/>
     </row>
     <row r="40" spans="1:13" s="16" customFormat="1" ht="25.5" customHeight="1">
-      <c r="A40" s="19" t="s">
-        <v>14</v>
-      </c>
-      <c r="B40" s="20" t="s">
-        <v>1762</v>
-      </c>
-      <c r="C40" s="20" t="s">
-        <v>1763</v>
-      </c>
-      <c r="D40" s="20" t="s">
-        <v>1764</v>
-      </c>
+      <c r="A40" s="19"/>
+      <c r="B40" s="20"/>
+      <c r="C40" s="20"/>
+      <c r="D40" s="20"/>
       <c r="E40" s="26"/>
-      <c r="F40" s="26">
-        <v>1799</v>
-      </c>
-      <c r="G40" s="26" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
+      <c r="F40" s="26"/>
+      <c r="G40" s="26"/>
       <c r="H40" s="26"/>
-      <c r="I40" s="26">
-        <v>2415</v>
-      </c>
-      <c r="J40" s="26" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
+      <c r="I40" s="26"/>
+      <c r="J40" s="26"/>
       <c r="K40" s="26"/>
-      <c r="L40" s="26">
-        <v>1798</v>
-      </c>
-      <c r="M40" s="26" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
+      <c r="L40" s="26"/>
+      <c r="M40" s="26"/>
     </row>
     <row r="41" spans="1:13" s="16" customFormat="1" ht="25.5" customHeight="1">
       <c r="A41" s="19"/>
@@ -80104,7 +79153,7 @@
     <mergeCell ref="A1:M1"/>
   </mergeCells>
   <phoneticPr fontId="26" type="noConversion"/>
-  <conditionalFormatting sqref="G4:G40">
+  <conditionalFormatting sqref="G4">
     <cfRule type="cellIs" dxfId="5" priority="2" operator="greaterThan">
       <formula>0</formula>
     </cfRule>
@@ -80112,7 +79161,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="J4:J40">
+  <conditionalFormatting sqref="J4">
     <cfRule type="cellIs" dxfId="3" priority="4" operator="greaterThan">
       <formula>0</formula>
     </cfRule>
@@ -80120,7 +79169,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="M4:M40">
+  <conditionalFormatting sqref="M4">
     <cfRule type="cellIs" dxfId="1" priority="6" operator="greaterThan">
       <formula>0</formula>
     </cfRule>

--- a/fuel_cost_chungcheong.xlsx
+++ b/fuel_cost_chungcheong.xlsx
@@ -74970,10 +74970,8 @@
         <f t="shared" si="177"/>
         <v/>
       </c>
-      <c r="Q876" s="12" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
+      <c r="Q876" s="12" t="s">
+        <v>61</v>
       </c>
       <c r="R876" s="13" t="str">
         <f t="shared" si="178"/>

--- a/fuel_cost_chungcheong.xlsx
+++ b/fuel_cost_chungcheong.xlsx
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4892" uniqueCount="1767">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4724" uniqueCount="1765">
   <si>
     <t>유류비 계산(혼유, 지역화폐 등)</t>
   </si>
@@ -5369,9 +5369,6 @@
     <t>충남 아산시 탕정면 이순신대로 695-5</t>
   </si>
   <si>
-    <t>가격변동</t>
-  </si>
-  <si>
     <t>한솔주유소</t>
   </si>
   <si>
@@ -5391,9 +5388,6 @@
   </si>
   <si>
     <t>충북 청주시 서원구 현도면 청남로 502</t>
-  </si>
-  <si>
-    <t>신규</t>
   </si>
 </sst>
 </file>
@@ -10316,7 +10310,7 @@
         <v>8</v>
       </c>
       <c r="C58" s="11" t="s">
-        <v>1761</v>
+        <v>1760</v>
       </c>
       <c r="D58" s="11" t="s">
         <v>59</v>
@@ -10325,7 +10319,7 @@
         <v>26</v>
       </c>
       <c r="F58" s="11" t="s">
-        <v>1762</v>
+        <v>1761</v>
       </c>
       <c r="G58" s="12">
         <v>1827</v>
@@ -43106,7 +43100,7 @@
         <v>6</v>
       </c>
       <c r="C468" s="11" t="s">
-        <v>1759</v>
+        <v>1758</v>
       </c>
       <c r="D468" s="11" t="s">
         <v>59</v>
@@ -43115,7 +43109,7 @@
         <v>60</v>
       </c>
       <c r="F468" s="11" t="s">
-        <v>1760</v>
+        <v>1759</v>
       </c>
       <c r="G468" s="12">
         <v>1998</v>
@@ -67857,7 +67851,7 @@
         <v>1838</v>
       </c>
       <c r="K785" s="12">
-        <f t="shared" ref="K785:K807" si="170">IF(AND(IFERROR(SEARCH("현대오일뱅크",$C785),0)&gt;0,IFERROR(SEARCH("직영",$C785),0)&gt;0),$B$13,0)</f>
+        <f t="shared" ref="K785:K808" si="170">IF(AND(IFERROR(SEARCH("현대오일뱅크",$C785),0)&gt;0,IFERROR(SEARCH("직영",$C785),0)&gt;0),$B$13,0)</f>
         <v>0</v>
       </c>
       <c r="L785" s="12">
@@ -69394,27 +69388,27 @@
         <v/>
       </c>
       <c r="B805" s="11" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="C805" s="11" t="s">
-        <v>128</v>
-      </c>
-      <c r="D805" s="15" t="s">
+        <v>1763</v>
+      </c>
+      <c r="D805" s="11" t="s">
         <v>45</v>
       </c>
       <c r="E805" s="11" t="s">
         <v>26</v>
       </c>
       <c r="F805" s="11" t="s">
-        <v>129</v>
+        <v>1764</v>
       </c>
       <c r="G805" s="12">
-        <v>1872</v>
+        <v>2080</v>
       </c>
       <c r="H805" s="12"/>
       <c r="I805" s="12"/>
       <c r="J805" s="12">
-        <v>1792</v>
+        <v>1807</v>
       </c>
       <c r="K805" s="12">
         <f t="shared" si="170"/>
@@ -69422,7 +69416,7 @@
       </c>
       <c r="L805" s="12">
         <f t="shared" si="159"/>
-        <v>1872</v>
+        <v>2080</v>
       </c>
       <c r="M805" s="12" t="str">
         <f t="shared" si="160"/>
@@ -69430,7 +69424,7 @@
       </c>
       <c r="N805" s="12">
         <f t="shared" si="161"/>
-        <v>1792</v>
+        <v>1807</v>
       </c>
       <c r="O805" s="12" t="str">
         <f t="shared" si="162"/>
@@ -69440,7 +69434,9 @@
         <f t="shared" si="163"/>
         <v/>
       </c>
-      <c r="Q805" s="12"/>
+      <c r="Q805" s="12" t="str">
+        <v>Y</v>
+      </c>
       <c r="R805" s="13" t="str">
         <f t="shared" si="164"/>
         <v/>
@@ -69475,16 +69471,16 @@
         <v>6</v>
       </c>
       <c r="C806" s="11" t="s">
-        <v>1075</v>
-      </c>
-      <c r="D806" s="11" t="s">
-        <v>57</v>
+        <v>128</v>
+      </c>
+      <c r="D806" s="15" t="s">
+        <v>45</v>
       </c>
       <c r="E806" s="11" t="s">
         <v>26</v>
       </c>
       <c r="F806" s="11" t="s">
-        <v>1076</v>
+        <v>129</v>
       </c>
       <c r="G806" s="12">
         <v>1872</v>
@@ -69492,7 +69488,7 @@
       <c r="H806" s="12"/>
       <c r="I806" s="12"/>
       <c r="J806" s="12">
-        <v>1839</v>
+        <v>1792</v>
       </c>
       <c r="K806" s="12">
         <f t="shared" si="170"/>
@@ -69508,7 +69504,7 @@
       </c>
       <c r="N806" s="12">
         <f t="shared" si="161"/>
-        <v>1839</v>
+        <v>1792</v>
       </c>
       <c r="O806" s="12" t="str">
         <f t="shared" si="162"/>
@@ -69550,19 +69546,19 @@
         <v/>
       </c>
       <c r="B807" s="11" t="s">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="C807" s="11" t="s">
-        <v>296</v>
-      </c>
-      <c r="D807" s="15" t="s">
-        <v>45</v>
+        <v>1075</v>
+      </c>
+      <c r="D807" s="11" t="s">
+        <v>57</v>
       </c>
       <c r="E807" s="11" t="s">
         <v>26</v>
       </c>
       <c r="F807" s="11" t="s">
-        <v>297</v>
+        <v>1076</v>
       </c>
       <c r="G807" s="12">
         <v>1872</v>
@@ -69570,7 +69566,7 @@
       <c r="H807" s="12"/>
       <c r="I807" s="12"/>
       <c r="J807" s="12">
-        <v>1852</v>
+        <v>1839</v>
       </c>
       <c r="K807" s="12">
         <f t="shared" si="170"/>
@@ -69586,7 +69582,7 @@
       </c>
       <c r="N807" s="12">
         <f t="shared" si="161"/>
-        <v>1852</v>
+        <v>1839</v>
       </c>
       <c r="O807" s="12" t="str">
         <f t="shared" si="162"/>
@@ -69628,34 +69624,35 @@
         <v/>
       </c>
       <c r="B808" s="11" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="C808" s="11" t="s">
-        <v>210</v>
+        <v>296</v>
       </c>
       <c r="D808" s="15" t="s">
         <v>45</v>
       </c>
       <c r="E808" s="11" t="s">
-        <v>60</v>
+        <v>26</v>
       </c>
       <c r="F808" s="11" t="s">
-        <v>211</v>
+        <v>297</v>
       </c>
       <c r="G808" s="12">
-        <v>1874</v>
+        <v>1872</v>
       </c>
       <c r="H808" s="12"/>
       <c r="I808" s="12"/>
       <c r="J808" s="12">
-        <v>1854</v>
+        <v>1852</v>
       </c>
       <c r="K808" s="12">
+        <f t="shared" si="170"/>
         <v>0</v>
       </c>
       <c r="L808" s="12">
         <f t="shared" si="159"/>
-        <v>1874</v>
+        <v>1872</v>
       </c>
       <c r="M808" s="12" t="str">
         <f t="shared" si="160"/>
@@ -69663,7 +69660,7 @@
       </c>
       <c r="N808" s="12">
         <f t="shared" si="161"/>
-        <v>1854</v>
+        <v>1852</v>
       </c>
       <c r="O808" s="12" t="str">
         <f t="shared" si="162"/>
@@ -69699,41 +69696,40 @@
         <v>1000000000000000</v>
       </c>
     </row>
-    <row r="809" spans="1:23" s="7" customFormat="1" ht="28.5" customHeight="1">
+    <row r="809" spans="1:23" s="2" customFormat="1" ht="28.5" customHeight="1">
       <c r="A809" s="11" t="str">
         <f t="shared" si="158"/>
         <v/>
       </c>
       <c r="B809" s="11" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="C809" s="11" t="s">
-        <v>945</v>
-      </c>
-      <c r="D809" s="11" t="s">
-        <v>69</v>
+        <v>210</v>
+      </c>
+      <c r="D809" s="15" t="s">
+        <v>45</v>
       </c>
       <c r="E809" s="11" t="s">
-        <v>26</v>
+        <v>60</v>
       </c>
       <c r="F809" s="11" t="s">
-        <v>946</v>
+        <v>211</v>
       </c>
       <c r="G809" s="12">
-        <v>1875</v>
+        <v>1874</v>
       </c>
       <c r="H809" s="12"/>
       <c r="I809" s="12"/>
       <c r="J809" s="12">
-        <v>1855</v>
+        <v>1854</v>
       </c>
       <c r="K809" s="12">
-        <f>IF(AND(IFERROR(SEARCH("현대오일뱅크",$C809),0)&gt;0,IFERROR(SEARCH("직영",$C809),0)&gt;0),$B$13,0)</f>
         <v>0</v>
       </c>
       <c r="L809" s="12">
         <f t="shared" si="159"/>
-        <v>1875</v>
+        <v>1874</v>
       </c>
       <c r="M809" s="12" t="str">
         <f t="shared" si="160"/>
@@ -69741,7 +69737,7 @@
       </c>
       <c r="N809" s="12">
         <f t="shared" si="161"/>
-        <v>1855</v>
+        <v>1854</v>
       </c>
       <c r="O809" s="12" t="str">
         <f t="shared" si="162"/>
@@ -69777,7 +69773,7 @@
         <v>1000000000000000</v>
       </c>
     </row>
-    <row r="810" spans="1:23" s="16" customFormat="1" ht="28.5" customHeight="1">
+    <row r="810" spans="1:23" s="7" customFormat="1" ht="28.5" customHeight="1">
       <c r="A810" s="11" t="str">
         <f t="shared" si="158"/>
         <v/>
@@ -69786,16 +69782,16 @@
         <v>8</v>
       </c>
       <c r="C810" s="11" t="s">
-        <v>638</v>
+        <v>945</v>
       </c>
       <c r="D810" s="11" t="s">
         <v>69</v>
       </c>
       <c r="E810" s="11" t="s">
-        <v>60</v>
+        <v>26</v>
       </c>
       <c r="F810" s="11" t="s">
-        <v>639</v>
+        <v>946</v>
       </c>
       <c r="G810" s="12">
         <v>1875</v>
@@ -69803,7 +69799,7 @@
       <c r="H810" s="12"/>
       <c r="I810" s="12"/>
       <c r="J810" s="12">
-        <v>1859</v>
+        <v>1855</v>
       </c>
       <c r="K810" s="12">
         <f>IF(AND(IFERROR(SEARCH("현대오일뱅크",$C810),0)&gt;0,IFERROR(SEARCH("직영",$C810),0)&gt;0),$B$13,0)</f>
@@ -69819,7 +69815,7 @@
       </c>
       <c r="N810" s="12">
         <f t="shared" si="161"/>
-        <v>1859</v>
+        <v>1855</v>
       </c>
       <c r="O810" s="12" t="str">
         <f t="shared" si="162"/>
@@ -69861,19 +69857,19 @@
         <v/>
       </c>
       <c r="B811" s="11" t="s">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="C811" s="11" t="s">
-        <v>1184</v>
+        <v>638</v>
       </c>
       <c r="D811" s="11" t="s">
         <v>69</v>
       </c>
       <c r="E811" s="11" t="s">
-        <v>26</v>
+        <v>60</v>
       </c>
       <c r="F811" s="11" t="s">
-        <v>1185</v>
+        <v>639</v>
       </c>
       <c r="G811" s="12">
         <v>1875</v>
@@ -69881,7 +69877,7 @@
       <c r="H811" s="12"/>
       <c r="I811" s="12"/>
       <c r="J811" s="12">
-        <v>1865</v>
+        <v>1859</v>
       </c>
       <c r="K811" s="12">
         <f>IF(AND(IFERROR(SEARCH("현대오일뱅크",$C811),0)&gt;0,IFERROR(SEARCH("직영",$C811),0)&gt;0),$B$13,0)</f>
@@ -69897,7 +69893,7 @@
       </c>
       <c r="N811" s="12">
         <f t="shared" si="161"/>
-        <v>1865</v>
+        <v>1859</v>
       </c>
       <c r="O811" s="12" t="str">
         <f t="shared" si="162"/>
@@ -69933,25 +69929,25 @@
         <v>1000000000000000</v>
       </c>
     </row>
-    <row r="812" spans="1:23" s="2" customFormat="1" ht="28.5" customHeight="1">
+    <row r="812" spans="1:23" s="16" customFormat="1" ht="28.5" customHeight="1">
       <c r="A812" s="11" t="str">
         <f t="shared" si="158"/>
         <v/>
       </c>
       <c r="B812" s="11" t="s">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="C812" s="11" t="s">
-        <v>1510</v>
-      </c>
-      <c r="D812" s="15" t="s">
-        <v>45</v>
+        <v>1184</v>
+      </c>
+      <c r="D812" s="11" t="s">
+        <v>69</v>
       </c>
       <c r="E812" s="11" t="s">
-        <v>60</v>
+        <v>26</v>
       </c>
       <c r="F812" s="11" t="s">
-        <v>1511</v>
+        <v>1185</v>
       </c>
       <c r="G812" s="12">
         <v>1875</v>
@@ -70011,25 +70007,25 @@
         <v>1000000000000000</v>
       </c>
     </row>
-    <row r="813" spans="1:23" s="7" customFormat="1" ht="28.5" customHeight="1">
+    <row r="813" spans="1:23" s="2" customFormat="1" ht="28.5" customHeight="1">
       <c r="A813" s="11" t="str">
         <f t="shared" si="158"/>
         <v/>
       </c>
       <c r="B813" s="11" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="C813" s="11" t="s">
-        <v>1514</v>
-      </c>
-      <c r="D813" s="11" t="s">
-        <v>57</v>
+        <v>1510</v>
+      </c>
+      <c r="D813" s="15" t="s">
+        <v>45</v>
       </c>
       <c r="E813" s="11" t="s">
-        <v>26</v>
+        <v>60</v>
       </c>
       <c r="F813" s="11" t="s">
-        <v>1515</v>
+        <v>1511</v>
       </c>
       <c r="G813" s="12">
         <v>1875</v>
@@ -70037,7 +70033,7 @@
       <c r="H813" s="12"/>
       <c r="I813" s="12"/>
       <c r="J813" s="12">
-        <v>1868</v>
+        <v>1865</v>
       </c>
       <c r="K813" s="12">
         <f>IF(AND(IFERROR(SEARCH("현대오일뱅크",$C813),0)&gt;0,IFERROR(SEARCH("직영",$C813),0)&gt;0),$B$13,0)</f>
@@ -70053,7 +70049,7 @@
       </c>
       <c r="N813" s="12">
         <f t="shared" si="161"/>
-        <v>1868</v>
+        <v>1865</v>
       </c>
       <c r="O813" s="12" t="str">
         <f t="shared" si="162"/>
@@ -70089,25 +70085,25 @@
         <v>1000000000000000</v>
       </c>
     </row>
-    <row r="814" spans="1:23" s="2" customFormat="1" ht="28.5" customHeight="1">
+    <row r="814" spans="1:23" s="7" customFormat="1" ht="28.5" customHeight="1">
       <c r="A814" s="11" t="str">
         <f t="shared" si="158"/>
         <v/>
       </c>
       <c r="B814" s="11" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="C814" s="11" t="s">
-        <v>190</v>
-      </c>
-      <c r="D814" s="15" t="s">
-        <v>45</v>
+        <v>1514</v>
+      </c>
+      <c r="D814" s="11" t="s">
+        <v>57</v>
       </c>
       <c r="E814" s="11" t="s">
-        <v>60</v>
+        <v>26</v>
       </c>
       <c r="F814" s="11" t="s">
-        <v>191</v>
+        <v>1515</v>
       </c>
       <c r="G814" s="12">
         <v>1875</v>
@@ -70115,9 +70111,10 @@
       <c r="H814" s="12"/>
       <c r="I814" s="12"/>
       <c r="J814" s="12">
-        <v>1870</v>
+        <v>1868</v>
       </c>
       <c r="K814" s="12">
+        <f>IF(AND(IFERROR(SEARCH("현대오일뱅크",$C814),0)&gt;0,IFERROR(SEARCH("직영",$C814),0)&gt;0),$B$13,0)</f>
         <v>0</v>
       </c>
       <c r="L814" s="12">
@@ -70130,7 +70127,7 @@
       </c>
       <c r="N814" s="12">
         <f t="shared" si="161"/>
-        <v>1870</v>
+        <v>1868</v>
       </c>
       <c r="O814" s="12" t="str">
         <f t="shared" si="162"/>
@@ -70175,7 +70172,7 @@
         <v>12</v>
       </c>
       <c r="C815" s="11" t="s">
-        <v>204</v>
+        <v>190</v>
       </c>
       <c r="D815" s="15" t="s">
         <v>45</v>
@@ -70184,7 +70181,7 @@
         <v>60</v>
       </c>
       <c r="F815" s="11" t="s">
-        <v>205</v>
+        <v>191</v>
       </c>
       <c r="G815" s="12">
         <v>1875</v>
@@ -70243,7 +70240,7 @@
         <v>1000000000000000</v>
       </c>
     </row>
-    <row r="816" spans="1:23" s="7" customFormat="1" ht="28.5" customHeight="1">
+    <row r="816" spans="1:23" s="2" customFormat="1" ht="28.5" customHeight="1">
       <c r="A816" s="11" t="str">
         <f t="shared" si="158"/>
         <v/>
@@ -70252,7 +70249,7 @@
         <v>12</v>
       </c>
       <c r="C816" s="11" t="s">
-        <v>218</v>
+        <v>204</v>
       </c>
       <c r="D816" s="15" t="s">
         <v>45</v>
@@ -70261,7 +70258,7 @@
         <v>60</v>
       </c>
       <c r="F816" s="11" t="s">
-        <v>219</v>
+        <v>205</v>
       </c>
       <c r="G816" s="12">
         <v>1875</v>
@@ -70320,25 +70317,25 @@
         <v>1000000000000000</v>
       </c>
     </row>
-    <row r="817" spans="1:23" s="2" customFormat="1" ht="28.5" customHeight="1">
+    <row r="817" spans="1:23" s="7" customFormat="1" ht="28.5" customHeight="1">
       <c r="A817" s="11" t="str">
         <f t="shared" si="158"/>
         <v/>
       </c>
       <c r="B817" s="11" t="s">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="C817" s="11" t="s">
-        <v>136</v>
+        <v>218</v>
       </c>
       <c r="D817" s="15" t="s">
         <v>45</v>
       </c>
       <c r="E817" s="11" t="s">
-        <v>26</v>
+        <v>60</v>
       </c>
       <c r="F817" s="11" t="s">
-        <v>137</v>
+        <v>219</v>
       </c>
       <c r="G817" s="12">
         <v>1875</v>
@@ -70346,10 +70343,9 @@
       <c r="H817" s="12"/>
       <c r="I817" s="12"/>
       <c r="J817" s="12">
-        <v>1875</v>
+        <v>1870</v>
       </c>
       <c r="K817" s="12">
-        <f t="shared" ref="K817:K848" si="171">IF(AND(IFERROR(SEARCH("현대오일뱅크",$C817),0)&gt;0,IFERROR(SEARCH("직영",$C817),0)&gt;0),$B$13,0)</f>
         <v>0</v>
       </c>
       <c r="L817" s="12">
@@ -70362,7 +70358,7 @@
       </c>
       <c r="N817" s="12">
         <f t="shared" si="161"/>
-        <v>1875</v>
+        <v>1870</v>
       </c>
       <c r="O817" s="12" t="str">
         <f t="shared" si="162"/>
@@ -70398,41 +70394,41 @@
         <v>1000000000000000</v>
       </c>
     </row>
-    <row r="818" spans="1:23" s="7" customFormat="1" ht="28.5" customHeight="1">
+    <row r="818" spans="1:23" s="2" customFormat="1" ht="28.5" customHeight="1">
       <c r="A818" s="11" t="str">
         <f t="shared" si="158"/>
         <v/>
       </c>
       <c r="B818" s="11" t="s">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="C818" s="11" t="s">
-        <v>1323</v>
-      </c>
-      <c r="D818" s="11" t="s">
-        <v>57</v>
+        <v>136</v>
+      </c>
+      <c r="D818" s="15" t="s">
+        <v>45</v>
       </c>
       <c r="E818" s="11" t="s">
         <v>26</v>
       </c>
       <c r="F818" s="11" t="s">
-        <v>1324</v>
+        <v>137</v>
       </c>
       <c r="G818" s="12">
-        <v>1878</v>
+        <v>1875</v>
       </c>
       <c r="H818" s="12"/>
       <c r="I818" s="12"/>
       <c r="J818" s="12">
-        <v>1857</v>
+        <v>1875</v>
       </c>
       <c r="K818" s="12">
-        <f t="shared" si="171"/>
+        <f t="shared" ref="K818:K849" si="171">IF(AND(IFERROR(SEARCH("현대오일뱅크",$C818),0)&gt;0,IFERROR(SEARCH("직영",$C818),0)&gt;0),$B$13,0)</f>
         <v>0</v>
       </c>
       <c r="L818" s="12">
         <f t="shared" si="159"/>
-        <v>1878</v>
+        <v>1875</v>
       </c>
       <c r="M818" s="12" t="str">
         <f t="shared" si="160"/>
@@ -70440,7 +70436,7 @@
       </c>
       <c r="N818" s="12">
         <f t="shared" si="161"/>
-        <v>1857</v>
+        <v>1875</v>
       </c>
       <c r="O818" s="12" t="str">
         <f t="shared" si="162"/>
@@ -70485,7 +70481,7 @@
         <v>14</v>
       </c>
       <c r="C819" s="11" t="s">
-        <v>681</v>
+        <v>1323</v>
       </c>
       <c r="D819" s="11" t="s">
         <v>57</v>
@@ -70494,7 +70490,7 @@
         <v>26</v>
       </c>
       <c r="F819" s="11" t="s">
-        <v>682</v>
+        <v>1324</v>
       </c>
       <c r="G819" s="12">
         <v>1878</v>
@@ -70502,7 +70498,7 @@
       <c r="H819" s="12"/>
       <c r="I819" s="12"/>
       <c r="J819" s="12">
-        <v>1878</v>
+        <v>1857</v>
       </c>
       <c r="K819" s="12">
         <f t="shared" si="171"/>
@@ -70518,7 +70514,7 @@
       </c>
       <c r="N819" s="12">
         <f t="shared" si="161"/>
-        <v>1878</v>
+        <v>1857</v>
       </c>
       <c r="O819" s="12" t="str">
         <f t="shared" si="162"/>
@@ -70554,16 +70550,16 @@
         <v>1000000000000000</v>
       </c>
     </row>
-    <row r="820" spans="1:23" s="2" customFormat="1" ht="28.5" customHeight="1">
+    <row r="820" spans="1:23" s="7" customFormat="1" ht="28.5" customHeight="1">
       <c r="A820" s="11" t="str">
         <f t="shared" si="158"/>
         <v/>
       </c>
       <c r="B820" s="11" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="C820" s="11" t="s">
-        <v>1327</v>
+        <v>681</v>
       </c>
       <c r="D820" s="11" t="s">
         <v>57</v>
@@ -70572,15 +70568,15 @@
         <v>26</v>
       </c>
       <c r="F820" s="11" t="s">
-        <v>1328</v>
+        <v>682</v>
       </c>
       <c r="G820" s="12">
-        <v>1879</v>
+        <v>1878</v>
       </c>
       <c r="H820" s="12"/>
       <c r="I820" s="12"/>
       <c r="J820" s="12">
-        <v>1839</v>
+        <v>1878</v>
       </c>
       <c r="K820" s="12">
         <f t="shared" si="171"/>
@@ -70588,7 +70584,7 @@
       </c>
       <c r="L820" s="12">
         <f t="shared" si="159"/>
-        <v>1879</v>
+        <v>1878</v>
       </c>
       <c r="M820" s="12" t="str">
         <f t="shared" si="160"/>
@@ -70596,7 +70592,7 @@
       </c>
       <c r="N820" s="12">
         <f t="shared" si="161"/>
-        <v>1839</v>
+        <v>1878</v>
       </c>
       <c r="O820" s="12" t="str">
         <f t="shared" si="162"/>
@@ -70632,25 +70628,25 @@
         <v>1000000000000000</v>
       </c>
     </row>
-    <row r="821" spans="1:23" s="16" customFormat="1" ht="28.5" customHeight="1">
+    <row r="821" spans="1:23" s="2" customFormat="1" ht="28.5" customHeight="1">
       <c r="A821" s="11" t="str">
         <f t="shared" si="158"/>
         <v/>
       </c>
       <c r="B821" s="11" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="C821" s="11" t="s">
-        <v>1303</v>
-      </c>
-      <c r="D821" s="15" t="s">
-        <v>59</v>
+        <v>1327</v>
+      </c>
+      <c r="D821" s="11" t="s">
+        <v>57</v>
       </c>
       <c r="E821" s="11" t="s">
         <v>26</v>
       </c>
       <c r="F821" s="11" t="s">
-        <v>1304</v>
+        <v>1328</v>
       </c>
       <c r="G821" s="12">
         <v>1879</v>
@@ -70658,7 +70654,7 @@
       <c r="H821" s="12"/>
       <c r="I821" s="12"/>
       <c r="J821" s="12">
-        <v>1865</v>
+        <v>1839</v>
       </c>
       <c r="K821" s="12">
         <f t="shared" si="171"/>
@@ -70674,7 +70670,7 @@
       </c>
       <c r="N821" s="12">
         <f t="shared" si="161"/>
-        <v>1865</v>
+        <v>1839</v>
       </c>
       <c r="O821" s="12" t="str">
         <f t="shared" si="162"/>
@@ -70710,7 +70706,7 @@
         <v>1000000000000000</v>
       </c>
     </row>
-    <row r="822" spans="1:23" s="2" customFormat="1" ht="28.5" customHeight="1">
+    <row r="822" spans="1:23" s="16" customFormat="1" ht="28.5" customHeight="1">
       <c r="A822" s="11" t="str">
         <f t="shared" si="158"/>
         <v/>
@@ -70719,16 +70715,16 @@
         <v>14</v>
       </c>
       <c r="C822" s="11" t="s">
-        <v>1317</v>
+        <v>1303</v>
       </c>
       <c r="D822" s="15" t="s">
-        <v>45</v>
+        <v>59</v>
       </c>
       <c r="E822" s="11" t="s">
-        <v>60</v>
+        <v>26</v>
       </c>
       <c r="F822" s="11" t="s">
-        <v>1318</v>
+        <v>1304</v>
       </c>
       <c r="G822" s="12">
         <v>1879</v>
@@ -70736,7 +70732,7 @@
       <c r="H822" s="12"/>
       <c r="I822" s="12"/>
       <c r="J822" s="12">
-        <v>1869</v>
+        <v>1865</v>
       </c>
       <c r="K822" s="12">
         <f t="shared" si="171"/>
@@ -70752,7 +70748,7 @@
       </c>
       <c r="N822" s="12">
         <f t="shared" si="161"/>
-        <v>1869</v>
+        <v>1865</v>
       </c>
       <c r="O822" s="12" t="str">
         <f t="shared" si="162"/>
@@ -70797,16 +70793,16 @@
         <v>14</v>
       </c>
       <c r="C823" s="11" t="s">
-        <v>1641</v>
+        <v>1317</v>
       </c>
       <c r="D823" s="15" t="s">
-        <v>78</v>
+        <v>45</v>
       </c>
       <c r="E823" s="11" t="s">
-        <v>26</v>
+        <v>60</v>
       </c>
       <c r="F823" s="11" t="s">
-        <v>1642</v>
+        <v>1318</v>
       </c>
       <c r="G823" s="12">
         <v>1879</v>
@@ -70875,16 +70871,16 @@
         <v>14</v>
       </c>
       <c r="C824" s="11" t="s">
-        <v>1067</v>
+        <v>1641</v>
       </c>
       <c r="D824" s="15" t="s">
-        <v>45</v>
+        <v>78</v>
       </c>
       <c r="E824" s="11" t="s">
-        <v>60</v>
+        <v>26</v>
       </c>
       <c r="F824" s="11" t="s">
-        <v>1068</v>
+        <v>1642</v>
       </c>
       <c r="G824" s="12">
         <v>1879</v>
@@ -70892,7 +70888,7 @@
       <c r="H824" s="12"/>
       <c r="I824" s="12"/>
       <c r="J824" s="12">
-        <v>1879</v>
+        <v>1869</v>
       </c>
       <c r="K824" s="12">
         <f t="shared" si="171"/>
@@ -70908,7 +70904,7 @@
       </c>
       <c r="N824" s="12">
         <f t="shared" si="161"/>
-        <v>1879</v>
+        <v>1869</v>
       </c>
       <c r="O824" s="12" t="str">
         <f t="shared" si="162"/>
@@ -70950,27 +70946,27 @@
         <v/>
       </c>
       <c r="B825" s="11" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="C825" s="11" t="s">
-        <v>244</v>
+        <v>1067</v>
       </c>
       <c r="D825" s="15" t="s">
-        <v>78</v>
+        <v>45</v>
       </c>
       <c r="E825" s="11" t="s">
         <v>60</v>
       </c>
       <c r="F825" s="11" t="s">
-        <v>245</v>
+        <v>1068</v>
       </c>
       <c r="G825" s="12">
-        <v>1884</v>
+        <v>1879</v>
       </c>
       <c r="H825" s="12"/>
       <c r="I825" s="12"/>
       <c r="J825" s="12">
-        <v>1889</v>
+        <v>1879</v>
       </c>
       <c r="K825" s="12">
         <f t="shared" si="171"/>
@@ -70978,7 +70974,7 @@
       </c>
       <c r="L825" s="12">
         <f t="shared" si="159"/>
-        <v>1884</v>
+        <v>1879</v>
       </c>
       <c r="M825" s="12" t="str">
         <f t="shared" si="160"/>
@@ -70986,7 +70982,7 @@
       </c>
       <c r="N825" s="12">
         <f t="shared" si="161"/>
-        <v>1889</v>
+        <v>1879</v>
       </c>
       <c r="O825" s="12" t="str">
         <f t="shared" si="162"/>
@@ -71022,7 +71018,7 @@
         <v>1000000000000000</v>
       </c>
     </row>
-    <row r="826" spans="1:23" s="7" customFormat="1" ht="28.5" customHeight="1">
+    <row r="826" spans="1:23" s="2" customFormat="1" ht="28.5" customHeight="1">
       <c r="A826" s="11" t="str">
         <f t="shared" si="158"/>
         <v/>
@@ -71031,24 +71027,24 @@
         <v>12</v>
       </c>
       <c r="C826" s="11" t="s">
-        <v>795</v>
+        <v>244</v>
       </c>
       <c r="D826" s="15" t="s">
-        <v>57</v>
+        <v>78</v>
       </c>
       <c r="E826" s="11" t="s">
-        <v>26</v>
+        <v>60</v>
       </c>
       <c r="F826" s="11" t="s">
-        <v>796</v>
+        <v>245</v>
       </c>
       <c r="G826" s="12">
-        <v>1885</v>
+        <v>1884</v>
       </c>
       <c r="H826" s="12"/>
       <c r="I826" s="12"/>
       <c r="J826" s="12">
-        <v>1825</v>
+        <v>1889</v>
       </c>
       <c r="K826" s="12">
         <f t="shared" si="171"/>
@@ -71056,7 +71052,7 @@
       </c>
       <c r="L826" s="12">
         <f t="shared" si="159"/>
-        <v>1885</v>
+        <v>1884</v>
       </c>
       <c r="M826" s="12" t="str">
         <f t="shared" si="160"/>
@@ -71064,7 +71060,7 @@
       </c>
       <c r="N826" s="12">
         <f t="shared" si="161"/>
-        <v>1825</v>
+        <v>1889</v>
       </c>
       <c r="O826" s="12" t="str">
         <f t="shared" si="162"/>
@@ -71100,25 +71096,25 @@
         <v>1000000000000000</v>
       </c>
     </row>
-    <row r="827" spans="1:23" s="16" customFormat="1" ht="28.5" customHeight="1">
+    <row r="827" spans="1:23" s="7" customFormat="1" ht="28.5" customHeight="1">
       <c r="A827" s="11" t="str">
         <f t="shared" si="158"/>
         <v/>
       </c>
       <c r="B827" s="11" t="s">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="C827" s="11" t="s">
-        <v>1277</v>
+        <v>795</v>
       </c>
       <c r="D827" s="15" t="s">
-        <v>45</v>
+        <v>57</v>
       </c>
       <c r="E827" s="11" t="s">
-        <v>60</v>
+        <v>26</v>
       </c>
       <c r="F827" s="11" t="s">
-        <v>1278</v>
+        <v>796</v>
       </c>
       <c r="G827" s="12">
         <v>1885</v>
@@ -71126,7 +71122,7 @@
       <c r="H827" s="12"/>
       <c r="I827" s="12"/>
       <c r="J827" s="12">
-        <v>1850</v>
+        <v>1825</v>
       </c>
       <c r="K827" s="12">
         <f t="shared" si="171"/>
@@ -71142,7 +71138,7 @@
       </c>
       <c r="N827" s="12">
         <f t="shared" si="161"/>
-        <v>1850</v>
+        <v>1825</v>
       </c>
       <c r="O827" s="12" t="str">
         <f t="shared" si="162"/>
@@ -71178,25 +71174,25 @@
         <v>1000000000000000</v>
       </c>
     </row>
-    <row r="828" spans="1:23" s="2" customFormat="1" ht="28.5" customHeight="1">
+    <row r="828" spans="1:23" s="16" customFormat="1" ht="28.5" customHeight="1">
       <c r="A828" s="11" t="str">
         <f t="shared" si="158"/>
         <v/>
       </c>
       <c r="B828" s="11" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="C828" s="11" t="s">
-        <v>1720</v>
-      </c>
-      <c r="D828" s="11" t="s">
-        <v>57</v>
+        <v>1277</v>
+      </c>
+      <c r="D828" s="15" t="s">
+        <v>45</v>
       </c>
       <c r="E828" s="11" t="s">
-        <v>26</v>
+        <v>60</v>
       </c>
       <c r="F828" s="11" t="s">
-        <v>1721</v>
+        <v>1278</v>
       </c>
       <c r="G828" s="12">
         <v>1885</v>
@@ -71204,7 +71200,7 @@
       <c r="H828" s="12"/>
       <c r="I828" s="12"/>
       <c r="J828" s="12">
-        <v>1875</v>
+        <v>1850</v>
       </c>
       <c r="K828" s="12">
         <f t="shared" si="171"/>
@@ -71220,7 +71216,7 @@
       </c>
       <c r="N828" s="12">
         <f t="shared" si="161"/>
-        <v>1875</v>
+        <v>1850</v>
       </c>
       <c r="O828" s="12" t="str">
         <f t="shared" si="162"/>
@@ -71262,19 +71258,19 @@
         <v/>
       </c>
       <c r="B829" s="11" t="s">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="C829" s="11" t="s">
-        <v>1134</v>
-      </c>
-      <c r="D829" s="15" t="s">
-        <v>59</v>
+        <v>1720</v>
+      </c>
+      <c r="D829" s="11" t="s">
+        <v>57</v>
       </c>
       <c r="E829" s="11" t="s">
-        <v>60</v>
+        <v>26</v>
       </c>
       <c r="F829" s="11" t="s">
-        <v>1135</v>
+        <v>1721</v>
       </c>
       <c r="G829" s="12">
         <v>1885</v>
@@ -71340,27 +71336,27 @@
         <v/>
       </c>
       <c r="B830" s="11" t="s">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="C830" s="11" t="s">
-        <v>1253</v>
-      </c>
-      <c r="D830" s="11" t="s">
-        <v>57</v>
+        <v>1134</v>
+      </c>
+      <c r="D830" s="15" t="s">
+        <v>59</v>
       </c>
       <c r="E830" s="11" t="s">
         <v>60</v>
       </c>
       <c r="F830" s="11" t="s">
-        <v>1254</v>
+        <v>1135</v>
       </c>
       <c r="G830" s="12">
-        <v>1887</v>
+        <v>1885</v>
       </c>
       <c r="H830" s="12"/>
       <c r="I830" s="12"/>
       <c r="J830" s="12">
-        <v>1857</v>
+        <v>1875</v>
       </c>
       <c r="K830" s="12">
         <f t="shared" si="171"/>
@@ -71368,7 +71364,7 @@
       </c>
       <c r="L830" s="12">
         <f t="shared" si="159"/>
-        <v>1887</v>
+        <v>1885</v>
       </c>
       <c r="M830" s="12" t="str">
         <f t="shared" si="160"/>
@@ -71376,7 +71372,7 @@
       </c>
       <c r="N830" s="12">
         <f t="shared" si="161"/>
-        <v>1857</v>
+        <v>1875</v>
       </c>
       <c r="O830" s="12" t="str">
         <f t="shared" si="162"/>
@@ -71412,33 +71408,33 @@
         <v>1000000000000000</v>
       </c>
     </row>
-    <row r="831" spans="1:23" s="7" customFormat="1" ht="28.5" customHeight="1">
+    <row r="831" spans="1:23" s="2" customFormat="1" ht="28.5" customHeight="1">
       <c r="A831" s="11" t="str">
         <f t="shared" si="158"/>
         <v/>
       </c>
       <c r="B831" s="11" t="s">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="C831" s="11" t="s">
-        <v>537</v>
-      </c>
-      <c r="D831" s="15" t="s">
-        <v>59</v>
+        <v>1253</v>
+      </c>
+      <c r="D831" s="11" t="s">
+        <v>57</v>
       </c>
       <c r="E831" s="11" t="s">
         <v>60</v>
       </c>
       <c r="F831" s="11" t="s">
-        <v>538</v>
+        <v>1254</v>
       </c>
       <c r="G831" s="12">
-        <v>1888</v>
+        <v>1887</v>
       </c>
       <c r="H831" s="12"/>
       <c r="I831" s="12"/>
       <c r="J831" s="12">
-        <v>1878</v>
+        <v>1857</v>
       </c>
       <c r="K831" s="12">
         <f t="shared" si="171"/>
@@ -71446,7 +71442,7 @@
       </c>
       <c r="L831" s="12">
         <f t="shared" si="159"/>
-        <v>1888</v>
+        <v>1887</v>
       </c>
       <c r="M831" s="12" t="str">
         <f t="shared" si="160"/>
@@ -71454,7 +71450,7 @@
       </c>
       <c r="N831" s="12">
         <f t="shared" si="161"/>
-        <v>1878</v>
+        <v>1857</v>
       </c>
       <c r="O831" s="12" t="str">
         <f t="shared" si="162"/>
@@ -71499,24 +71495,24 @@
         <v>10</v>
       </c>
       <c r="C832" s="11" t="s">
-        <v>1168</v>
-      </c>
-      <c r="D832" s="11" t="s">
-        <v>57</v>
+        <v>537</v>
+      </c>
+      <c r="D832" s="15" t="s">
+        <v>59</v>
       </c>
       <c r="E832" s="11" t="s">
-        <v>26</v>
+        <v>60</v>
       </c>
       <c r="F832" s="11" t="s">
-        <v>1169</v>
+        <v>538</v>
       </c>
       <c r="G832" s="12">
-        <v>1889</v>
+        <v>1888</v>
       </c>
       <c r="H832" s="12"/>
       <c r="I832" s="12"/>
       <c r="J832" s="12">
-        <v>1859</v>
+        <v>1878</v>
       </c>
       <c r="K832" s="12">
         <f t="shared" si="171"/>
@@ -71524,7 +71520,7 @@
       </c>
       <c r="L832" s="12">
         <f t="shared" si="159"/>
-        <v>1889</v>
+        <v>1888</v>
       </c>
       <c r="M832" s="12" t="str">
         <f t="shared" si="160"/>
@@ -71532,7 +71528,7 @@
       </c>
       <c r="N832" s="12">
         <f t="shared" si="161"/>
-        <v>1859</v>
+        <v>1878</v>
       </c>
       <c r="O832" s="12" t="str">
         <f t="shared" si="162"/>
@@ -71574,19 +71570,19 @@
         <v/>
       </c>
       <c r="B833" s="11" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="C833" s="11" t="s">
-        <v>893</v>
+        <v>1168</v>
       </c>
       <c r="D833" s="11" t="s">
-        <v>69</v>
+        <v>57</v>
       </c>
       <c r="E833" s="11" t="s">
-        <v>60</v>
+        <v>26</v>
       </c>
       <c r="F833" s="11" t="s">
-        <v>894</v>
+        <v>1169</v>
       </c>
       <c r="G833" s="12">
         <v>1889</v>
@@ -71594,7 +71590,7 @@
       <c r="H833" s="12"/>
       <c r="I833" s="12"/>
       <c r="J833" s="12">
-        <v>1869</v>
+        <v>1859</v>
       </c>
       <c r="K833" s="12">
         <f t="shared" si="171"/>
@@ -71610,7 +71606,7 @@
       </c>
       <c r="N833" s="12">
         <f t="shared" si="161"/>
-        <v>1869</v>
+        <v>1859</v>
       </c>
       <c r="O833" s="12" t="str">
         <f t="shared" si="162"/>
@@ -71646,7 +71642,7 @@
         <v>1000000000000000</v>
       </c>
     </row>
-    <row r="834" spans="1:23" s="2" customFormat="1" ht="28.5" customHeight="1">
+    <row r="834" spans="1:23" s="7" customFormat="1" ht="28.5" customHeight="1">
       <c r="A834" s="11" t="str">
         <f t="shared" si="158"/>
         <v/>
@@ -71655,16 +71651,16 @@
         <v>14</v>
       </c>
       <c r="C834" s="11" t="s">
-        <v>1629</v>
-      </c>
-      <c r="D834" s="15" t="s">
-        <v>45</v>
+        <v>893</v>
+      </c>
+      <c r="D834" s="11" t="s">
+        <v>69</v>
       </c>
       <c r="E834" s="11" t="s">
         <v>60</v>
       </c>
       <c r="F834" s="11" t="s">
-        <v>1630</v>
+        <v>894</v>
       </c>
       <c r="G834" s="12">
         <v>1889</v>
@@ -71730,19 +71726,19 @@
         <v/>
       </c>
       <c r="B835" s="11" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="C835" s="11" t="s">
-        <v>632</v>
+        <v>1629</v>
       </c>
       <c r="D835" s="15" t="s">
-        <v>59</v>
+        <v>45</v>
       </c>
       <c r="E835" s="11" t="s">
         <v>60</v>
       </c>
       <c r="F835" s="11" t="s">
-        <v>633</v>
+        <v>1630</v>
       </c>
       <c r="G835" s="12">
         <v>1889</v>
@@ -71750,7 +71746,7 @@
       <c r="H835" s="12"/>
       <c r="I835" s="12"/>
       <c r="J835" s="12">
-        <v>1879</v>
+        <v>1869</v>
       </c>
       <c r="K835" s="12">
         <f t="shared" si="171"/>
@@ -71766,7 +71762,7 @@
       </c>
       <c r="N835" s="12">
         <f t="shared" si="161"/>
-        <v>1879</v>
+        <v>1869</v>
       </c>
       <c r="O835" s="12" t="str">
         <f t="shared" si="162"/>
@@ -71802,16 +71798,16 @@
         <v>1000000000000000</v>
       </c>
     </row>
-    <row r="836" spans="1:23" s="16" customFormat="1" ht="28.5" customHeight="1">
+    <row r="836" spans="1:23" s="2" customFormat="1" ht="28.5" customHeight="1">
       <c r="A836" s="11" t="str">
         <f t="shared" si="158"/>
         <v/>
       </c>
       <c r="B836" s="11" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="C836" s="11" t="s">
-        <v>1160</v>
+        <v>632</v>
       </c>
       <c r="D836" s="15" t="s">
         <v>59</v>
@@ -71820,7 +71816,7 @@
         <v>60</v>
       </c>
       <c r="F836" s="11" t="s">
-        <v>1161</v>
+        <v>633</v>
       </c>
       <c r="G836" s="12">
         <v>1889</v>
@@ -71880,7 +71876,7 @@
         <v>1000000000000000</v>
       </c>
     </row>
-    <row r="837" spans="1:23" s="2" customFormat="1" ht="28.5" customHeight="1">
+    <row r="837" spans="1:23" s="16" customFormat="1" ht="28.5" customHeight="1">
       <c r="A837" s="11" t="str">
         <f t="shared" si="158"/>
         <v/>
@@ -71889,16 +71885,16 @@
         <v>10</v>
       </c>
       <c r="C837" s="11" t="s">
-        <v>250</v>
-      </c>
-      <c r="D837" s="11" t="s">
-        <v>78</v>
+        <v>1160</v>
+      </c>
+      <c r="D837" s="15" t="s">
+        <v>59</v>
       </c>
       <c r="E837" s="11" t="s">
         <v>60</v>
       </c>
       <c r="F837" s="11" t="s">
-        <v>251</v>
+        <v>1161</v>
       </c>
       <c r="G837" s="12">
         <v>1889</v>
@@ -71906,7 +71902,7 @@
       <c r="H837" s="12"/>
       <c r="I837" s="12"/>
       <c r="J837" s="12">
-        <v>1883</v>
+        <v>1879</v>
       </c>
       <c r="K837" s="12">
         <f t="shared" si="171"/>
@@ -71922,7 +71918,7 @@
       </c>
       <c r="N837" s="12">
         <f t="shared" si="161"/>
-        <v>1883</v>
+        <v>1879</v>
       </c>
       <c r="O837" s="12" t="str">
         <f t="shared" si="162"/>
@@ -71964,19 +71960,19 @@
         <v/>
       </c>
       <c r="B838" s="11" t="s">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="C838" s="11" t="s">
-        <v>397</v>
+        <v>250</v>
       </c>
       <c r="D838" s="11" t="s">
-        <v>69</v>
+        <v>78</v>
       </c>
       <c r="E838" s="11" t="s">
         <v>60</v>
       </c>
       <c r="F838" s="11" t="s">
-        <v>398</v>
+        <v>251</v>
       </c>
       <c r="G838" s="12">
         <v>1889</v>
@@ -71984,7 +71980,7 @@
       <c r="H838" s="12"/>
       <c r="I838" s="12"/>
       <c r="J838" s="12">
-        <v>1889</v>
+        <v>1883</v>
       </c>
       <c r="K838" s="12">
         <f t="shared" si="171"/>
@@ -72000,7 +71996,7 @@
       </c>
       <c r="N838" s="12">
         <f t="shared" si="161"/>
-        <v>1889</v>
+        <v>1883</v>
       </c>
       <c r="O838" s="12" t="str">
         <f t="shared" si="162"/>
@@ -72042,19 +72038,19 @@
         <v/>
       </c>
       <c r="B839" s="11" t="s">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="C839" s="11" t="s">
-        <v>1216</v>
-      </c>
-      <c r="D839" s="15" t="s">
-        <v>45</v>
+        <v>397</v>
+      </c>
+      <c r="D839" s="11" t="s">
+        <v>69</v>
       </c>
       <c r="E839" s="11" t="s">
-        <v>26</v>
+        <v>60</v>
       </c>
       <c r="F839" s="11" t="s">
-        <v>1217</v>
+        <v>398</v>
       </c>
       <c r="G839" s="12">
         <v>1889</v>
@@ -72062,7 +72058,7 @@
       <c r="H839" s="12"/>
       <c r="I839" s="12"/>
       <c r="J839" s="12">
-        <v>1899</v>
+        <v>1889</v>
       </c>
       <c r="K839" s="12">
         <f t="shared" si="171"/>
@@ -72078,7 +72074,7 @@
       </c>
       <c r="N839" s="12">
         <f t="shared" si="161"/>
-        <v>1899</v>
+        <v>1889</v>
       </c>
       <c r="O839" s="12" t="str">
         <f t="shared" si="162"/>
@@ -72120,27 +72116,27 @@
         <v/>
       </c>
       <c r="B840" s="11" t="s">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="C840" s="11" t="s">
-        <v>503</v>
+        <v>1216</v>
       </c>
       <c r="D840" s="15" t="s">
-        <v>78</v>
+        <v>45</v>
       </c>
       <c r="E840" s="11" t="s">
-        <v>60</v>
+        <v>26</v>
       </c>
       <c r="F840" s="11" t="s">
-        <v>504</v>
+        <v>1217</v>
       </c>
       <c r="G840" s="12">
-        <v>1890</v>
+        <v>1889</v>
       </c>
       <c r="H840" s="12"/>
       <c r="I840" s="12"/>
       <c r="J840" s="12">
-        <v>1880</v>
+        <v>1899</v>
       </c>
       <c r="K840" s="12">
         <f t="shared" si="171"/>
@@ -72148,7 +72144,7 @@
       </c>
       <c r="L840" s="12">
         <f t="shared" si="159"/>
-        <v>1890</v>
+        <v>1889</v>
       </c>
       <c r="M840" s="12" t="str">
         <f t="shared" si="160"/>
@@ -72156,7 +72152,7 @@
       </c>
       <c r="N840" s="12">
         <f t="shared" si="161"/>
-        <v>1880</v>
+        <v>1899</v>
       </c>
       <c r="O840" s="12" t="str">
         <f t="shared" si="162"/>
@@ -72192,7 +72188,7 @@
         <v>1000000000000000</v>
       </c>
     </row>
-    <row r="841" spans="1:23" s="16" customFormat="1" ht="28.5" customHeight="1">
+    <row r="841" spans="1:23" s="2" customFormat="1" ht="28.5" customHeight="1">
       <c r="A841" s="11" t="str">
         <f t="shared" si="158"/>
         <v/>
@@ -72201,16 +72197,16 @@
         <v>16</v>
       </c>
       <c r="C841" s="11" t="s">
-        <v>1235</v>
-      </c>
-      <c r="D841" s="11" t="s">
-        <v>69</v>
+        <v>503</v>
+      </c>
+      <c r="D841" s="15" t="s">
+        <v>78</v>
       </c>
       <c r="E841" s="11" t="s">
         <v>60</v>
       </c>
       <c r="F841" s="11" t="s">
-        <v>1236</v>
+        <v>504</v>
       </c>
       <c r="G841" s="12">
         <v>1890</v>
@@ -72270,7 +72266,7 @@
         <v>1000000000000000</v>
       </c>
     </row>
-    <row r="842" spans="1:23" s="2" customFormat="1" ht="28.5" customHeight="1">
+    <row r="842" spans="1:23" s="16" customFormat="1" ht="28.5" customHeight="1">
       <c r="A842" s="11" t="str">
         <f t="shared" si="158"/>
         <v/>
@@ -72279,7 +72275,7 @@
         <v>16</v>
       </c>
       <c r="C842" s="11" t="s">
-        <v>1237</v>
+        <v>1235</v>
       </c>
       <c r="D842" s="11" t="s">
         <v>69</v>
@@ -72288,7 +72284,7 @@
         <v>60</v>
       </c>
       <c r="F842" s="11" t="s">
-        <v>1238</v>
+        <v>1236</v>
       </c>
       <c r="G842" s="12">
         <v>1890</v>
@@ -72357,16 +72353,16 @@
         <v>16</v>
       </c>
       <c r="C843" s="11" t="s">
-        <v>1350</v>
+        <v>1237</v>
       </c>
       <c r="D843" s="11" t="s">
         <v>69</v>
       </c>
       <c r="E843" s="11" t="s">
-        <v>26</v>
+        <v>60</v>
       </c>
       <c r="F843" s="11" t="s">
-        <v>1351</v>
+        <v>1238</v>
       </c>
       <c r="G843" s="12">
         <v>1890</v>
@@ -72432,27 +72428,27 @@
         <v/>
       </c>
       <c r="B844" s="11" t="s">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="C844" s="11" t="s">
-        <v>1570</v>
+        <v>1350</v>
       </c>
       <c r="D844" s="11" t="s">
-        <v>78</v>
+        <v>69</v>
       </c>
       <c r="E844" s="11" t="s">
-        <v>60</v>
+        <v>26</v>
       </c>
       <c r="F844" s="11" t="s">
-        <v>1571</v>
+        <v>1351</v>
       </c>
       <c r="G844" s="12">
-        <v>1895</v>
+        <v>1890</v>
       </c>
       <c r="H844" s="12"/>
       <c r="I844" s="12"/>
       <c r="J844" s="12">
-        <v>1839</v>
+        <v>1880</v>
       </c>
       <c r="K844" s="12">
         <f t="shared" si="171"/>
@@ -72460,7 +72456,7 @@
       </c>
       <c r="L844" s="12">
         <f t="shared" si="159"/>
-        <v>1895</v>
+        <v>1890</v>
       </c>
       <c r="M844" s="12" t="str">
         <f t="shared" si="160"/>
@@ -72468,7 +72464,7 @@
       </c>
       <c r="N844" s="12">
         <f t="shared" si="161"/>
-        <v>1839</v>
+        <v>1880</v>
       </c>
       <c r="O844" s="12" t="str">
         <f t="shared" si="162"/>
@@ -72504,25 +72500,25 @@
         <v>1000000000000000</v>
       </c>
     </row>
-    <row r="845" spans="1:23" s="7" customFormat="1" ht="28.5" customHeight="1">
+    <row r="845" spans="1:23" s="2" customFormat="1" ht="28.5" customHeight="1">
       <c r="A845" s="11" t="str">
         <f t="shared" si="158"/>
         <v/>
       </c>
       <c r="B845" s="11" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="C845" s="11" t="s">
-        <v>422</v>
-      </c>
-      <c r="D845" s="15" t="s">
-        <v>45</v>
+        <v>1570</v>
+      </c>
+      <c r="D845" s="11" t="s">
+        <v>78</v>
       </c>
       <c r="E845" s="11" t="s">
-        <v>26</v>
+        <v>60</v>
       </c>
       <c r="F845" s="11" t="s">
-        <v>423</v>
+        <v>1571</v>
       </c>
       <c r="G845" s="12">
         <v>1895</v>
@@ -72530,7 +72526,7 @@
       <c r="H845" s="12"/>
       <c r="I845" s="12"/>
       <c r="J845" s="12">
-        <v>1875</v>
+        <v>1839</v>
       </c>
       <c r="K845" s="12">
         <f t="shared" si="171"/>
@@ -72546,7 +72542,7 @@
       </c>
       <c r="N845" s="12">
         <f t="shared" si="161"/>
-        <v>1875</v>
+        <v>1839</v>
       </c>
       <c r="O845" s="12" t="str">
         <f t="shared" si="162"/>
@@ -72588,19 +72584,19 @@
         <v/>
       </c>
       <c r="B846" s="11" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="C846" s="11" t="s">
-        <v>1558</v>
+        <v>422</v>
       </c>
       <c r="D846" s="15" t="s">
-        <v>59</v>
+        <v>45</v>
       </c>
       <c r="E846" s="11" t="s">
-        <v>60</v>
+        <v>26</v>
       </c>
       <c r="F846" s="11" t="s">
-        <v>1561</v>
+        <v>423</v>
       </c>
       <c r="G846" s="12">
         <v>1895</v>
@@ -72660,7 +72656,7 @@
         <v>1000000000000000</v>
       </c>
     </row>
-    <row r="847" spans="1:23" s="16" customFormat="1" ht="28.5" customHeight="1">
+    <row r="847" spans="1:23" s="7" customFormat="1" ht="28.5" customHeight="1">
       <c r="A847" s="11" t="str">
         <f t="shared" ref="A847:A883" si="172">IF($T847="","",RANK(T847,$T$15:$T$883,1))</f>
         <v/>
@@ -72669,16 +72665,16 @@
         <v>10</v>
       </c>
       <c r="C847" s="11" t="s">
-        <v>1670</v>
-      </c>
-      <c r="D847" s="11" t="s">
-        <v>57</v>
+        <v>1558</v>
+      </c>
+      <c r="D847" s="15" t="s">
+        <v>59</v>
       </c>
       <c r="E847" s="11" t="s">
         <v>60</v>
       </c>
       <c r="F847" s="11" t="s">
-        <v>1671</v>
+        <v>1561</v>
       </c>
       <c r="G847" s="12">
         <v>1895</v>
@@ -72744,19 +72740,19 @@
         <v/>
       </c>
       <c r="B848" s="11" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="C848" s="11" t="s">
-        <v>1071</v>
-      </c>
-      <c r="D848" s="15" t="s">
+        <v>1670</v>
+      </c>
+      <c r="D848" s="11" t="s">
         <v>57</v>
       </c>
       <c r="E848" s="11" t="s">
         <v>60</v>
       </c>
       <c r="F848" s="11" t="s">
-        <v>1072</v>
+        <v>1671</v>
       </c>
       <c r="G848" s="12">
         <v>1895</v>
@@ -72764,7 +72760,7 @@
       <c r="H848" s="12"/>
       <c r="I848" s="12"/>
       <c r="J848" s="12">
-        <v>1885</v>
+        <v>1875</v>
       </c>
       <c r="K848" s="12">
         <f t="shared" si="171"/>
@@ -72780,7 +72776,7 @@
       </c>
       <c r="N848" s="12">
         <f t="shared" si="175"/>
-        <v>1885</v>
+        <v>1875</v>
       </c>
       <c r="O848" s="12" t="str">
         <f t="shared" si="176"/>
@@ -72816,25 +72812,25 @@
         <v>1000000000000000</v>
       </c>
     </row>
-    <row r="849" spans="1:23" s="7" customFormat="1" ht="28.5" customHeight="1">
+    <row r="849" spans="1:23" s="16" customFormat="1" ht="28.5" customHeight="1">
       <c r="A849" s="11" t="str">
         <f t="shared" si="172"/>
         <v/>
       </c>
       <c r="B849" s="11" t="s">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="C849" s="11" t="s">
-        <v>1225</v>
-      </c>
-      <c r="D849" s="11" t="s">
-        <v>69</v>
+        <v>1071</v>
+      </c>
+      <c r="D849" s="15" t="s">
+        <v>57</v>
       </c>
       <c r="E849" s="11" t="s">
         <v>60</v>
       </c>
       <c r="F849" s="11" t="s">
-        <v>1226</v>
+        <v>1072</v>
       </c>
       <c r="G849" s="12">
         <v>1895</v>
@@ -72842,10 +72838,10 @@
       <c r="H849" s="12"/>
       <c r="I849" s="12"/>
       <c r="J849" s="12">
-        <v>1890</v>
+        <v>1885</v>
       </c>
       <c r="K849" s="12">
-        <f t="shared" ref="K849:K880" si="184">IF(AND(IFERROR(SEARCH("현대오일뱅크",$C849),0)&gt;0,IFERROR(SEARCH("직영",$C849),0)&gt;0),$B$13,0)</f>
+        <f t="shared" si="171"/>
         <v>0</v>
       </c>
       <c r="L849" s="12">
@@ -72858,7 +72854,7 @@
       </c>
       <c r="N849" s="12">
         <f t="shared" si="175"/>
-        <v>1890</v>
+        <v>1885</v>
       </c>
       <c r="O849" s="12" t="str">
         <f t="shared" si="176"/>
@@ -72894,41 +72890,41 @@
         <v>1000000000000000</v>
       </c>
     </row>
-    <row r="850" spans="1:23" s="16" customFormat="1" ht="28.5" customHeight="1">
+    <row r="850" spans="1:23" s="7" customFormat="1" ht="28.5" customHeight="1">
       <c r="A850" s="11" t="str">
         <f t="shared" si="172"/>
         <v/>
       </c>
       <c r="B850" s="11" t="s">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="C850" s="11" t="s">
-        <v>1357</v>
-      </c>
-      <c r="D850" s="15" t="s">
-        <v>59</v>
+        <v>1225</v>
+      </c>
+      <c r="D850" s="11" t="s">
+        <v>69</v>
       </c>
       <c r="E850" s="11" t="s">
         <v>60</v>
       </c>
       <c r="F850" s="11" t="s">
-        <v>1358</v>
+        <v>1226</v>
       </c>
       <c r="G850" s="12">
-        <v>1897</v>
+        <v>1895</v>
       </c>
       <c r="H850" s="12"/>
       <c r="I850" s="12"/>
       <c r="J850" s="12">
-        <v>1877</v>
+        <v>1890</v>
       </c>
       <c r="K850" s="12">
-        <f t="shared" si="184"/>
+        <f t="shared" ref="K850:K881" si="184">IF(AND(IFERROR(SEARCH("현대오일뱅크",$C850),0)&gt;0,IFERROR(SEARCH("직영",$C850),0)&gt;0),$B$13,0)</f>
         <v>0</v>
       </c>
       <c r="L850" s="12">
         <f t="shared" si="173"/>
-        <v>1897</v>
+        <v>1895</v>
       </c>
       <c r="M850" s="12" t="str">
         <f t="shared" si="174"/>
@@ -72936,7 +72932,7 @@
       </c>
       <c r="N850" s="12">
         <f t="shared" si="175"/>
-        <v>1877</v>
+        <v>1890</v>
       </c>
       <c r="O850" s="12" t="str">
         <f t="shared" si="176"/>
@@ -72972,7 +72968,7 @@
         <v>1000000000000000</v>
       </c>
     </row>
-    <row r="851" spans="1:23" s="2" customFormat="1" ht="28.5" customHeight="1">
+    <row r="851" spans="1:23" s="16" customFormat="1" ht="28.5" customHeight="1">
       <c r="A851" s="11" t="str">
         <f t="shared" si="172"/>
         <v/>
@@ -72981,16 +72977,16 @@
         <v>12</v>
       </c>
       <c r="C851" s="11" t="s">
-        <v>1566</v>
+        <v>1357</v>
       </c>
       <c r="D851" s="15" t="s">
-        <v>45</v>
+        <v>59</v>
       </c>
       <c r="E851" s="11" t="s">
-        <v>26</v>
+        <v>60</v>
       </c>
       <c r="F851" s="11" t="s">
-        <v>1567</v>
+        <v>1358</v>
       </c>
       <c r="G851" s="12">
         <v>1897</v>
@@ -72998,7 +72994,7 @@
       <c r="H851" s="12"/>
       <c r="I851" s="12"/>
       <c r="J851" s="12">
-        <v>1887</v>
+        <v>1877</v>
       </c>
       <c r="K851" s="12">
         <f t="shared" si="184"/>
@@ -73014,7 +73010,7 @@
       </c>
       <c r="N851" s="12">
         <f t="shared" si="175"/>
-        <v>1887</v>
+        <v>1877</v>
       </c>
       <c r="O851" s="12" t="str">
         <f t="shared" si="176"/>
@@ -73056,27 +73052,27 @@
         <v/>
       </c>
       <c r="B852" s="11" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="C852" s="11" t="s">
-        <v>840</v>
+        <v>1566</v>
       </c>
       <c r="D852" s="15" t="s">
-        <v>78</v>
+        <v>45</v>
       </c>
       <c r="E852" s="11" t="s">
         <v>26</v>
       </c>
       <c r="F852" s="11" t="s">
-        <v>841</v>
+        <v>1567</v>
       </c>
       <c r="G852" s="12">
-        <v>1898</v>
+        <v>1897</v>
       </c>
       <c r="H852" s="12"/>
       <c r="I852" s="12"/>
       <c r="J852" s="12">
-        <v>1858</v>
+        <v>1887</v>
       </c>
       <c r="K852" s="12">
         <f t="shared" si="184"/>
@@ -73084,7 +73080,7 @@
       </c>
       <c r="L852" s="12">
         <f t="shared" si="173"/>
-        <v>1898</v>
+        <v>1897</v>
       </c>
       <c r="M852" s="12" t="str">
         <f t="shared" si="174"/>
@@ -73092,7 +73088,7 @@
       </c>
       <c r="N852" s="12">
         <f t="shared" si="175"/>
-        <v>1858</v>
+        <v>1887</v>
       </c>
       <c r="O852" s="12" t="str">
         <f t="shared" si="176"/>
@@ -73134,27 +73130,27 @@
         <v/>
       </c>
       <c r="B853" s="11" t="s">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="C853" s="11" t="s">
-        <v>1729</v>
-      </c>
-      <c r="D853" s="11" t="s">
-        <v>59</v>
+        <v>840</v>
+      </c>
+      <c r="D853" s="15" t="s">
+        <v>78</v>
       </c>
       <c r="E853" s="11" t="s">
-        <v>60</v>
+        <v>26</v>
       </c>
       <c r="F853" s="11" t="s">
-        <v>1730</v>
+        <v>841</v>
       </c>
       <c r="G853" s="12">
-        <v>1899</v>
+        <v>1898</v>
       </c>
       <c r="H853" s="12"/>
       <c r="I853" s="12"/>
       <c r="J853" s="12">
-        <v>1869</v>
+        <v>1858</v>
       </c>
       <c r="K853" s="12">
         <f t="shared" si="184"/>
@@ -73162,7 +73158,7 @@
       </c>
       <c r="L853" s="12">
         <f t="shared" si="173"/>
-        <v>1899</v>
+        <v>1898</v>
       </c>
       <c r="M853" s="12" t="str">
         <f t="shared" si="174"/>
@@ -73170,7 +73166,7 @@
       </c>
       <c r="N853" s="12">
         <f t="shared" si="175"/>
-        <v>1869</v>
+        <v>1858</v>
       </c>
       <c r="O853" s="12" t="str">
         <f t="shared" si="176"/>
@@ -73206,25 +73202,25 @@
         <v>1000000000000000</v>
       </c>
     </row>
-    <row r="854" spans="1:23" s="7" customFormat="1" ht="28.5" customHeight="1">
+    <row r="854" spans="1:23" s="2" customFormat="1" ht="28.5" customHeight="1">
       <c r="A854" s="11" t="str">
         <f t="shared" si="172"/>
         <v/>
       </c>
       <c r="B854" s="11" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="C854" s="11" t="s">
-        <v>761</v>
+        <v>1729</v>
       </c>
       <c r="D854" s="11" t="s">
-        <v>69</v>
+        <v>59</v>
       </c>
       <c r="E854" s="11" t="s">
-        <v>26</v>
+        <v>60</v>
       </c>
       <c r="F854" s="11" t="s">
-        <v>762</v>
+        <v>1730</v>
       </c>
       <c r="G854" s="12">
         <v>1899</v>
@@ -73290,19 +73286,19 @@
         <v/>
       </c>
       <c r="B855" s="11" t="s">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="C855" s="11" t="s">
-        <v>414</v>
-      </c>
-      <c r="D855" s="15" t="s">
-        <v>59</v>
+        <v>761</v>
+      </c>
+      <c r="D855" s="11" t="s">
+        <v>69</v>
       </c>
       <c r="E855" s="11" t="s">
-        <v>60</v>
+        <v>26</v>
       </c>
       <c r="F855" s="11" t="s">
-        <v>417</v>
+        <v>762</v>
       </c>
       <c r="G855" s="12">
         <v>1899</v>
@@ -73310,7 +73306,7 @@
       <c r="H855" s="12"/>
       <c r="I855" s="12"/>
       <c r="J855" s="12">
-        <v>1889</v>
+        <v>1869</v>
       </c>
       <c r="K855" s="12">
         <f t="shared" si="184"/>
@@ -73326,7 +73322,7 @@
       </c>
       <c r="N855" s="12">
         <f t="shared" si="175"/>
-        <v>1889</v>
+        <v>1869</v>
       </c>
       <c r="O855" s="12" t="str">
         <f t="shared" si="176"/>
@@ -73362,25 +73358,25 @@
         <v>1000000000000000</v>
       </c>
     </row>
-    <row r="856" spans="1:23" s="2" customFormat="1" ht="28.5" customHeight="1">
+    <row r="856" spans="1:23" s="7" customFormat="1" ht="28.5" customHeight="1">
       <c r="A856" s="11" t="str">
         <f t="shared" si="172"/>
         <v/>
       </c>
       <c r="B856" s="11" t="s">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="C856" s="11" t="s">
-        <v>336</v>
+        <v>414</v>
       </c>
       <c r="D856" s="15" t="s">
         <v>59</v>
       </c>
       <c r="E856" s="11" t="s">
-        <v>26</v>
+        <v>60</v>
       </c>
       <c r="F856" s="11" t="s">
-        <v>337</v>
+        <v>417</v>
       </c>
       <c r="G856" s="12">
         <v>1899</v>
@@ -73449,16 +73445,16 @@
         <v>14</v>
       </c>
       <c r="C857" s="11" t="s">
-        <v>832</v>
-      </c>
-      <c r="D857" s="11" t="s">
-        <v>57</v>
+        <v>336</v>
+      </c>
+      <c r="D857" s="15" t="s">
+        <v>59</v>
       </c>
       <c r="E857" s="11" t="s">
         <v>26</v>
       </c>
       <c r="F857" s="11" t="s">
-        <v>833</v>
+        <v>337</v>
       </c>
       <c r="G857" s="12">
         <v>1899</v>
@@ -73527,7 +73523,7 @@
         <v>14</v>
       </c>
       <c r="C858" s="11" t="s">
-        <v>1090</v>
+        <v>832</v>
       </c>
       <c r="D858" s="11" t="s">
         <v>57</v>
@@ -73536,7 +73532,7 @@
         <v>26</v>
       </c>
       <c r="F858" s="11" t="s">
-        <v>1091</v>
+        <v>833</v>
       </c>
       <c r="G858" s="12">
         <v>1899</v>
@@ -73544,7 +73540,7 @@
       <c r="H858" s="12"/>
       <c r="I858" s="12"/>
       <c r="J858" s="12">
-        <v>1895</v>
+        <v>1889</v>
       </c>
       <c r="K858" s="12">
         <f t="shared" si="184"/>
@@ -73560,7 +73556,7 @@
       </c>
       <c r="N858" s="12">
         <f t="shared" si="175"/>
-        <v>1895</v>
+        <v>1889</v>
       </c>
       <c r="O858" s="12" t="str">
         <f t="shared" si="176"/>
@@ -73605,16 +73601,16 @@
         <v>14</v>
       </c>
       <c r="C859" s="11" t="s">
-        <v>1301</v>
-      </c>
-      <c r="D859" s="15" t="s">
-        <v>45</v>
+        <v>1090</v>
+      </c>
+      <c r="D859" s="11" t="s">
+        <v>57</v>
       </c>
       <c r="E859" s="11" t="s">
         <v>26</v>
       </c>
       <c r="F859" s="11" t="s">
-        <v>1302</v>
+        <v>1091</v>
       </c>
       <c r="G859" s="12">
         <v>1899</v>
@@ -73680,19 +73676,19 @@
         <v/>
       </c>
       <c r="B860" s="11" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="C860" s="11" t="s">
-        <v>973</v>
+        <v>1301</v>
       </c>
       <c r="D860" s="15" t="s">
         <v>45</v>
       </c>
       <c r="E860" s="11" t="s">
-        <v>60</v>
+        <v>26</v>
       </c>
       <c r="F860" s="11" t="s">
-        <v>974</v>
+        <v>1302</v>
       </c>
       <c r="G860" s="12">
         <v>1899</v>
@@ -73700,7 +73696,7 @@
       <c r="H860" s="12"/>
       <c r="I860" s="12"/>
       <c r="J860" s="12">
-        <v>1898</v>
+        <v>1895</v>
       </c>
       <c r="K860" s="12">
         <f t="shared" si="184"/>
@@ -73716,7 +73712,7 @@
       </c>
       <c r="N860" s="12">
         <f t="shared" si="175"/>
-        <v>1898</v>
+        <v>1895</v>
       </c>
       <c r="O860" s="12" t="str">
         <f t="shared" si="176"/>
@@ -73758,19 +73754,19 @@
         <v/>
       </c>
       <c r="B861" s="11" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="C861" s="11" t="s">
-        <v>1138</v>
+        <v>973</v>
       </c>
       <c r="D861" s="15" t="s">
         <v>45</v>
       </c>
       <c r="E861" s="11" t="s">
-        <v>26</v>
+        <v>60</v>
       </c>
       <c r="F861" s="11" t="s">
-        <v>1139</v>
+        <v>974</v>
       </c>
       <c r="G861" s="12">
         <v>1899</v>
@@ -73839,16 +73835,16 @@
         <v>10</v>
       </c>
       <c r="C862" s="11" t="s">
-        <v>162</v>
-      </c>
-      <c r="D862" s="11" t="s">
-        <v>59</v>
+        <v>1138</v>
+      </c>
+      <c r="D862" s="15" t="s">
+        <v>45</v>
       </c>
       <c r="E862" s="11" t="s">
         <v>26</v>
       </c>
       <c r="F862" s="11" t="s">
-        <v>163</v>
+        <v>1139</v>
       </c>
       <c r="G862" s="12">
         <v>1899</v>
@@ -73856,7 +73852,7 @@
       <c r="H862" s="12"/>
       <c r="I862" s="12"/>
       <c r="J862" s="12">
-        <v>1899</v>
+        <v>1898</v>
       </c>
       <c r="K862" s="12">
         <f t="shared" si="184"/>
@@ -73872,7 +73868,7 @@
       </c>
       <c r="N862" s="12">
         <f t="shared" si="175"/>
-        <v>1899</v>
+        <v>1898</v>
       </c>
       <c r="O862" s="12" t="str">
         <f t="shared" si="176"/>
@@ -73917,16 +73913,16 @@
         <v>10</v>
       </c>
       <c r="C863" s="11" t="s">
-        <v>507</v>
-      </c>
-      <c r="D863" s="15" t="s">
+        <v>162</v>
+      </c>
+      <c r="D863" s="11" t="s">
         <v>59</v>
       </c>
       <c r="E863" s="11" t="s">
-        <v>60</v>
+        <v>26</v>
       </c>
       <c r="F863" s="11" t="s">
-        <v>508</v>
+        <v>163</v>
       </c>
       <c r="G863" s="12">
         <v>1899</v>
@@ -73995,7 +73991,7 @@
         <v>10</v>
       </c>
       <c r="C864" s="11" t="s">
-        <v>967</v>
+        <v>507</v>
       </c>
       <c r="D864" s="15" t="s">
         <v>59</v>
@@ -74004,7 +74000,7 @@
         <v>60</v>
       </c>
       <c r="F864" s="11" t="s">
-        <v>968</v>
+        <v>508</v>
       </c>
       <c r="G864" s="12">
         <v>1899</v>
@@ -74073,24 +74069,24 @@
         <v>10</v>
       </c>
       <c r="C865" s="11" t="s">
-        <v>517</v>
+        <v>967</v>
       </c>
       <c r="D865" s="15" t="s">
-        <v>78</v>
+        <v>59</v>
       </c>
       <c r="E865" s="11" t="s">
         <v>60</v>
       </c>
       <c r="F865" s="11" t="s">
-        <v>518</v>
+        <v>968</v>
       </c>
       <c r="G865" s="12">
-        <v>1907</v>
+        <v>1899</v>
       </c>
       <c r="H865" s="12"/>
       <c r="I865" s="12"/>
       <c r="J865" s="12">
-        <v>1896</v>
+        <v>1899</v>
       </c>
       <c r="K865" s="12">
         <f t="shared" si="184"/>
@@ -74098,7 +74094,7 @@
       </c>
       <c r="L865" s="12">
         <f t="shared" si="173"/>
-        <v>1907</v>
+        <v>1899</v>
       </c>
       <c r="M865" s="12" t="str">
         <f t="shared" si="174"/>
@@ -74106,7 +74102,7 @@
       </c>
       <c r="N865" s="12">
         <f t="shared" si="175"/>
-        <v>1896</v>
+        <v>1899</v>
       </c>
       <c r="O865" s="12" t="str">
         <f t="shared" si="176"/>
@@ -74151,7 +74147,7 @@
         <v>10</v>
       </c>
       <c r="C866" s="11" t="s">
-        <v>1613</v>
+        <v>517</v>
       </c>
       <c r="D866" s="15" t="s">
         <v>78</v>
@@ -74160,15 +74156,15 @@
         <v>60</v>
       </c>
       <c r="F866" s="11" t="s">
-        <v>1614</v>
+        <v>518</v>
       </c>
       <c r="G866" s="12">
-        <v>1908</v>
+        <v>1907</v>
       </c>
       <c r="H866" s="12"/>
       <c r="I866" s="12"/>
       <c r="J866" s="12">
-        <v>1878</v>
+        <v>1896</v>
       </c>
       <c r="K866" s="12">
         <f t="shared" si="184"/>
@@ -74176,7 +74172,7 @@
       </c>
       <c r="L866" s="12">
         <f t="shared" si="173"/>
-        <v>1908</v>
+        <v>1907</v>
       </c>
       <c r="M866" s="12" t="str">
         <f t="shared" si="174"/>
@@ -74184,7 +74180,7 @@
       </c>
       <c r="N866" s="12">
         <f t="shared" si="175"/>
-        <v>1878</v>
+        <v>1896</v>
       </c>
       <c r="O866" s="12" t="str">
         <f t="shared" si="176"/>
@@ -74226,27 +74222,27 @@
         <v/>
       </c>
       <c r="B867" s="11" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="C867" s="11" t="s">
-        <v>1098</v>
+        <v>1613</v>
       </c>
       <c r="D867" s="15" t="s">
-        <v>45</v>
+        <v>78</v>
       </c>
       <c r="E867" s="11" t="s">
-        <v>26</v>
+        <v>60</v>
       </c>
       <c r="F867" s="11" t="s">
-        <v>1099</v>
+        <v>1614</v>
       </c>
       <c r="G867" s="12">
-        <v>1909</v>
+        <v>1908</v>
       </c>
       <c r="H867" s="12"/>
       <c r="I867" s="12"/>
       <c r="J867" s="12">
-        <v>1899</v>
+        <v>1878</v>
       </c>
       <c r="K867" s="12">
         <f t="shared" si="184"/>
@@ -74254,7 +74250,7 @@
       </c>
       <c r="L867" s="12">
         <f t="shared" si="173"/>
-        <v>1909</v>
+        <v>1908</v>
       </c>
       <c r="M867" s="12" t="str">
         <f t="shared" si="174"/>
@@ -74262,7 +74258,7 @@
       </c>
       <c r="N867" s="12">
         <f t="shared" si="175"/>
-        <v>1899</v>
+        <v>1878</v>
       </c>
       <c r="O867" s="12" t="str">
         <f t="shared" si="176"/>
@@ -74298,33 +74294,33 @@
         <v>1000000000000000</v>
       </c>
     </row>
-    <row r="868" spans="1:23" s="16" customFormat="1" ht="28.5" customHeight="1">
+    <row r="868" spans="1:23" s="2" customFormat="1" ht="28.5" customHeight="1">
       <c r="A868" s="11" t="str">
         <f t="shared" si="172"/>
         <v/>
       </c>
       <c r="B868" s="11" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="C868" s="11" t="s">
-        <v>1329</v>
-      </c>
-      <c r="D868" s="11" t="s">
-        <v>57</v>
+        <v>1098</v>
+      </c>
+      <c r="D868" s="15" t="s">
+        <v>45</v>
       </c>
       <c r="E868" s="11" t="s">
-        <v>60</v>
+        <v>26</v>
       </c>
       <c r="F868" s="11" t="s">
-        <v>1330</v>
+        <v>1099</v>
       </c>
       <c r="G868" s="12">
-        <v>1919</v>
+        <v>1909</v>
       </c>
       <c r="H868" s="12"/>
       <c r="I868" s="12"/>
       <c r="J868" s="12">
-        <v>1919</v>
+        <v>1899</v>
       </c>
       <c r="K868" s="12">
         <f t="shared" si="184"/>
@@ -74332,7 +74328,7 @@
       </c>
       <c r="L868" s="12">
         <f t="shared" si="173"/>
-        <v>1919</v>
+        <v>1909</v>
       </c>
       <c r="M868" s="12" t="str">
         <f t="shared" si="174"/>
@@ -74340,7 +74336,7 @@
       </c>
       <c r="N868" s="12">
         <f t="shared" si="175"/>
-        <v>1919</v>
+        <v>1899</v>
       </c>
       <c r="O868" s="12" t="str">
         <f t="shared" si="176"/>
@@ -74376,33 +74372,33 @@
         <v>1000000000000000</v>
       </c>
     </row>
-    <row r="869" spans="1:23" s="7" customFormat="1" ht="28.5" customHeight="1">
+    <row r="869" spans="1:23" s="16" customFormat="1" ht="28.5" customHeight="1">
       <c r="A869" s="11" t="str">
         <f t="shared" si="172"/>
         <v/>
       </c>
       <c r="B869" s="11" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="C869" s="11" t="s">
-        <v>834</v>
-      </c>
-      <c r="D869" s="15" t="s">
-        <v>59</v>
+        <v>1329</v>
+      </c>
+      <c r="D869" s="11" t="s">
+        <v>57</v>
       </c>
       <c r="E869" s="11" t="s">
-        <v>26</v>
+        <v>60</v>
       </c>
       <c r="F869" s="11" t="s">
-        <v>835</v>
+        <v>1330</v>
       </c>
       <c r="G869" s="12">
-        <v>1928</v>
+        <v>1919</v>
       </c>
       <c r="H869" s="12"/>
       <c r="I869" s="12"/>
       <c r="J869" s="12">
-        <v>1918</v>
+        <v>1919</v>
       </c>
       <c r="K869" s="12">
         <f t="shared" si="184"/>
@@ -74410,7 +74406,7 @@
       </c>
       <c r="L869" s="12">
         <f t="shared" si="173"/>
-        <v>1928</v>
+        <v>1919</v>
       </c>
       <c r="M869" s="12" t="str">
         <f t="shared" si="174"/>
@@ -74418,7 +74414,7 @@
       </c>
       <c r="N869" s="12">
         <f t="shared" si="175"/>
-        <v>1918</v>
+        <v>1919</v>
       </c>
       <c r="O869" s="12" t="str">
         <f t="shared" si="176"/>
@@ -74460,19 +74456,19 @@
         <v/>
       </c>
       <c r="B870" s="11" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="C870" s="11" t="s">
-        <v>722</v>
+        <v>834</v>
       </c>
       <c r="D870" s="15" t="s">
         <v>59</v>
       </c>
       <c r="E870" s="11" t="s">
-        <v>60</v>
+        <v>26</v>
       </c>
       <c r="F870" s="11" t="s">
-        <v>723</v>
+        <v>835</v>
       </c>
       <c r="G870" s="12">
         <v>1928</v>
@@ -74480,7 +74476,7 @@
       <c r="H870" s="12"/>
       <c r="I870" s="12"/>
       <c r="J870" s="12">
-        <v>1928</v>
+        <v>1918</v>
       </c>
       <c r="K870" s="12">
         <f t="shared" si="184"/>
@@ -74496,7 +74492,7 @@
       </c>
       <c r="N870" s="12">
         <f t="shared" si="175"/>
-        <v>1928</v>
+        <v>1918</v>
       </c>
       <c r="O870" s="12" t="str">
         <f t="shared" si="176"/>
@@ -74538,27 +74534,27 @@
         <v/>
       </c>
       <c r="B871" s="11" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="C871" s="11" t="s">
-        <v>704</v>
+        <v>722</v>
       </c>
       <c r="D871" s="15" t="s">
-        <v>78</v>
+        <v>59</v>
       </c>
       <c r="E871" s="11" t="s">
         <v>60</v>
       </c>
       <c r="F871" s="11" t="s">
-        <v>705</v>
+        <v>723</v>
       </c>
       <c r="G871" s="12">
-        <v>1929</v>
+        <v>1928</v>
       </c>
       <c r="H871" s="12"/>
       <c r="I871" s="12"/>
       <c r="J871" s="12">
-        <v>1895</v>
+        <v>1928</v>
       </c>
       <c r="K871" s="12">
         <f t="shared" si="184"/>
@@ -74566,7 +74562,7 @@
       </c>
       <c r="L871" s="12">
         <f t="shared" si="173"/>
-        <v>1929</v>
+        <v>1928</v>
       </c>
       <c r="M871" s="12" t="str">
         <f t="shared" si="174"/>
@@ -74574,7 +74570,7 @@
       </c>
       <c r="N871" s="12">
         <f t="shared" si="175"/>
-        <v>1895</v>
+        <v>1928</v>
       </c>
       <c r="O871" s="12" t="str">
         <f t="shared" si="176"/>
@@ -74610,25 +74606,25 @@
         <v>1000000000000000</v>
       </c>
     </row>
-    <row r="872" spans="1:23" s="16" customFormat="1" ht="28.5" customHeight="1">
+    <row r="872" spans="1:23" s="7" customFormat="1" ht="28.5" customHeight="1">
       <c r="A872" s="11" t="str">
         <f t="shared" si="172"/>
         <v/>
       </c>
       <c r="B872" s="11" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="C872" s="11" t="s">
-        <v>836</v>
+        <v>704</v>
       </c>
       <c r="D872" s="15" t="s">
-        <v>45</v>
+        <v>78</v>
       </c>
       <c r="E872" s="11" t="s">
         <v>60</v>
       </c>
       <c r="F872" s="11" t="s">
-        <v>837</v>
+        <v>705</v>
       </c>
       <c r="G872" s="12">
         <v>1929</v>
@@ -74636,7 +74632,7 @@
       <c r="H872" s="12"/>
       <c r="I872" s="12"/>
       <c r="J872" s="12">
-        <v>1918</v>
+        <v>1895</v>
       </c>
       <c r="K872" s="12">
         <f t="shared" si="184"/>
@@ -74652,7 +74648,7 @@
       </c>
       <c r="N872" s="12">
         <f t="shared" si="175"/>
-        <v>1918</v>
+        <v>1895</v>
       </c>
       <c r="O872" s="12" t="str">
         <f t="shared" si="176"/>
@@ -74688,33 +74684,33 @@
         <v>1000000000000000</v>
       </c>
     </row>
-    <row r="873" spans="1:23" s="2" customFormat="1" ht="28.5" customHeight="1">
+    <row r="873" spans="1:23" s="16" customFormat="1" ht="28.5" customHeight="1">
       <c r="A873" s="11" t="str">
         <f t="shared" si="172"/>
         <v/>
       </c>
       <c r="B873" s="11" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="C873" s="11" t="s">
-        <v>604</v>
-      </c>
-      <c r="D873" s="11" t="s">
-        <v>57</v>
+        <v>836</v>
+      </c>
+      <c r="D873" s="15" t="s">
+        <v>45</v>
       </c>
       <c r="E873" s="11" t="s">
         <v>60</v>
       </c>
       <c r="F873" s="11" t="s">
-        <v>605</v>
+        <v>837</v>
       </c>
       <c r="G873" s="12">
-        <v>1939</v>
+        <v>1929</v>
       </c>
       <c r="H873" s="12"/>
       <c r="I873" s="12"/>
       <c r="J873" s="12">
-        <v>1919</v>
+        <v>1918</v>
       </c>
       <c r="K873" s="12">
         <f t="shared" si="184"/>
@@ -74722,7 +74718,7 @@
       </c>
       <c r="L873" s="12">
         <f t="shared" si="173"/>
-        <v>1939</v>
+        <v>1929</v>
       </c>
       <c r="M873" s="12" t="str">
         <f t="shared" si="174"/>
@@ -74730,7 +74726,7 @@
       </c>
       <c r="N873" s="12">
         <f t="shared" si="175"/>
-        <v>1919</v>
+        <v>1918</v>
       </c>
       <c r="O873" s="12" t="str">
         <f t="shared" si="176"/>
@@ -74772,27 +74768,27 @@
         <v/>
       </c>
       <c r="B874" s="11" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="C874" s="11" t="s">
-        <v>769</v>
-      </c>
-      <c r="D874" s="15" t="s">
-        <v>78</v>
+        <v>604</v>
+      </c>
+      <c r="D874" s="11" t="s">
+        <v>57</v>
       </c>
       <c r="E874" s="11" t="s">
-        <v>26</v>
+        <v>60</v>
       </c>
       <c r="F874" s="11" t="s">
-        <v>770</v>
+        <v>605</v>
       </c>
       <c r="G874" s="12">
-        <v>2199</v>
+        <v>1939</v>
       </c>
       <c r="H874" s="12"/>
       <c r="I874" s="12"/>
       <c r="J874" s="12">
-        <v>2199</v>
+        <v>1919</v>
       </c>
       <c r="K874" s="12">
         <f t="shared" si="184"/>
@@ -74800,7 +74796,7 @@
       </c>
       <c r="L874" s="12">
         <f t="shared" si="173"/>
-        <v>2199</v>
+        <v>1939</v>
       </c>
       <c r="M874" s="12" t="str">
         <f t="shared" si="174"/>
@@ -74808,7 +74804,7 @@
       </c>
       <c r="N874" s="12">
         <f t="shared" si="175"/>
-        <v>2199</v>
+        <v>1919</v>
       </c>
       <c r="O874" s="12" t="str">
         <f t="shared" si="176"/>
@@ -74818,9 +74814,7 @@
         <f t="shared" si="177"/>
         <v/>
       </c>
-      <c r="Q874" s="12" t="s">
-        <v>61</v>
-      </c>
+      <c r="Q874" s="12"/>
       <c r="R874" s="13" t="str">
         <f t="shared" si="178"/>
         <v/>
@@ -74846,33 +74840,33 @@
         <v>1000000000000000</v>
       </c>
     </row>
-    <row r="875" spans="1:23" s="16" customFormat="1" ht="28.5" customHeight="1">
+    <row r="875" spans="1:23" s="2" customFormat="1" ht="28.5" customHeight="1">
       <c r="A875" s="11" t="str">
         <f t="shared" si="172"/>
         <v/>
       </c>
       <c r="B875" s="11" t="s">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="C875" s="11" t="s">
-        <v>654</v>
+        <v>769</v>
       </c>
       <c r="D875" s="15" t="s">
-        <v>59</v>
+        <v>78</v>
       </c>
       <c r="E875" s="11" t="s">
-        <v>60</v>
+        <v>26</v>
       </c>
       <c r="F875" s="11" t="s">
-        <v>656</v>
+        <v>770</v>
       </c>
       <c r="G875" s="12">
-        <v>1995</v>
+        <v>2199</v>
       </c>
       <c r="H875" s="12"/>
       <c r="I875" s="12"/>
       <c r="J875" s="12">
-        <v>1995</v>
+        <v>2199</v>
       </c>
       <c r="K875" s="12">
         <f t="shared" si="184"/>
@@ -74880,7 +74874,7 @@
       </c>
       <c r="L875" s="12">
         <f t="shared" si="173"/>
-        <v>1995</v>
+        <v>2199</v>
       </c>
       <c r="M875" s="12" t="str">
         <f t="shared" si="174"/>
@@ -74888,7 +74882,7 @@
       </c>
       <c r="N875" s="12">
         <f t="shared" si="175"/>
-        <v>1995</v>
+        <v>2199</v>
       </c>
       <c r="O875" s="12" t="str">
         <f t="shared" si="176"/>
@@ -74898,7 +74892,9 @@
         <f t="shared" si="177"/>
         <v/>
       </c>
-      <c r="Q875" s="12"/>
+      <c r="Q875" s="12" t="s">
+        <v>61</v>
+      </c>
       <c r="R875" s="13" t="str">
         <f t="shared" si="178"/>
         <v/>
@@ -74924,7 +74920,7 @@
         <v>1000000000000000</v>
       </c>
     </row>
-    <row r="876" spans="1:23" s="2" customFormat="1" ht="28.5" customHeight="1">
+    <row r="876" spans="1:23" s="16" customFormat="1" ht="28.5" customHeight="1">
       <c r="A876" s="11" t="str">
         <f t="shared" si="172"/>
         <v/>
@@ -74933,24 +74929,24 @@
         <v>14</v>
       </c>
       <c r="C876" s="11" t="s">
-        <v>362</v>
-      </c>
-      <c r="D876" s="11" t="s">
-        <v>57</v>
+        <v>654</v>
+      </c>
+      <c r="D876" s="15" t="s">
+        <v>59</v>
       </c>
       <c r="E876" s="11" t="s">
         <v>60</v>
       </c>
       <c r="F876" s="11" t="s">
-        <v>363</v>
+        <v>656</v>
       </c>
       <c r="G876" s="12">
-        <v>1999</v>
+        <v>1995</v>
       </c>
       <c r="H876" s="12"/>
       <c r="I876" s="12"/>
       <c r="J876" s="12">
-        <v>1989</v>
+        <v>1995</v>
       </c>
       <c r="K876" s="12">
         <f t="shared" si="184"/>
@@ -74958,7 +74954,7 @@
       </c>
       <c r="L876" s="12">
         <f t="shared" si="173"/>
-        <v>1999</v>
+        <v>1995</v>
       </c>
       <c r="M876" s="12" t="str">
         <f t="shared" si="174"/>
@@ -74966,7 +74962,7 @@
       </c>
       <c r="N876" s="12">
         <f t="shared" si="175"/>
-        <v>1989</v>
+        <v>1995</v>
       </c>
       <c r="O876" s="12" t="str">
         <f t="shared" si="176"/>
@@ -75008,27 +75004,27 @@
         <v/>
       </c>
       <c r="B877" s="11" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="C877" s="11" t="s">
-        <v>1764</v>
+        <v>362</v>
       </c>
       <c r="D877" s="11" t="s">
-        <v>45</v>
+        <v>57</v>
       </c>
       <c r="E877" s="11" t="s">
-        <v>26</v>
+        <v>60</v>
       </c>
       <c r="F877" s="11" t="s">
-        <v>1765</v>
+        <v>363</v>
       </c>
       <c r="G877" s="12">
-        <v>2080</v>
+        <v>1999</v>
       </c>
       <c r="H877" s="12"/>
       <c r="I877" s="12"/>
       <c r="J877" s="12">
-        <v>1807</v>
+        <v>1989</v>
       </c>
       <c r="K877" s="12">
         <f t="shared" si="184"/>
@@ -75036,7 +75032,7 @@
       </c>
       <c r="L877" s="12">
         <f t="shared" si="173"/>
-        <v>2080</v>
+        <v>1999</v>
       </c>
       <c r="M877" s="12" t="str">
         <f t="shared" si="174"/>
@@ -75044,7 +75040,7 @@
       </c>
       <c r="N877" s="12">
         <f t="shared" si="175"/>
-        <v>1807</v>
+        <v>1989</v>
       </c>
       <c r="O877" s="12" t="str">
         <f t="shared" si="176"/>
@@ -75341,7 +75337,7 @@
         <v>1869</v>
       </c>
       <c r="K881" s="12">
-        <f>IF(AND(IFERROR(SEARCH("현대오일뱅크",$C881),0)&gt;0,IFERROR(SEARCH("직영",$C881),0)&gt;0),$B$13,0)</f>
+        <f t="shared" si="184"/>
         <v>0</v>
       </c>
       <c r="L881" s="12" t="str">
@@ -75602,7 +75598,7 @@
     </row>
     <row r="2" spans="1:13" s="16" customFormat="1" ht="21" customHeight="1">
       <c r="A2" s="18" t="s">
-        <v>1763</v>
+        <v>1762</v>
       </c>
     </row>
     <row r="3" spans="1:13" s="16" customFormat="1" ht="27.75" customHeight="1">
@@ -75647,1702 +75643,634 @@
       </c>
     </row>
     <row r="4" spans="1:13" s="16" customFormat="1" ht="25.5" customHeight="1">
-      <c r="A4" s="19" t="s">
-        <v>6</v>
-      </c>
-      <c r="B4" s="20" t="s">
-        <v>564</v>
-      </c>
-      <c r="C4" s="20" t="s">
-        <v>565</v>
-      </c>
-      <c r="D4" s="20" t="s">
-        <v>1758</v>
-      </c>
-      <c r="E4" s="26">
-        <v>1819</v>
-      </c>
-      <c r="F4" s="26">
-        <v>1819</v>
-      </c>
-      <c r="G4" s="26">
-        <f t="shared" ref="G4:G45" si="0">IF(OR(E4="",F4=""),"",F4-E4)</f>
-        <v>0</v>
-      </c>
-      <c r="H4" s="26">
-        <v>2345</v>
-      </c>
-      <c r="I4" s="26">
-        <v>2340</v>
-      </c>
-      <c r="J4" s="26">
-        <f t="shared" ref="J4:J45" si="1">IF(OR(H4="",I4=""),"",I4-H4)</f>
-        <v>-5</v>
-      </c>
-      <c r="K4" s="26">
-        <v>1798</v>
-      </c>
-      <c r="L4" s="26">
-        <v>1798</v>
-      </c>
-      <c r="M4" s="26">
-        <f t="shared" ref="M4:M45" si="2">IF(OR(K4="",L4=""),"",L4-K4)</f>
-        <v>0</v>
-      </c>
+      <c r="A4" s="19"/>
+      <c r="B4" s="20"/>
+      <c r="C4" s="20"/>
+      <c r="D4" s="20"/>
+      <c r="E4" s="26"/>
+      <c r="F4" s="26"/>
+      <c r="G4" s="26"/>
+      <c r="H4" s="26"/>
+      <c r="I4" s="26"/>
+      <c r="J4" s="26"/>
+      <c r="K4" s="26"/>
+      <c r="L4" s="26"/>
+      <c r="M4" s="26"/>
     </row>
     <row r="5" spans="1:13" s="16" customFormat="1" ht="25.5" customHeight="1">
-      <c r="A5" s="19" t="s">
-        <v>10</v>
-      </c>
-      <c r="B5" s="20" t="s">
-        <v>1718</v>
-      </c>
-      <c r="C5" s="20" t="s">
-        <v>1719</v>
-      </c>
-      <c r="D5" s="20" t="s">
-        <v>1758</v>
-      </c>
-      <c r="E5" s="26">
-        <v>1819</v>
-      </c>
-      <c r="F5" s="26">
-        <v>1819</v>
-      </c>
-      <c r="G5" s="26">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="H5" s="26">
-        <v>2358</v>
-      </c>
-      <c r="I5" s="26">
-        <v>2363</v>
-      </c>
-      <c r="J5" s="26">
-        <f t="shared" si="1"/>
-        <v>5</v>
-      </c>
-      <c r="K5" s="26">
-        <v>1809</v>
-      </c>
-      <c r="L5" s="26">
-        <v>1809</v>
-      </c>
-      <c r="M5" s="26">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
+      <c r="A5" s="19"/>
+      <c r="B5" s="20"/>
+      <c r="C5" s="20"/>
+      <c r="D5" s="20"/>
+      <c r="E5" s="26"/>
+      <c r="F5" s="26"/>
+      <c r="G5" s="26"/>
+      <c r="H5" s="26"/>
+      <c r="I5" s="26"/>
+      <c r="J5" s="26"/>
+      <c r="K5" s="26"/>
+      <c r="L5" s="26"/>
+      <c r="M5" s="26"/>
     </row>
     <row r="6" spans="1:13" s="16" customFormat="1" ht="25.5" customHeight="1">
-      <c r="A6" s="19" t="s">
-        <v>6</v>
-      </c>
-      <c r="B6" s="20" t="s">
-        <v>990</v>
-      </c>
-      <c r="C6" s="20" t="s">
-        <v>991</v>
-      </c>
-      <c r="D6" s="20" t="s">
-        <v>1758</v>
-      </c>
-      <c r="E6" s="26">
-        <v>1829</v>
-      </c>
-      <c r="F6" s="26">
-        <v>1829</v>
-      </c>
-      <c r="G6" s="26">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="H6" s="26">
-        <v>2392</v>
-      </c>
-      <c r="I6" s="26">
-        <v>2399</v>
-      </c>
-      <c r="J6" s="26">
-        <f t="shared" si="1"/>
-        <v>7</v>
-      </c>
-      <c r="K6" s="26">
-        <v>1828</v>
-      </c>
-      <c r="L6" s="26">
-        <v>1828</v>
-      </c>
-      <c r="M6" s="26">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
+      <c r="A6" s="19"/>
+      <c r="B6" s="20"/>
+      <c r="C6" s="20"/>
+      <c r="D6" s="20"/>
+      <c r="E6" s="26"/>
+      <c r="F6" s="26"/>
+      <c r="G6" s="26"/>
+      <c r="H6" s="26"/>
+      <c r="I6" s="26"/>
+      <c r="J6" s="26"/>
+      <c r="K6" s="26"/>
+      <c r="L6" s="26"/>
+      <c r="M6" s="26"/>
     </row>
     <row r="7" spans="1:13" s="16" customFormat="1" ht="25.5" customHeight="1">
-      <c r="A7" s="19" t="s">
-        <v>6</v>
-      </c>
-      <c r="B7" s="20" t="s">
-        <v>549</v>
-      </c>
-      <c r="C7" s="20" t="s">
-        <v>550</v>
-      </c>
-      <c r="D7" s="20" t="s">
-        <v>1758</v>
-      </c>
-      <c r="E7" s="26">
-        <v>1825</v>
-      </c>
-      <c r="F7" s="26">
-        <v>1798</v>
-      </c>
-      <c r="G7" s="26">
-        <f t="shared" si="0"/>
-        <v>-27</v>
-      </c>
-      <c r="H7" s="26">
-        <v>2398</v>
-      </c>
-      <c r="I7" s="26">
-        <v>2289</v>
-      </c>
-      <c r="J7" s="26">
-        <f t="shared" si="1"/>
-        <v>-109</v>
-      </c>
-      <c r="K7" s="26">
-        <v>1819</v>
-      </c>
-      <c r="L7" s="26">
-        <v>1819</v>
-      </c>
-      <c r="M7" s="26">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
+      <c r="A7" s="19"/>
+      <c r="B7" s="20"/>
+      <c r="C7" s="20"/>
+      <c r="D7" s="20"/>
+      <c r="E7" s="26"/>
+      <c r="F7" s="26"/>
+      <c r="G7" s="26"/>
+      <c r="H7" s="26"/>
+      <c r="I7" s="26"/>
+      <c r="J7" s="26"/>
+      <c r="K7" s="26"/>
+      <c r="L7" s="26"/>
+      <c r="M7" s="26"/>
     </row>
     <row r="8" spans="1:13" s="16" customFormat="1" ht="25.5" customHeight="1">
-      <c r="A8" s="19" t="s">
-        <v>12</v>
-      </c>
-      <c r="B8" s="20" t="s">
-        <v>1273</v>
-      </c>
-      <c r="C8" s="20" t="s">
-        <v>1274</v>
-      </c>
-      <c r="D8" s="20" t="s">
-        <v>1758</v>
-      </c>
-      <c r="E8" s="26">
-        <v>1819</v>
-      </c>
-      <c r="F8" s="26">
-        <v>1819</v>
-      </c>
-      <c r="G8" s="26">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="H8" s="26">
-        <v>2459</v>
-      </c>
-      <c r="I8" s="26">
-        <v>2459</v>
-      </c>
-      <c r="J8" s="26">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="K8" s="26">
-        <v>1849</v>
-      </c>
-      <c r="L8" s="26">
-        <v>1819</v>
-      </c>
-      <c r="M8" s="26">
-        <f t="shared" si="2"/>
-        <v>-30</v>
-      </c>
+      <c r="A8" s="19"/>
+      <c r="B8" s="20"/>
+      <c r="C8" s="20"/>
+      <c r="D8" s="20"/>
+      <c r="E8" s="26"/>
+      <c r="F8" s="26"/>
+      <c r="G8" s="26"/>
+      <c r="H8" s="26"/>
+      <c r="I8" s="26"/>
+      <c r="J8" s="26"/>
+      <c r="K8" s="26"/>
+      <c r="L8" s="26"/>
+      <c r="M8" s="26"/>
     </row>
     <row r="9" spans="1:13" s="16" customFormat="1" ht="25.5" customHeight="1">
-      <c r="A9" s="19" t="s">
-        <v>18</v>
-      </c>
-      <c r="B9" s="20" t="s">
-        <v>1455</v>
-      </c>
-      <c r="C9" s="20" t="s">
-        <v>1456</v>
-      </c>
-      <c r="D9" s="20" t="s">
-        <v>1758</v>
-      </c>
-      <c r="E9" s="26">
-        <v>1855</v>
-      </c>
-      <c r="F9" s="26">
-        <v>1855</v>
-      </c>
-      <c r="G9" s="26">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
+      <c r="A9" s="19"/>
+      <c r="B9" s="20"/>
+      <c r="C9" s="20"/>
+      <c r="D9" s="20"/>
+      <c r="E9" s="26"/>
+      <c r="F9" s="26"/>
+      <c r="G9" s="26"/>
       <c r="H9" s="26"/>
       <c r="I9" s="26"/>
-      <c r="J9" s="26" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K9" s="26">
-        <v>1835</v>
-      </c>
-      <c r="L9" s="26">
-        <v>1795</v>
-      </c>
-      <c r="M9" s="26">
-        <f t="shared" si="2"/>
-        <v>-40</v>
-      </c>
+      <c r="J9" s="26"/>
+      <c r="K9" s="26"/>
+      <c r="L9" s="26"/>
+      <c r="M9" s="26"/>
     </row>
     <row r="10" spans="1:13" s="16" customFormat="1" ht="25.5" customHeight="1">
-      <c r="A10" s="19" t="s">
-        <v>16</v>
-      </c>
-      <c r="B10" s="20" t="s">
-        <v>1643</v>
-      </c>
-      <c r="C10" s="20" t="s">
-        <v>1644</v>
-      </c>
-      <c r="D10" s="20" t="s">
-        <v>1758</v>
-      </c>
-      <c r="E10" s="26">
-        <v>1865</v>
-      </c>
-      <c r="F10" s="26">
-        <v>1989</v>
-      </c>
-      <c r="G10" s="26">
-        <f t="shared" si="0"/>
-        <v>124</v>
-      </c>
+      <c r="A10" s="19"/>
+      <c r="B10" s="20"/>
+      <c r="C10" s="20"/>
+      <c r="D10" s="20"/>
+      <c r="E10" s="26"/>
+      <c r="F10" s="26"/>
+      <c r="G10" s="26"/>
       <c r="H10" s="26"/>
       <c r="I10" s="26"/>
-      <c r="J10" s="26" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K10" s="26">
-        <v>1825</v>
-      </c>
-      <c r="L10" s="26">
-        <v>1825</v>
-      </c>
-      <c r="M10" s="26">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
+      <c r="J10" s="26"/>
+      <c r="K10" s="26"/>
+      <c r="L10" s="26"/>
+      <c r="M10" s="26"/>
     </row>
     <row r="11" spans="1:13" s="16" customFormat="1" ht="25.5" customHeight="1">
-      <c r="A11" s="19" t="s">
-        <v>12</v>
-      </c>
-      <c r="B11" s="20" t="s">
-        <v>1144</v>
-      </c>
-      <c r="C11" s="20" t="s">
-        <v>1145</v>
-      </c>
-      <c r="D11" s="20" t="s">
-        <v>1758</v>
-      </c>
-      <c r="E11" s="26">
-        <v>1827</v>
-      </c>
-      <c r="F11" s="26">
-        <v>1812</v>
-      </c>
-      <c r="G11" s="26">
-        <f t="shared" si="0"/>
-        <v>-15</v>
-      </c>
+      <c r="A11" s="19"/>
+      <c r="B11" s="20"/>
+      <c r="C11" s="20"/>
+      <c r="D11" s="20"/>
+      <c r="E11" s="26"/>
+      <c r="F11" s="26"/>
+      <c r="G11" s="26"/>
       <c r="H11" s="26"/>
       <c r="I11" s="26"/>
-      <c r="J11" s="26" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K11" s="26">
-        <v>1827</v>
-      </c>
-      <c r="L11" s="26">
-        <v>1812</v>
-      </c>
-      <c r="M11" s="26">
-        <f t="shared" si="2"/>
-        <v>-15</v>
-      </c>
+      <c r="J11" s="26"/>
+      <c r="K11" s="26"/>
+      <c r="L11" s="26"/>
+      <c r="M11" s="26"/>
     </row>
     <row r="12" spans="1:13" s="16" customFormat="1" ht="25.5" customHeight="1">
-      <c r="A12" s="19" t="s">
-        <v>10</v>
-      </c>
-      <c r="B12" s="20" t="s">
-        <v>1022</v>
-      </c>
-      <c r="C12" s="20" t="s">
-        <v>1023</v>
-      </c>
-      <c r="D12" s="20" t="s">
-        <v>1758</v>
-      </c>
-      <c r="E12" s="26">
-        <v>1828</v>
-      </c>
-      <c r="F12" s="26">
-        <v>1845</v>
-      </c>
-      <c r="G12" s="26">
-        <f t="shared" si="0"/>
-        <v>17</v>
-      </c>
+      <c r="A12" s="19"/>
+      <c r="B12" s="20"/>
+      <c r="C12" s="20"/>
+      <c r="D12" s="20"/>
+      <c r="E12" s="26"/>
+      <c r="F12" s="26"/>
+      <c r="G12" s="26"/>
       <c r="H12" s="26"/>
       <c r="I12" s="26"/>
-      <c r="J12" s="26" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K12" s="26">
-        <v>1809</v>
-      </c>
-      <c r="L12" s="26">
-        <v>1809</v>
-      </c>
-      <c r="M12" s="26">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
+      <c r="J12" s="26"/>
+      <c r="K12" s="26"/>
+      <c r="L12" s="26"/>
+      <c r="M12" s="26"/>
     </row>
     <row r="13" spans="1:13" s="16" customFormat="1" ht="25.5" customHeight="1">
-      <c r="A13" s="19" t="s">
-        <v>12</v>
-      </c>
-      <c r="B13" s="20" t="s">
-        <v>853</v>
-      </c>
-      <c r="C13" s="20" t="s">
-        <v>854</v>
-      </c>
-      <c r="D13" s="20" t="s">
-        <v>1758</v>
-      </c>
-      <c r="E13" s="26">
-        <v>1828</v>
-      </c>
-      <c r="F13" s="26">
-        <v>1828</v>
-      </c>
-      <c r="G13" s="26">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
+      <c r="A13" s="19"/>
+      <c r="B13" s="20"/>
+      <c r="C13" s="20"/>
+      <c r="D13" s="20"/>
+      <c r="E13" s="26"/>
+      <c r="F13" s="26"/>
+      <c r="G13" s="26"/>
       <c r="H13" s="26"/>
       <c r="I13" s="26"/>
-      <c r="J13" s="26" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K13" s="26">
-        <v>1828</v>
-      </c>
-      <c r="L13" s="26">
-        <v>1878</v>
-      </c>
-      <c r="M13" s="26">
-        <f t="shared" si="2"/>
-        <v>50</v>
-      </c>
+      <c r="J13" s="26"/>
+      <c r="K13" s="26"/>
+      <c r="L13" s="26"/>
+      <c r="M13" s="26"/>
     </row>
     <row r="14" spans="1:13" s="16" customFormat="1" ht="25.5" customHeight="1">
-      <c r="A14" s="19" t="s">
-        <v>10</v>
-      </c>
-      <c r="B14" s="20" t="s">
-        <v>495</v>
-      </c>
-      <c r="C14" s="20" t="s">
-        <v>496</v>
-      </c>
-      <c r="D14" s="20" t="s">
-        <v>1758</v>
-      </c>
-      <c r="E14" s="26">
-        <v>1859</v>
-      </c>
-      <c r="F14" s="26">
-        <v>1859</v>
-      </c>
-      <c r="G14" s="26">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
+      <c r="A14" s="19"/>
+      <c r="B14" s="20"/>
+      <c r="C14" s="20"/>
+      <c r="D14" s="20"/>
+      <c r="E14" s="26"/>
+      <c r="F14" s="26"/>
+      <c r="G14" s="26"/>
       <c r="H14" s="26"/>
       <c r="I14" s="26"/>
-      <c r="J14" s="26" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K14" s="26">
-        <v>1839</v>
-      </c>
-      <c r="L14" s="26">
-        <v>1824</v>
-      </c>
-      <c r="M14" s="26">
-        <f t="shared" si="2"/>
-        <v>-15</v>
-      </c>
+      <c r="J14" s="26"/>
+      <c r="K14" s="26"/>
+      <c r="L14" s="26"/>
+      <c r="M14" s="26"/>
     </row>
     <row r="15" spans="1:13" s="16" customFormat="1" ht="25.5" customHeight="1">
-      <c r="A15" s="19" t="s">
-        <v>12</v>
-      </c>
-      <c r="B15" s="20" t="s">
-        <v>713</v>
-      </c>
-      <c r="C15" s="20" t="s">
-        <v>714</v>
-      </c>
-      <c r="D15" s="20" t="s">
-        <v>1758</v>
-      </c>
-      <c r="E15" s="26">
-        <v>1867</v>
-      </c>
-      <c r="F15" s="26">
-        <v>1867</v>
-      </c>
-      <c r="G15" s="26">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
+      <c r="A15" s="19"/>
+      <c r="B15" s="20"/>
+      <c r="C15" s="20"/>
+      <c r="D15" s="20"/>
+      <c r="E15" s="26"/>
+      <c r="F15" s="26"/>
+      <c r="G15" s="26"/>
       <c r="H15" s="26"/>
       <c r="I15" s="26"/>
-      <c r="J15" s="26" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K15" s="26">
-        <v>1832</v>
-      </c>
-      <c r="L15" s="26">
-        <v>1847</v>
-      </c>
-      <c r="M15" s="26">
-        <f t="shared" si="2"/>
-        <v>15</v>
-      </c>
+      <c r="J15" s="26"/>
+      <c r="K15" s="26"/>
+      <c r="L15" s="26"/>
+      <c r="M15" s="26"/>
     </row>
     <row r="16" spans="1:13" s="16" customFormat="1" ht="25.5" customHeight="1">
-      <c r="A16" s="19" t="s">
-        <v>14</v>
-      </c>
-      <c r="B16" s="20" t="s">
-        <v>1291</v>
-      </c>
-      <c r="C16" s="20" t="s">
-        <v>1292</v>
-      </c>
-      <c r="D16" s="20" t="s">
-        <v>1758</v>
-      </c>
-      <c r="E16" s="26">
-        <v>1879</v>
-      </c>
-      <c r="F16" s="26">
-        <v>1885</v>
-      </c>
-      <c r="G16" s="26">
-        <f t="shared" si="0"/>
-        <v>6</v>
-      </c>
+      <c r="A16" s="19"/>
+      <c r="B16" s="20"/>
+      <c r="C16" s="20"/>
+      <c r="D16" s="20"/>
+      <c r="E16" s="26"/>
+      <c r="F16" s="26"/>
+      <c r="G16" s="26"/>
       <c r="H16" s="26"/>
       <c r="I16" s="26"/>
-      <c r="J16" s="26" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K16" s="26">
-        <v>1858</v>
-      </c>
-      <c r="L16" s="26">
-        <v>1858</v>
-      </c>
-      <c r="M16" s="26">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
+      <c r="J16" s="26"/>
+      <c r="K16" s="26"/>
+      <c r="L16" s="26"/>
+      <c r="M16" s="26"/>
     </row>
     <row r="17" spans="1:13" s="16" customFormat="1" ht="25.5" customHeight="1">
-      <c r="A17" s="19" t="s">
-        <v>6</v>
-      </c>
-      <c r="B17" s="20" t="s">
-        <v>620</v>
-      </c>
-      <c r="C17" s="20" t="s">
-        <v>621</v>
-      </c>
-      <c r="D17" s="20" t="s">
-        <v>1758</v>
-      </c>
-      <c r="E17" s="26">
-        <v>1892</v>
-      </c>
-      <c r="F17" s="26">
-        <v>1892</v>
-      </c>
-      <c r="G17" s="26">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
+      <c r="A17" s="19"/>
+      <c r="B17" s="20"/>
+      <c r="C17" s="20"/>
+      <c r="D17" s="20"/>
+      <c r="E17" s="26"/>
+      <c r="F17" s="26"/>
+      <c r="G17" s="26"/>
       <c r="H17" s="26"/>
       <c r="I17" s="26"/>
-      <c r="J17" s="26" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K17" s="26">
-        <v>1792</v>
-      </c>
-      <c r="L17" s="26">
-        <v>1812</v>
-      </c>
-      <c r="M17" s="26">
-        <f t="shared" si="2"/>
-        <v>20</v>
-      </c>
+      <c r="J17" s="26"/>
+      <c r="K17" s="26"/>
+      <c r="L17" s="26"/>
+      <c r="M17" s="26"/>
     </row>
     <row r="18" spans="1:13" s="16" customFormat="1" ht="25.5" customHeight="1">
-      <c r="A18" s="19" t="s">
-        <v>12</v>
-      </c>
-      <c r="B18" s="20" t="s">
-        <v>1154</v>
-      </c>
-      <c r="C18" s="20" t="s">
-        <v>1155</v>
-      </c>
-      <c r="D18" s="20" t="s">
-        <v>1758</v>
-      </c>
-      <c r="E18" s="26">
-        <v>1898</v>
-      </c>
-      <c r="F18" s="26">
-        <v>1898</v>
-      </c>
-      <c r="G18" s="26">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
+      <c r="A18" s="19"/>
+      <c r="B18" s="20"/>
+      <c r="C18" s="20"/>
+      <c r="D18" s="20"/>
+      <c r="E18" s="26"/>
+      <c r="F18" s="26"/>
+      <c r="G18" s="26"/>
       <c r="H18" s="26"/>
       <c r="I18" s="26"/>
-      <c r="J18" s="26" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K18" s="26">
-        <v>1878</v>
-      </c>
-      <c r="L18" s="26">
-        <v>1863</v>
-      </c>
-      <c r="M18" s="26">
-        <f t="shared" si="2"/>
-        <v>-15</v>
-      </c>
+      <c r="J18" s="26"/>
+      <c r="K18" s="26"/>
+      <c r="L18" s="26"/>
+      <c r="M18" s="26"/>
     </row>
     <row r="19" spans="1:13" s="16" customFormat="1" ht="25.5" customHeight="1">
-      <c r="A19" s="19" t="s">
-        <v>14</v>
-      </c>
-      <c r="B19" s="20" t="s">
-        <v>414</v>
-      </c>
-      <c r="C19" s="20" t="s">
-        <v>416</v>
-      </c>
-      <c r="D19" s="20" t="s">
-        <v>1758</v>
-      </c>
-      <c r="E19" s="26">
-        <v>1899</v>
-      </c>
-      <c r="F19" s="26">
-        <v>1999</v>
-      </c>
-      <c r="G19" s="26">
-        <f t="shared" si="0"/>
-        <v>100</v>
-      </c>
+      <c r="A19" s="19"/>
+      <c r="B19" s="20"/>
+      <c r="C19" s="20"/>
+      <c r="D19" s="20"/>
+      <c r="E19" s="26"/>
+      <c r="F19" s="26"/>
+      <c r="G19" s="26"/>
       <c r="H19" s="26"/>
       <c r="I19" s="26"/>
-      <c r="J19" s="26" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K19" s="26">
-        <v>1869</v>
-      </c>
-      <c r="L19" s="26">
-        <v>1869</v>
-      </c>
-      <c r="M19" s="26">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
+      <c r="J19" s="26"/>
+      <c r="K19" s="26"/>
+      <c r="L19" s="26"/>
+      <c r="M19" s="26"/>
     </row>
     <row r="20" spans="1:13" s="16" customFormat="1" ht="25.5" customHeight="1">
-      <c r="A20" s="19" t="s">
-        <v>6</v>
-      </c>
-      <c r="B20" s="20" t="s">
-        <v>809</v>
-      </c>
-      <c r="C20" s="20" t="s">
-        <v>810</v>
-      </c>
-      <c r="D20" s="20" t="s">
-        <v>1758</v>
-      </c>
-      <c r="E20" s="26">
-        <v>1949</v>
-      </c>
-      <c r="F20" s="26">
-        <v>1949</v>
-      </c>
-      <c r="G20" s="26">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
+      <c r="A20" s="19"/>
+      <c r="B20" s="20"/>
+      <c r="C20" s="20"/>
+      <c r="D20" s="20"/>
+      <c r="E20" s="26"/>
+      <c r="F20" s="26"/>
+      <c r="G20" s="26"/>
       <c r="H20" s="26"/>
       <c r="I20" s="26"/>
-      <c r="J20" s="26" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K20" s="26">
-        <v>1939</v>
-      </c>
-      <c r="L20" s="26">
-        <v>2039</v>
-      </c>
-      <c r="M20" s="26">
-        <f t="shared" si="2"/>
-        <v>100</v>
-      </c>
+      <c r="J20" s="26"/>
+      <c r="K20" s="26"/>
+      <c r="L20" s="26"/>
+      <c r="M20" s="26"/>
     </row>
     <row r="21" spans="1:13" s="16" customFormat="1" ht="25.5" customHeight="1">
-      <c r="A21" s="19" t="s">
-        <v>12</v>
-      </c>
-      <c r="B21" s="20" t="s">
-        <v>439</v>
-      </c>
-      <c r="C21" s="20" t="s">
-        <v>441</v>
-      </c>
-      <c r="D21" s="20" t="s">
-        <v>1758</v>
-      </c>
-      <c r="E21" s="26">
-        <v>1799</v>
-      </c>
-      <c r="F21" s="26">
-        <v>1814</v>
-      </c>
-      <c r="G21" s="26">
-        <f t="shared" si="0"/>
-        <v>15</v>
-      </c>
+      <c r="A21" s="19"/>
+      <c r="B21" s="20"/>
+      <c r="C21" s="20"/>
+      <c r="D21" s="20"/>
+      <c r="E21" s="26"/>
+      <c r="F21" s="26"/>
+      <c r="G21" s="26"/>
       <c r="H21" s="26"/>
       <c r="I21" s="26"/>
-      <c r="J21" s="26" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K21" s="26">
-        <v>1824</v>
-      </c>
-      <c r="L21" s="26">
-        <v>1824</v>
-      </c>
-      <c r="M21" s="26">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
+      <c r="J21" s="26"/>
+      <c r="K21" s="26"/>
+      <c r="L21" s="26"/>
+      <c r="M21" s="26"/>
     </row>
     <row r="22" spans="1:13" s="16" customFormat="1" ht="25.5" customHeight="1">
-      <c r="A22" s="19" t="s">
-        <v>6</v>
-      </c>
-      <c r="B22" s="20" t="s">
-        <v>953</v>
-      </c>
-      <c r="C22" s="20" t="s">
-        <v>954</v>
-      </c>
-      <c r="D22" s="20" t="s">
-        <v>1758</v>
-      </c>
-      <c r="E22" s="26">
-        <v>1813</v>
-      </c>
-      <c r="F22" s="26">
-        <v>1818</v>
-      </c>
-      <c r="G22" s="26">
-        <f t="shared" si="0"/>
-        <v>5</v>
-      </c>
+      <c r="A22" s="19"/>
+      <c r="B22" s="20"/>
+      <c r="C22" s="20"/>
+      <c r="D22" s="20"/>
+      <c r="E22" s="26"/>
+      <c r="F22" s="26"/>
+      <c r="G22" s="26"/>
       <c r="H22" s="26"/>
       <c r="I22" s="26"/>
-      <c r="J22" s="26" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K22" s="26">
-        <v>1791</v>
-      </c>
-      <c r="L22" s="26">
-        <v>1799</v>
-      </c>
-      <c r="M22" s="26">
-        <f t="shared" si="2"/>
-        <v>8</v>
-      </c>
+      <c r="J22" s="26"/>
+      <c r="K22" s="26"/>
+      <c r="L22" s="26"/>
+      <c r="M22" s="26"/>
     </row>
     <row r="23" spans="1:13" s="16" customFormat="1" ht="25.5" customHeight="1">
-      <c r="A23" s="19" t="s">
-        <v>12</v>
-      </c>
-      <c r="B23" s="20" t="s">
-        <v>75</v>
-      </c>
-      <c r="C23" s="20" t="s">
-        <v>76</v>
-      </c>
-      <c r="D23" s="20" t="s">
-        <v>1758</v>
-      </c>
-      <c r="E23" s="26">
-        <v>1814</v>
-      </c>
-      <c r="F23" s="26">
-        <v>1814</v>
-      </c>
-      <c r="G23" s="26">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
+      <c r="A23" s="19"/>
+      <c r="B23" s="20"/>
+      <c r="C23" s="20"/>
+      <c r="D23" s="20"/>
+      <c r="E23" s="26"/>
+      <c r="F23" s="26"/>
+      <c r="G23" s="26"/>
       <c r="H23" s="26"/>
       <c r="I23" s="26"/>
-      <c r="J23" s="26" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K23" s="26">
-        <v>1794</v>
-      </c>
-      <c r="L23" s="26">
-        <v>1999</v>
-      </c>
-      <c r="M23" s="26">
-        <f t="shared" si="2"/>
-        <v>205</v>
-      </c>
+      <c r="J23" s="26"/>
+      <c r="K23" s="26"/>
+      <c r="L23" s="26"/>
+      <c r="M23" s="26"/>
     </row>
     <row r="24" spans="1:13" s="16" customFormat="1" ht="25.5" customHeight="1">
-      <c r="A24" s="19" t="s">
-        <v>10</v>
-      </c>
-      <c r="B24" s="20" t="s">
-        <v>1287</v>
-      </c>
-      <c r="C24" s="20" t="s">
-        <v>1288</v>
-      </c>
-      <c r="D24" s="20" t="s">
-        <v>1758</v>
-      </c>
-      <c r="E24" s="26">
-        <v>1819</v>
-      </c>
-      <c r="F24" s="26">
-        <v>1829</v>
-      </c>
-      <c r="G24" s="26">
-        <f t="shared" si="0"/>
-        <v>10</v>
-      </c>
+      <c r="A24" s="19"/>
+      <c r="B24" s="20"/>
+      <c r="C24" s="20"/>
+      <c r="D24" s="20"/>
+      <c r="E24" s="26"/>
+      <c r="F24" s="26"/>
+      <c r="G24" s="26"/>
       <c r="H24" s="26"/>
       <c r="I24" s="26"/>
-      <c r="J24" s="26" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K24" s="26">
-        <v>1798</v>
-      </c>
-      <c r="L24" s="26">
-        <v>1798</v>
-      </c>
-      <c r="M24" s="26">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
+      <c r="J24" s="26"/>
+      <c r="K24" s="26"/>
+      <c r="L24" s="26"/>
+      <c r="M24" s="26"/>
     </row>
     <row r="25" spans="1:13" s="16" customFormat="1" ht="25.5" customHeight="1">
-      <c r="A25" s="19" t="s">
-        <v>6</v>
-      </c>
-      <c r="B25" s="20" t="s">
-        <v>553</v>
-      </c>
-      <c r="C25" s="20" t="s">
-        <v>556</v>
-      </c>
-      <c r="D25" s="20" t="s">
-        <v>1758</v>
-      </c>
-      <c r="E25" s="26">
-        <v>1825</v>
-      </c>
-      <c r="F25" s="26">
-        <v>1825</v>
-      </c>
-      <c r="G25" s="26">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
+      <c r="A25" s="19"/>
+      <c r="B25" s="20"/>
+      <c r="C25" s="20"/>
+      <c r="D25" s="20"/>
+      <c r="E25" s="26"/>
+      <c r="F25" s="26"/>
+      <c r="G25" s="26"/>
       <c r="H25" s="26"/>
       <c r="I25" s="26"/>
-      <c r="J25" s="26" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K25" s="26">
-        <v>1813</v>
-      </c>
-      <c r="L25" s="26">
-        <v>1850</v>
-      </c>
-      <c r="M25" s="26">
-        <f t="shared" si="2"/>
-        <v>37</v>
-      </c>
+      <c r="J25" s="26"/>
+      <c r="K25" s="26"/>
+      <c r="L25" s="26"/>
+      <c r="M25" s="26"/>
     </row>
     <row r="26" spans="1:13" s="16" customFormat="1" ht="25.5" customHeight="1">
-      <c r="A26" s="19" t="s">
-        <v>6</v>
-      </c>
-      <c r="B26" s="20" t="s">
-        <v>1724</v>
-      </c>
-      <c r="C26" s="20" t="s">
-        <v>1725</v>
-      </c>
-      <c r="D26" s="20" t="s">
-        <v>1758</v>
-      </c>
-      <c r="E26" s="26">
-        <v>1828</v>
-      </c>
-      <c r="F26" s="26">
-        <v>1825</v>
-      </c>
-      <c r="G26" s="26">
-        <f t="shared" si="0"/>
-        <v>-3</v>
-      </c>
+      <c r="A26" s="19"/>
+      <c r="B26" s="20"/>
+      <c r="C26" s="20"/>
+      <c r="D26" s="20"/>
+      <c r="E26" s="26"/>
+      <c r="F26" s="26"/>
+      <c r="G26" s="26"/>
       <c r="H26" s="26"/>
       <c r="I26" s="26"/>
-      <c r="J26" s="26" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K26" s="26">
-        <v>1813</v>
-      </c>
-      <c r="L26" s="26">
-        <v>1813</v>
-      </c>
-      <c r="M26" s="26">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
+      <c r="J26" s="26"/>
+      <c r="K26" s="26"/>
+      <c r="L26" s="26"/>
+      <c r="M26" s="26"/>
     </row>
     <row r="27" spans="1:13" s="16" customFormat="1" ht="25.5" customHeight="1">
-      <c r="A27" s="19" t="s">
-        <v>10</v>
-      </c>
-      <c r="B27" s="20" t="s">
-        <v>1000</v>
-      </c>
-      <c r="C27" s="20" t="s">
-        <v>1001</v>
-      </c>
-      <c r="D27" s="20" t="s">
-        <v>1758</v>
-      </c>
-      <c r="E27" s="26">
-        <v>1828</v>
-      </c>
-      <c r="F27" s="26">
-        <v>1818</v>
-      </c>
-      <c r="G27" s="26">
-        <f t="shared" si="0"/>
-        <v>-10</v>
-      </c>
+      <c r="A27" s="19"/>
+      <c r="B27" s="20"/>
+      <c r="C27" s="20"/>
+      <c r="D27" s="20"/>
+      <c r="E27" s="26"/>
+      <c r="F27" s="26"/>
+      <c r="G27" s="26"/>
       <c r="H27" s="26"/>
       <c r="I27" s="26"/>
-      <c r="J27" s="26" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K27" s="26">
-        <v>1818</v>
-      </c>
-      <c r="L27" s="26">
-        <v>1818</v>
-      </c>
-      <c r="M27" s="26">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
+      <c r="J27" s="26"/>
+      <c r="K27" s="26"/>
+      <c r="L27" s="26"/>
+      <c r="M27" s="26"/>
     </row>
     <row r="28" spans="1:13" s="16" customFormat="1" ht="25.5" customHeight="1">
-      <c r="A28" s="19" t="s">
-        <v>10</v>
-      </c>
-      <c r="B28" s="20" t="s">
-        <v>740</v>
-      </c>
-      <c r="C28" s="20" t="s">
-        <v>741</v>
-      </c>
-      <c r="D28" s="20" t="s">
-        <v>1758</v>
-      </c>
-      <c r="E28" s="26">
-        <v>1829</v>
-      </c>
-      <c r="F28" s="26">
-        <v>1839</v>
-      </c>
-      <c r="G28" s="26">
-        <f t="shared" si="0"/>
-        <v>10</v>
-      </c>
+      <c r="A28" s="19"/>
+      <c r="B28" s="20"/>
+      <c r="C28" s="20"/>
+      <c r="D28" s="20"/>
+      <c r="E28" s="26"/>
+      <c r="F28" s="26"/>
+      <c r="G28" s="26"/>
       <c r="H28" s="26"/>
       <c r="I28" s="26"/>
-      <c r="J28" s="26" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K28" s="26">
-        <v>1819</v>
-      </c>
-      <c r="L28" s="26">
-        <v>1819</v>
-      </c>
-      <c r="M28" s="26">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
+      <c r="J28" s="26"/>
+      <c r="K28" s="26"/>
+      <c r="L28" s="26"/>
+      <c r="M28" s="26"/>
     </row>
     <row r="29" spans="1:13" s="16" customFormat="1" ht="25.5" customHeight="1">
-      <c r="A29" s="19" t="s">
-        <v>6</v>
-      </c>
-      <c r="B29" s="20" t="s">
-        <v>128</v>
-      </c>
-      <c r="C29" s="20" t="s">
-        <v>129</v>
-      </c>
-      <c r="D29" s="20" t="s">
-        <v>1758</v>
-      </c>
-      <c r="E29" s="26">
-        <v>1832</v>
-      </c>
-      <c r="F29" s="26">
-        <v>1872</v>
-      </c>
-      <c r="G29" s="26">
-        <f t="shared" si="0"/>
-        <v>40</v>
-      </c>
+      <c r="A29" s="19"/>
+      <c r="B29" s="20"/>
+      <c r="C29" s="20"/>
+      <c r="D29" s="20"/>
+      <c r="E29" s="26"/>
+      <c r="F29" s="26"/>
+      <c r="G29" s="26"/>
       <c r="H29" s="26"/>
       <c r="I29" s="26"/>
-      <c r="J29" s="26" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K29" s="26">
-        <v>1792</v>
-      </c>
-      <c r="L29" s="26">
-        <v>1792</v>
-      </c>
-      <c r="M29" s="26">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
+      <c r="J29" s="26"/>
+      <c r="K29" s="26"/>
+      <c r="L29" s="26"/>
+      <c r="M29" s="26"/>
     </row>
     <row r="30" spans="1:13" s="16" customFormat="1" ht="25.5" customHeight="1">
-      <c r="A30" s="19" t="s">
-        <v>8</v>
-      </c>
-      <c r="B30" s="20" t="s">
-        <v>600</v>
-      </c>
-      <c r="C30" s="20" t="s">
-        <v>1744</v>
-      </c>
-      <c r="D30" s="20" t="s">
-        <v>1758</v>
-      </c>
-      <c r="E30" s="26">
-        <v>1834</v>
-      </c>
-      <c r="F30" s="26">
-        <v>1834</v>
-      </c>
-      <c r="G30" s="26">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
+      <c r="A30" s="19"/>
+      <c r="B30" s="20"/>
+      <c r="C30" s="20"/>
+      <c r="D30" s="20"/>
+      <c r="E30" s="26"/>
+      <c r="F30" s="26"/>
+      <c r="G30" s="26"/>
       <c r="H30" s="26"/>
-      <c r="I30" s="26">
-        <v>2399</v>
-      </c>
-      <c r="J30" s="26" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K30" s="26">
-        <v>1820</v>
-      </c>
-      <c r="L30" s="26">
-        <v>1820</v>
-      </c>
-      <c r="M30" s="26">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
+      <c r="I30" s="26"/>
+      <c r="J30" s="26"/>
+      <c r="K30" s="26"/>
+      <c r="L30" s="26"/>
+      <c r="M30" s="26"/>
     </row>
     <row r="31" spans="1:13" s="16" customFormat="1" ht="25.5" customHeight="1">
-      <c r="A31" s="19" t="s">
-        <v>8</v>
-      </c>
-      <c r="B31" s="20" t="s">
-        <v>720</v>
-      </c>
-      <c r="C31" s="20" t="s">
-        <v>721</v>
-      </c>
-      <c r="D31" s="20" t="s">
-        <v>1758</v>
-      </c>
-      <c r="E31" s="26">
-        <v>1838</v>
-      </c>
-      <c r="F31" s="26">
-        <v>1828</v>
-      </c>
-      <c r="G31" s="26">
-        <f t="shared" si="0"/>
-        <v>-10</v>
-      </c>
+      <c r="A31" s="19"/>
+      <c r="B31" s="20"/>
+      <c r="C31" s="20"/>
+      <c r="D31" s="20"/>
+      <c r="E31" s="26"/>
+      <c r="F31" s="26"/>
+      <c r="G31" s="26"/>
       <c r="H31" s="26"/>
       <c r="I31" s="26"/>
-      <c r="J31" s="26" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K31" s="26">
-        <v>1823</v>
-      </c>
-      <c r="L31" s="26">
-        <v>1813</v>
-      </c>
-      <c r="M31" s="26">
-        <f t="shared" si="2"/>
-        <v>-10</v>
-      </c>
+      <c r="J31" s="26"/>
+      <c r="K31" s="26"/>
+      <c r="L31" s="26"/>
+      <c r="M31" s="26"/>
     </row>
     <row r="32" spans="1:13" s="16" customFormat="1" ht="25.5" customHeight="1">
-      <c r="A32" s="19" t="s">
-        <v>10</v>
-      </c>
-      <c r="B32" s="20" t="s">
-        <v>744</v>
-      </c>
-      <c r="C32" s="20" t="s">
-        <v>745</v>
-      </c>
-      <c r="D32" s="20" t="s">
-        <v>1758</v>
-      </c>
-      <c r="E32" s="26">
-        <v>1839</v>
-      </c>
-      <c r="F32" s="26">
-        <v>1828</v>
-      </c>
-      <c r="G32" s="26">
-        <f t="shared" si="0"/>
-        <v>-11</v>
-      </c>
+      <c r="A32" s="19"/>
+      <c r="B32" s="20"/>
+      <c r="C32" s="20"/>
+      <c r="D32" s="20"/>
+      <c r="E32" s="26"/>
+      <c r="F32" s="26"/>
+      <c r="G32" s="26"/>
       <c r="H32" s="26"/>
       <c r="I32" s="26"/>
-      <c r="J32" s="26" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K32" s="26">
-        <v>1828</v>
-      </c>
-      <c r="L32" s="26">
-        <v>1817</v>
-      </c>
-      <c r="M32" s="26">
-        <f t="shared" si="2"/>
-        <v>-11</v>
-      </c>
+      <c r="J32" s="26"/>
+      <c r="K32" s="26"/>
+      <c r="L32" s="26"/>
+      <c r="M32" s="26"/>
     </row>
     <row r="33" spans="1:13" s="16" customFormat="1" ht="25.5" customHeight="1">
-      <c r="A33" s="19" t="s">
-        <v>10</v>
-      </c>
-      <c r="B33" s="20" t="s">
-        <v>879</v>
-      </c>
-      <c r="C33" s="20" t="s">
-        <v>880</v>
-      </c>
-      <c r="D33" s="20" t="s">
-        <v>1758</v>
-      </c>
-      <c r="E33" s="26">
-        <v>1839</v>
-      </c>
-      <c r="F33" s="26">
-        <v>1834</v>
-      </c>
-      <c r="G33" s="26">
-        <f t="shared" si="0"/>
-        <v>-5</v>
-      </c>
+      <c r="A33" s="19"/>
+      <c r="B33" s="20"/>
+      <c r="C33" s="20"/>
+      <c r="D33" s="20"/>
+      <c r="E33" s="26"/>
+      <c r="F33" s="26"/>
+      <c r="G33" s="26"/>
       <c r="H33" s="26"/>
       <c r="I33" s="26"/>
-      <c r="J33" s="26" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K33" s="26">
-        <v>1828</v>
-      </c>
-      <c r="L33" s="26">
-        <v>1823</v>
-      </c>
-      <c r="M33" s="26">
-        <f t="shared" si="2"/>
-        <v>-5</v>
-      </c>
+      <c r="J33" s="26"/>
+      <c r="K33" s="26"/>
+      <c r="L33" s="26"/>
+      <c r="M33" s="26"/>
     </row>
     <row r="34" spans="1:13" s="16" customFormat="1" ht="25.5" customHeight="1">
-      <c r="A34" s="19" t="s">
-        <v>18</v>
-      </c>
-      <c r="B34" s="20" t="s">
-        <v>1339</v>
-      </c>
-      <c r="C34" s="20" t="s">
-        <v>1341</v>
-      </c>
-      <c r="D34" s="20" t="s">
-        <v>1758</v>
-      </c>
-      <c r="E34" s="26">
-        <v>1842</v>
-      </c>
-      <c r="F34" s="26">
-        <v>1842</v>
-      </c>
-      <c r="G34" s="26">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
+      <c r="A34" s="19"/>
+      <c r="B34" s="20"/>
+      <c r="C34" s="20"/>
+      <c r="D34" s="20"/>
+      <c r="E34" s="26"/>
+      <c r="F34" s="26"/>
+      <c r="G34" s="26"/>
       <c r="H34" s="26"/>
       <c r="I34" s="26"/>
-      <c r="J34" s="26" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K34" s="26">
-        <v>1832</v>
-      </c>
-      <c r="L34" s="26">
-        <v>1850</v>
-      </c>
-      <c r="M34" s="26">
-        <f t="shared" si="2"/>
-        <v>18</v>
-      </c>
+      <c r="J34" s="26"/>
+      <c r="K34" s="26"/>
+      <c r="L34" s="26"/>
+      <c r="M34" s="26"/>
     </row>
     <row r="35" spans="1:13" s="16" customFormat="1" ht="25.5" customHeight="1">
-      <c r="A35" s="19" t="s">
-        <v>6</v>
-      </c>
-      <c r="B35" s="20" t="s">
-        <v>693</v>
-      </c>
-      <c r="C35" s="20" t="s">
-        <v>694</v>
-      </c>
-      <c r="D35" s="20" t="s">
-        <v>1758</v>
-      </c>
-      <c r="E35" s="26">
-        <v>1849</v>
-      </c>
-      <c r="F35" s="26">
-        <v>1849</v>
-      </c>
-      <c r="G35" s="26">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
+      <c r="A35" s="19"/>
+      <c r="B35" s="20"/>
+      <c r="C35" s="20"/>
+      <c r="D35" s="20"/>
+      <c r="E35" s="26"/>
+      <c r="F35" s="26"/>
+      <c r="G35" s="26"/>
       <c r="H35" s="26"/>
       <c r="I35" s="26"/>
-      <c r="J35" s="26" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K35" s="26">
-        <v>1799</v>
-      </c>
-      <c r="L35" s="26">
-        <v>1834</v>
-      </c>
-      <c r="M35" s="26">
-        <f t="shared" si="2"/>
-        <v>35</v>
-      </c>
+      <c r="J35" s="26"/>
+      <c r="K35" s="26"/>
+      <c r="L35" s="26"/>
+      <c r="M35" s="26"/>
     </row>
     <row r="36" spans="1:13" s="16" customFormat="1" ht="25.5" customHeight="1">
-      <c r="A36" s="19" t="s">
-        <v>12</v>
-      </c>
-      <c r="B36" s="20" t="s">
-        <v>1685</v>
-      </c>
-      <c r="C36" s="20" t="s">
-        <v>1686</v>
-      </c>
-      <c r="D36" s="20" t="s">
-        <v>1758</v>
-      </c>
-      <c r="E36" s="26">
-        <v>1849</v>
-      </c>
-      <c r="F36" s="26">
-        <v>1849</v>
-      </c>
-      <c r="G36" s="26">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
+      <c r="A36" s="19"/>
+      <c r="B36" s="20"/>
+      <c r="C36" s="20"/>
+      <c r="D36" s="20"/>
+      <c r="E36" s="26"/>
+      <c r="F36" s="26"/>
+      <c r="G36" s="26"/>
       <c r="H36" s="26"/>
       <c r="I36" s="26"/>
-      <c r="J36" s="26" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K36" s="26">
-        <v>1839</v>
-      </c>
-      <c r="L36" s="26">
-        <v>1859</v>
-      </c>
-      <c r="M36" s="26">
-        <f t="shared" si="2"/>
-        <v>20</v>
-      </c>
+      <c r="J36" s="26"/>
+      <c r="K36" s="26"/>
+      <c r="L36" s="26"/>
+      <c r="M36" s="26"/>
     </row>
     <row r="37" spans="1:13" s="16" customFormat="1" ht="25.5" customHeight="1">
-      <c r="A37" s="19" t="s">
-        <v>10</v>
-      </c>
-      <c r="B37" s="20" t="s">
-        <v>857</v>
-      </c>
-      <c r="C37" s="20" t="s">
-        <v>858</v>
-      </c>
-      <c r="D37" s="20" t="s">
-        <v>1758</v>
-      </c>
-      <c r="E37" s="26">
-        <v>1855</v>
-      </c>
-      <c r="F37" s="26">
-        <v>1855</v>
-      </c>
-      <c r="G37" s="26">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
+      <c r="A37" s="19"/>
+      <c r="B37" s="20"/>
+      <c r="C37" s="20"/>
+      <c r="D37" s="20"/>
+      <c r="E37" s="26"/>
+      <c r="F37" s="26"/>
+      <c r="G37" s="26"/>
       <c r="H37" s="26"/>
       <c r="I37" s="26"/>
-      <c r="J37" s="26" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K37" s="26">
-        <v>1825</v>
-      </c>
-      <c r="L37" s="26">
-        <v>1875</v>
-      </c>
-      <c r="M37" s="26">
-        <f t="shared" si="2"/>
-        <v>50</v>
-      </c>
+      <c r="J37" s="26"/>
+      <c r="K37" s="26"/>
+      <c r="L37" s="26"/>
+      <c r="M37" s="26"/>
     </row>
     <row r="38" spans="1:13" s="16" customFormat="1" ht="25.5" customHeight="1">
-      <c r="A38" s="19" t="s">
-        <v>16</v>
-      </c>
-      <c r="B38" s="20" t="s">
-        <v>1462</v>
-      </c>
-      <c r="C38" s="20" t="s">
-        <v>1463</v>
-      </c>
-      <c r="D38" s="20" t="s">
-        <v>1758</v>
-      </c>
-      <c r="E38" s="26">
-        <v>1860</v>
-      </c>
-      <c r="F38" s="26">
-        <v>1860</v>
-      </c>
-      <c r="G38" s="26">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
+      <c r="A38" s="19"/>
+      <c r="B38" s="20"/>
+      <c r="C38" s="20"/>
+      <c r="D38" s="20"/>
+      <c r="E38" s="26"/>
+      <c r="F38" s="26"/>
+      <c r="G38" s="26"/>
       <c r="H38" s="26"/>
       <c r="I38" s="26"/>
-      <c r="J38" s="26" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K38" s="26">
-        <v>1820</v>
-      </c>
-      <c r="L38" s="26">
-        <v>1840</v>
-      </c>
-      <c r="M38" s="26">
-        <f t="shared" si="2"/>
-        <v>20</v>
-      </c>
+      <c r="J38" s="26"/>
+      <c r="K38" s="26"/>
+      <c r="L38" s="26"/>
+      <c r="M38" s="26"/>
     </row>
     <row r="39" spans="1:13" s="16" customFormat="1" ht="25.5" customHeight="1">
-      <c r="A39" s="19" t="s">
-        <v>14</v>
-      </c>
-      <c r="B39" s="20" t="s">
-        <v>771</v>
-      </c>
-      <c r="C39" s="20" t="s">
-        <v>772</v>
-      </c>
-      <c r="D39" s="20" t="s">
-        <v>1758</v>
-      </c>
-      <c r="E39" s="26">
-        <v>1869</v>
-      </c>
-      <c r="F39" s="26">
-        <v>1869</v>
-      </c>
-      <c r="G39" s="26">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
+      <c r="A39" s="19"/>
+      <c r="B39" s="20"/>
+      <c r="C39" s="20"/>
+      <c r="D39" s="20"/>
+      <c r="E39" s="26"/>
+      <c r="F39" s="26"/>
+      <c r="G39" s="26"/>
       <c r="H39" s="26"/>
       <c r="I39" s="26"/>
-      <c r="J39" s="26" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K39" s="26">
-        <v>1839</v>
-      </c>
-      <c r="L39" s="26">
-        <v>1834</v>
-      </c>
-      <c r="M39" s="26">
-        <f t="shared" si="2"/>
-        <v>-5</v>
-      </c>
+      <c r="J39" s="26"/>
+      <c r="K39" s="26"/>
+      <c r="L39" s="26"/>
+      <c r="M39" s="26"/>
     </row>
     <row r="40" spans="1:13" s="16" customFormat="1" ht="25.5" customHeight="1">
-      <c r="A40" s="19" t="s">
-        <v>10</v>
-      </c>
-      <c r="B40" s="20" t="s">
-        <v>445</v>
-      </c>
-      <c r="C40" s="20" t="s">
-        <v>446</v>
-      </c>
-      <c r="D40" s="20" t="s">
-        <v>1758</v>
-      </c>
-      <c r="E40" s="26">
-        <v>1870</v>
-      </c>
-      <c r="F40" s="26">
-        <v>1870</v>
-      </c>
-      <c r="G40" s="26">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
+      <c r="A40" s="19"/>
+      <c r="B40" s="20"/>
+      <c r="C40" s="20"/>
+      <c r="D40" s="20"/>
+      <c r="E40" s="26"/>
+      <c r="F40" s="26"/>
+      <c r="G40" s="26"/>
       <c r="H40" s="26"/>
       <c r="I40" s="26"/>
-      <c r="J40" s="26" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K40" s="26">
-        <v>1860</v>
-      </c>
-      <c r="L40" s="26">
-        <v>1900</v>
-      </c>
-      <c r="M40" s="26">
-        <f t="shared" si="2"/>
-        <v>40</v>
-      </c>
+      <c r="J40" s="26"/>
+      <c r="K40" s="26"/>
+      <c r="L40" s="26"/>
+      <c r="M40" s="26"/>
     </row>
     <row r="41" spans="1:13" s="16" customFormat="1" ht="25.5" customHeight="1">
-      <c r="A41" s="19" t="s">
-        <v>14</v>
-      </c>
-      <c r="B41" s="20" t="s">
-        <v>1738</v>
-      </c>
-      <c r="C41" s="20" t="s">
-        <v>1739</v>
-      </c>
-      <c r="D41" s="20" t="s">
-        <v>1758</v>
-      </c>
-      <c r="E41" s="26">
-        <v>1879</v>
-      </c>
-      <c r="F41" s="26">
-        <v>1869</v>
-      </c>
-      <c r="G41" s="26">
-        <f t="shared" si="0"/>
-        <v>-10</v>
-      </c>
+      <c r="A41" s="19"/>
+      <c r="B41" s="20"/>
+      <c r="C41" s="20"/>
+      <c r="D41" s="20"/>
+      <c r="E41" s="26"/>
+      <c r="F41" s="26"/>
+      <c r="G41" s="26"/>
       <c r="H41" s="26"/>
       <c r="I41" s="26"/>
-      <c r="J41" s="26" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K41" s="26">
-        <v>1869</v>
-      </c>
-      <c r="L41" s="26">
-        <v>1869</v>
-      </c>
-      <c r="M41" s="26">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
+      <c r="J41" s="26"/>
+      <c r="K41" s="26"/>
+      <c r="L41" s="26"/>
+      <c r="M41" s="26"/>
     </row>
     <row r="42" spans="1:13" s="16" customFormat="1" ht="25.5" customHeight="1">
-      <c r="A42" s="19" t="s">
-        <v>16</v>
-      </c>
-      <c r="B42" s="20" t="s">
-        <v>1720</v>
-      </c>
-      <c r="C42" s="20" t="s">
-        <v>1721</v>
-      </c>
-      <c r="D42" s="20" t="s">
-        <v>1758</v>
-      </c>
-      <c r="E42" s="26">
-        <v>1895</v>
-      </c>
-      <c r="F42" s="26">
-        <v>1885</v>
-      </c>
-      <c r="G42" s="26">
-        <f t="shared" si="0"/>
-        <v>-10</v>
-      </c>
+      <c r="A42" s="19"/>
+      <c r="B42" s="20"/>
+      <c r="C42" s="20"/>
+      <c r="D42" s="20"/>
+      <c r="E42" s="26"/>
+      <c r="F42" s="26"/>
+      <c r="G42" s="26"/>
       <c r="H42" s="26"/>
       <c r="I42" s="26"/>
-      <c r="J42" s="26" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K42" s="26">
-        <v>1875</v>
-      </c>
-      <c r="L42" s="26">
-        <v>1875</v>
-      </c>
-      <c r="M42" s="26">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
+      <c r="J42" s="26"/>
+      <c r="K42" s="26"/>
+      <c r="L42" s="26"/>
+      <c r="M42" s="26"/>
     </row>
     <row r="43" spans="1:13" s="16" customFormat="1" ht="25.5" customHeight="1">
-      <c r="A43" s="19" t="s">
-        <v>10</v>
-      </c>
-      <c r="B43" s="20" t="s">
-        <v>507</v>
-      </c>
-      <c r="C43" s="20" t="s">
-        <v>508</v>
-      </c>
-      <c r="D43" s="20" t="s">
-        <v>1758</v>
-      </c>
-      <c r="E43" s="26">
-        <v>1899</v>
-      </c>
-      <c r="F43" s="26">
-        <v>1899</v>
-      </c>
-      <c r="G43" s="26">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
+      <c r="A43" s="19"/>
+      <c r="B43" s="20"/>
+      <c r="C43" s="20"/>
+      <c r="D43" s="20"/>
+      <c r="E43" s="26"/>
+      <c r="F43" s="26"/>
+      <c r="G43" s="26"/>
       <c r="H43" s="26"/>
       <c r="I43" s="26"/>
-      <c r="J43" s="26" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K43" s="26">
-        <v>1884</v>
-      </c>
-      <c r="L43" s="26">
-        <v>1899</v>
-      </c>
-      <c r="M43" s="26">
-        <f t="shared" si="2"/>
-        <v>15</v>
-      </c>
+      <c r="J43" s="26"/>
+      <c r="K43" s="26"/>
+      <c r="L43" s="26"/>
+      <c r="M43" s="26"/>
     </row>
     <row r="44" spans="1:13" s="16" customFormat="1" ht="25.5" customHeight="1">
-      <c r="A44" s="19" t="s">
-        <v>14</v>
-      </c>
-      <c r="B44" s="20" t="s">
-        <v>1098</v>
-      </c>
-      <c r="C44" s="20" t="s">
-        <v>1099</v>
-      </c>
-      <c r="D44" s="20" t="s">
-        <v>1758</v>
-      </c>
-      <c r="E44" s="26">
-        <v>1909</v>
-      </c>
-      <c r="F44" s="26">
-        <v>1909</v>
-      </c>
-      <c r="G44" s="26">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
+      <c r="A44" s="19"/>
+      <c r="B44" s="20"/>
+      <c r="C44" s="20"/>
+      <c r="D44" s="20"/>
+      <c r="E44" s="26"/>
+      <c r="F44" s="26"/>
+      <c r="G44" s="26"/>
       <c r="H44" s="26"/>
       <c r="I44" s="26"/>
-      <c r="J44" s="26" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K44" s="26">
-        <v>1850</v>
-      </c>
-      <c r="L44" s="26">
-        <v>1899</v>
-      </c>
-      <c r="M44" s="26">
-        <f t="shared" si="2"/>
-        <v>49</v>
-      </c>
+      <c r="J44" s="26"/>
+      <c r="K44" s="26"/>
+      <c r="L44" s="26"/>
+      <c r="M44" s="26"/>
     </row>
     <row r="45" spans="1:13" s="16" customFormat="1" ht="25.5" customHeight="1">
-      <c r="A45" s="19" t="s">
-        <v>10</v>
-      </c>
-      <c r="B45" s="20" t="s">
-        <v>1764</v>
-      </c>
-      <c r="C45" s="20" t="s">
-        <v>1765</v>
-      </c>
-      <c r="D45" s="20" t="s">
-        <v>1766</v>
-      </c>
+      <c r="A45" s="19"/>
+      <c r="B45" s="20"/>
+      <c r="C45" s="20"/>
+      <c r="D45" s="20"/>
       <c r="E45" s="26"/>
-      <c r="F45" s="26">
-        <v>2080</v>
-      </c>
-      <c r="G45" s="26" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
+      <c r="F45" s="26"/>
+      <c r="G45" s="26"/>
       <c r="H45" s="26"/>
       <c r="I45" s="26"/>
-      <c r="J45" s="26" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
+      <c r="J45" s="26"/>
       <c r="K45" s="26"/>
-      <c r="L45" s="26">
-        <v>1807</v>
-      </c>
-      <c r="M45" s="26" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
+      <c r="L45" s="26"/>
+      <c r="M45" s="26"/>
     </row>
     <row r="46" spans="1:13" s="16" customFormat="1" ht="25.5" customHeight="1">
       <c r="A46" s="19"/>
@@ -80319,7 +79247,7 @@
     <mergeCell ref="A1:M1"/>
   </mergeCells>
   <phoneticPr fontId="26" type="noConversion"/>
-  <conditionalFormatting sqref="G4:G45">
+  <conditionalFormatting sqref="G4">
     <cfRule type="cellIs" dxfId="5" priority="2" operator="greaterThan">
       <formula>0</formula>
     </cfRule>
@@ -80327,7 +79255,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="J4:J45">
+  <conditionalFormatting sqref="J4">
     <cfRule type="cellIs" dxfId="3" priority="4" operator="greaterThan">
       <formula>0</formula>
     </cfRule>
@@ -80335,7 +79263,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="M4:M45">
+  <conditionalFormatting sqref="M4">
     <cfRule type="cellIs" dxfId="1" priority="6" operator="greaterThan">
       <formula>0</formula>
     </cfRule>
